--- a/Results/Hydrogen/hydrogen ionising radiation results.xlsx
+++ b/Results/Hydrogen/hydrogen ionising radiation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1960553098999436</v>
+        <v>0.1960553098999485</v>
       </c>
       <c r="C2" t="n">
-        <v>4.32500600843438</v>
+        <v>4.325006008434364</v>
       </c>
       <c r="D2" t="n">
-        <v>1.259704037882085</v>
+        <v>1.259704037882083</v>
       </c>
       <c r="E2" t="n">
-        <v>4.32500600843438</v>
+        <v>4.325006008434364</v>
       </c>
       <c r="F2" t="n">
-        <v>4.32500600843438</v>
+        <v>4.325006008434364</v>
       </c>
       <c r="G2" t="n">
-        <v>2.923106055940252</v>
+        <v>2.923106055940246</v>
       </c>
       <c r="H2" t="n">
-        <v>2.574194643174246</v>
+        <v>2.57419464317424</v>
       </c>
       <c r="I2" t="n">
-        <v>4.32500600843438</v>
+        <v>4.325006008434364</v>
       </c>
       <c r="J2" t="n">
-        <v>8.526089849471242</v>
+        <v>8.526089849471225</v>
       </c>
       <c r="K2" t="n">
-        <v>4.88676172368076</v>
+        <v>4.886761723680754</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7705894485987509</v>
+        <v>0.7751452579882272</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03296382691735582</v>
+        <v>0.03296382691735586</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03778238176121542</v>
+        <v>0.03778238176121543</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03296382691735582</v>
+        <v>0.03296382691735586</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03826467204741116</v>
+        <v>0.03826467204741119</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826467204741115</v>
+        <v>0.03826467204741112</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03355958211431152</v>
+        <v>0.03355958211431149</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03296382691735582</v>
+        <v>0.03296382691735586</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03692082551381445</v>
+        <v>0.0369208255138145</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03296382691735582</v>
+        <v>0.03296382691735586</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03296382691735582</v>
+        <v>0.03296382691735586</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03296382691735582</v>
+        <v>0.03296382691735586</v>
       </c>
     </row>
     <row r="4">
@@ -595,31 +595,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>43.91235459336696</v>
+        <v>11.57477339792476</v>
       </c>
       <c r="C4" t="n">
         <v>11.57971226689881</v>
       </c>
       <c r="D4" t="n">
-        <v>11.56926556127892</v>
+        <v>11.56926569967811</v>
       </c>
       <c r="E4" t="n">
-        <v>7.14752606524254</v>
+        <v>7.147526065242543</v>
       </c>
       <c r="F4" t="n">
         <v>11.57795047849279</v>
       </c>
       <c r="G4" t="n">
-        <v>43.91295034856393</v>
+        <v>43.91295034856391</v>
       </c>
       <c r="H4" t="n">
         <v>43.9157116215785</v>
       </c>
       <c r="I4" t="n">
-        <v>43.91631159196346</v>
+        <v>11.57873039652122</v>
       </c>
       <c r="J4" t="n">
-        <v>12.16217123515683</v>
+        <v>12.16217123515681</v>
       </c>
       <c r="K4" t="n">
         <v>11.57653230419806</v>
@@ -635,13 +635,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05390690453333394</v>
+        <v>0.05390690453333385</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05786390312979262</v>
+        <v>0.05786390312979255</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05390601571753488</v>
+        <v>0.05390601571753482</v>
       </c>
       <c r="E5" t="n">
         <v>0.05793839572930764</v>
@@ -650,22 +650,22 @@
         <v>0.05793839572930764</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0545026597302896</v>
+        <v>0.05450265973028956</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05390690453333394</v>
+        <v>0.05390690453333385</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05786390312979262</v>
+        <v>0.05786390312979255</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05390690453333394</v>
+        <v>0.05390690453333385</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05390690453333394</v>
+        <v>0.05390690453333385</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05390690453333394</v>
+        <v>0.05390690453333385</v>
       </c>
     </row>
     <row r="6">
@@ -675,7 +675,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07086292183957438</v>
+        <v>0.07086292183957429</v>
       </c>
       <c r="C6" t="n">
         <v>0.1042335877837092</v>
@@ -684,28 +684,28 @@
         <v>0.1062815471969317</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09620215150936706</v>
+        <v>0.09620215150936703</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07579478492320395</v>
+        <v>0.07579478492320386</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1007943578719726</v>
+        <v>0.1007943578719725</v>
       </c>
       <c r="H6" t="n">
         <v>0.1001986026750252</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1041556012714756</v>
+        <v>0.1041556012714755</v>
       </c>
       <c r="J6" t="n">
-        <v>0.100204367927861</v>
+        <v>0.1002043679278609</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07031799651125058</v>
+        <v>0.07031799651125038</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1308421742718102</v>
+        <v>0.1308421742718101</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1727775396232705</v>
+        <v>0.1727775396232706</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2176879615655751</v>
+        <v>0.2176879615655749</v>
       </c>
       <c r="D7" t="n">
         <v>0.2137310039973903</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2649473761386701</v>
+        <v>0.26494737613867</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2176879578024842</v>
+        <v>0.2176879578024839</v>
       </c>
       <c r="G7" t="n">
         <v>0.2143267181660721</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2137309629691161</v>
+        <v>0.2137309629691163</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2176879615655751</v>
+        <v>0.2176879615655749</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2137309629691161</v>
+        <v>0.2137309629691163</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1621632821828377</v>
+        <v>0.1900024059023614</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2137309629691161</v>
+        <v>0.2137309629691163</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.624945224691871</v>
+        <v>0.6249452246918715</v>
       </c>
       <c r="C8" t="n">
-        <v>1.015193910563295</v>
+        <v>1.015193910563294</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6021764319636752</v>
+        <v>0.6021764319636755</v>
       </c>
       <c r="E8" t="n">
-        <v>1.015193910563295</v>
+        <v>1.015193910563294</v>
       </c>
       <c r="F8" t="n">
-        <v>1.015193910563295</v>
+        <v>1.015193910563294</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5681917716274727</v>
+        <v>0.5681917716274729</v>
       </c>
       <c r="H8" t="n">
         <v>0.5802053287495579</v>
       </c>
       <c r="I8" t="n">
-        <v>1.015193910563295</v>
+        <v>1.015193910563294</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4561251798564366</v>
+        <v>0.4561251798564364</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5243639154386316</v>
+        <v>0.5243639154386326</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6141849535654179</v>
+        <v>0.614184953565418</v>
       </c>
     </row>
     <row r="9">
@@ -795,37 +795,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6173394710879192</v>
+        <v>0.6173394710879198</v>
       </c>
       <c r="C9" t="n">
-        <v>1.053702370961795</v>
+        <v>1.053702370961794</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6080665851354209</v>
+        <v>0.6080665851354218</v>
       </c>
       <c r="E9" t="n">
-        <v>1.053702370961795</v>
+        <v>1.053702370961794</v>
       </c>
       <c r="F9" t="n">
-        <v>1.053702370961795</v>
+        <v>1.053702370961794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5943833566067177</v>
+        <v>0.5943833566067193</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5991621612936823</v>
+        <v>0.5991621612936828</v>
       </c>
       <c r="I9" t="n">
-        <v>1.053702370961795</v>
+        <v>1.053702370961794</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5486459075366961</v>
+        <v>0.5486459075366955</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5763788527968787</v>
+        <v>0.5763788527968792</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6129675682987252</v>
+        <v>0.6129675682987255</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06164263840607503</v>
+        <v>0.06164263840607537</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9697890330236297</v>
+        <v>0.9697890330236286</v>
       </c>
       <c r="D2" t="n">
-        <v>2.769417898482202</v>
+        <v>2.769417898482208</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9697890330236297</v>
+        <v>0.9697890330236286</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9697890330236297</v>
+        <v>0.9697890330236286</v>
       </c>
       <c r="G2" t="n">
-        <v>2.388325005553829</v>
+        <v>2.38832500555383</v>
       </c>
       <c r="H2" t="n">
-        <v>5.15373787915154</v>
+        <v>5.153737879151546</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9697890330236297</v>
+        <v>0.9697890330236286</v>
       </c>
       <c r="J2" t="n">
         <v>3.992506952498963</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6579462034500205</v>
+        <v>0.6579462034500214</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3111101333425238</v>
+        <v>2.408372328660529</v>
       </c>
     </row>
     <row r="3">
@@ -954,25 +954,25 @@
         <v>0.01855084700518985</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01972269426337994</v>
+        <v>0.01972269426337986</v>
       </c>
       <c r="D3" t="n">
         <v>0.01855084700518985</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02016957627116291</v>
+        <v>0.02016957627116282</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02016957627116291</v>
+        <v>0.02016957627116283</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01903952992783613</v>
+        <v>0.01903952992783616</v>
       </c>
       <c r="H3" t="n">
         <v>0.01855084700518985</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02182384692286242</v>
+        <v>0.02182384692286233</v>
       </c>
       <c r="J3" t="n">
         <v>0.01855084700518985</v>
@@ -991,34 +991,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.26741334586026</v>
+        <v>38.26741334586033</v>
       </c>
       <c r="C4" t="n">
-        <v>10.07322207224973</v>
+        <v>10.07322207224974</v>
       </c>
       <c r="D4" t="n">
-        <v>10.07428326110776</v>
+        <v>38.26842142192119</v>
       </c>
       <c r="E4" t="n">
-        <v>6.209390110534452</v>
+        <v>6.209390110534459</v>
       </c>
       <c r="F4" t="n">
         <v>10.07524269748449</v>
       </c>
       <c r="G4" t="n">
-        <v>38.26790202878292</v>
+        <v>10.07281513205942</v>
       </c>
       <c r="H4" t="n">
-        <v>38.27156530350518</v>
+        <v>38.27156530350515</v>
       </c>
       <c r="I4" t="n">
         <v>10.07559944905444</v>
       </c>
       <c r="J4" t="n">
-        <v>38.27008790925323</v>
+        <v>38.27008790925321</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06973576275579</v>
+        <v>10.06973576275578</v>
       </c>
       <c r="L4" t="n">
         <v>10.0726479959372</v>
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03321332059392332</v>
+        <v>0.03321332059392329</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03648632051159591</v>
+        <v>0.03648632051159575</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03321298417640829</v>
+        <v>0.03321298417640815</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03626024506770481</v>
+        <v>0.03626024506770464</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03626024506770481</v>
+        <v>0.03626024506770464</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03370200351656961</v>
+        <v>0.03370200351656955</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03321332059392332</v>
+        <v>0.03321332059392329</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03648632051159591</v>
+        <v>0.03648632051159575</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03321332059392332</v>
+        <v>0.03321332059392329</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03321332059392332</v>
+        <v>0.03321332059392329</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03321332059392332</v>
+        <v>0.03321332059392329</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04715722835051269</v>
+        <v>0.04715722835051243</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07205569035282428</v>
+        <v>0.07205569035282404</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07352236941657329</v>
+        <v>0.07352236941657313</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06610594905841971</v>
+        <v>0.06610594905841947</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05098776572316685</v>
+        <v>0.05098776572316664</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06948299150081019</v>
+        <v>0.06948299150080998</v>
       </c>
       <c r="H6" t="n">
-        <v>0.068994308578237</v>
+        <v>0.06899430857823688</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07226730849583644</v>
+        <v>0.07226730849583615</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06899860016164101</v>
+        <v>0.06899860016164089</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04675159337655611</v>
+        <v>0.046751593376556</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09180496483645113</v>
+        <v>0.09180496483645079</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09380751597339534</v>
+        <v>0.09380751597339515</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1194865554227327</v>
+        <v>0.1194865554227325</v>
       </c>
       <c r="D7" t="n">
-        <v>0.116213556692785</v>
+        <v>0.1162135566927847</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1453425619159415</v>
+        <v>0.1453425619159411</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1194864841305427</v>
+        <v>0.1194864841305423</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1167022384277066</v>
+        <v>0.1167022384277063</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1162135555050602</v>
+        <v>0.11621355550506</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1194865554227327</v>
+        <v>0.1194865554227325</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1162135555050602</v>
+        <v>0.11621355550506</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1032314087046611</v>
+        <v>0.1032314087046608</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1162135555050602</v>
+        <v>0.11621355550506</v>
       </c>
     </row>
     <row r="8">
@@ -1151,37 +1151,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6179879649091988</v>
+        <v>0.6179879649091984</v>
       </c>
       <c r="C8" t="n">
-        <v>1.069263967757614</v>
+        <v>1.069263967757615</v>
       </c>
       <c r="D8" t="n">
-        <v>0.54530066622495</v>
+        <v>0.5453006662249498</v>
       </c>
       <c r="E8" t="n">
-        <v>1.069263967757614</v>
+        <v>1.069263967757615</v>
       </c>
       <c r="F8" t="n">
-        <v>1.069263967757614</v>
+        <v>1.069263967757615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.558233363856852</v>
+        <v>0.5582333638568516</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4996318233978235</v>
+        <v>0.4996318233978241</v>
       </c>
       <c r="I8" t="n">
-        <v>1.069263967757614</v>
+        <v>1.069263967757615</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5257775037864499</v>
+        <v>0.5257775037864496</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6015369461170834</v>
+        <v>0.601536946117083</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6122377779387606</v>
+        <v>0.5672854966150311</v>
       </c>
     </row>
     <row r="9">
@@ -1191,13 +1191,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6089843740088305</v>
+        <v>0.60898437400883</v>
       </c>
       <c r="C9" t="n">
         <v>1.066984057883211</v>
       </c>
       <c r="D9" t="n">
-        <v>0.579381254453331</v>
+        <v>0.5793812544533302</v>
       </c>
       <c r="E9" t="n">
         <v>1.066984057883211</v>
@@ -1206,22 +1206,22 @@
         <v>1.066984057883211</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5845035076536375</v>
+        <v>0.5845035076536381</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5608897879532687</v>
+        <v>0.5608897879532689</v>
       </c>
       <c r="I9" t="n">
         <v>1.066984057883211</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5714632006855206</v>
+        <v>0.5714632006855203</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6022849017331846</v>
+        <v>0.6022849017331849</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6066473951849601</v>
+        <v>0.6066473951849596</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.046116129654659</v>
+        <v>3.046116129654665</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6403633215199004</v>
+        <v>0.6403633215199021</v>
       </c>
       <c r="D2" t="n">
-        <v>1.478134101825893</v>
+        <v>1.478134101825913</v>
       </c>
       <c r="E2" t="n">
-        <v>2.762144075844975</v>
+        <v>2.762144075844978</v>
       </c>
       <c r="F2" t="n">
-        <v>2.762144075844975</v>
+        <v>2.762144075844978</v>
       </c>
       <c r="G2" t="n">
-        <v>1.980426758706902</v>
+        <v>1.980426758706898</v>
       </c>
       <c r="H2" t="n">
-        <v>2.745859483932703</v>
+        <v>2.745859483932701</v>
       </c>
       <c r="I2" t="n">
-        <v>2.762144075844975</v>
+        <v>2.762144075844978</v>
       </c>
       <c r="J2" t="n">
-        <v>4.070241217360013</v>
+        <v>4.070241217360019</v>
       </c>
       <c r="K2" t="n">
-        <v>2.744385242897051</v>
+        <v>2.744385242897018</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8917835784817428</v>
+        <v>0.8917835784817457</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02378906340013705</v>
+        <v>0.02378906340013707</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02150353132817733</v>
+        <v>0.02150353132817734</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02378906340013705</v>
+        <v>0.02378906340013708</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02731373472559912</v>
+        <v>0.02731373472559913</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02731373472559913</v>
+        <v>0.02731373472559914</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02422939951143893</v>
+        <v>0.02422939951143906</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02378906340013705</v>
+        <v>0.02378906340013708</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02671629461435248</v>
+        <v>0.02671629461435237</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02378906340013697</v>
+        <v>0.02378906340013708</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02378906340013705</v>
+        <v>0.02378906340013708</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02378906340013705</v>
+        <v>0.02378906340013708</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.40325772281095</v>
+        <v>10.63836679806289</v>
       </c>
       <c r="C4" t="n">
-        <v>10.63490111895242</v>
+        <v>10.63490111895241</v>
       </c>
       <c r="D4" t="n">
-        <v>10.6367055744153</v>
+        <v>10.63670560337563</v>
       </c>
       <c r="E4" t="n">
-        <v>6.562795912322088</v>
+        <v>6.562795912322085</v>
       </c>
       <c r="F4" t="n">
-        <v>10.64134354234739</v>
+        <v>10.6413435423474</v>
       </c>
       <c r="G4" t="n">
-        <v>40.40369805892222</v>
+        <v>40.40369805892221</v>
       </c>
       <c r="H4" t="n">
-        <v>40.40807774265991</v>
+        <v>40.40807774265989</v>
       </c>
       <c r="I4" t="n">
-        <v>40.40618495402515</v>
+        <v>40.40618495402513</v>
       </c>
       <c r="J4" t="n">
-        <v>40.40608309637918</v>
+        <v>40.40608309637919</v>
       </c>
       <c r="K4" t="n">
         <v>10.63919488846955</v>
       </c>
       <c r="L4" t="n">
-        <v>10.63762014578711</v>
+        <v>10.6376201457871</v>
       </c>
     </row>
     <row r="5">
@@ -1427,37 +1427,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0399639350679958</v>
+        <v>0.03996393506799598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03991309207036281</v>
+        <v>0.03991309207036276</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03996350298001239</v>
+        <v>0.03996350298001258</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04293266307807684</v>
+        <v>0.04293266307807683</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04293266307807684</v>
+        <v>0.04293266307807683</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04040427117929782</v>
+        <v>0.040404271179298</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0399639350679958</v>
+        <v>0.03996393506799598</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04289116628221128</v>
+        <v>0.04289116628221129</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0399639350679958</v>
+        <v>0.03996393506799598</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0399639350679958</v>
+        <v>0.03996393506799598</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0399639350679958</v>
+        <v>0.03996393506799598</v>
       </c>
     </row>
     <row r="6">
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05348472076636247</v>
+        <v>0.05348472076636256</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0767813737725033</v>
+        <v>0.07678137377308346</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08161948568627232</v>
+        <v>0.08161948568627246</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07338157160429323</v>
+        <v>0.07338157160429316</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05717562680898791</v>
+        <v>0.05717562680898784</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07722783827430978</v>
+        <v>0.0772278382743098</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0767875021631213</v>
+        <v>0.07678750216312151</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07971473337722319</v>
+        <v>0.0797147333772231</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07679208178352899</v>
+        <v>0.07679208178352921</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05305185964198348</v>
+        <v>0.05305185964198357</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1011292058383579</v>
+        <v>0.101129205838358</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1099282229931909</v>
+        <v>0.1099282229931901</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1356297041720922</v>
+        <v>0.1356297041720913</v>
       </c>
       <c r="D7" t="n">
-        <v>0.13568057857494</v>
+        <v>0.1356805785749402</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1683254390764168</v>
+        <v>0.1683254390764167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1386077753764028</v>
+        <v>0.1386077753764019</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1361208832810277</v>
+        <v>0.1361208832810266</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1356805471697251</v>
+        <v>0.1356805471697244</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1386077783839407</v>
+        <v>0.1386077783839399</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1356805471697251</v>
+        <v>0.1356805471697244</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1032537661183037</v>
+        <v>0.1207595626135711</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1356805471697251</v>
+        <v>0.1356805471697244</v>
       </c>
     </row>
     <row r="8">
@@ -1547,13 +1547,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03626645087264693</v>
+        <v>-0.03626645087264703</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9266937570077308</v>
+        <v>0.9266937570077319</v>
       </c>
       <c r="D8" t="n">
-        <v>1.077706398549912</v>
+        <v>1.07770639854991</v>
       </c>
       <c r="E8" t="n">
         <v>1.009780938293803</v>
@@ -1562,22 +1562,22 @@
         <v>1.009780938293803</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5280301881075233</v>
+        <v>0.5280301881075241</v>
       </c>
       <c r="H8" t="n">
-        <v>1.055850584457574</v>
+        <v>1.055850584457575</v>
       </c>
       <c r="I8" t="n">
         <v>1.009780938293803</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6032715131673456</v>
+        <v>0.6032715131673457</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7115230680668363</v>
+        <v>0.7115230680668365</v>
       </c>
       <c r="L8" t="n">
-        <v>1.191867489734711</v>
+        <v>1.191867489734712</v>
       </c>
     </row>
     <row r="9">
@@ -1587,34 +1587,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003482867751383951</v>
+        <v>0.003482867751383966</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9203143139004617</v>
+        <v>0.9203143139004619</v>
       </c>
       <c r="D9" t="n">
-        <v>1.080358738518783</v>
+        <v>1.080358738518784</v>
       </c>
       <c r="E9" t="n">
         <v>1.030220544802774</v>
       </c>
       <c r="F9" t="n">
-        <v>1.030220544802774</v>
+        <v>1.030220544802773</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5452227404613822</v>
+        <v>0.5452227404613831</v>
       </c>
       <c r="H9" t="n">
-        <v>1.071507886323409</v>
+        <v>1.07150788632341</v>
       </c>
       <c r="I9" t="n">
-        <v>1.030220544802774</v>
+        <v>1.030220544802773</v>
       </c>
       <c r="J9" t="n">
-        <v>0.645217775386237</v>
+        <v>0.6452177753862379</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7366440058303985</v>
+        <v>0.7366440058304006</v>
       </c>
       <c r="L9" t="n">
         <v>1.183348748025931</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.664242935536041</v>
+        <v>1.66424293553604</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4048636521308366</v>
+        <v>0.404863652130836</v>
       </c>
       <c r="D2" t="n">
-        <v>1.512657121738279</v>
+        <v>1.512657121738278</v>
       </c>
       <c r="E2" t="n">
-        <v>1.313714705599414</v>
+        <v>1.313714705599409</v>
       </c>
       <c r="F2" t="n">
-        <v>1.313714705599414</v>
+        <v>1.313714705599409</v>
       </c>
       <c r="G2" t="n">
-        <v>1.297873658794063</v>
+        <v>1.297873658794057</v>
       </c>
       <c r="H2" t="n">
-        <v>2.214748472458765</v>
+        <v>2.214748472458764</v>
       </c>
       <c r="I2" t="n">
-        <v>1.313714705599414</v>
+        <v>1.313714705599409</v>
       </c>
       <c r="J2" t="n">
-        <v>2.78052461782466</v>
+        <v>2.780524617824656</v>
       </c>
       <c r="K2" t="n">
-        <v>1.355063623393795</v>
+        <v>1.355063623393792</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6512552293962197</v>
+        <v>0.6512552293962175</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01767294305015762</v>
+        <v>0.01767294305015713</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01587094121639201</v>
+        <v>0.015870941216392</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01767294305015762</v>
+        <v>0.01767294305015713</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02035092678417916</v>
+        <v>0.02035092678417909</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02035092678417916</v>
+        <v>0.02035092678417912</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0180879721996982</v>
+        <v>0.01808797219969774</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01767294305015762</v>
+        <v>0.01767294305015713</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02043788176339835</v>
+        <v>0.02043788176339834</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01767294305015762</v>
+        <v>0.01767294305015713</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01767294305015762</v>
+        <v>0.01767294305015713</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01767294305015762</v>
+        <v>0.01767294305015713</v>
       </c>
     </row>
     <row r="4">
@@ -1783,25 +1783,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.25803499646351</v>
+        <v>38.25803499646354</v>
       </c>
       <c r="C4" t="n">
         <v>10.06623177732574</v>
       </c>
       <c r="D4" t="n">
-        <v>10.0686390594903</v>
+        <v>38.25850544816349</v>
       </c>
       <c r="E4" t="n">
-        <v>6.207173109228788</v>
+        <v>6.207173109228791</v>
       </c>
       <c r="F4" t="n">
         <v>10.07102515673249</v>
       </c>
       <c r="G4" t="n">
-        <v>10.06878191482543</v>
+        <v>10.06878191482542</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26233550208971</v>
+        <v>38.26233550208968</v>
       </c>
       <c r="I4" t="n">
         <v>10.07113182438912</v>
@@ -1813,7 +1813,7 @@
         <v>10.06827730722447</v>
       </c>
       <c r="L4" t="n">
-        <v>10.0680172154215</v>
+        <v>10.06801721542149</v>
       </c>
     </row>
     <row r="5">
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02930873607868768</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02926666441068763</v>
+        <v>0.02926666441068762</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02930835438254915</v>
+        <v>0.02930835438254947</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03206133926601117</v>
+        <v>0.03206133926601114</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03206133926601117</v>
+        <v>0.03206133926601114</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02972376522822794</v>
+        <v>0.02972376522822812</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02930873607868768</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03207367479192847</v>
+        <v>0.03207367479192845</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02930873607868768</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02930873607868768</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02930873607868768</v>
+        <v>0.02930873607868767</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03958238905424814</v>
+        <v>0.03958238905424726</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05684332092649907</v>
+        <v>0.0568433209269445</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06048289802436769</v>
+        <v>0.06048289802436724</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05491672872710204</v>
+        <v>0.05491672872710193</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04288892767786293</v>
+        <v>0.04288892767786284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0573083853649574</v>
+        <v>0.05730838536495755</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05689335621554287</v>
+        <v>0.05689335621554239</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0596582949286579</v>
+        <v>0.05965829492865779</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05689675828091653</v>
+        <v>0.05689675828091631</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03926082895489315</v>
+        <v>0.03926082895489193</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07497610890205451</v>
+        <v>0.07497610890205331</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07301680347412588</v>
+        <v>0.07301680347412499</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0897558326282135</v>
+        <v>0.08975583262821347</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08979792055234369</v>
+        <v>0.08979792055234372</v>
       </c>
       <c r="E7" t="n">
         <v>0.1119278755107869</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09256282962885877</v>
+        <v>0.09256282962885867</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0902129334457541</v>
+        <v>0.0902129334457538</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08979790429621337</v>
+        <v>0.08979790429621344</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09256284300945428</v>
+        <v>0.09256284300945425</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08979790429621337</v>
+        <v>0.08979790429621344</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08007487541269337</v>
+        <v>0.0800748754126929</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08979790429621337</v>
+        <v>0.08979790429621344</v>
       </c>
     </row>
     <row r="8">
@@ -1943,37 +1943,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01298949236560231</v>
+        <v>-0.01298949236560191</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9290764566008625</v>
+        <v>0.9290764566008619</v>
       </c>
       <c r="D8" t="n">
         <v>1.066232243776106</v>
       </c>
       <c r="E8" t="n">
-        <v>1.035332730748297</v>
+        <v>1.035332730748298</v>
       </c>
       <c r="F8" t="n">
-        <v>1.035332730748297</v>
+        <v>1.035332730748298</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5370309806331449</v>
+        <v>0.5370309806331451</v>
       </c>
       <c r="H8" t="n">
-        <v>1.055442700981085</v>
+        <v>1.055442700981084</v>
       </c>
       <c r="I8" t="n">
-        <v>1.035332730748297</v>
+        <v>1.035332730748298</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6230816348252322</v>
+        <v>0.6230816348252315</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7343528221950623</v>
+        <v>0.7343528221950618</v>
       </c>
       <c r="L8" t="n">
-        <v>1.192865831955773</v>
+        <v>1.192865831955771</v>
       </c>
     </row>
     <row r="9">
@@ -1983,31 +1983,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.009773280024194938</v>
+        <v>0.00977328002419464</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9199336502342875</v>
+        <v>0.9199336502342889</v>
       </c>
       <c r="D9" t="n">
-        <v>1.070688063655536</v>
+        <v>1.070688063655535</v>
       </c>
       <c r="E9" t="n">
-        <v>1.037248915663538</v>
+        <v>1.037248915663537</v>
       </c>
       <c r="F9" t="n">
-        <v>1.037248915663538</v>
+        <v>1.037248915663537</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5462161201461621</v>
+        <v>0.5462161201461616</v>
       </c>
       <c r="H9" t="n">
-        <v>1.066336722041636</v>
+        <v>1.066336722041634</v>
       </c>
       <c r="I9" t="n">
-        <v>1.037248915663538</v>
+        <v>1.037248915663537</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6503780480144915</v>
+        <v>0.6503780480144905</v>
       </c>
       <c r="K9" t="n">
         <v>0.7417064818128745</v>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8205170598971148</v>
+        <v>0.820517059897116</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2603663900424646</v>
+        <v>0.2603663900424912</v>
       </c>
       <c r="D2" t="n">
-        <v>1.63452399700401</v>
+        <v>1.634523997004037</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4536471152291351</v>
+        <v>0.4536471152291341</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4536471152291351</v>
+        <v>0.4536471152291341</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9138048723027397</v>
+        <v>0.9138048723027491</v>
       </c>
       <c r="H2" t="n">
-        <v>1.791896253236253</v>
+        <v>1.791896253236249</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4536471152291351</v>
+        <v>0.4536471152291341</v>
       </c>
       <c r="J2" t="n">
-        <v>2.21059567862122</v>
+        <v>2.210595678621216</v>
       </c>
       <c r="K2" t="n">
-        <v>0.516007055428325</v>
+        <v>0.5160070554283254</v>
       </c>
       <c r="L2" t="n">
-        <v>0.35045695703162</v>
+        <v>0.3504569570316212</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01353020126459335</v>
+        <v>0.01353020126459336</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01222286857983234</v>
+        <v>0.01222286857983237</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01353020126459335</v>
+        <v>0.01353020126459337</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01554141074782482</v>
+        <v>0.01554141074782484</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01554141074782482</v>
+        <v>0.01554141074782484</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01392916878544558</v>
+        <v>0.01392916878544555</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01353020126459335</v>
+        <v>0.01353020126459337</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01619210020985764</v>
+        <v>0.0161921002098577</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01353020126459335</v>
+        <v>0.01353020126459336</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01353020126459335</v>
+        <v>0.01353020126459337</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01353020126459335</v>
+        <v>0.01353020126459337</v>
       </c>
     </row>
     <row r="4">
@@ -2179,13 +2179,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.24925601898418</v>
+        <v>10.06193008645181</v>
       </c>
       <c r="C4" t="n">
-        <v>10.06059835433641</v>
+        <v>10.0605983543364</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06353713255279</v>
+        <v>10.06353713255282</v>
       </c>
       <c r="E4" t="n">
         <v>6.200073086571384</v>
@@ -2194,22 +2194,22 @@
         <v>10.0643876746881</v>
       </c>
       <c r="G4" t="n">
-        <v>10.06232905397267</v>
+        <v>38.24965498650501</v>
       </c>
       <c r="H4" t="n">
-        <v>38.25326815095777</v>
+        <v>38.25326815095776</v>
       </c>
       <c r="I4" t="n">
-        <v>10.06459198539708</v>
+        <v>38.25191791792942</v>
       </c>
       <c r="J4" t="n">
-        <v>10.57350460049342</v>
+        <v>38.2517715532467</v>
       </c>
       <c r="K4" t="n">
         <v>10.06123138573862</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06178500206281</v>
+        <v>10.0617850020628</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02248964259931026</v>
+        <v>0.02248964259931049</v>
       </c>
       <c r="C5" t="n">
         <v>0.02245364066034338</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02248923156270704</v>
+        <v>0.02248923156270691</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0250620728333381</v>
+        <v>0.02506207283333802</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0250620728333381</v>
+        <v>0.02506207283333802</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02288861012016264</v>
+        <v>0.02288861012016255</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02248964259931026</v>
+        <v>0.02248964259931049</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02515154154457485</v>
+        <v>0.02515154154457482</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02248964259931026</v>
+        <v>0.02248964259931049</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02248964259931026</v>
+        <v>0.02248964259931049</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02248964259931026</v>
+        <v>0.02248964259931049</v>
       </c>
     </row>
     <row r="6">
@@ -2259,37 +2259,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0308511895617432</v>
+        <v>0.030851189561743</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04440583812064922</v>
+        <v>0.04440583812026375</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04735937693239529</v>
+        <v>0.04735937693239525</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04337292818552017</v>
+        <v>0.04337292818552019</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03389337433116513</v>
+        <v>0.0338933743311652</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04492315853306963</v>
+        <v>0.04492315853306943</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04452419101237348</v>
+        <v>0.0445241910123734</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0471860899574816</v>
+        <v>0.0471860899574818</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0445268781211254</v>
+        <v>0.04452687812112549</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0305972065425762</v>
+        <v>0.03059720654257625</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05880678431956834</v>
+        <v>0.05880678431956828</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05299326383181768</v>
+        <v>0.05299326383181743</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06503197832492782</v>
+        <v>0.06503197832492751</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06506798939745369</v>
+        <v>0.06506798939745304</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08166383139810916</v>
+        <v>0.08166383139810932</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06772986096526483</v>
+        <v>0.06772986096526336</v>
       </c>
       <c r="G7" t="n">
         <v>0.0654669477847472</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06506798026389492</v>
+        <v>0.0650679802638954</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06772987920915924</v>
+        <v>0.06772987920915906</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06506798026389492</v>
+        <v>0.0650679802638954</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05778800360786701</v>
+        <v>0.04986375457942763</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06506798026389492</v>
+        <v>0.0650679802638954</v>
       </c>
     </row>
     <row r="8">
@@ -2339,37 +2339,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002929264260533834</v>
+        <v>0.002929264260533907</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9309413586115602</v>
+        <v>0.9309413586115595</v>
       </c>
       <c r="D8" t="n">
-        <v>1.057021002846223</v>
+        <v>1.057021002846225</v>
       </c>
       <c r="E8" t="n">
-        <v>1.052549184758658</v>
+        <v>1.052549184758659</v>
       </c>
       <c r="F8" t="n">
-        <v>1.052549184758658</v>
+        <v>1.052549184758659</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5429265792016411</v>
+        <v>0.542926579201641</v>
       </c>
       <c r="H8" t="n">
-        <v>1.058313305265896</v>
+        <v>1.058313305265897</v>
       </c>
       <c r="I8" t="n">
-        <v>1.052549184758658</v>
+        <v>1.052549184758659</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6322873573263377</v>
+        <v>0.6322873573263391</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7516035942988922</v>
+        <v>0.7516035942988925</v>
       </c>
       <c r="L8" t="n">
-        <v>1.196713579601304</v>
+        <v>1.196713579601303</v>
       </c>
     </row>
     <row r="9">
@@ -2379,34 +2379,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01396292553753657</v>
+        <v>0.01396292553753656</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9198215673280133</v>
+        <v>0.919821567328012</v>
       </c>
       <c r="D9" t="n">
-        <v>1.063370134789638</v>
+        <v>1.063370134789639</v>
       </c>
       <c r="E9" t="n">
-        <v>1.042237955385044</v>
+        <v>1.042237955385043</v>
       </c>
       <c r="F9" t="n">
-        <v>1.042237955385044</v>
+        <v>1.042237955385043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5467993986146888</v>
+        <v>0.5467993986146886</v>
       </c>
       <c r="H9" t="n">
         <v>1.063931181878818</v>
       </c>
       <c r="I9" t="n">
-        <v>1.042237955385044</v>
+        <v>1.042237955385043</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6518471942123937</v>
+        <v>0.6518471942123945</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7469551582021484</v>
+        <v>0.7469551582021479</v>
       </c>
       <c r="L9" t="n">
         <v>1.182153259736697</v>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.963693015655051</v>
+        <v>2.963693015655054</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4885787337731565</v>
+        <v>0.4885787337738239</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559134217022471</v>
+        <v>1.559134217022507</v>
       </c>
       <c r="E2" t="n">
-        <v>2.517142796928532</v>
+        <v>2.517142796928544</v>
       </c>
       <c r="F2" t="n">
-        <v>2.517142796928532</v>
+        <v>2.517142796928544</v>
       </c>
       <c r="G2" t="n">
-        <v>1.948324188744589</v>
+        <v>1.94832418874462</v>
       </c>
       <c r="H2" t="n">
-        <v>5.201077989882059</v>
+        <v>5.201077989882067</v>
       </c>
       <c r="I2" t="n">
-        <v>2.517142796928532</v>
+        <v>2.517142796928544</v>
       </c>
       <c r="J2" t="n">
-        <v>4.022819101598187</v>
+        <v>4.022819101598192</v>
       </c>
       <c r="K2" t="n">
         <v>2.440162760863803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4776289383961775</v>
+        <v>0.4776289383961806</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02298377229411368</v>
+        <v>0.02298377229411451</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02056728801463124</v>
+        <v>0.02056728801463311</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02298377229411368</v>
+        <v>0.02298377229411451</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02619268131639449</v>
+        <v>0.02619268131639443</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02619268131639447</v>
+        <v>0.02619268131639443</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02341572994424401</v>
+        <v>0.02341572994424357</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02298377229411368</v>
+        <v>0.02298377229411451</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0258573554711806</v>
+        <v>0.02585735547118029</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02298377229411368</v>
+        <v>0.02298377229411451</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02298377229411368</v>
+        <v>0.02298377229411451</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02298377229411368</v>
+        <v>0.02298377229411451</v>
       </c>
     </row>
     <row r="4">
@@ -2575,7 +2575,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.4017550743721</v>
+        <v>10.63712249891232</v>
       </c>
       <c r="C4" t="n">
         <v>10.63347906060108</v>
@@ -2584,25 +2584,25 @@
         <v>10.63578925460249</v>
       </c>
       <c r="E4" t="n">
-        <v>6.561145615295803</v>
+        <v>6.561145615295809</v>
       </c>
       <c r="F4" t="n">
         <v>10.63995166019024</v>
       </c>
       <c r="G4" t="n">
-        <v>10.63755445656245</v>
+        <v>10.63755445656244</v>
       </c>
       <c r="H4" t="n">
         <v>40.40724691257221</v>
       </c>
       <c r="I4" t="n">
-        <v>40.40462865754921</v>
+        <v>10.63999608208938</v>
       </c>
       <c r="J4" t="n">
-        <v>40.4046759817337</v>
+        <v>40.40467598173367</v>
       </c>
       <c r="K4" t="n">
-        <v>10.63751661898261</v>
+        <v>10.63751661898262</v>
       </c>
       <c r="L4" t="n">
         <v>10.636280947643</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03895287330394697</v>
+        <v>0.03895287330394823</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03889640853789977</v>
+        <v>0.03889640853790069</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03895246359745811</v>
+        <v>0.03895246359745871</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04183441754421809</v>
+        <v>0.04183441754421897</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04183441754421809</v>
+        <v>0.04183441754421897</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03938483095407726</v>
+        <v>0.03938483095407839</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03895287330394697</v>
+        <v>0.03895287330394823</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04182645648101388</v>
+        <v>0.04182645648101513</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03895287330394697</v>
+        <v>0.03895287330394823</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03895287330394697</v>
+        <v>0.03895287330394823</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03895287330394697</v>
+        <v>0.03895287330394823</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05238115697573829</v>
+        <v>0.05238115697573828</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0754505263067875</v>
+        <v>0.07545052630678808</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08028707118513785</v>
+        <v>0.08028707118513914</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07205793424122386</v>
+        <v>0.0720579342412252</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05599238759276925</v>
+        <v>0.05599238759277102</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07592634910099069</v>
+        <v>0.07592634910099268</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07549439145099102</v>
+        <v>0.0754943914509926</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07836797462792733</v>
+        <v>0.07836797462792985</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07549893381953592</v>
+        <v>0.075498933819537</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05195181678277869</v>
+        <v>0.05195181678277987</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09963809751662153</v>
+        <v>0.09963809751662335</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1070380840844689</v>
+        <v>0.1070380840844717</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1321573871035032</v>
+        <v>0.1321573871035078</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1322138522754605</v>
+        <v>0.1322138522754657</v>
       </c>
       <c r="E7" t="n">
-        <v>0.164139692546476</v>
+        <v>0.1641396925464826</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1350873989837701</v>
+        <v>0.1350873989837753</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1326458095196806</v>
+        <v>0.132645809519685</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1322138518695504</v>
+        <v>0.1322138518695548</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1350874350466173</v>
+        <v>0.135087435046622</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1322138518695504</v>
+        <v>0.1322138518695548</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1005130662642738</v>
+        <v>0.1005130662642783</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1322138518695504</v>
+        <v>0.1322138518695548</v>
       </c>
     </row>
     <row r="8">
@@ -2735,34 +2735,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03218921087411605</v>
+        <v>-0.03218921087411598</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9293127130399672</v>
+        <v>0.9293127130399662</v>
       </c>
       <c r="D8" t="n">
-        <v>1.074457604608388</v>
+        <v>1.074457604608387</v>
       </c>
       <c r="E8" t="n">
-        <v>1.014213224905565</v>
+        <v>1.014213224905566</v>
       </c>
       <c r="F8" t="n">
-        <v>1.014213224905565</v>
+        <v>1.014213224905566</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5283139872980316</v>
+        <v>0.5283139872980303</v>
       </c>
       <c r="H8" t="n">
-        <v>1.004436055427479</v>
+        <v>1.00443605542748</v>
       </c>
       <c r="I8" t="n">
-        <v>1.014213224905565</v>
+        <v>1.014213224905566</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6039922116336288</v>
+        <v>0.6039922116336298</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7160264712456533</v>
+        <v>0.7160264712456531</v>
       </c>
       <c r="L8" t="n">
         <v>1.199697804762866</v>
@@ -2775,34 +2775,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.006439660633475777</v>
+        <v>0.00643966063347591</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9209316167428692</v>
+        <v>0.9209316167428691</v>
       </c>
       <c r="D9" t="n">
-        <v>1.078250022141638</v>
+        <v>1.078250022141636</v>
       </c>
       <c r="E9" t="n">
-        <v>1.031356703192231</v>
+        <v>1.031356703192232</v>
       </c>
       <c r="F9" t="n">
-        <v>1.031356703192231</v>
+        <v>1.031356703192232</v>
       </c>
       <c r="G9" t="n">
         <v>0.5450945817234989</v>
       </c>
       <c r="H9" t="n">
-        <v>1.049828131094318</v>
+        <v>1.049828131094317</v>
       </c>
       <c r="I9" t="n">
-        <v>1.031356703192231</v>
+        <v>1.031356703192232</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6453347933014338</v>
+        <v>0.645334793301434</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7370454220843042</v>
+        <v>0.7370454220843052</v>
       </c>
       <c r="L9" t="n">
         <v>1.186282929309624</v>
@@ -2891,34 +2891,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.444451810011893</v>
+        <v>1.444451810011891</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1947636355479003</v>
+        <v>0.1947636355479005</v>
       </c>
       <c r="D2" t="n">
         <v>1.611626490461503</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9562582942841562</v>
+        <v>0.9562582942841579</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9562582942841562</v>
+        <v>0.9562582942841579</v>
       </c>
       <c r="G2" t="n">
-        <v>1.276512866966101</v>
+        <v>1.276512866966097</v>
       </c>
       <c r="H2" t="n">
-        <v>7.518928521791657</v>
+        <v>7.518928521791654</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9562582942841562</v>
+        <v>0.9562582942841579</v>
       </c>
       <c r="J2" t="n">
         <v>2.373142965962557</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9601655268521179</v>
+        <v>0.9601655268521174</v>
       </c>
       <c r="L2" t="n">
         <v>0.1813258419793943</v>
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01693795533799911</v>
+        <v>0.01693795533799913</v>
       </c>
       <c r="C3" t="n">
         <v>0.01471676235264079</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01693795533799911</v>
+        <v>0.01693795533799913</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01922309703409543</v>
+        <v>0.01922309703409542</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01922309703409545</v>
+        <v>0.01922309703409542</v>
       </c>
       <c r="G3" t="n">
         <v>0.01733746511412001</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01693795533799911</v>
+        <v>0.01693795533799913</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01960342445984825</v>
+        <v>0.01960342445984824</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01693795533799911</v>
+        <v>0.01693795533799913</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01693795533799911</v>
+        <v>0.01693795533799913</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01693795533799911</v>
+        <v>0.01693795533799913</v>
       </c>
     </row>
     <row r="4">
@@ -2971,28 +2971,28 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.0671067370399</v>
+        <v>10.06710673703989</v>
       </c>
       <c r="C4" t="n">
         <v>10.0646065231555</v>
       </c>
       <c r="D4" t="n">
-        <v>38.25785574375225</v>
+        <v>10.06774080047203</v>
       </c>
       <c r="E4" t="n">
-        <v>6.205211587243013</v>
+        <v>6.205211587243009</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06956586374593</v>
+        <v>10.06956586374592</v>
       </c>
       <c r="G4" t="n">
-        <v>10.067506246816</v>
+        <v>38.25742338186004</v>
       </c>
       <c r="H4" t="n">
-        <v>38.2661913639696</v>
+        <v>38.26619136396958</v>
       </c>
       <c r="I4" t="n">
-        <v>10.06977220616174</v>
+        <v>38.25968934120581</v>
       </c>
       <c r="J4" t="n">
         <v>10.57869086158841</v>
@@ -3011,37 +3011,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02896427686755869</v>
+        <v>0.0289642768675587</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02891154277366314</v>
+        <v>0.02891154277366315</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02896401196405924</v>
+        <v>0.02896401196405927</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03160729873396542</v>
+        <v>0.03160729873396544</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03160729873396542</v>
+        <v>0.03160729873396544</v>
       </c>
       <c r="G5" t="n">
         <v>0.02936378664367957</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02896427686755869</v>
+        <v>0.0289642768675587</v>
       </c>
       <c r="I5" t="n">
         <v>0.03162974598940781</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02896427686755869</v>
+        <v>0.0289642768675587</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02896427686755869</v>
+        <v>0.0289642768675587</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02896427686755869</v>
+        <v>0.0289642768675587</v>
       </c>
     </row>
     <row r="6">
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03983928534774585</v>
+        <v>0.03983928534774589</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05795951561244821</v>
+        <v>0.0579595156124482</v>
       </c>
       <c r="D6" t="n">
         <v>0.06180180422642662</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05570461590378409</v>
+        <v>0.05570461590378402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04306813503610205</v>
+        <v>0.04306813503610204</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0584293781202903</v>
+        <v>0.05842937812029027</v>
       </c>
       <c r="H6" t="n">
         <v>0.05802986834533105</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06069533746601856</v>
+        <v>0.06069533746601854</v>
       </c>
       <c r="J6" t="n">
         <v>0.05803344327535723</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03950138593298865</v>
+        <v>0.03950138593298866</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07703145331900607</v>
+        <v>0.07703145331900602</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07049888029545039</v>
+        <v>0.0704988802954504</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08684277913777573</v>
+        <v>0.08684277913777577</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08689546288259735</v>
+        <v>0.08689546288259734</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1084821984347045</v>
+        <v>0.1084821984347044</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08956089823516411</v>
+        <v>0.08956089823516407</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08729502300779222</v>
+        <v>0.08729502300779216</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08689551323167127</v>
+        <v>0.08689551323167126</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08956098235352046</v>
+        <v>0.08956098235352039</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08689551323167127</v>
+        <v>0.08689551323167126</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07739521853725675</v>
+        <v>0.06624923862573885</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08689551323167127</v>
+        <v>0.08689551323167126</v>
       </c>
     </row>
     <row r="8">
@@ -3131,34 +3131,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.006351056312792698</v>
+        <v>-0.006351056312792684</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9332419448808512</v>
+        <v>0.9332419448808507</v>
       </c>
       <c r="D8" t="n">
-        <v>1.06222348007334</v>
+        <v>1.062223480073339</v>
       </c>
       <c r="E8" t="n">
-        <v>1.042438151930786</v>
+        <v>1.042438151930787</v>
       </c>
       <c r="F8" t="n">
-        <v>1.042438151930786</v>
+        <v>1.042438151930787</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5370662490239763</v>
+        <v>0.5370662490239764</v>
       </c>
       <c r="H8" t="n">
-        <v>0.939718191816197</v>
+        <v>0.9397181918161982</v>
       </c>
       <c r="I8" t="n">
-        <v>1.042438151930786</v>
+        <v>1.042438151930787</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6326566563487819</v>
+        <v>0.6326566563487815</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7402823315297554</v>
+        <v>0.7402823315297559</v>
       </c>
       <c r="L8" t="n">
         <v>1.202664089661443</v>
@@ -3171,10 +3171,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01332405639739615</v>
+        <v>0.01332405639739617</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9211702470162489</v>
+        <v>0.9211702470162508</v>
       </c>
       <c r="D9" t="n">
         <v>1.068149755253655</v>
@@ -3186,10 +3186,10 @@
         <v>1.039273161791285</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5459718237724369</v>
+        <v>0.545971823772437</v>
       </c>
       <c r="H9" t="n">
-        <v>1.018403523625263</v>
+        <v>1.018403523625264</v>
       </c>
       <c r="I9" t="n">
         <v>1.039273161791285</v>
@@ -3198,10 +3198,10 @@
         <v>0.654367478746804</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7420201222058</v>
+        <v>0.7420201222058008</v>
       </c>
       <c r="L9" t="n">
-        <v>1.185934405794513</v>
+        <v>1.185934405794514</v>
       </c>
     </row>
   </sheetData>
@@ -3287,13 +3287,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6193486447824771</v>
+        <v>0.6193486447824766</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08531576319712439</v>
+        <v>0.08531576319712454</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563254771769572</v>
+        <v>1.563254771769568</v>
       </c>
       <c r="E2" t="n">
         <v>0.2655385165724852</v>
@@ -3302,22 +3302,22 @@
         <v>0.2655385165724852</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7675489936075069</v>
+        <v>0.7675489936075058</v>
       </c>
       <c r="H2" t="n">
-        <v>5.387212611858695</v>
+        <v>5.387212611858693</v>
       </c>
       <c r="I2" t="n">
         <v>0.2655385165724852</v>
       </c>
       <c r="J2" t="n">
-        <v>1.326804953757653</v>
+        <v>1.326804953757652</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2474445491499508</v>
+        <v>0.2474445491499483</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05347117959582271</v>
+        <v>0.05347117959582267</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0133242125360882</v>
+        <v>0.01332421253608821</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01086114650649172</v>
+        <v>0.01086114650649174</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0133242125360882</v>
+        <v>0.01332421253608821</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01484128469186281</v>
+        <v>0.01484128469186276</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01484128469186281</v>
+        <v>0.01484128469186276</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01371750154848895</v>
+        <v>0.01371750154849006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0133242125360882</v>
+        <v>0.01332421253608821</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01594984727540529</v>
+        <v>0.01594984727540628</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0133242125360882</v>
+        <v>0.01332421253608821</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0133242125360882</v>
+        <v>0.01332421253608821</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0133242125360882</v>
+        <v>0.01332421253608821</v>
       </c>
     </row>
     <row r="4">
@@ -3367,37 +3367,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.24868512641659</v>
+        <v>38.24868512641651</v>
       </c>
       <c r="C4" t="n">
-        <v>10.05966368285084</v>
+        <v>10.05966368285087</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06302574457076</v>
+        <v>10.06302574457075</v>
       </c>
       <c r="E4" t="n">
-        <v>6.199168189685287</v>
+        <v>6.199168189685284</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06373003164412</v>
+        <v>10.06373003164411</v>
       </c>
       <c r="G4" t="n">
-        <v>38.24907841542897</v>
+        <v>38.24907841542891</v>
       </c>
       <c r="H4" t="n">
         <v>38.25960984112437</v>
       </c>
       <c r="I4" t="n">
-        <v>10.06396029237374</v>
+        <v>10.06396029237373</v>
       </c>
       <c r="J4" t="n">
-        <v>38.25179088188038</v>
+        <v>38.25179088188035</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06029716798884</v>
+        <v>10.06029716798881</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06112023974038</v>
+        <v>10.06112023974037</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02247479205166922</v>
+        <v>0.02247479205166924</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02243501344126069</v>
+        <v>0.02243501344126068</v>
       </c>
       <c r="D5" t="n">
         <v>0.02247467076796004</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02490849766912897</v>
+        <v>0.0249084976691289</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02490849766912897</v>
+        <v>0.0249084976691289</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02286808106406997</v>
+        <v>0.02286808106406996</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02247479205166922</v>
+        <v>0.02247479205166924</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02510042679098631</v>
+        <v>0.02510042679098624</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02247479205166922</v>
+        <v>0.02247479205166924</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02247479205166922</v>
+        <v>0.02247479205166924</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02247479205166922</v>
+        <v>0.02247479205166924</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0315530857907319</v>
+        <v>0.03155308579073192</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04609344622136517</v>
+        <v>0.04609344622136509</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04937448635881021</v>
+        <v>0.04937448635881024</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04474112995114236</v>
+        <v>0.04474112995114234</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03453218856483158</v>
+        <v>0.0345321885648315</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04670705266288322</v>
+        <v>0.04670705266288316</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04631376365210737</v>
+        <v>0.04631376365210731</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04893939838979959</v>
+        <v>0.04893939838979957</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04631666450568744</v>
+        <v>0.04631666450568742</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03127889862500832</v>
+        <v>0.03127889862500829</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06173252590420993</v>
+        <v>0.06173252590420994</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0498632593565355</v>
+        <v>0.04986325935653554</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06131192922032585</v>
+        <v>0.06131192922032586</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06135166835388551</v>
+        <v>0.06135166835388565</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07723465117822539</v>
+        <v>0.07723465117822492</v>
       </c>
       <c r="F7" t="n">
         <v>0.06397727724976104</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06174499684313513</v>
+        <v>0.06174499684313501</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06135170783073438</v>
+        <v>0.06135170783073431</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06397734257005148</v>
+        <v>0.0639773425700515</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06135170783073438</v>
+        <v>0.06135170783073431</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05469523906235798</v>
+        <v>0.05442517931767193</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06135170783073438</v>
+        <v>0.06135170783073431</v>
       </c>
     </row>
     <row r="8">
@@ -3527,13 +3527,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00895510195585424</v>
+        <v>0.00895510195585422</v>
       </c>
       <c r="C8" t="n">
         <v>0.9348323752604306</v>
       </c>
       <c r="D8" t="n">
-        <v>1.058479422140231</v>
+        <v>1.058479422140232</v>
       </c>
       <c r="E8" t="n">
         <v>1.056780367294897</v>
@@ -3542,22 +3542,22 @@
         <v>1.056780367294897</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5463704478814927</v>
+        <v>0.5463704478814925</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9806728201718676</v>
+        <v>0.9806728201718673</v>
       </c>
       <c r="I8" t="n">
         <v>1.056780367294897</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6534358120997122</v>
+        <v>0.6534358120997124</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7565597770485619</v>
+        <v>0.7565597770485626</v>
       </c>
       <c r="L8" t="n">
-        <v>1.203235028977704</v>
+        <v>1.203235028977705</v>
       </c>
     </row>
     <row r="9">
@@ -3567,10 +3567,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01716248127608211</v>
+        <v>0.01716248127608208</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9212673145918673</v>
+        <v>0.9212673145918675</v>
       </c>
       <c r="D9" t="n">
         <v>1.063815374991317</v>
@@ -3582,7 +3582,7 @@
         <v>1.043793790260949</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5482024652082267</v>
+        <v>0.5482024652082261</v>
       </c>
       <c r="H9" t="n">
         <v>1.032232027756985</v>
@@ -3594,10 +3594,10 @@
         <v>0.6608554852011878</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7480811145937163</v>
+        <v>0.7480811145937166</v>
       </c>
       <c r="L9" t="n">
-        <v>1.1849642088035</v>
+        <v>1.184964208803501</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.903588045814503</v>
+        <v>2.903588045814501</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4084694818238297</v>
+        <v>0.4084694818238299</v>
       </c>
       <c r="D2" t="n">
-        <v>1.901183491548043</v>
+        <v>1.90118349154802</v>
       </c>
       <c r="E2" t="n">
-        <v>2.326309595408257</v>
+        <v>2.32630959540825</v>
       </c>
       <c r="F2" t="n">
-        <v>2.326309595408257</v>
+        <v>2.32630959540825</v>
       </c>
       <c r="G2" t="n">
-        <v>2.082457240133765</v>
+        <v>2.082457240133768</v>
       </c>
       <c r="H2" t="n">
-        <v>5.208858633866036</v>
+        <v>5.208858633866038</v>
       </c>
       <c r="I2" t="n">
-        <v>2.326309595408257</v>
+        <v>2.32630959540825</v>
       </c>
       <c r="J2" t="n">
-        <v>4.830025422458911</v>
+        <v>4.83002542245891</v>
       </c>
       <c r="K2" t="n">
-        <v>2.437459202341747</v>
+        <v>2.437459202341746</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3872807613629947</v>
+        <v>0.3872807613629927</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02260284929879119</v>
+        <v>0.02260284929879032</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02004352652127641</v>
+        <v>0.02004352652127637</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02260284929879119</v>
+        <v>0.02260284929879032</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0254939772520923</v>
+        <v>0.02549397725209235</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0254939772520923</v>
+        <v>0.02549397725209235</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02302361755584124</v>
+        <v>0.0230236175558412</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02260284929879119</v>
+        <v>0.02260284929879032</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02540509557464987</v>
+        <v>0.0254050955746499</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02260284929879119</v>
+        <v>0.02260284929879032</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02260284929879119</v>
+        <v>0.02260284929879032</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02260284929879119</v>
+        <v>0.02260284929879032</v>
       </c>
     </row>
     <row r="4">
@@ -3763,37 +3763,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.40195064882609</v>
+        <v>10.63706173772527</v>
       </c>
       <c r="C4" t="n">
         <v>10.63311733651147</v>
       </c>
       <c r="D4" t="n">
-        <v>10.6363228208333</v>
+        <v>10.63632282083305</v>
       </c>
       <c r="E4" t="n">
-        <v>6.56046659638114</v>
+        <v>6.560466596381143</v>
       </c>
       <c r="F4" t="n">
         <v>10.63972474771523</v>
       </c>
       <c r="G4" t="n">
-        <v>40.40237141708315</v>
+        <v>40.40237141708314</v>
       </c>
       <c r="H4" t="n">
-        <v>40.40751802543394</v>
+        <v>40.40751802543393</v>
       </c>
       <c r="I4" t="n">
-        <v>10.63986398400114</v>
+        <v>40.40475289510195</v>
       </c>
       <c r="J4" t="n">
-        <v>40.40494562313337</v>
+        <v>40.40494562313336</v>
       </c>
       <c r="K4" t="n">
         <v>10.63736301050355</v>
       </c>
       <c r="L4" t="n">
-        <v>10.63621422948432</v>
+        <v>10.63621422948431</v>
       </c>
     </row>
     <row r="5">
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03891972187444631</v>
+        <v>0.03891972187444628</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03885306023544275</v>
+        <v>0.0388530602354427</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03891931420915986</v>
+        <v>0.03891931420915939</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04171587181477547</v>
+        <v>0.04171587181477542</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04171587181477547</v>
+        <v>0.04171587181477542</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03934049013149629</v>
+        <v>0.03934049013149581</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03891972187444631</v>
+        <v>0.03891972187444628</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04172196815030499</v>
+        <v>0.04172196815030496</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03891972187444631</v>
+        <v>0.03891972187444628</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03891972187444631</v>
+        <v>0.03891972187444628</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03891972187444631</v>
+        <v>0.03891972187444628</v>
       </c>
     </row>
     <row r="6">
@@ -3843,34 +3843,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05265008667581816</v>
+        <v>0.05265008667581751</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0761714218205813</v>
+        <v>0.07617142182058111</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08113010532540757</v>
+        <v>0.08113010532540683</v>
       </c>
       <c r="E6" t="n">
         <v>0.07258905192205385</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05619666603736661</v>
+        <v>0.05619666603736666</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07665959472338475</v>
+        <v>0.07665959472338439</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07623882646647671</v>
+        <v>0.07623882646647655</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07904107274219349</v>
+        <v>0.07904107274219344</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07624346228576789</v>
+        <v>0.07624346228576744</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05221191372747525</v>
+        <v>0.05221191372747489</v>
       </c>
       <c r="L6" t="n">
         <v>0.1008792375954437</v>
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1085880407449897</v>
+        <v>0.1085880407449879</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1342583812848711</v>
+        <v>0.1342583812848698</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1343250488253652</v>
+        <v>0.1343250488253635</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1668272028688229</v>
+        <v>0.1668272028688207</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1371272520256732</v>
+        <v>0.1371272520256716</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1347458111809243</v>
+        <v>0.1347458111809229</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1343250429238742</v>
+        <v>0.1343250429238728</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1371272891997332</v>
+        <v>0.1371272891997321</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1343250429238742</v>
+        <v>0.1343250429238728</v>
       </c>
       <c r="K7" t="n">
-        <v>0.118807921576955</v>
+        <v>0.1194129252665656</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1343250429238742</v>
+        <v>0.1343250429238728</v>
       </c>
     </row>
     <row r="8">
@@ -3923,13 +3923,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03009455303866779</v>
+        <v>-0.03009455303866835</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9275379268549522</v>
+        <v>0.9275379268549532</v>
       </c>
       <c r="D8" t="n">
-        <v>1.065755854923228</v>
+        <v>1.06575585492323</v>
       </c>
       <c r="E8" t="n">
         <v>1.017908776610086</v>
@@ -3938,7 +3938,7 @@
         <v>1.017908776610086</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5250976296088524</v>
+        <v>0.5250976296088525</v>
       </c>
       <c r="H8" t="n">
         <v>1.003481752851723</v>
@@ -3947,13 +3947,13 @@
         <v>1.017908776610086</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5871306634276949</v>
+        <v>0.5871306634276962</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7147006373500365</v>
+        <v>0.7147006373500354</v>
       </c>
       <c r="L8" t="n">
-        <v>1.201517651756432</v>
+        <v>1.201517651756433</v>
       </c>
     </row>
     <row r="9">
@@ -3963,34 +3963,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007732092404525591</v>
+        <v>0.007732092404525104</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9181506980715421</v>
+        <v>0.9181506980715427</v>
       </c>
       <c r="D9" t="n">
-        <v>1.074251903882498</v>
+        <v>1.074251903882499</v>
       </c>
       <c r="E9" t="n">
-        <v>1.032478963231194</v>
+        <v>1.032478963231196</v>
       </c>
       <c r="F9" t="n">
-        <v>1.032478963231194</v>
+        <v>1.032478963231196</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5436703270668848</v>
+        <v>0.5436703270668851</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04898546452212</v>
+        <v>1.048985464522121</v>
       </c>
       <c r="I9" t="n">
-        <v>1.032478963231194</v>
+        <v>1.032478963231196</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6389694023106236</v>
+        <v>0.6389694023106245</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7357100914785091</v>
+        <v>0.7357100914785096</v>
       </c>
       <c r="L9" t="n">
         <v>1.187036240809044</v>
@@ -4079,37 +4079,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.346363529729435</v>
+        <v>1.346363529729434</v>
       </c>
       <c r="C2" t="n">
-        <v>0.185852552460774</v>
+        <v>0.1858525524607738</v>
       </c>
       <c r="D2" t="n">
-        <v>1.907896124115103</v>
+        <v>1.907896124115106</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8609165703685439</v>
+        <v>0.8609165703685415</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8609165703685439</v>
+        <v>0.8609165703685415</v>
       </c>
       <c r="G2" t="n">
         <v>1.344311576691635</v>
       </c>
       <c r="H2" t="n">
-        <v>6.768073975336802</v>
+        <v>6.768073975336796</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8609165703685439</v>
+        <v>0.8609165703685415</v>
       </c>
       <c r="J2" t="n">
-        <v>2.410709824575226</v>
+        <v>2.410709824575229</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9221026410195758</v>
+        <v>0.9221026410195751</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09165518102479191</v>
+        <v>0.09165518102479145</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01625240095023282</v>
+        <v>0.01625240095023286</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01409420903199884</v>
+        <v>0.01409420903199882</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01625240095023282</v>
+        <v>0.01625240095023286</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01833310666165952</v>
+        <v>0.01833310666165951</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01833310666165953</v>
+        <v>0.01833310666165951</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01664464177856848</v>
+        <v>0.01664464177856842</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01625240095023282</v>
+        <v>0.01625240095023286</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01887088041350181</v>
+        <v>0.01887088041350175</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01625240095023282</v>
+        <v>0.01625240095023286</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01625240095023282</v>
+        <v>0.01625240095023286</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01625240095023282</v>
+        <v>0.01625240095023286</v>
       </c>
     </row>
     <row r="4">
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.25595536183867</v>
+        <v>10.06619825122398</v>
       </c>
       <c r="C4" t="n">
         <v>10.06366660257708</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06741468470701</v>
+        <v>10.06741466619206</v>
       </c>
       <c r="E4" t="n">
-        <v>6.204071161583108</v>
+        <v>6.204071161583099</v>
       </c>
       <c r="F4" t="n">
         <v>10.06858293632509</v>
@@ -4180,10 +4180,10 @@
         <v>38.26463625788895</v>
       </c>
       <c r="I4" t="n">
-        <v>10.06881673068725</v>
+        <v>38.25857384130192</v>
       </c>
       <c r="J4" t="n">
-        <v>10.57780145636981</v>
+        <v>38.25889806978539</v>
       </c>
       <c r="K4" t="n">
         <v>10.06539271149165</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02800423446109363</v>
+        <v>0.02800423446109355</v>
       </c>
       <c r="C5" t="n">
         <v>0.02794776033556164</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02800395386373687</v>
+        <v>0.02800395386373685</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03058064580641448</v>
+        <v>0.03058064580641452</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03058064580641448</v>
+        <v>0.03058064580641452</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02839647528942909</v>
+        <v>0.02839647528942908</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02800423446109363</v>
+        <v>0.02800423446109355</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03062271392436242</v>
+        <v>0.03062271392436247</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02800423446109363</v>
+        <v>0.02800423446109355</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02800423446109363</v>
+        <v>0.02800423446109355</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02800423446109363</v>
+        <v>0.02800423446109355</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03866510511751963</v>
+        <v>0.03866510511751956</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05627640661567945</v>
+        <v>0.05627640661567937</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06004041127091853</v>
+        <v>0.06004041127091832</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0541132558337987</v>
+        <v>0.0541132558337986</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04181985277557752</v>
+        <v>0.04181985277557746</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05676156661387907</v>
+        <v>0.05676156661387892</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05636932578663537</v>
+        <v>0.0563693257866351</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05898780524881243</v>
+        <v>0.05898780524881234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05637280513635771</v>
+        <v>0.05637280513635754</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03833624013238662</v>
+        <v>0.03833624013238678</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07486286464286533</v>
+        <v>0.07486286464286532</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07035035118135384</v>
+        <v>0.07035035118135369</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08676245602292947</v>
+        <v>0.0867624560229293</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08681889185840888</v>
+        <v>0.08681889185840864</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1084416721572396</v>
+        <v>0.1084416721572395</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08943733458864166</v>
+        <v>0.08943733458864156</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08721117097679683</v>
+        <v>0.08721117097679679</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0868189301484614</v>
+        <v>0.08681893014846126</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08943740961173016</v>
+        <v>0.08943740961173012</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0868189301484614</v>
+        <v>0.08681893014846126</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06608205952188245</v>
+        <v>0.07727695471317418</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0868189301484614</v>
+        <v>0.08681893014846126</v>
       </c>
     </row>
     <row r="8">
@@ -4319,10 +4319,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.068177539190523e-05</v>
+        <v>7.068177539190944e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9266588446536178</v>
+        <v>0.9266588446536171</v>
       </c>
       <c r="D8" t="n">
         <v>1.054111737153135</v>
@@ -4334,22 +4334,22 @@
         <v>1.041135607516666</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5338960657418265</v>
+        <v>0.5338960657418261</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9549930739582042</v>
+        <v>0.9549930739582034</v>
       </c>
       <c r="I8" t="n">
         <v>1.041135607516666</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6310906603318259</v>
+        <v>0.6310906603318256</v>
       </c>
       <c r="K8" t="n">
-        <v>0.732727756269941</v>
+        <v>0.7327277562699422</v>
       </c>
       <c r="L8" t="n">
-        <v>1.204161003984843</v>
+        <v>1.204161003984842</v>
       </c>
     </row>
     <row r="9">
@@ -4362,31 +4362,31 @@
         <v>0.01831245886937309</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9145724532691994</v>
+        <v>0.9145724532691989</v>
       </c>
       <c r="D9" t="n">
-        <v>1.0643413067605</v>
+        <v>1.064341306760499</v>
       </c>
       <c r="E9" t="n">
-        <v>1.036666090129656</v>
+        <v>1.036666090129655</v>
       </c>
       <c r="F9" t="n">
-        <v>1.036666090129656</v>
+        <v>1.036666090129655</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5437824107084056</v>
+        <v>0.5437824107084048</v>
       </c>
       <c r="H9" t="n">
-        <v>1.024105093269192</v>
+        <v>1.024105093269191</v>
       </c>
       <c r="I9" t="n">
-        <v>1.036666090129656</v>
+        <v>1.036666090129655</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6533329580106747</v>
+        <v>0.6533329580106739</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7340548333805069</v>
+        <v>0.734054833380508</v>
       </c>
       <c r="L9" t="n">
         <v>1.18631896876919</v>
@@ -4475,37 +4475,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6258312111887094</v>
+        <v>0.6258312111887093</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08934728281835518</v>
+        <v>0.0893472828183547</v>
       </c>
       <c r="D2" t="n">
         <v>2.02152437665848</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2379512882338544</v>
+        <v>0.2379512882338541</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2379512882338544</v>
+        <v>0.2379512882338541</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9111029128113943</v>
+        <v>0.9111029128113961</v>
       </c>
       <c r="H2" t="n">
-        <v>5.14496736773534</v>
+        <v>5.144967367735346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2379512882338544</v>
+        <v>0.2379512882338541</v>
       </c>
       <c r="J2" t="n">
-        <v>1.330752135447427</v>
+        <v>1.330752135447428</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3214102268436433</v>
+        <v>0.3214102268436434</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05252789357939544</v>
+        <v>0.0525278935793954</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01221439674909702</v>
+        <v>0.01221439674909703</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01030537846684965</v>
+        <v>0.01030537846684926</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01221439674909702</v>
+        <v>0.01221439674909703</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01405528082489351</v>
+        <v>0.01405528082489355</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01405528082489349</v>
+        <v>0.01405528082489355</v>
       </c>
       <c r="G3" t="n">
         <v>0.01260191082459668</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01221439674909702</v>
+        <v>0.01221439674909703</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01480246003620342</v>
+        <v>0.01480246003620344</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01221439674909702</v>
+        <v>0.01221439674909703</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01221439674909702</v>
+        <v>0.01221439674909703</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01221439674909702</v>
+        <v>0.01221439674909703</v>
       </c>
     </row>
     <row r="4">
@@ -4555,31 +4555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.24695118691498</v>
+        <v>10.0598350329816</v>
       </c>
       <c r="C4" t="n">
-        <v>10.05810446054121</v>
+        <v>10.0581044605412</v>
       </c>
       <c r="D4" t="n">
         <v>10.06226369987075</v>
       </c>
       <c r="E4" t="n">
-        <v>6.197597853354349</v>
+        <v>6.19759785335435</v>
       </c>
       <c r="F4" t="n">
         <v>10.06218488854183</v>
       </c>
       <c r="G4" t="n">
-        <v>38.24733870099051</v>
+        <v>38.24733870099047</v>
       </c>
       <c r="H4" t="n">
-        <v>38.25584543195812</v>
+        <v>38.25584543195808</v>
       </c>
       <c r="I4" t="n">
-        <v>10.06242309626871</v>
+        <v>38.24953925020208</v>
       </c>
       <c r="J4" t="n">
-        <v>38.2498052941013</v>
+        <v>10.57114604361334</v>
       </c>
       <c r="K4" t="n">
         <v>10.05882312085034</v>
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0211949555621684</v>
+        <v>0.02119495556216839</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02115058194702761</v>
+        <v>0.02115058194702734</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02119474028107258</v>
+        <v>0.02119474028107255</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02372058752173419</v>
+        <v>0.02372058752173421</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02372058752173419</v>
+        <v>0.02372058752173421</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02158246963766804</v>
+        <v>0.02158246963766802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0211949555621684</v>
+        <v>0.02119495556216839</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02378301884927479</v>
+        <v>0.0237830188492748</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0211949555621684</v>
+        <v>0.02119495556216839</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0211949555621684</v>
+        <v>0.02119495556216839</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0211949555621684</v>
+        <v>0.02119495556216839</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02972826793381208</v>
+        <v>0.02972826793381212</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04337955503036475</v>
+        <v>0.04337955503036442</v>
       </c>
       <c r="D6" t="n">
         <v>0.04633236619459009</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0422568413999981</v>
+        <v>0.0422568413999982</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03271514746374004</v>
+        <v>0.03271514746374007</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04386822220789149</v>
+        <v>0.04386822220789152</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04348070813369639</v>
+        <v>0.04348070813369643</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04606877141949826</v>
+        <v>0.04606877141949827</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04348341085489443</v>
+        <v>0.04348341085489444</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02947280929887025</v>
+        <v>0.02947280929887027</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05784628185576877</v>
+        <v>0.05784628185576882</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05073142147480261</v>
+        <v>0.05073142147480258</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06248140727273736</v>
+        <v>0.06248140727273713</v>
       </c>
       <c r="D7" t="n">
         <v>0.06252574872874637</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07872417828798385</v>
+        <v>0.07872417828798382</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06511378217682212</v>
+        <v>0.06511378217682208</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0629132949633779</v>
+        <v>0.06291329496337779</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06252578088787818</v>
+        <v>0.06252578088787814</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0651138441749846</v>
+        <v>0.06511384417498457</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06252578088787818</v>
+        <v>0.06252578088787814</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05541481818711952</v>
+        <v>0.05541481818711948</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06252578088787818</v>
+        <v>0.06252578088787814</v>
       </c>
     </row>
     <row r="8">
@@ -4715,13 +4715,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01759237189909978</v>
+        <v>0.01759237189909972</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9249606572598373</v>
+        <v>0.9249606572598369</v>
       </c>
       <c r="D8" t="n">
-        <v>1.046047538484214</v>
+        <v>1.046047538484215</v>
       </c>
       <c r="E8" t="n">
         <v>1.054802856206777</v>
@@ -4733,16 +4733,16 @@
         <v>0.5419211879297843</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9846356636919389</v>
+        <v>0.98463566369194</v>
       </c>
       <c r="I8" t="n">
         <v>1.054802856206777</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6513777839982451</v>
+        <v>0.6513777839982461</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7495683907234059</v>
+        <v>0.7495683907234063</v>
       </c>
       <c r="L8" t="n">
         <v>1.202557810122987</v>
@@ -4755,34 +4755,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02575675300807707</v>
+        <v>0.02575675300807703</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9116079363732319</v>
+        <v>0.9116079363732325</v>
       </c>
       <c r="D9" t="n">
         <v>1.058033778695846</v>
       </c>
       <c r="E9" t="n">
-        <v>1.041465078435019</v>
+        <v>1.04146507843502</v>
       </c>
       <c r="F9" t="n">
-        <v>1.041465078435019</v>
+        <v>1.04146507843502</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5457881099931732</v>
+        <v>0.5457881099931733</v>
       </c>
       <c r="H9" t="n">
-        <v>1.033122785933237</v>
+        <v>1.033122785933239</v>
       </c>
       <c r="I9" t="n">
-        <v>1.041465078435019</v>
+        <v>1.04146507843502</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6588854230065728</v>
+        <v>0.6588854230065737</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7422394123362167</v>
+        <v>0.742239412336216</v>
       </c>
       <c r="L9" t="n">
         <v>1.184288755447979</v>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1242535799683273</v>
+        <v>0.1242535799683244</v>
       </c>
       <c r="C2" t="n">
-        <v>4.335246877166779</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9368530088032219</v>
+        <v>0.9368530088032229</v>
       </c>
       <c r="E2" t="n">
-        <v>4.335246877166779</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="F2" t="n">
-        <v>4.335246877166779</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="G2" t="n">
-        <v>2.390384601107909</v>
+        <v>2.39038460110791</v>
       </c>
       <c r="H2" t="n">
-        <v>1.599038994266159</v>
+        <v>1.599038994266163</v>
       </c>
       <c r="I2" t="n">
-        <v>4.335246877166779</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="J2" t="n">
-        <v>7.352009281699731</v>
+        <v>7.352009281699722</v>
       </c>
       <c r="K2" t="n">
-        <v>4.390613384984448</v>
+        <v>4.390613384984459</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2448958427016514</v>
+        <v>0.2448958427016453</v>
       </c>
     </row>
     <row r="3">
@@ -4911,37 +4911,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03286033572997872</v>
+        <v>0.03286033572997875</v>
       </c>
       <c r="C3" t="n">
         <v>0.03853912356884832</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03286033572997872</v>
+        <v>0.03286033572997875</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03891417067751819</v>
+        <v>0.03891417067751818</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03891417067751819</v>
+        <v>0.03891417067751818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0334831814295771</v>
+        <v>0.03348318142957708</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03286033572997872</v>
+        <v>0.03286033572997875</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03698975519013426</v>
+        <v>0.03698975519013432</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03286033572997872</v>
+        <v>0.03286033572997875</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03286033572997872</v>
+        <v>0.03286033572997875</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03286033572997872</v>
+        <v>0.03286033572997875</v>
       </c>
     </row>
     <row r="4">
@@ -4951,37 +4951,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.09062859625048</v>
+        <v>41.09062859625051</v>
       </c>
       <c r="C4" t="n">
         <v>10.83938926933231</v>
       </c>
       <c r="D4" t="n">
-        <v>10.82744286499731</v>
+        <v>10.8274428649973</v>
       </c>
       <c r="E4" t="n">
-        <v>6.692045131214749</v>
+        <v>6.692045131214753</v>
       </c>
       <c r="F4" t="n">
-        <v>10.83663604753642</v>
+        <v>10.83663604753641</v>
       </c>
       <c r="G4" t="n">
-        <v>10.83334553345539</v>
+        <v>41.09125144195009</v>
       </c>
       <c r="H4" t="n">
-        <v>10.83106889613637</v>
+        <v>41.09340021470117</v>
       </c>
       <c r="I4" t="n">
-        <v>41.09475801571063</v>
+        <v>41.09475801571062</v>
       </c>
       <c r="J4" t="n">
-        <v>41.09276858809032</v>
+        <v>41.09276858809034</v>
       </c>
       <c r="K4" t="n">
-        <v>10.83458287117104</v>
+        <v>10.83458287117105</v>
       </c>
       <c r="L4" t="n">
-        <v>10.83077494908722</v>
+        <v>10.83077494908724</v>
       </c>
     </row>
     <row r="5">
@@ -4991,37 +4991,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05149071663393525</v>
+        <v>0.05149071663393541</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05562013609409085</v>
+        <v>0.05562013609409087</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05148979519241331</v>
+        <v>0.05148979519241358</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05573271982539232</v>
+        <v>0.05573271982539228</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05573271982539232</v>
+        <v>0.05573271982539228</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05211356233353364</v>
+        <v>0.05211356233353367</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05149071663393525</v>
+        <v>0.05149071663393541</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05562013609409085</v>
+        <v>0.05562013609409087</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05149071663393525</v>
+        <v>0.05149071663393541</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05149071663393525</v>
+        <v>0.05149071663393541</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05149071663393525</v>
+        <v>0.05149071663393541</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06589377616446197</v>
+        <v>0.0658937761644619</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0956598758592697</v>
+        <v>0.0956598758592698</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09670911016675419</v>
+        <v>0.09670911016675443</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08866738043474914</v>
+        <v>0.08866738043474931</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07089994599368504</v>
+        <v>0.07089994599368514</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0920396000715621</v>
+        <v>0.09203960007156232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09141675437197964</v>
+        <v>0.09141675437198012</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09554617383211934</v>
+        <v>0.0955461738321194</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09142177032601927</v>
+        <v>0.09142177032601952</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06541967374432789</v>
+        <v>0.06541967374432818</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1180776392669883</v>
+        <v>0.1180776392669887</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1448418153880121</v>
+        <v>0.1448418153880123</v>
       </c>
       <c r="C7" t="n">
         <v>0.1819136488488363</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1777842634854173</v>
+        <v>0.1777842634854175</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2199285383526051</v>
+        <v>0.2199285383526052</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1819136579818527</v>
+        <v>0.1819136579818529</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1784070750882791</v>
+        <v>0.1784070750882793</v>
       </c>
       <c r="H7" t="n">
-        <v>0.177784229388681</v>
+        <v>0.1777842293886813</v>
       </c>
       <c r="I7" t="n">
         <v>0.1819136488488363</v>
       </c>
       <c r="J7" t="n">
-        <v>0.177784229388681</v>
+        <v>0.1777842293886813</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1586972796828052</v>
+        <v>0.1586972796828059</v>
       </c>
       <c r="L7" t="n">
-        <v>0.177784229388681</v>
+        <v>0.1777842293886813</v>
       </c>
     </row>
     <row r="8">
@@ -5111,13 +5111,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6258330838306558</v>
+        <v>0.6258330838306557</v>
       </c>
       <c r="C8" t="n">
         <v>1.004828651558832</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6070238678615872</v>
+        <v>0.6070238678615877</v>
       </c>
       <c r="E8" t="n">
         <v>1.004828651558832</v>
@@ -5126,7 +5126,7 @@
         <v>1.004828651558832</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5750517474769311</v>
+        <v>0.5750517474769324</v>
       </c>
       <c r="H8" t="n">
         <v>0.5959691628935057</v>
@@ -5135,13 +5135,13 @@
         <v>1.004828651558832</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4692080935396262</v>
+        <v>0.4692080935396272</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5272043066063179</v>
+        <v>0.5272043066063178</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6151088641376908</v>
+        <v>0.6235578974287787</v>
       </c>
     </row>
     <row r="9">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6173756973265635</v>
+        <v>0.6173756973265643</v>
       </c>
       <c r="C9" t="n">
         <v>1.049793323130445</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6097153784107751</v>
+        <v>0.6097153784107749</v>
       </c>
       <c r="E9" t="n">
         <v>1.049793323130445</v>
@@ -5166,22 +5166,22 @@
         <v>1.049793323130445</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5969303968912689</v>
+        <v>0.5969303968912687</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6052420827224904</v>
+        <v>0.60524208272249</v>
       </c>
       <c r="I9" t="n">
         <v>1.049793323130445</v>
       </c>
       <c r="J9" t="n">
-        <v>0.553643897886232</v>
+        <v>0.5536438978862335</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5772101531688019</v>
+        <v>0.5772101531688025</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6130175145416686</v>
+        <v>0.6164523036586739</v>
       </c>
     </row>
   </sheetData>
@@ -5267,13 +5267,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.221683868847721</v>
+        <v>0.2216838688477219</v>
       </c>
       <c r="C2" t="n">
         <v>2.991289698298492</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6912939597222619</v>
+        <v>0.6912939597222554</v>
       </c>
       <c r="E2" t="n">
         <v>2.991289698298492</v>
@@ -5291,13 +5291,13 @@
         <v>2.991289698298492</v>
       </c>
       <c r="J2" t="n">
-        <v>5.595391334199201</v>
+        <v>5.595391334199205</v>
       </c>
       <c r="K2" t="n">
         <v>2.323498709889595</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5112864492849</v>
+        <v>0.2691355411526296</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02608963641164969</v>
+        <v>0.02608963641165016</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03086377582055353</v>
+        <v>0.03086377582055356</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02608963641164969</v>
+        <v>0.02608963641165018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03117960046540177</v>
+        <v>0.03117960046540181</v>
       </c>
       <c r="F3" t="n">
         <v>0.03117960046540181</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02669227275840622</v>
+        <v>0.02669227275840654</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02608963641164969</v>
+        <v>0.02608963641165018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03008975063229359</v>
+        <v>0.03008975063229362</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02608963641164969</v>
+        <v>0.02608963641165018</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02608963641164969</v>
+        <v>0.02608963641165018</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02608963641164969</v>
+        <v>0.02608963641165018</v>
       </c>
     </row>
     <row r="4">
@@ -5347,31 +5347,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.0847379861777</v>
+        <v>38.27598029646879</v>
       </c>
       <c r="C4" t="n">
-        <v>10.09087565353529</v>
+        <v>10.09087565353528</v>
       </c>
       <c r="D4" t="n">
         <v>10.08151434332728</v>
       </c>
       <c r="E4" t="n">
-        <v>6.226633046312213</v>
+        <v>6.226633046312212</v>
       </c>
       <c r="F4" t="n">
         <v>10.08895683983584</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08534062252445</v>
+        <v>38.27658293281553</v>
       </c>
       <c r="H4" t="n">
-        <v>38.27851943556379</v>
+        <v>38.27851943556378</v>
       </c>
       <c r="I4" t="n">
-        <v>10.08873810039834</v>
+        <v>38.2799804106894</v>
       </c>
       <c r="J4" t="n">
-        <v>10.59713169718851</v>
+        <v>38.27794125299145</v>
       </c>
       <c r="K4" t="n">
         <v>10.08528050570703</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04013029783590134</v>
+        <v>0.04013029783590195</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0441304120565455</v>
+        <v>0.04413041205654551</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04012961342298813</v>
+        <v>0.04012961342298866</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04413962997381741</v>
+        <v>0.04413962997381745</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04413962997381741</v>
+        <v>0.04413962997381745</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04073293418265825</v>
+        <v>0.04073293418265841</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04013029783590134</v>
+        <v>0.04013029783590197</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0441304120565455</v>
+        <v>0.04413041205654551</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04013029783590134</v>
+        <v>0.04013029783590197</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04013029783590134</v>
+        <v>0.04013029783590197</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04013029783590134</v>
+        <v>0.04013029783590197</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05138307070739005</v>
+        <v>0.05138307070738975</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07489869032221901</v>
+        <v>0.07489869032258917</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07492910024976658</v>
+        <v>0.07492910024976648</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06956355650765265</v>
+        <v>0.06956355650765257</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05600727972928576</v>
+        <v>0.05600727972928578</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07148784189518219</v>
+        <v>0.07148784189518237</v>
       </c>
       <c r="H6" t="n">
         <v>0.0708852055484647</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07488531976906942</v>
+        <v>0.07488531976906938</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07088903824370366</v>
+        <v>0.07088903824370425</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05102080854314821</v>
+        <v>0.05102080854314872</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09125681610117359</v>
+        <v>0.09125681610117378</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1034727101087505</v>
+        <v>0.1034727101087507</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1303668325222639</v>
+        <v>0.1303668325222637</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1263667378905634</v>
+        <v>0.1263667378905635</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1567860513416714</v>
+        <v>0.1567860513416711</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1303668333928472</v>
+        <v>0.130366833392847</v>
       </c>
       <c r="G7" t="n">
         <v>0.1269693546483768</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1263667183016199</v>
+        <v>0.1263667183016202</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1303668325222639</v>
+        <v>0.1303668325222637</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1263667183016199</v>
+        <v>0.1263667183016202</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09753907034375538</v>
+        <v>0.0975390703437556</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1263667183016199</v>
+        <v>0.1263667183016202</v>
       </c>
     </row>
     <row r="8">
@@ -5507,13 +5507,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6173830557208817</v>
+        <v>0.6173830557208828</v>
       </c>
       <c r="C8" t="n">
         <v>1.024215407007019</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6054944507529552</v>
+        <v>0.6054944507529557</v>
       </c>
       <c r="E8" t="n">
         <v>1.024215407007019</v>
@@ -5522,22 +5522,22 @@
         <v>1.024215407007019</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5820132784661654</v>
+        <v>0.5820132784661662</v>
       </c>
       <c r="H8" t="n">
-        <v>0.595433285865994</v>
+        <v>0.595433285865996</v>
       </c>
       <c r="I8" t="n">
         <v>1.024215407007019</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4927020346510377</v>
+        <v>0.492702034651038</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5613482875303398</v>
+        <v>0.5613482875303408</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6120959821000446</v>
+        <v>0.616853236219208</v>
       </c>
     </row>
     <row r="9">
@@ -5547,37 +5547,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6106337838702194</v>
+        <v>0.6106337838702204</v>
       </c>
       <c r="C9" t="n">
-        <v>1.053731453017322</v>
+        <v>1.053731453017323</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6057920756933002</v>
+        <v>0.6057920756933013</v>
       </c>
       <c r="E9" t="n">
-        <v>1.053731453017322</v>
+        <v>1.053731453017323</v>
       </c>
       <c r="F9" t="n">
-        <v>1.053731453017322</v>
+        <v>1.053731453017323</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5964040738226124</v>
+        <v>0.5964040738226137</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6017187633833734</v>
+        <v>0.601718763383374</v>
       </c>
       <c r="I9" t="n">
-        <v>1.053731453017322</v>
+        <v>1.053731453017323</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5599014292167068</v>
+        <v>0.5599014292167077</v>
       </c>
       <c r="K9" t="n">
-        <v>0.587814401912519</v>
+        <v>0.5878144019125198</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6104220317965728</v>
+        <v>0.6104220317965737</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.317111718943366</v>
+        <v>0.3171117189433663</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9117973034433606</v>
+        <v>0.9117973034433594</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7488213551010463</v>
+        <v>0.7488213551010457</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9117973034433606</v>
+        <v>0.9117973034433594</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9117973034433606</v>
+        <v>0.9117973034433594</v>
       </c>
       <c r="G2" t="n">
-        <v>1.343400349221436</v>
+        <v>1.343400349221434</v>
       </c>
       <c r="H2" t="n">
-        <v>2.591070816450763</v>
+        <v>2.591070816450765</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9117973034433606</v>
+        <v>0.9117973034433594</v>
       </c>
       <c r="J2" t="n">
-        <v>4.217985729546888</v>
+        <v>4.217985729546887</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6920168409159783</v>
+        <v>0.692016840915975</v>
       </c>
       <c r="L2" t="n">
-        <v>0.413809938889704</v>
+        <v>0.4138099388897047</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01615964062339335</v>
+        <v>0.01615964062339327</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01826169611503714</v>
+        <v>0.01826169611503708</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01615964062339335</v>
+        <v>0.01615964062339327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01865117285275369</v>
+        <v>0.01865117285275366</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01865117285275369</v>
+        <v>0.01865117285275365</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01668985035719543</v>
+        <v>0.0166898503571954</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01615964062339335</v>
+        <v>0.01615964062339327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01969747053254723</v>
+        <v>0.01969747053254719</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01615964062339335</v>
+        <v>0.01615964062339327</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01615964062339335</v>
+        <v>0.01615964062339327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01615964062339335</v>
+        <v>0.01615964062339327</v>
       </c>
     </row>
     <row r="4">
@@ -5746,31 +5746,31 @@
         <v>10.06830202191764</v>
       </c>
       <c r="C4" t="n">
-        <v>10.07100668473108</v>
+        <v>10.07100668473107</v>
       </c>
       <c r="D4" t="n">
-        <v>38.2576457654198</v>
+        <v>38.25764576541981</v>
       </c>
       <c r="E4" t="n">
-        <v>6.20718636043578</v>
+        <v>6.207186360435776</v>
       </c>
       <c r="F4" t="n">
         <v>10.07170324611435</v>
       </c>
       <c r="G4" t="n">
-        <v>10.06883223165145</v>
+        <v>10.06883223165144</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26066696608908</v>
+        <v>38.26066696608909</v>
       </c>
       <c r="I4" t="n">
-        <v>38.26096936995719</v>
+        <v>38.2609693699572</v>
       </c>
       <c r="J4" t="n">
-        <v>38.25960918575014</v>
+        <v>10.58067450992286</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06738086603336</v>
+        <v>10.06738086603335</v>
       </c>
       <c r="L4" t="n">
         <v>10.06808566120696</v>
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02702321416605398</v>
+        <v>0.02702321416605397</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03056104407520796</v>
+        <v>0.03056104407520787</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0270229016300817</v>
+        <v>0.02702290163008165</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03032596274293059</v>
+        <v>0.03032596274293056</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03032596274293059</v>
+        <v>0.03032596274293056</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02755342389985615</v>
+        <v>0.0275534238998561</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02702321416605398</v>
+        <v>0.02702321416605396</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03056104407520796</v>
+        <v>0.03056104407520787</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02702321416605398</v>
+        <v>0.02702321416605396</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02702321416605398</v>
+        <v>0.02702321416605396</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02702321416605398</v>
+        <v>0.02702321416605396</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03703269125013758</v>
+        <v>0.0370326912501376</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05651517891264919</v>
+        <v>0.05651517891264907</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05655084793012309</v>
+        <v>0.05655084793012302</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05211745385491657</v>
+        <v>0.0521174538549165</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0409429082526934</v>
+        <v>0.04094290825269332</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05372892688390485</v>
+        <v>0.05372892688390478</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05319871715016609</v>
+        <v>0.053198717150166</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05673654705925667</v>
+        <v>0.05673654705925657</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05320189420886288</v>
+        <v>0.05320189420886283</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03673239902183048</v>
+        <v>0.03673239902183043</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07008548295723162</v>
+        <v>0.07008548295723145</v>
       </c>
     </row>
     <row r="7">
@@ -5866,34 +5866,34 @@
         <v>0.06991961044916863</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08958880281207873</v>
+        <v>0.08958880281207872</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08605097518856458</v>
+        <v>0.08605097518856464</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1082040120740146</v>
+        <v>0.1082040120740144</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08958876838348871</v>
+        <v>0.08958876838348864</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08658118263672687</v>
+        <v>0.08658118263672711</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08605097290292479</v>
+        <v>0.08605097290292485</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08958880281207873</v>
+        <v>0.08958880281207872</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08605097290292479</v>
+        <v>0.08605097290292485</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07670439910580186</v>
+        <v>0.07670439910580189</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08605097290292479</v>
+        <v>0.08605097290292485</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6074837246741284</v>
+        <v>0.6074837246741293</v>
       </c>
       <c r="C8" t="n">
-        <v>1.068214382093849</v>
+        <v>1.06821438209385</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5961029914309164</v>
+        <v>0.5961029914309175</v>
       </c>
       <c r="E8" t="n">
-        <v>1.068214382093849</v>
+        <v>1.06821438209385</v>
       </c>
       <c r="F8" t="n">
-        <v>1.068214382093849</v>
+        <v>1.06821438209385</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5817054701048057</v>
+        <v>0.5817054701048059</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5563025282299837</v>
+        <v>0.5563025282299847</v>
       </c>
       <c r="I8" t="n">
-        <v>1.068214382093849</v>
+        <v>1.06821438209385</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5176702293644794</v>
+        <v>0.5176702293644796</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5963336001799235</v>
+        <v>0.5963336001799249</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6067906971884398</v>
+        <v>0.6067906971884408</v>
       </c>
     </row>
     <row r="9">
@@ -5943,13 +5943,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6025183360010659</v>
+        <v>0.6025183360010667</v>
       </c>
       <c r="C9" t="n">
         <v>1.065327175243392</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5978835434000395</v>
+        <v>0.5978835434000408</v>
       </c>
       <c r="E9" t="n">
         <v>1.065327175243392</v>
@@ -5958,22 +5958,22 @@
         <v>1.065327175243392</v>
       </c>
       <c r="G9" t="n">
-        <v>0.591983454202012</v>
+        <v>0.5919834542020127</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5817274268844368</v>
+        <v>0.5817274268844375</v>
       </c>
       <c r="I9" t="n">
         <v>1.065327175243392</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5659750944515861</v>
+        <v>0.5659750944515871</v>
       </c>
       <c r="K9" t="n">
-        <v>0.597977961228716</v>
+        <v>0.597977961228717</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6022424668612827</v>
+        <v>0.6022424668612832</v>
       </c>
     </row>
   </sheetData>
@@ -6059,37 +6059,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1673303144462298</v>
+        <v>0.167330314446228</v>
       </c>
       <c r="C2" t="n">
-        <v>4.612570278743786</v>
+        <v>4.612570278743782</v>
       </c>
       <c r="D2" t="n">
-        <v>2.472370714428741</v>
+        <v>2.472370714428738</v>
       </c>
       <c r="E2" t="n">
-        <v>4.612570278743786</v>
+        <v>4.612570278743782</v>
       </c>
       <c r="F2" t="n">
-        <v>4.612570278743786</v>
+        <v>4.612570278743782</v>
       </c>
       <c r="G2" t="n">
-        <v>3.738352655538466</v>
+        <v>3.738352655538463</v>
       </c>
       <c r="H2" t="n">
-        <v>5.72758689474396</v>
+        <v>5.727586894743957</v>
       </c>
       <c r="I2" t="n">
-        <v>4.612570278743786</v>
+        <v>4.612570278743782</v>
       </c>
       <c r="J2" t="n">
-        <v>10.64136125462162</v>
+        <v>10.64136125462161</v>
       </c>
       <c r="K2" t="n">
-        <v>4.945577949074085</v>
+        <v>4.94557794907408</v>
       </c>
       <c r="L2" t="n">
-        <v>0.5360129320832541</v>
+        <v>4.565046466293285</v>
       </c>
     </row>
     <row r="3">
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03612569439359904</v>
+        <v>0.03612569439359836</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04006045030050727</v>
+        <v>0.04006045030050724</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03612569439359904</v>
+        <v>0.03612569439359836</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04055440348226373</v>
+        <v>0.04055440348226372</v>
       </c>
       <c r="F3" t="n">
         <v>0.04055440348226373</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03670319102191373</v>
+        <v>0.03670319102191342</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03612569439359904</v>
+        <v>0.03612569439359836</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03996651574010619</v>
+        <v>0.03996651574010617</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03612569439359904</v>
+        <v>0.03612569439359836</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03612569439359904</v>
+        <v>0.03612569439359836</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03612569439359904</v>
+        <v>0.03612569439359836</v>
       </c>
     </row>
     <row r="4">
@@ -6139,37 +6139,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.84081660748374</v>
+        <v>10.84081660748373</v>
       </c>
       <c r="C4" t="n">
         <v>10.84510083064795</v>
       </c>
       <c r="D4" t="n">
-        <v>10.83676280538215</v>
+        <v>41.10634276588195</v>
       </c>
       <c r="E4" t="n">
-        <v>6.697540763555266</v>
+        <v>6.697540763555265</v>
       </c>
       <c r="F4" t="n">
         <v>10.84406780108459</v>
       </c>
       <c r="G4" t="n">
-        <v>41.10627800595249</v>
+        <v>10.84139410411205</v>
       </c>
       <c r="H4" t="n">
-        <v>41.1099998519614</v>
+        <v>41.10999985196143</v>
       </c>
       <c r="I4" t="n">
-        <v>41.10954133067076</v>
+        <v>10.84465742883025</v>
       </c>
       <c r="J4" t="n">
-        <v>41.10863975724842</v>
+        <v>41.10863975724838</v>
       </c>
       <c r="K4" t="n">
         <v>10.8420857943722</v>
       </c>
       <c r="L4" t="n">
-        <v>10.83983775976721</v>
+        <v>10.83983775976722</v>
       </c>
     </row>
     <row r="5">
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0601361099754949</v>
+        <v>0.06013610997549471</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06397693132200244</v>
+        <v>0.06397693132200249</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06013529852476644</v>
+        <v>0.06013529852476632</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06391575842889133</v>
+        <v>0.06391575842889129</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06391575842889133</v>
+        <v>0.06391575842889129</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06071360660381001</v>
+        <v>0.06071360660380953</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0601361099754949</v>
+        <v>0.06013610997549471</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06397693132200244</v>
+        <v>0.06397693132200249</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0601361099754949</v>
+        <v>0.06013610997549471</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0601361099754949</v>
+        <v>0.06013610997549471</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0601361099754949</v>
+        <v>0.06013610997549471</v>
       </c>
     </row>
     <row r="6">
@@ -6219,37 +6219,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07960499462486446</v>
+        <v>0.07960499462486414</v>
       </c>
       <c r="C6" t="n">
-        <v>0.116531609275823</v>
+        <v>0.1165316092753366</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1196130775010634</v>
+        <v>0.119613077501063</v>
       </c>
       <c r="E6" t="n">
         <v>0.1074743246033717</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0844601968366582</v>
+        <v>0.08446019683665827</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1133194167613683</v>
+        <v>0.1133194167613682</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1127419201330867</v>
+        <v>0.1127419201330862</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1165827414795609</v>
+        <v>0.1165827414795611</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1127484324479002</v>
+        <v>0.1127484324478998</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07898945922438828</v>
+        <v>0.07898945922438794</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1473562096535373</v>
+        <v>0.1473562096535372</v>
       </c>
     </row>
     <row r="7">
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1861618332455532</v>
+        <v>0.1861618332455527</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2338944341230433</v>
+        <v>0.2338944341230432</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2300536326261681</v>
+        <v>0.2300536326261678</v>
       </c>
       <c r="E7" t="n">
         <v>0.2845445693529115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2338943816138553</v>
+        <v>0.233894381613855</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2306311094048507</v>
+        <v>0.2306311094048504</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2300536127765358</v>
+        <v>0.2300536127765355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2338944341230433</v>
+        <v>0.2338944341230432</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2300536127765358</v>
+        <v>0.2300536127765355</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1747860225474932</v>
+        <v>0.204622551688645</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2300536127765358</v>
+        <v>0.2300536127765355</v>
       </c>
     </row>
     <row r="8">
@@ -6299,37 +6299,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6315226092764857</v>
+        <v>0.6315226092764856</v>
       </c>
       <c r="C8" t="n">
-        <v>1.002031322262651</v>
+        <v>1.002031322262652</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5721642971736479</v>
+        <v>0.5721642971736478</v>
       </c>
       <c r="E8" t="n">
-        <v>1.002031322262651</v>
+        <v>1.002031322262652</v>
       </c>
       <c r="F8" t="n">
-        <v>1.002031322262651</v>
+        <v>1.002031322262652</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5455257820898121</v>
+        <v>0.5455257820898115</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5048063335201154</v>
+        <v>0.5048063335201151</v>
       </c>
       <c r="I8" t="n">
-        <v>1.002031322262651</v>
+        <v>1.002031322262652</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4044316249367655</v>
+        <v>0.4044316249367654</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5129209872291065</v>
+        <v>0.5129209872291063</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5417937563053155</v>
+        <v>0.6241119428034476</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6235231770419754</v>
+        <v>0.6235231770419748</v>
       </c>
       <c r="C9" t="n">
-        <v>1.051225653374081</v>
+        <v>1.051225653374082</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5993485686712002</v>
+        <v>0.5993485686712005</v>
       </c>
       <c r="E9" t="n">
-        <v>1.051225653374081</v>
+        <v>1.051225653374082</v>
       </c>
       <c r="F9" t="n">
-        <v>1.051225653374081</v>
+        <v>1.051225653374082</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5886160168632996</v>
+        <v>0.5886160168632991</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5720332161151573</v>
+        <v>0.5720332161151566</v>
       </c>
       <c r="I9" t="n">
-        <v>1.051225653374081</v>
+        <v>1.051225653374082</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5311182520918577</v>
+        <v>0.5311182520918576</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5752239241152645</v>
+        <v>0.5752239241152639</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6205126351885433</v>
+        <v>0.5870474319302548</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.100836308583414</v>
+        <v>0.1008363085834129</v>
       </c>
       <c r="C2" t="n">
-        <v>2.88962086504384</v>
+        <v>2.889620865043844</v>
       </c>
       <c r="D2" t="n">
-        <v>2.192089015196643</v>
+        <v>2.192089015196613</v>
       </c>
       <c r="E2" t="n">
-        <v>2.88962086504384</v>
+        <v>2.889620865043844</v>
       </c>
       <c r="F2" t="n">
-        <v>2.88962086504384</v>
+        <v>2.889620865043844</v>
       </c>
       <c r="G2" t="n">
         <v>2.660143901551328</v>
       </c>
       <c r="H2" t="n">
-        <v>4.155441310643006</v>
+        <v>4.15544131064299</v>
       </c>
       <c r="I2" t="n">
-        <v>2.88962086504384</v>
+        <v>2.889620865043844</v>
       </c>
       <c r="J2" t="n">
-        <v>5.75376959433751</v>
+        <v>5.753769594337482</v>
       </c>
       <c r="K2" t="n">
-        <v>1.620966911867662</v>
+        <v>1.620966911867651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2141997802229291</v>
+        <v>0.2141997802228859</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02735388854811923</v>
+        <v>0.02735388854811438</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03059733022293482</v>
+        <v>0.03059733022293521</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02735388854811923</v>
+        <v>0.02735388854811438</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03098294264182385</v>
+        <v>0.03098294264181662</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03098294264182627</v>
+        <v>0.03098294264181664</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02790833223798183</v>
+        <v>0.02790833223798551</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02735388854811923</v>
+        <v>0.02735388854811438</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03104665468024433</v>
+        <v>0.03104665468023643</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02735388854811923</v>
+        <v>0.02735388854811438</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02735388854811923</v>
+        <v>0.02735388854811438</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02735388854811923</v>
+        <v>0.02735388854811438</v>
       </c>
     </row>
     <row r="4">
@@ -6535,37 +6535,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.0870952591127</v>
+        <v>38.28453688228209</v>
       </c>
       <c r="C4" t="n">
         <v>10.09150861610127</v>
       </c>
       <c r="D4" t="n">
-        <v>10.08652851764002</v>
+        <v>10.08652864290189</v>
       </c>
       <c r="E4" t="n">
         <v>6.227284726362002</v>
       </c>
       <c r="F4" t="n">
-        <v>10.09113480527775</v>
+        <v>10.09113480527776</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08764970280256</v>
+        <v>10.08764970280258</v>
       </c>
       <c r="H4" t="n">
-        <v>38.2883059500852</v>
+        <v>10.08788799125727</v>
       </c>
       <c r="I4" t="n">
-        <v>10.09078802524483</v>
+        <v>10.09078802524482</v>
       </c>
       <c r="J4" t="n">
-        <v>10.60017005520719</v>
+        <v>38.28735389187705</v>
       </c>
       <c r="K4" t="n">
-        <v>10.08501633475017</v>
+        <v>10.08501633475016</v>
       </c>
       <c r="L4" t="n">
-        <v>10.08781837329542</v>
+        <v>10.0878183732954</v>
       </c>
     </row>
     <row r="5">
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04519315924770943</v>
+        <v>0.0451931592476595</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04888592537973796</v>
+        <v>0.04888592537978157</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0451925427891864</v>
+        <v>0.04519254278917334</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04878038044695245</v>
+        <v>0.04878038044696701</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04878038044695245</v>
+        <v>0.04878038044696701</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04574760293752889</v>
+        <v>0.045747602937531</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04519315924770943</v>
+        <v>0.0451931592476595</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04888592537973796</v>
+        <v>0.04888592537978157</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04519315924770943</v>
+        <v>0.0451931592476595</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04519315924770943</v>
+        <v>0.0451931592476595</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04519315924770943</v>
+        <v>0.0451931592476595</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0599606107052816</v>
+        <v>0.05996061070522555</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08833753173530735</v>
+        <v>0.08833753173530166</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08987842134196207</v>
+        <v>0.08987842134196662</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08157064773850077</v>
+        <v>0.08157064773848602</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06437625696178638</v>
+        <v>0.06437625696177653</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08529465369507876</v>
+        <v>0.08529465369508143</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08474021000522043</v>
+        <v>0.08474021000521853</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08843297613730795</v>
+        <v>0.0884329761373321</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08474507987780608</v>
+        <v>0.08474507987780147</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0595003169288158</v>
+        <v>0.05950031692878358</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1106245734839675</v>
+        <v>0.1106245734839152</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1290702688513676</v>
+        <v>0.1290702688513797</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1626610622226237</v>
+        <v>0.1626610622226391</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1589683044024929</v>
+        <v>0.1589683044025288</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1971626963274145</v>
+        <v>0.1971626963273869</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1626610119006228</v>
+        <v>0.1626610119006172</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1595227397803855</v>
+        <v>0.1595227397803882</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1589682960905466</v>
+        <v>0.1589682960905166</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1626610622226237</v>
+        <v>0.1626610622226391</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1589682960905466</v>
+        <v>0.1589682960905166</v>
       </c>
       <c r="K7" t="n">
-        <v>0.140942447602232</v>
+        <v>0.1409424476022423</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1589682960905466</v>
+        <v>0.1589682960905166</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6232372536661261</v>
+        <v>0.6232372536661319</v>
       </c>
       <c r="C8" t="n">
-        <v>1.026963275304121</v>
+        <v>1.02696327530413</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5634707596631298</v>
+        <v>0.5634707596631188</v>
       </c>
       <c r="E8" t="n">
-        <v>1.026963275304121</v>
+        <v>1.02696327530413</v>
       </c>
       <c r="F8" t="n">
-        <v>1.026963275304121</v>
+        <v>1.02696327530413</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5549104509018224</v>
+        <v>0.5549104509018186</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5162257176357807</v>
+        <v>0.5162257176357685</v>
       </c>
       <c r="I8" t="n">
-        <v>1.026963275304121</v>
+        <v>1.02696327530413</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4825721140537808</v>
+        <v>0.4825721140537807</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5821913855986768</v>
+        <v>0.5821913855986642</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5229848217361489</v>
+        <v>0.5229848217361492</v>
       </c>
     </row>
     <row r="9">
@@ -6735,37 +6735,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6146311803270048</v>
+        <v>0.6146311803270038</v>
       </c>
       <c r="C9" t="n">
-        <v>1.05563138515108</v>
+        <v>1.055631385151081</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5902903004469291</v>
+        <v>0.5902903004469384</v>
       </c>
       <c r="E9" t="n">
-        <v>1.05563138515108</v>
+        <v>1.055631385151081</v>
       </c>
       <c r="F9" t="n">
-        <v>1.05563138515108</v>
+        <v>1.055631385151081</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5868484835990511</v>
+        <v>0.5868484835990451</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5711473512587532</v>
+        <v>0.5711473512587388</v>
       </c>
       <c r="I9" t="n">
-        <v>1.05563138515108</v>
+        <v>1.055631385151081</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5573935119358817</v>
+        <v>0.5573935119358779</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5979157251623018</v>
+        <v>0.5979157251622972</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6136341577634489</v>
+        <v>0.5738762940192774</v>
       </c>
     </row>
   </sheetData>
@@ -6851,37 +6851,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09437802176290294</v>
+        <v>0.09437802176290264</v>
       </c>
       <c r="C2" t="n">
-        <v>1.465335809898433</v>
+        <v>1.465335809898434</v>
       </c>
       <c r="D2" t="n">
         <v>1.104720419027534</v>
       </c>
       <c r="E2" t="n">
-        <v>1.465335809898433</v>
+        <v>1.465335809898434</v>
       </c>
       <c r="F2" t="n">
-        <v>1.465335809898433</v>
+        <v>1.465335809898434</v>
       </c>
       <c r="G2" t="n">
-        <v>1.708064654915962</v>
+        <v>1.708064654915967</v>
       </c>
       <c r="H2" t="n">
-        <v>3.950566189615341</v>
+        <v>3.950566189615344</v>
       </c>
       <c r="I2" t="n">
-        <v>1.465335809898433</v>
+        <v>1.465335809898434</v>
       </c>
       <c r="J2" t="n">
-        <v>2.10177706423977</v>
+        <v>2.101777064239767</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3970182440324512</v>
+        <v>0.3970182440324518</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4208478776188957</v>
+        <v>3.595600971792674</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01874666526735148</v>
+        <v>0.01874666526735133</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02133695193560995</v>
+        <v>0.02133695193560996</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01874666526735148</v>
+        <v>0.01874666526735133</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02167952470390076</v>
+        <v>0.02167952470390081</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02167952470390076</v>
+        <v>0.02167952470390079</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01928213136544804</v>
+        <v>0.01928213136544816</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01874666526735148</v>
+        <v>0.01874666526735133</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02231746843470425</v>
+        <v>0.0223174684347043</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01874666526735148</v>
+        <v>0.01874666526735133</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01874666526735148</v>
+        <v>0.01874666526735133</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01874666526735148</v>
+        <v>0.01874666526735133</v>
       </c>
     </row>
     <row r="4">
@@ -6937,31 +6937,31 @@
         <v>10.07450354766287</v>
       </c>
       <c r="D4" t="n">
-        <v>38.26391866009033</v>
+        <v>10.0703265506182</v>
       </c>
       <c r="E4" t="n">
-        <v>6.21076248624923</v>
+        <v>6.210762486249222</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07483750082017</v>
+        <v>10.07483750082018</v>
       </c>
       <c r="G4" t="n">
-        <v>10.07141469842892</v>
+        <v>38.26400109291245</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26689664679213</v>
+        <v>38.26689664679211</v>
       </c>
       <c r="I4" t="n">
-        <v>10.07445003549817</v>
+        <v>10.07445003549818</v>
       </c>
       <c r="J4" t="n">
-        <v>10.5829143251545</v>
+        <v>38.26587915918515</v>
       </c>
       <c r="K4" t="n">
         <v>10.06877900585781</v>
       </c>
       <c r="L4" t="n">
-        <v>10.07195720452279</v>
+        <v>10.07195720452278</v>
       </c>
     </row>
     <row r="5">
@@ -6971,37 +6971,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03126171517345974</v>
+        <v>0.0312617151734602</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03483251834081298</v>
+        <v>0.03483251834081307</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03126129164733359</v>
+        <v>0.03126129164733375</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03467664852969036</v>
+        <v>0.03467664852969043</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03467664852969036</v>
+        <v>0.03467664852969043</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03179718127155728</v>
+        <v>0.0317971812715571</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03126171517345974</v>
+        <v>0.0312617151734602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03483251834081298</v>
+        <v>0.03483251834081307</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03126171517345974</v>
+        <v>0.0312617151734602</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03126171517345974</v>
+        <v>0.0312617151734602</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03126171517345974</v>
+        <v>0.0312617151734602</v>
       </c>
     </row>
     <row r="6">
@@ -7011,34 +7011,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04205500981425526</v>
+        <v>0.04205500981425515</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06325678226332447</v>
+        <v>0.06325678226351625</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06351715092083622</v>
+        <v>0.06351715092083621</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05841059585061312</v>
+        <v>0.05841059585061319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04609655800089763</v>
+        <v>0.04609655800089767</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06036661813085878</v>
+        <v>0.06036661813085867</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05983115203277001</v>
+        <v>0.05983115203277021</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0634019552001145</v>
+        <v>0.06340195520011464</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05983464553134377</v>
+        <v>0.05983464553134335</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04172480884813558</v>
+        <v>0.0417248088481354</v>
       </c>
       <c r="L6" t="n">
         <v>0.07839981897595556</v>
@@ -7051,34 +7051,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08284248633156449</v>
+        <v>0.08284248633156456</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1054304146745593</v>
+        <v>0.1054304146745595</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1018595991621079</v>
+        <v>0.1018595991621081</v>
       </c>
       <c r="E7" t="n">
         <v>0.127375694171753</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1054303598204741</v>
+        <v>0.1054303598204743</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1023950776053032</v>
+        <v>0.1023950776053034</v>
       </c>
       <c r="H7" t="n">
         <v>0.1018596115072065</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1054304146745593</v>
+        <v>0.1054304146745595</v>
       </c>
       <c r="J7" t="n">
         <v>0.1018596115072065</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09084100930212725</v>
+        <v>0.09039397119294573</v>
       </c>
       <c r="L7" t="n">
         <v>0.1018596115072065</v>
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6142741618688423</v>
+        <v>0.6142741618688412</v>
       </c>
       <c r="C8" t="n">
         <v>1.05573911630181</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5870290749113354</v>
+        <v>0.5870290749113347</v>
       </c>
       <c r="E8" t="n">
         <v>1.05573911630181</v>
@@ -7106,22 +7106,22 @@
         <v>1.05573911630181</v>
       </c>
       <c r="G8" t="n">
-        <v>0.57253019019554</v>
+        <v>0.5725301901955395</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5222781257722852</v>
+        <v>0.5222781257722848</v>
       </c>
       <c r="I8" t="n">
         <v>1.05573911630181</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5654421092827862</v>
+        <v>0.5654421092827859</v>
       </c>
       <c r="K8" t="n">
-        <v>0.605870051292602</v>
+        <v>0.6058700512926019</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6068063756606311</v>
+        <v>0.6068063756606309</v>
       </c>
     </row>
     <row r="9">
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6058183994809059</v>
+        <v>0.6058183994809051</v>
       </c>
       <c r="C9" t="n">
         <v>1.061177261831145</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5947224212211191</v>
+        <v>0.594722421221118</v>
       </c>
       <c r="E9" t="n">
         <v>1.061177261831145</v>
@@ -7146,10 +7146,10 @@
         <v>1.061177261831145</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5888013377896183</v>
+        <v>0.5888013377896174</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5684363851075578</v>
+        <v>0.5684363851075577</v>
       </c>
       <c r="I9" t="n">
         <v>1.061177261831145</v>
@@ -7158,10 +7158,10 @@
         <v>0.5859487578168101</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6023960020531591</v>
+        <v>0.6023960020531581</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6027837846588223</v>
+        <v>0.5745629246972244</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.139695901784434</v>
+        <v>0.1396959017844443</v>
       </c>
       <c r="C2" t="n">
-        <v>4.43865663223263</v>
+        <v>4.438656632232634</v>
       </c>
       <c r="D2" t="n">
-        <v>1.086474333092758</v>
+        <v>1.086474333092605</v>
       </c>
       <c r="E2" t="n">
-        <v>4.43865663223263</v>
+        <v>4.438656632232634</v>
       </c>
       <c r="F2" t="n">
-        <v>4.43865663223263</v>
+        <v>4.438656632232634</v>
       </c>
       <c r="G2" t="n">
-        <v>2.641256196054723</v>
+        <v>2.641256196054666</v>
       </c>
       <c r="H2" t="n">
-        <v>2.004847323075104</v>
+        <v>2.004847323074885</v>
       </c>
       <c r="I2" t="n">
-        <v>4.43865663223263</v>
+        <v>4.438656632232634</v>
       </c>
       <c r="J2" t="n">
-        <v>9.685434219495281</v>
+        <v>9.685434219495336</v>
       </c>
       <c r="K2" t="n">
-        <v>4.693591645060528</v>
+        <v>4.693591645060521</v>
       </c>
       <c r="L2" t="n">
-        <v>1.103213777181752</v>
+        <v>1.103213777181782</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03357123929464854</v>
+        <v>0.03357123929464209</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03888042604873899</v>
+        <v>0.03888042604873193</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03357123929464854</v>
+        <v>0.03357123929464209</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03928307800019413</v>
+        <v>0.03928307800019318</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03928307800019413</v>
+        <v>0.03928307800018947</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03418745167000239</v>
+        <v>0.03418745167000167</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03357123929464854</v>
+        <v>0.03357123929464209</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03765875339046318</v>
+        <v>0.03765875339046065</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03357123929464854</v>
+        <v>0.03357123929464209</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03357123929464854</v>
+        <v>0.03357123929464209</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03357123929464854</v>
+        <v>0.03357123929464209</v>
       </c>
     </row>
     <row r="4">
@@ -7330,31 +7330,31 @@
         <v>10.83540618926669</v>
       </c>
       <c r="C4" t="n">
-        <v>10.84157608654279</v>
+        <v>10.84157608654277</v>
       </c>
       <c r="D4" t="n">
-        <v>10.82986011102101</v>
+        <v>10.829860111021</v>
       </c>
       <c r="E4" t="n">
-        <v>6.69410613089802</v>
+        <v>6.694106130898023</v>
       </c>
       <c r="F4" t="n">
-        <v>10.83912875681331</v>
+        <v>10.83912875681332</v>
       </c>
       <c r="G4" t="n">
         <v>41.09458193595858</v>
       </c>
       <c r="H4" t="n">
-        <v>41.09681674968915</v>
+        <v>41.09681674968916</v>
       </c>
       <c r="I4" t="n">
-        <v>10.83949370336252</v>
+        <v>41.09805323767891</v>
       </c>
       <c r="J4" t="n">
-        <v>41.09619567379495</v>
+        <v>41.09619567379492</v>
       </c>
       <c r="K4" t="n">
-        <v>10.83748627470404</v>
+        <v>10.83748627470402</v>
       </c>
       <c r="L4" t="n">
         <v>10.83343414618965</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0531868402401235</v>
+        <v>0.05318684024011153</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05727435433593815</v>
+        <v>0.05727435433596374</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0531859550816292</v>
+        <v>0.0531859550816505</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05733250992630695</v>
+        <v>0.05733250992629255</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05733250992630695</v>
+        <v>0.05733250992629255</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05380305261547736</v>
+        <v>0.05380305261547584</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0531868402401235</v>
+        <v>0.05318684024011153</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05727435433593815</v>
+        <v>0.05727435433596374</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0531868402401235</v>
+        <v>0.05318684024011153</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0531868402401235</v>
+        <v>0.05318684024011153</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0531868402401235</v>
+        <v>0.05318684024011153</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06867351395822721</v>
+        <v>0.06867351395825964</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09982612259202629</v>
+        <v>0.09982612259257426</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1012760096817593</v>
+        <v>0.1012760096817585</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09243431667111102</v>
+        <v>0.09243431667108405</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07365220866070957</v>
+        <v>0.07365220866070489</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0962929315493538</v>
+        <v>0.09629293154933198</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09567671917400491</v>
+        <v>0.09567671917403017</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09976423326981457</v>
+        <v>0.09976423326979429</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09568202603572291</v>
+        <v>0.09568202603567458</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06817191556139257</v>
+        <v>0.06817191556137535</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1238838249543681</v>
+        <v>0.1238838249543946</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1537782036437965</v>
+        <v>0.1537782036437425</v>
       </c>
       <c r="C7" t="n">
-        <v>0.193155056144804</v>
+        <v>0.1931550561448176</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1890675787530691</v>
+        <v>0.1890675787530548</v>
       </c>
       <c r="E7" t="n">
-        <v>0.233878241170129</v>
+        <v>0.2338782411701066</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1931550590094902</v>
+        <v>0.1931550590095068</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1896837544243431</v>
+        <v>0.1896837544243295</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1890675420489892</v>
+        <v>0.1890675420489916</v>
       </c>
       <c r="I7" t="n">
-        <v>0.193155056144804</v>
+        <v>0.1931550561448176</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1890675420489892</v>
+        <v>0.1890675420489916</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1677912236158527</v>
+        <v>0.1686207762226849</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1890675420489892</v>
+        <v>0.1890675420489916</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6274403553950173</v>
+        <v>0.6274403553950191</v>
       </c>
       <c r="C8" t="n">
-        <v>1.003461489958252</v>
+        <v>1.00346148995825</v>
       </c>
       <c r="D8" t="n">
-        <v>0.604453395326725</v>
+        <v>0.604453395326735</v>
       </c>
       <c r="E8" t="n">
-        <v>1.003461489958252</v>
+        <v>1.00346148995825</v>
       </c>
       <c r="F8" t="n">
-        <v>1.003461489958252</v>
+        <v>1.00346148995825</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5694720214692918</v>
+        <v>0.5694720214692891</v>
       </c>
       <c r="H8" t="n">
-        <v>0.586137845954121</v>
+        <v>0.5861378459541245</v>
       </c>
       <c r="I8" t="n">
-        <v>1.003461489958252</v>
+        <v>1.00346148995825</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4204901962895872</v>
+        <v>0.4204901962895892</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5192158799061575</v>
+        <v>0.5192158799061568</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6218749908292985</v>
+        <v>0.6088287918999442</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6191597055665288</v>
+        <v>0.6191597055665224</v>
       </c>
       <c r="C9" t="n">
-        <v>1.050174396659429</v>
+        <v>1.050174396659428</v>
       </c>
       <c r="D9" t="n">
-        <v>0.609797937873014</v>
+        <v>0.6097979378730145</v>
       </c>
       <c r="E9" t="n">
-        <v>1.050174396659429</v>
+        <v>1.050174396659428</v>
       </c>
       <c r="F9" t="n">
-        <v>1.050174396659429</v>
+        <v>1.050174396659428</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5957686828488024</v>
+        <v>0.5957686828488001</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6023781911595854</v>
+        <v>0.6023781911595852</v>
       </c>
       <c r="I9" t="n">
-        <v>1.050174396659429</v>
+        <v>1.050174396659428</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5349501145829261</v>
+        <v>0.5349501145829257</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5750864200843097</v>
+        <v>0.5750864200843063</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6168989517891268</v>
+        <v>0.6115952888502358</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07778142155586673</v>
+        <v>0.07778142155586688</v>
       </c>
       <c r="C2" t="n">
-        <v>2.74455009570099</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9082887058755831</v>
+        <v>0.9082887058755852</v>
       </c>
       <c r="E2" t="n">
-        <v>2.744550095700989</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="F2" t="n">
-        <v>2.744550095700989</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="G2" t="n">
-        <v>2.26414754250996</v>
+        <v>2.264147542509961</v>
       </c>
       <c r="H2" t="n">
-        <v>8.05208323771922</v>
+        <v>8.052083237719208</v>
       </c>
       <c r="I2" t="n">
-        <v>2.74455009570099</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="J2" t="n">
-        <v>6.447332410157681</v>
+        <v>6.44733241015767</v>
       </c>
       <c r="K2" t="n">
-        <v>2.093963470468325</v>
+        <v>2.093963470468322</v>
       </c>
       <c r="L2" t="n">
-        <v>2.513674515133979</v>
+        <v>0.1523588442896019</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02626278084114243</v>
+        <v>0.02626278084114242</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02994380495198276</v>
+        <v>0.02994380495198267</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02626278084114243</v>
+        <v>0.02626278084114242</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03031284899495771</v>
+        <v>0.03031284899495767</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03031284899495771</v>
+        <v>0.03031284899495766</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02682849724310768</v>
+        <v>0.02682849724310813</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02626278084114223</v>
+        <v>0.02626278084114242</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03002733710560634</v>
+        <v>0.03002733710560631</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02626278084114243</v>
+        <v>0.02626278084114242</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02626278084114243</v>
+        <v>0.02626278084114242</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02626278084114243</v>
+        <v>0.02626278084114242</v>
       </c>
     </row>
     <row r="4">
@@ -7723,37 +7723,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.08596149709408</v>
+        <v>38.28057319053681</v>
       </c>
       <c r="C4" t="n">
         <v>10.09014850121162</v>
       </c>
       <c r="D4" t="n">
-        <v>10.08230643944039</v>
+        <v>10.08230643944038</v>
       </c>
       <c r="E4" t="n">
-        <v>6.225900620053294</v>
+        <v>6.225900620053297</v>
       </c>
       <c r="F4" t="n">
-        <v>10.08948484814313</v>
+        <v>10.08948484814314</v>
       </c>
       <c r="G4" t="n">
-        <v>38.28113890693875</v>
+        <v>10.08652721349604</v>
       </c>
       <c r="H4" t="n">
         <v>38.28527874230883</v>
       </c>
       <c r="I4" t="n">
-        <v>38.28433774680124</v>
+        <v>38.28433774680125</v>
       </c>
       <c r="J4" t="n">
-        <v>38.28300694822548</v>
+        <v>10.59849882408579</v>
       </c>
       <c r="K4" t="n">
         <v>10.08500237030977</v>
       </c>
       <c r="L4" t="n">
-        <v>10.0854149710831</v>
+        <v>10.08541497108309</v>
       </c>
     </row>
     <row r="5">
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04257201397699416</v>
+        <v>0.04257201397699435</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04633657024145823</v>
+        <v>0.04633657024145824</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04257138717317468</v>
+        <v>0.04257138717317423</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04628372153347775</v>
+        <v>0.04628372153347773</v>
       </c>
       <c r="F5" t="n">
         <v>0.04628372153347775</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04313773037896004</v>
+        <v>0.04313773037896006</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04257201397699416</v>
+        <v>0.04257201397699435</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04633657024145823</v>
+        <v>0.04633657024145824</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04257201397699416</v>
+        <v>0.04257201397699435</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04257201397699416</v>
+        <v>0.04257201397699435</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04257201397699416</v>
+        <v>0.04257201397699435</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05618819020403136</v>
+        <v>0.05618819020403162</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08279433302151831</v>
+        <v>0.08279433302185885</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08382094029190612</v>
+        <v>0.08382094029190602</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07653973515733427</v>
+        <v>0.07653973515733431</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06064707566219182</v>
+        <v>0.06064707566219178</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07964089132085207</v>
+        <v>0.07964089132085198</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07907517491896504</v>
+        <v>0.07907517491896587</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08283973118335021</v>
+        <v>0.08283973118335018</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07907967283546266</v>
+        <v>0.07907967283546347</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05576305271547852</v>
+        <v>0.05576305271547955</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1029825442026524</v>
+        <v>0.1029825442026526</v>
       </c>
     </row>
     <row r="7">
@@ -7843,37 +7843,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1165419358137283</v>
+        <v>0.1165419358137284</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1469593277031889</v>
+        <v>0.146959327703189</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1431947120705616</v>
+        <v>0.1431947120705622</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1777159510318395</v>
+        <v>0.1777159510318394</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1469592235562778</v>
+        <v>0.1469592235562777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1437604878406902</v>
+        <v>0.1437604878406905</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1431947714387259</v>
+        <v>0.1431947714387249</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1469593277031889</v>
+        <v>0.146959327703189</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1431947714387259</v>
+        <v>0.1431947714387249</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1277519888338251</v>
+        <v>0.1096341092594724</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1431947714387259</v>
+        <v>0.1431947714387249</v>
       </c>
     </row>
     <row r="8">
@@ -7889,7 +7889,7 @@
         <v>1.030759833191594</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6004761247477467</v>
+        <v>0.6004761247477474</v>
       </c>
       <c r="E8" t="n">
         <v>1.030759833191594</v>
@@ -7898,22 +7898,22 @@
         <v>1.030759833191594</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5666271554476509</v>
+        <v>0.5666271554476517</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4274787248575953</v>
+        <v>0.4274787248575954</v>
       </c>
       <c r="I8" t="n">
         <v>1.030759833191594</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4748960910546514</v>
+        <v>0.4748960910546521</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5688114422432895</v>
+        <v>0.5688114422432906</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6214890878713571</v>
+        <v>0.5703995346714181</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6141252786688203</v>
+        <v>0.6141252786688199</v>
       </c>
       <c r="C9" t="n">
-        <v>1.05663995443651</v>
+        <v>1.056639954436509</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6049321023668816</v>
+        <v>0.6049321023668814</v>
       </c>
       <c r="E9" t="n">
-        <v>1.05663995443651</v>
+        <v>1.056639954436509</v>
       </c>
       <c r="F9" t="n">
-        <v>1.05663995443651</v>
+        <v>1.056639954436509</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5912223993598887</v>
+        <v>0.591222399359889</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5346539668959569</v>
+        <v>0.5346539668959568</v>
       </c>
       <c r="I9" t="n">
-        <v>1.05663995443651</v>
+        <v>1.056639954436509</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5538405214847614</v>
+        <v>0.553840521484761</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5920375818717999</v>
+        <v>0.5920375818717997</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6134920114529703</v>
+        <v>0.5927222921816677</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen ionising radiation results.xlsx
+++ b/Results/Hydrogen/hydrogen ionising radiation results.xlsx
@@ -515,37 +515,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1960553098999485</v>
+        <v>0.1960553098999518</v>
       </c>
       <c r="C2" t="n">
-        <v>4.325006008434364</v>
+        <v>4.325006008434366</v>
       </c>
       <c r="D2" t="n">
-        <v>1.259704037882083</v>
+        <v>1.259704037882085</v>
       </c>
       <c r="E2" t="n">
-        <v>4.325006008434364</v>
+        <v>4.325006008434366</v>
       </c>
       <c r="F2" t="n">
-        <v>4.325006008434364</v>
+        <v>4.325006008434366</v>
       </c>
       <c r="G2" t="n">
-        <v>2.923106055940246</v>
+        <v>2.923106055940242</v>
       </c>
       <c r="H2" t="n">
-        <v>2.57419464317424</v>
+        <v>2.574194643174236</v>
       </c>
       <c r="I2" t="n">
-        <v>4.325006008434364</v>
+        <v>4.325006008434366</v>
       </c>
       <c r="J2" t="n">
-        <v>8.526089849471225</v>
+        <v>8.526089849471239</v>
       </c>
       <c r="K2" t="n">
-        <v>4.886761723680754</v>
+        <v>4.886761723680758</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7751452579882272</v>
+        <v>0.7705894485987509</v>
       </c>
     </row>
     <row r="3">
@@ -555,37 +555,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03296382691735586</v>
+        <v>0.0329638269173558</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03778238176121543</v>
+        <v>0.03778238176121539</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03296382691735586</v>
+        <v>0.0329638269173558</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03826467204741119</v>
+        <v>0.03826467204741115</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826467204741112</v>
+        <v>0.03826467204741115</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03355958211431149</v>
+        <v>0.03355958211431152</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03296382691735586</v>
+        <v>0.0329638269173558</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0369208255138145</v>
+        <v>0.03692082551381447</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03296382691735586</v>
+        <v>0.0329638269173558</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03296382691735586</v>
+        <v>0.0329638269173558</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03296382691735586</v>
+        <v>0.0329638269173558</v>
       </c>
     </row>
     <row r="4">
@@ -595,37 +595,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.57477339792476</v>
+        <v>11.57477339792477</v>
       </c>
       <c r="C4" t="n">
         <v>11.57971226689881</v>
       </c>
       <c r="D4" t="n">
-        <v>11.56926569967811</v>
+        <v>11.56926556127892</v>
       </c>
       <c r="E4" t="n">
-        <v>7.147526065242543</v>
+        <v>7.147526065242538</v>
       </c>
       <c r="F4" t="n">
         <v>11.57795047849279</v>
       </c>
       <c r="G4" t="n">
-        <v>43.91295034856391</v>
+        <v>43.91295034856396</v>
       </c>
       <c r="H4" t="n">
-        <v>43.9157116215785</v>
+        <v>43.91571162157847</v>
       </c>
       <c r="I4" t="n">
-        <v>11.57873039652122</v>
+        <v>43.91631159196346</v>
       </c>
       <c r="J4" t="n">
-        <v>12.16217123515681</v>
+        <v>43.91486381961504</v>
       </c>
       <c r="K4" t="n">
         <v>11.57653230419806</v>
       </c>
       <c r="L4" t="n">
-        <v>11.57245861523563</v>
+        <v>11.57245861523564</v>
       </c>
     </row>
     <row r="5">
@@ -635,37 +635,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05390690453333385</v>
+        <v>0.05390690453333383</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05786390312979255</v>
+        <v>0.0578639031297925</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05390601571753482</v>
+        <v>0.05390601571753477</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05793839572930764</v>
+        <v>0.05793839572930755</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05793839572930764</v>
+        <v>0.05793839572930755</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05450265973028956</v>
+        <v>0.05450265973028955</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05390690453333385</v>
+        <v>0.05390690453333383</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05786390312979255</v>
+        <v>0.0578639031297925</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05390690453333385</v>
+        <v>0.05390690453333383</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05390690453333385</v>
+        <v>0.05390690453333383</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05390690453333385</v>
+        <v>0.05390690453333383</v>
       </c>
     </row>
     <row r="6">
@@ -675,37 +675,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07086292183957429</v>
+        <v>0.07086292183957421</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1042335877837092</v>
+        <v>0.1042335877843662</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1062815471969317</v>
+        <v>0.1062815471969315</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09620215150936703</v>
+        <v>0.09620215150936688</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07579478492320386</v>
+        <v>0.07579478492320381</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1007943578719725</v>
+        <v>0.1007943578719724</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1001986026750252</v>
+        <v>0.1001986026750251</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1041556012714755</v>
+        <v>0.1041556012714753</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1002043679278609</v>
+        <v>0.1002043679278607</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07031799651125038</v>
+        <v>0.07031799651125037</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1308421742718101</v>
+        <v>0.1308421742718099</v>
       </c>
     </row>
     <row r="7">
@@ -715,37 +715,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1727775396232706</v>
+        <v>0.1727775396232705</v>
       </c>
       <c r="C7" t="n">
         <v>0.2176879615655749</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2137310039973903</v>
+        <v>0.21373100399739</v>
       </c>
       <c r="E7" t="n">
-        <v>0.26494737613867</v>
+        <v>0.2649473761386699</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2176879578024839</v>
+        <v>0.2176879578024838</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2143267181660721</v>
+        <v>0.2143267181660719</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2137309629691163</v>
+        <v>0.2137309629691162</v>
       </c>
       <c r="I7" t="n">
         <v>0.2176879615655749</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2137309629691163</v>
+        <v>0.2137309629691162</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1900024059023614</v>
+        <v>0.1621632821828374</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2137309629691163</v>
+        <v>0.2137309629691162</v>
       </c>
     </row>
     <row r="8">
@@ -755,37 +755,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6249452246918715</v>
+        <v>0.6249452246918714</v>
       </c>
       <c r="C8" t="n">
-        <v>1.015193910563294</v>
+        <v>1.015193910563293</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6021764319636755</v>
+        <v>0.6021764319636749</v>
       </c>
       <c r="E8" t="n">
-        <v>1.015193910563294</v>
+        <v>1.015193910563293</v>
       </c>
       <c r="F8" t="n">
-        <v>1.015193910563294</v>
+        <v>1.015193910563293</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5681917716274729</v>
+        <v>0.5681917716274731</v>
       </c>
       <c r="H8" t="n">
         <v>0.5802053287495579</v>
       </c>
       <c r="I8" t="n">
-        <v>1.015193910563294</v>
+        <v>1.015193910563293</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4561251798564364</v>
+        <v>0.4561251798564361</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5243639154386326</v>
+        <v>0.5243639154386325</v>
       </c>
       <c r="L8" t="n">
-        <v>0.614184953565418</v>
+        <v>0.6141849535654176</v>
       </c>
     </row>
     <row r="9">
@@ -795,13 +795,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6173394710879198</v>
+        <v>0.61733947108792</v>
       </c>
       <c r="C9" t="n">
         <v>1.053702370961794</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6080665851354218</v>
+        <v>0.6080665851354208</v>
       </c>
       <c r="E9" t="n">
         <v>1.053702370961794</v>
@@ -810,22 +810,22 @@
         <v>1.053702370961794</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5943833566067193</v>
+        <v>0.594383356606718</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5991621612936828</v>
+        <v>0.5991621612936827</v>
       </c>
       <c r="I9" t="n">
         <v>1.053702370961794</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5486459075366955</v>
+        <v>0.5486459075366954</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5763788527968792</v>
+        <v>0.5763788527968787</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6129675682987255</v>
+        <v>0.6132796857662609</v>
       </c>
     </row>
   </sheetData>
@@ -911,37 +911,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06164263840607537</v>
+        <v>0.06164263840607528</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9697890330236286</v>
+        <v>0.9697890330236296</v>
       </c>
       <c r="D2" t="n">
-        <v>2.769417898482208</v>
+        <v>2.769417898482206</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9697890330236286</v>
+        <v>0.9697890330236296</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9697890330236286</v>
+        <v>0.9697890330236296</v>
       </c>
       <c r="G2" t="n">
-        <v>2.38832500555383</v>
+        <v>2.388325005553826</v>
       </c>
       <c r="H2" t="n">
-        <v>5.153737879151546</v>
+        <v>5.153737879151559</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9697890330236286</v>
+        <v>0.9697890330236296</v>
       </c>
       <c r="J2" t="n">
         <v>3.992506952498963</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6579462034500214</v>
+        <v>0.6579462034500211</v>
       </c>
       <c r="L2" t="n">
-        <v>2.408372328660529</v>
+        <v>2.40837232866053</v>
       </c>
     </row>
     <row r="3">
@@ -951,37 +951,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01855084700518985</v>
+        <v>0.01855084700518965</v>
       </c>
       <c r="C3" t="n">
         <v>0.01972269426337986</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01855084700518985</v>
+        <v>0.01855084700518965</v>
       </c>
       <c r="E3" t="n">
+        <v>0.02016957627116284</v>
+      </c>
+      <c r="F3" t="n">
         <v>0.02016957627116282</v>
       </c>
-      <c r="F3" t="n">
-        <v>0.02016957627116283</v>
-      </c>
       <c r="G3" t="n">
-        <v>0.01903952992783616</v>
+        <v>0.01903952992783582</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01855084700518985</v>
+        <v>0.01855084700518965</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02182384692286233</v>
+        <v>0.02182384692286235</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01855084700518985</v>
+        <v>0.01855084700518965</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01855084700518985</v>
+        <v>0.01855084700518965</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01855084700518985</v>
+        <v>0.01855084700518965</v>
       </c>
     </row>
     <row r="4">
@@ -991,34 +991,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.26741334586033</v>
+        <v>10.07232644913677</v>
       </c>
       <c r="C4" t="n">
         <v>10.07322207224974</v>
       </c>
       <c r="D4" t="n">
-        <v>38.26842142192119</v>
+        <v>38.26842142192113</v>
       </c>
       <c r="E4" t="n">
-        <v>6.209390110534459</v>
+        <v>6.209390110534451</v>
       </c>
       <c r="F4" t="n">
         <v>10.07524269748449</v>
       </c>
       <c r="G4" t="n">
-        <v>10.07281513205942</v>
+        <v>38.26790202878298</v>
       </c>
       <c r="H4" t="n">
-        <v>38.27156530350515</v>
+        <v>38.27156530350516</v>
       </c>
       <c r="I4" t="n">
         <v>10.07559944905444</v>
       </c>
       <c r="J4" t="n">
-        <v>38.27008790925321</v>
+        <v>10.58470269869223</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06973576275578</v>
+        <v>10.0697357627558</v>
       </c>
       <c r="L4" t="n">
         <v>10.0726479959372</v>
@@ -1031,37 +1031,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03321332059392329</v>
+        <v>0.03321332059392356</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03648632051159575</v>
+        <v>0.03648632051159577</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03321298417640815</v>
+        <v>0.03321298417640864</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03626024506770464</v>
+        <v>0.03626024506770469</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03626024506770464</v>
+        <v>0.03626024506770471</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03370200351656955</v>
+        <v>0.0337020035165695</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03321332059392329</v>
+        <v>0.03321332059392356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03648632051159575</v>
+        <v>0.03648632051159577</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03321332059392329</v>
+        <v>0.03321332059392356</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03321332059392329</v>
+        <v>0.03321332059392356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03321332059392329</v>
+        <v>0.03321332059392356</v>
       </c>
     </row>
     <row r="6">
@@ -1071,37 +1071,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04715722835051243</v>
+        <v>0.04715722835051202</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07205569035282404</v>
+        <v>0.07205569035303527</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07352236941657313</v>
+        <v>0.07352236941657307</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06610594905841947</v>
+        <v>0.06610594905841949</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05098776572316664</v>
+        <v>0.05098776572316672</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06948299150080998</v>
+        <v>0.06948299150081022</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06899430857823688</v>
+        <v>0.06899430857823718</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07226730849583615</v>
+        <v>0.07226730849583626</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06899860016164089</v>
+        <v>0.06899860016164081</v>
       </c>
       <c r="K6" t="n">
-        <v>0.046751593376556</v>
+        <v>0.04675159337655652</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09180496483645079</v>
+        <v>0.09180496483645086</v>
       </c>
     </row>
     <row r="7">
@@ -1111,37 +1111,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09380751597339515</v>
+        <v>0.09380751597339507</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1194865554227325</v>
+        <v>0.1194865554227326</v>
       </c>
       <c r="D7" t="n">
         <v>0.1162135566927847</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1453425619159411</v>
+        <v>0.1453425619159412</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1194864841305423</v>
+        <v>0.1194864841305422</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1167022384277063</v>
+        <v>0.1167022384277065</v>
       </c>
       <c r="H7" t="n">
-        <v>0.11621355550506</v>
+        <v>0.1162135555050603</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1194865554227325</v>
+        <v>0.1194865554227326</v>
       </c>
       <c r="J7" t="n">
-        <v>0.11621355550506</v>
+        <v>0.1162135555050603</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1032314087046608</v>
+        <v>0.1032314087046611</v>
       </c>
       <c r="L7" t="n">
-        <v>0.11621355550506</v>
+        <v>0.1162135555050603</v>
       </c>
     </row>
     <row r="8">
@@ -1151,13 +1151,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6179879649091984</v>
+        <v>0.6179879649091979</v>
       </c>
       <c r="C8" t="n">
         <v>1.069263967757615</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5453006662249498</v>
+        <v>0.5453006662249501</v>
       </c>
       <c r="E8" t="n">
         <v>1.069263967757615</v>
@@ -1166,22 +1166,22 @@
         <v>1.069263967757615</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5582333638568516</v>
+        <v>0.5582333638568512</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4996318233978241</v>
+        <v>0.4996318233978235</v>
       </c>
       <c r="I8" t="n">
         <v>1.069263967757615</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5257775037864496</v>
+        <v>0.5257775037864504</v>
       </c>
       <c r="K8" t="n">
-        <v>0.601536946117083</v>
+        <v>0.6015369461170821</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5672854966150311</v>
+        <v>0.5672854966150294</v>
       </c>
     </row>
     <row r="9">
@@ -1191,7 +1191,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.60898437400883</v>
+        <v>0.6089843740088297</v>
       </c>
       <c r="C9" t="n">
         <v>1.066984057883211</v>
@@ -1206,22 +1206,22 @@
         <v>1.066984057883211</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5845035076536381</v>
+        <v>0.5845035076536377</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5608897879532689</v>
+        <v>0.5608897879532675</v>
       </c>
       <c r="I9" t="n">
         <v>1.066984057883211</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5714632006855203</v>
+        <v>0.5714632006855206</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6022849017331849</v>
+        <v>0.6022849017331845</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6066473951849596</v>
+        <v>0.5883727424032549</v>
       </c>
     </row>
   </sheetData>
@@ -1307,37 +1307,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.046116129654665</v>
+        <v>3.046116129654661</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6403633215199021</v>
+        <v>0.6403633215199011</v>
       </c>
       <c r="D2" t="n">
-        <v>1.478134101825913</v>
+        <v>1.478134101825914</v>
       </c>
       <c r="E2" t="n">
-        <v>2.762144075844978</v>
+        <v>2.762144075844979</v>
       </c>
       <c r="F2" t="n">
-        <v>2.762144075844978</v>
+        <v>2.762144075844979</v>
       </c>
       <c r="G2" t="n">
-        <v>1.980426758706898</v>
+        <v>1.980426758706899</v>
       </c>
       <c r="H2" t="n">
-        <v>2.745859483932701</v>
+        <v>2.7458594839327</v>
       </c>
       <c r="I2" t="n">
-        <v>2.762144075844978</v>
+        <v>2.762144075844979</v>
       </c>
       <c r="J2" t="n">
-        <v>4.070241217360019</v>
+        <v>4.070241217360011</v>
       </c>
       <c r="K2" t="n">
-        <v>2.744385242897018</v>
+        <v>2.744385242897013</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8917835784817457</v>
+        <v>0.8917835784817464</v>
       </c>
     </row>
     <row r="3">
@@ -1347,37 +1347,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02378906340013707</v>
+        <v>0.02378906340013709</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02150353132817734</v>
+        <v>0.02150353132817731</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02378906340013708</v>
+        <v>0.02378906340013709</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02731373472559913</v>
+        <v>0.02731373472559914</v>
       </c>
       <c r="F3" t="n">
         <v>0.02731373472559914</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02422939951143906</v>
+        <v>0.02422939951143913</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02378906340013708</v>
+        <v>0.02378906340013709</v>
       </c>
       <c r="I3" t="n">
         <v>0.02671629461435237</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02378906340013708</v>
+        <v>0.02378906340013709</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02378906340013708</v>
+        <v>0.02378906340013709</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02378906340013708</v>
+        <v>0.02378906340013709</v>
       </c>
     </row>
     <row r="4">
@@ -1387,37 +1387,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.63836679806289</v>
+        <v>40.40325772281095</v>
       </c>
       <c r="C4" t="n">
         <v>10.63490111895241</v>
       </c>
       <c r="D4" t="n">
-        <v>10.63670560337563</v>
+        <v>10.63670557441538</v>
       </c>
       <c r="E4" t="n">
-        <v>6.562795912322085</v>
+        <v>6.562795912322084</v>
       </c>
       <c r="F4" t="n">
         <v>10.6413435423474</v>
       </c>
       <c r="G4" t="n">
-        <v>40.40369805892221</v>
+        <v>10.6388071341742</v>
       </c>
       <c r="H4" t="n">
-        <v>40.40807774265989</v>
+        <v>40.40807774265987</v>
       </c>
       <c r="I4" t="n">
-        <v>40.40618495402513</v>
+        <v>10.64129402927711</v>
       </c>
       <c r="J4" t="n">
-        <v>40.40608309637919</v>
+        <v>40.40608309637921</v>
       </c>
       <c r="K4" t="n">
         <v>10.63919488846955</v>
       </c>
       <c r="L4" t="n">
-        <v>10.6376201457871</v>
+        <v>10.63762014578711</v>
       </c>
     </row>
     <row r="5">
@@ -1430,25 +1430,25 @@
         <v>0.03996393506799598</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03991309207036276</v>
+        <v>0.03991309207036278</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03996350298001258</v>
+        <v>0.03996350298001253</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04293266307807683</v>
+        <v>0.0429326630780768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04293266307807683</v>
+        <v>0.0429326630780768</v>
       </c>
       <c r="G5" t="n">
-        <v>0.040404271179298</v>
+        <v>0.04040427117929801</v>
       </c>
       <c r="H5" t="n">
         <v>0.03996393506799598</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04289116628221129</v>
+        <v>0.04289116628221133</v>
       </c>
       <c r="J5" t="n">
         <v>0.03996393506799598</v>
@@ -1467,37 +1467,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05348472076636256</v>
+        <v>0.05348472076636267</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07678137377308346</v>
+        <v>0.07678137377308349</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08161948568627246</v>
+        <v>0.08161948568627263</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07338157160429316</v>
+        <v>0.07338157160429329</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05717562680898784</v>
+        <v>0.05717562680898793</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0772278382743098</v>
+        <v>0.07722783827430985</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07678750216312151</v>
+        <v>0.07678750216312165</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0797147333772231</v>
+        <v>0.07971473337722315</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07679208178352921</v>
+        <v>0.07679208178352936</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05305185964198357</v>
+        <v>0.05305185964198363</v>
       </c>
       <c r="L6" t="n">
-        <v>0.101129205838358</v>
+        <v>0.1011292058383582</v>
       </c>
     </row>
     <row r="7">
@@ -1507,37 +1507,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1099282229931901</v>
+        <v>0.10992822299319</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1356297041720913</v>
+        <v>0.1356297041720912</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1356805785749402</v>
+        <v>0.1356805785749404</v>
       </c>
       <c r="E7" t="n">
         <v>0.1683254390764167</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1386077753764019</v>
+        <v>0.1386077753764018</v>
       </c>
       <c r="G7" t="n">
         <v>0.1361208832810266</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1356805471697244</v>
+        <v>0.1356805471697247</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1386077783839399</v>
+        <v>0.1386077783839398</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1356805471697244</v>
+        <v>0.1356805471697247</v>
       </c>
       <c r="K7" t="n">
         <v>0.1207595626135711</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1356805471697244</v>
+        <v>0.1356805471697247</v>
       </c>
     </row>
     <row r="8">
@@ -1547,7 +1547,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03626645087264703</v>
+        <v>-0.03626645087264685</v>
       </c>
       <c r="C8" t="n">
         <v>0.9266937570077319</v>
@@ -1556,10 +1556,10 @@
         <v>1.07770639854991</v>
       </c>
       <c r="E8" t="n">
-        <v>1.009780938293803</v>
+        <v>1.009780938293802</v>
       </c>
       <c r="F8" t="n">
-        <v>1.009780938293803</v>
+        <v>1.009780938293802</v>
       </c>
       <c r="G8" t="n">
         <v>0.5280301881075241</v>
@@ -1568,16 +1568,16 @@
         <v>1.055850584457575</v>
       </c>
       <c r="I8" t="n">
-        <v>1.009780938293803</v>
+        <v>1.009780938293802</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6032715131673457</v>
+        <v>0.6032715131673448</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7115230680668365</v>
+        <v>0.7115230680668366</v>
       </c>
       <c r="L8" t="n">
-        <v>1.191867489734712</v>
+        <v>1.191867489734711</v>
       </c>
     </row>
     <row r="9">
@@ -1587,22 +1587,22 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.003482867751383966</v>
+        <v>0.003482867751384055</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9203143139004619</v>
+        <v>0.9203143139004628</v>
       </c>
       <c r="D9" t="n">
         <v>1.080358738518784</v>
       </c>
       <c r="E9" t="n">
-        <v>1.030220544802774</v>
+        <v>1.030220544802773</v>
       </c>
       <c r="F9" t="n">
         <v>1.030220544802773</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5452227404613831</v>
+        <v>0.5452227404613829</v>
       </c>
       <c r="H9" t="n">
         <v>1.07150788632341</v>
@@ -1614,7 +1614,7 @@
         <v>0.6452177753862379</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7366440058304006</v>
+        <v>0.7366440058304005</v>
       </c>
       <c r="L9" t="n">
         <v>1.183348748025931</v>
@@ -1703,37 +1703,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.66424293553604</v>
+        <v>1.664242935536041</v>
       </c>
       <c r="C2" t="n">
-        <v>0.404863652130836</v>
+        <v>0.4048636521308361</v>
       </c>
       <c r="D2" t="n">
         <v>1.512657121738278</v>
       </c>
       <c r="E2" t="n">
-        <v>1.313714705599409</v>
+        <v>1.313714705599412</v>
       </c>
       <c r="F2" t="n">
-        <v>1.313714705599409</v>
+        <v>1.313714705599412</v>
       </c>
       <c r="G2" t="n">
-        <v>1.297873658794057</v>
+        <v>1.297873658794061</v>
       </c>
       <c r="H2" t="n">
         <v>2.214748472458764</v>
       </c>
       <c r="I2" t="n">
-        <v>1.313714705599409</v>
+        <v>1.313714705599412</v>
       </c>
       <c r="J2" t="n">
-        <v>2.780524617824656</v>
+        <v>2.780524617824658</v>
       </c>
       <c r="K2" t="n">
-        <v>1.355063623393792</v>
+        <v>1.355063623393793</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6512552293962175</v>
+        <v>0.6512552293962188</v>
       </c>
     </row>
     <row r="3">
@@ -1743,37 +1743,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01767294305015713</v>
+        <v>0.01767294305015751</v>
       </c>
       <c r="C3" t="n">
-        <v>0.015870941216392</v>
+        <v>0.01587094121639201</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01767294305015713</v>
+        <v>0.01767294305015751</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02035092678417909</v>
+        <v>0.02035092678417914</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02035092678417912</v>
+        <v>0.02035092678417914</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01808797219969774</v>
+        <v>0.01808797219969788</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01767294305015713</v>
+        <v>0.01767294305015751</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02043788176339834</v>
+        <v>0.02043788176339836</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01767294305015713</v>
+        <v>0.01767294305015751</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01767294305015713</v>
+        <v>0.01767294305015751</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01767294305015713</v>
+        <v>0.01767294305015751</v>
       </c>
     </row>
     <row r="4">
@@ -1783,13 +1783,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.25803499646354</v>
+        <v>38.25803499646351</v>
       </c>
       <c r="C4" t="n">
-        <v>10.06623177732574</v>
+        <v>10.06623177732575</v>
       </c>
       <c r="D4" t="n">
-        <v>38.25850544816349</v>
+        <v>38.2585054481635</v>
       </c>
       <c r="E4" t="n">
         <v>6.207173109228791</v>
@@ -1798,19 +1798,19 @@
         <v>10.07102515673249</v>
       </c>
       <c r="G4" t="n">
-        <v>10.06878191482542</v>
+        <v>38.25845002561306</v>
       </c>
       <c r="H4" t="n">
         <v>38.26233550208968</v>
       </c>
       <c r="I4" t="n">
-        <v>10.07113182438912</v>
+        <v>10.07113182438911</v>
       </c>
       <c r="J4" t="n">
-        <v>10.58000844617903</v>
+        <v>10.58000844617902</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06827730722447</v>
+        <v>10.06827730722448</v>
       </c>
       <c r="L4" t="n">
         <v>10.06801721542149</v>
@@ -1823,37 +1823,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02930873607868767</v>
+        <v>0.02930873607868764</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02926666441068762</v>
+        <v>0.02926666441068767</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02930835438254947</v>
+        <v>0.02930835438254917</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03206133926601114</v>
+        <v>0.03206133926601117</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03206133926601114</v>
+        <v>0.03206133926601117</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02972376522822812</v>
+        <v>0.02972376522822802</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02930873607868767</v>
+        <v>0.02930873607868764</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03207367479192845</v>
+        <v>0.03207367479192849</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02930873607868767</v>
+        <v>0.02930873607868764</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02930873607868767</v>
+        <v>0.02930873607868764</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02930873607868767</v>
+        <v>0.02930873607868764</v>
       </c>
     </row>
     <row r="6">
@@ -1863,37 +1863,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03958238905424726</v>
+        <v>0.03958238905424772</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0568433209269445</v>
+        <v>0.05684332092649917</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06048289802436724</v>
+        <v>0.06048289802436737</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05491672872710193</v>
+        <v>0.05491672872710197</v>
       </c>
       <c r="F6" t="n">
         <v>0.04288892767786284</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05730838536495755</v>
+        <v>0.05730838536495751</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05689335621554239</v>
+        <v>0.05689335621554303</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05965829492865779</v>
+        <v>0.05965829492865771</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05689675828091631</v>
+        <v>0.05689675828091657</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03926082895489193</v>
+        <v>0.0392608289548919</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07497610890205331</v>
+        <v>0.07497610890205401</v>
       </c>
     </row>
     <row r="7">
@@ -1903,37 +1903,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07301680347412499</v>
+        <v>0.07301680347412519</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08975583262821347</v>
+        <v>0.08975583262821354</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08979792055234372</v>
+        <v>0.08979792055234392</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1119278755107869</v>
+        <v>0.111927875510787</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09256282962885867</v>
+        <v>0.09256282962885888</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0902129334457538</v>
+        <v>0.09021293344575385</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08979790429621344</v>
+        <v>0.08979790429621355</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09256284300945425</v>
+        <v>0.09256284300945437</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08979790429621344</v>
+        <v>0.08979790429621355</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0800748754126929</v>
+        <v>0.08007487541269277</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08979790429621344</v>
+        <v>0.08979790429621355</v>
       </c>
     </row>
     <row r="8">
@@ -1943,10 +1943,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01298949236560191</v>
+        <v>-0.01298949236560181</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9290764566008619</v>
+        <v>0.9290764566008631</v>
       </c>
       <c r="D8" t="n">
         <v>1.066232243776106</v>
@@ -1958,22 +1958,22 @@
         <v>1.035332730748298</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5370309806331451</v>
+        <v>0.5370309806331444</v>
       </c>
       <c r="H8" t="n">
-        <v>1.055442700981084</v>
+        <v>1.055442700981085</v>
       </c>
       <c r="I8" t="n">
         <v>1.035332730748298</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6230816348252315</v>
+        <v>0.6230816348252317</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7343528221950618</v>
+        <v>0.7343528221950625</v>
       </c>
       <c r="L8" t="n">
-        <v>1.192865831955771</v>
+        <v>1.192865831955772</v>
       </c>
     </row>
     <row r="9">
@@ -1983,34 +1983,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00977328002419464</v>
+        <v>0.009773280024194737</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9199336502342889</v>
+        <v>0.9199336502342866</v>
       </c>
       <c r="D9" t="n">
         <v>1.070688063655535</v>
       </c>
       <c r="E9" t="n">
-        <v>1.037248915663537</v>
+        <v>1.037248915663538</v>
       </c>
       <c r="F9" t="n">
-        <v>1.037248915663537</v>
+        <v>1.037248915663538</v>
       </c>
       <c r="G9" t="n">
         <v>0.5462161201461616</v>
       </c>
       <c r="H9" t="n">
-        <v>1.066336722041634</v>
+        <v>1.066336722041636</v>
       </c>
       <c r="I9" t="n">
-        <v>1.037248915663537</v>
+        <v>1.037248915663538</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6503780480144905</v>
+        <v>0.6503780480144914</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7417064818128745</v>
+        <v>0.7417064818128742</v>
       </c>
       <c r="L9" t="n">
         <v>1.18200488717803</v>
@@ -2099,37 +2099,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.820517059897116</v>
+        <v>0.8205170598971161</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2603663900424912</v>
+        <v>0.2603663900424644</v>
       </c>
       <c r="D2" t="n">
-        <v>1.634523997004037</v>
+        <v>1.634523997004006</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4536471152291341</v>
+        <v>0.4536471152291348</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4536471152291341</v>
+        <v>0.4536471152291348</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9138048723027491</v>
+        <v>0.9138048723027484</v>
       </c>
       <c r="H2" t="n">
-        <v>1.791896253236249</v>
+        <v>1.791896253236251</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4536471152291341</v>
+        <v>0.4536471152291348</v>
       </c>
       <c r="J2" t="n">
-        <v>2.210595678621216</v>
+        <v>2.21059567862122</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5160070554283254</v>
+        <v>0.5160070554283337</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3504569570316212</v>
+        <v>0.3504569570316196</v>
       </c>
     </row>
     <row r="3">
@@ -2139,37 +2139,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01353020126459336</v>
+        <v>0.01353020126459328</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01222286857983237</v>
+        <v>0.01222286857983233</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01353020126459337</v>
+        <v>0.01353020126459327</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01554141074782484</v>
+        <v>0.01554141074782475</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01554141074782484</v>
+        <v>0.01554141074782476</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01392916878544555</v>
+        <v>0.01392916878544551</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01353020126459337</v>
+        <v>0.01353020126459327</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0161921002098577</v>
+        <v>0.01619210020985768</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01353020126459336</v>
+        <v>0.01353020126459327</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01353020126459337</v>
+        <v>0.01353020126459327</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01353020126459337</v>
+        <v>0.01353020126459327</v>
       </c>
     </row>
     <row r="4">
@@ -2182,34 +2182,34 @@
         <v>10.06193008645181</v>
       </c>
       <c r="C4" t="n">
-        <v>10.0605983543364</v>
+        <v>10.06059835433641</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06353713255282</v>
+        <v>10.06353710181743</v>
       </c>
       <c r="E4" t="n">
-        <v>6.200073086571384</v>
+        <v>6.200073086571381</v>
       </c>
       <c r="F4" t="n">
         <v>10.0643876746881</v>
       </c>
       <c r="G4" t="n">
-        <v>38.24965498650501</v>
+        <v>38.24965498650504</v>
       </c>
       <c r="H4" t="n">
         <v>38.25326815095776</v>
       </c>
       <c r="I4" t="n">
-        <v>38.25191791792942</v>
+        <v>38.25191791792945</v>
       </c>
       <c r="J4" t="n">
         <v>38.2517715532467</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06123138573862</v>
+        <v>10.06123138573822</v>
       </c>
       <c r="L4" t="n">
-        <v>10.0617850020628</v>
+        <v>10.06178500206281</v>
       </c>
     </row>
     <row r="5">
@@ -2219,37 +2219,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02248964259931049</v>
+        <v>0.0224896425993104</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02245364066034338</v>
+        <v>0.02245364066034333</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02248923156270691</v>
+        <v>0.02248923156270692</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02506207283333802</v>
+        <v>0.02506207283333804</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02506207283333802</v>
+        <v>0.02506207283333804</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02288861012016255</v>
+        <v>0.0228886101201626</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02248964259931049</v>
+        <v>0.0224896425993104</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02515154154457482</v>
+        <v>0.02515154154457476</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02248964259931049</v>
+        <v>0.0224896425993104</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02248964259931049</v>
+        <v>0.0224896425993104</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02248964259931049</v>
+        <v>0.0224896425993104</v>
       </c>
     </row>
     <row r="6">
@@ -2262,34 +2262,34 @@
         <v>0.030851189561743</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04440583812026375</v>
+        <v>0.04440583812064931</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04735937693239525</v>
+        <v>0.04735937693239529</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04337292818552019</v>
+        <v>0.04337292818552024</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0338933743311652</v>
+        <v>0.03389337433116513</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04492315853306943</v>
+        <v>0.04492315853306948</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0445241910123734</v>
+        <v>0.04452419101237357</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0471860899574818</v>
+        <v>0.04718608995748165</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04452687812112549</v>
+        <v>0.0445268781211255</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03059720654257625</v>
+        <v>0.03059720654257621</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05880678431956828</v>
+        <v>0.05880678431956845</v>
       </c>
     </row>
     <row r="7">
@@ -2299,37 +2299,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05299326383181743</v>
+        <v>0.05299326383181791</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06503197832492751</v>
+        <v>0.06503197832492801</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06506798939745304</v>
+        <v>0.06506798939745381</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08166383139810932</v>
+        <v>0.08166383139810945</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06772986096526336</v>
+        <v>0.06772986096526502</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0654669477847472</v>
+        <v>0.06546694778474726</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0650679802638954</v>
+        <v>0.06506798026389522</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06772987920915906</v>
+        <v>0.06772987920915942</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0650679802638954</v>
+        <v>0.06506798026389522</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04986375457942763</v>
+        <v>0.05778800360786734</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0650679802638954</v>
+        <v>0.06506798026389522</v>
       </c>
     </row>
     <row r="8">
@@ -2339,13 +2339,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002929264260533907</v>
+        <v>0.002929264260533969</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9309413586115595</v>
+        <v>0.9309413586115592</v>
       </c>
       <c r="D8" t="n">
-        <v>1.057021002846225</v>
+        <v>1.057021002846224</v>
       </c>
       <c r="E8" t="n">
         <v>1.052549184758659</v>
@@ -2354,7 +2354,7 @@
         <v>1.052549184758659</v>
       </c>
       <c r="G8" t="n">
-        <v>0.542926579201641</v>
+        <v>0.5429265792016402</v>
       </c>
       <c r="H8" t="n">
         <v>1.058313305265897</v>
@@ -2363,10 +2363,10 @@
         <v>1.052549184758659</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6322873573263391</v>
+        <v>0.6322873573263379</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7516035942988925</v>
+        <v>0.7516035942988911</v>
       </c>
       <c r="L8" t="n">
         <v>1.196713579601303</v>
@@ -2379,10 +2379,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01396292553753656</v>
+        <v>0.01396292553753658</v>
       </c>
       <c r="C9" t="n">
-        <v>0.919821567328012</v>
+        <v>0.9198215673280123</v>
       </c>
       <c r="D9" t="n">
         <v>1.063370134789639</v>
@@ -2394,7 +2394,7 @@
         <v>1.042237955385043</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5467993986146886</v>
+        <v>0.5467993986146892</v>
       </c>
       <c r="H9" t="n">
         <v>1.063931181878818</v>
@@ -2403,10 +2403,10 @@
         <v>1.042237955385043</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6518471942123945</v>
+        <v>0.6518471942123946</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7469551582021479</v>
+        <v>0.7469551582021484</v>
       </c>
       <c r="L9" t="n">
         <v>1.182153259736697</v>
@@ -2495,37 +2495,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.963693015655054</v>
+        <v>2.963693015655052</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4885787337738239</v>
+        <v>0.4885787337731562</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559134217022507</v>
+        <v>1.559134217022473</v>
       </c>
       <c r="E2" t="n">
-        <v>2.517142796928544</v>
+        <v>2.517142796928533</v>
       </c>
       <c r="F2" t="n">
-        <v>2.517142796928544</v>
+        <v>2.517142796928533</v>
       </c>
       <c r="G2" t="n">
-        <v>1.94832418874462</v>
+        <v>1.948324188744592</v>
       </c>
       <c r="H2" t="n">
-        <v>5.201077989882067</v>
+        <v>5.201077989882064</v>
       </c>
       <c r="I2" t="n">
-        <v>2.517142796928544</v>
+        <v>2.517142796928533</v>
       </c>
       <c r="J2" t="n">
-        <v>4.022819101598192</v>
+        <v>4.022819101598184</v>
       </c>
       <c r="K2" t="n">
         <v>2.440162760863803</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4776289383961806</v>
+        <v>0.4776289383961775</v>
       </c>
     </row>
     <row r="3">
@@ -2535,37 +2535,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02298377229411451</v>
+        <v>0.02298377229411371</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02056728801463311</v>
+        <v>0.02056728801463127</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02298377229411451</v>
+        <v>0.02298377229411371</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02619268131639443</v>
+        <v>0.0261926813163945</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02619268131639443</v>
+        <v>0.0261926813163945</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02341572994424357</v>
+        <v>0.02341572994424402</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02298377229411451</v>
+        <v>0.02298377229411371</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02585735547118029</v>
+        <v>0.02585735547118062</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02298377229411451</v>
+        <v>0.02298377229411371</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02298377229411451</v>
+        <v>0.02298377229411371</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02298377229411451</v>
+        <v>0.02298377229411371</v>
       </c>
     </row>
     <row r="4">
@@ -2578,31 +2578,31 @@
         <v>10.63712249891232</v>
       </c>
       <c r="C4" t="n">
-        <v>10.63347906060108</v>
+        <v>10.63347906060107</v>
       </c>
       <c r="D4" t="n">
-        <v>10.63578925460249</v>
+        <v>10.63578927791338</v>
       </c>
       <c r="E4" t="n">
-        <v>6.561145615295809</v>
+        <v>6.561145615295805</v>
       </c>
       <c r="F4" t="n">
         <v>10.63995166019024</v>
       </c>
       <c r="G4" t="n">
-        <v>10.63755445656244</v>
+        <v>10.63755445656245</v>
       </c>
       <c r="H4" t="n">
         <v>40.40724691257221</v>
       </c>
       <c r="I4" t="n">
-        <v>10.63999608208938</v>
+        <v>40.40462865754921</v>
       </c>
       <c r="J4" t="n">
-        <v>40.40467598173367</v>
+        <v>11.17744757392963</v>
       </c>
       <c r="K4" t="n">
-        <v>10.63751661898262</v>
+        <v>10.63751661898261</v>
       </c>
       <c r="L4" t="n">
         <v>10.636280947643</v>
@@ -2615,37 +2615,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03895287330394823</v>
+        <v>0.03895287330394701</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03889640853790069</v>
+        <v>0.0388964085378998</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03895246359745871</v>
+        <v>0.03895246359745817</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04183441754421897</v>
+        <v>0.0418344175442181</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04183441754421897</v>
+        <v>0.0418344175442181</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03938483095407839</v>
+        <v>0.03938483095407729</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03895287330394823</v>
+        <v>0.03895287330394701</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04182645648101513</v>
+        <v>0.0418264564810139</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03895287330394823</v>
+        <v>0.03895287330394701</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03895287330394823</v>
+        <v>0.03895287330394701</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03895287330394823</v>
+        <v>0.03895287330394701</v>
       </c>
     </row>
     <row r="6">
@@ -2655,37 +2655,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05238115697573828</v>
+        <v>0.05238115697573838</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07545052630678808</v>
+        <v>0.07545052630736568</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08028707118513914</v>
+        <v>0.08028707118513785</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0720579342412252</v>
+        <v>0.07205793424122403</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05599238759277102</v>
+        <v>0.05599238759276927</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07592634910099268</v>
+        <v>0.07592634910099082</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0754943914509926</v>
+        <v>0.07549439145099113</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07836797462792985</v>
+        <v>0.07836797462792743</v>
       </c>
       <c r="J6" t="n">
-        <v>0.075498933819537</v>
+        <v>0.07549893381953594</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05195181678277987</v>
+        <v>0.05195181678277874</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09963809751662335</v>
+        <v>0.0996380975166216</v>
       </c>
     </row>
     <row r="7">
@@ -2695,37 +2695,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1070380840844717</v>
+        <v>0.1070380840844688</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1321573871035078</v>
+        <v>0.1321573871035031</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1322138522754657</v>
+        <v>0.1322138522754604</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1641396925464826</v>
+        <v>0.164139692546476</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1350873989837753</v>
+        <v>0.1350873989837701</v>
       </c>
       <c r="G7" t="n">
-        <v>0.132645809519685</v>
+        <v>0.1326458095196807</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1322138518695548</v>
+        <v>0.1322138518695504</v>
       </c>
       <c r="I7" t="n">
-        <v>0.135087435046622</v>
+        <v>0.1350874350466173</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1322138518695548</v>
+        <v>0.1322138518695504</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1005130662642783</v>
+        <v>0.1176269133127303</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1322138518695548</v>
+        <v>0.1322138518695504</v>
       </c>
     </row>
     <row r="8">
@@ -2735,13 +2735,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03218921087411598</v>
+        <v>-0.03218921087411608</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9293127130399662</v>
+        <v>0.9293127130399674</v>
       </c>
       <c r="D8" t="n">
-        <v>1.074457604608387</v>
+        <v>1.074457604608388</v>
       </c>
       <c r="E8" t="n">
         <v>1.014213224905566</v>
@@ -2750,7 +2750,7 @@
         <v>1.014213224905566</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5283139872980303</v>
+        <v>0.5283139872980309</v>
       </c>
       <c r="H8" t="n">
         <v>1.00443605542748</v>
@@ -2759,13 +2759,13 @@
         <v>1.014213224905566</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6039922116336298</v>
+        <v>0.6039922116336292</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7160264712456531</v>
+        <v>0.7160264712456533</v>
       </c>
       <c r="L8" t="n">
-        <v>1.199697804762866</v>
+        <v>1.199697804762867</v>
       </c>
     </row>
     <row r="9">
@@ -2775,34 +2775,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.00643966063347591</v>
+        <v>0.006439660633475847</v>
       </c>
       <c r="C9" t="n">
         <v>0.9209316167428691</v>
       </c>
       <c r="D9" t="n">
-        <v>1.078250022141636</v>
+        <v>1.078250022141638</v>
       </c>
       <c r="E9" t="n">
-        <v>1.031356703192232</v>
+        <v>1.031356703192231</v>
       </c>
       <c r="F9" t="n">
-        <v>1.031356703192232</v>
+        <v>1.031356703192231</v>
       </c>
       <c r="G9" t="n">
         <v>0.5450945817234989</v>
       </c>
       <c r="H9" t="n">
-        <v>1.049828131094317</v>
+        <v>1.049828131094318</v>
       </c>
       <c r="I9" t="n">
-        <v>1.031356703192232</v>
+        <v>1.031356703192231</v>
       </c>
       <c r="J9" t="n">
-        <v>0.645334793301434</v>
+        <v>0.6453347933014336</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7370454220843052</v>
+        <v>0.7370454220843047</v>
       </c>
       <c r="L9" t="n">
         <v>1.186282929309624</v>
@@ -2894,34 +2894,34 @@
         <v>1.444451810011891</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1947636355479005</v>
+        <v>0.1947636355479004</v>
       </c>
       <c r="D2" t="n">
-        <v>1.611626490461503</v>
+        <v>1.611626490461505</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9562582942841579</v>
+        <v>0.9562582942841555</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9562582942841579</v>
+        <v>0.9562582942841555</v>
       </c>
       <c r="G2" t="n">
-        <v>1.276512866966097</v>
+        <v>1.276512866966089</v>
       </c>
       <c r="H2" t="n">
-        <v>7.518928521791654</v>
+        <v>7.518928521791651</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9562582942841579</v>
+        <v>0.9562582942841555</v>
       </c>
       <c r="J2" t="n">
-        <v>2.373142965962557</v>
+        <v>2.373142965962558</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9601655268521174</v>
+        <v>0.9601655268521173</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1813258419793943</v>
+        <v>0.1813258419793944</v>
       </c>
     </row>
     <row r="3">
@@ -2931,37 +2931,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01693795533799913</v>
+        <v>0.01693795533799916</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01471676235264079</v>
+        <v>0.01471676235264083</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01693795533799913</v>
+        <v>0.01693795533799916</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01922309703409542</v>
+        <v>0.01922309703409544</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01922309703409542</v>
+        <v>0.01922309703409544</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01733746511412001</v>
+        <v>0.01733746511412003</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01693795533799913</v>
+        <v>0.01693795533799916</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01960342445984824</v>
+        <v>0.01960342445984825</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01693795533799913</v>
+        <v>0.01693795533799916</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01693795533799913</v>
+        <v>0.01693795533799916</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01693795533799913</v>
+        <v>0.01693795533799916</v>
       </c>
     </row>
     <row r="4">
@@ -2971,31 +2971,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.06710673703989</v>
+        <v>10.0671067370399</v>
       </c>
       <c r="C4" t="n">
         <v>10.0646065231555</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06774080047203</v>
+        <v>38.25785574375224</v>
       </c>
       <c r="E4" t="n">
-        <v>6.205211587243009</v>
+        <v>6.205211587243014</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06956586374592</v>
+        <v>10.06956586374593</v>
       </c>
       <c r="G4" t="n">
-        <v>38.25742338186004</v>
+        <v>10.067506246816</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26619136396958</v>
+        <v>38.2661913639696</v>
       </c>
       <c r="I4" t="n">
-        <v>38.25968934120581</v>
+        <v>38.25968934120586</v>
       </c>
       <c r="J4" t="n">
-        <v>10.57869086158841</v>
+        <v>38.259974663973</v>
       </c>
       <c r="K4" t="n">
         <v>10.06641808967417</v>
@@ -3014,25 +3014,25 @@
         <v>0.0289642768675587</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02891154277366315</v>
+        <v>0.02891154277366317</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02896401196405927</v>
+        <v>0.02896401196405926</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03160729873396544</v>
+        <v>0.03160729873396542</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03160729873396544</v>
+        <v>0.03160729873396542</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02936378664367957</v>
+        <v>0.02936378664367958</v>
       </c>
       <c r="H5" t="n">
         <v>0.0289642768675587</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03162974598940781</v>
+        <v>0.03162974598940785</v>
       </c>
       <c r="J5" t="n">
         <v>0.0289642768675587</v>
@@ -3051,37 +3051,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03983928534774589</v>
+        <v>0.0398392853477459</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0579595156124482</v>
+        <v>0.05795951561200353</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06180180422642662</v>
+        <v>0.06180180422642663</v>
       </c>
       <c r="E6" t="n">
         <v>0.05570461590378402</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04306813503610204</v>
+        <v>0.04306813503610202</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05842937812029027</v>
+        <v>0.05842937812029035</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05802986834533105</v>
+        <v>0.05802986834533099</v>
       </c>
       <c r="I6" t="n">
         <v>0.06069533746601854</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05803344327535723</v>
+        <v>0.05803344327535722</v>
       </c>
       <c r="K6" t="n">
         <v>0.03950138593298866</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07703145331900602</v>
+        <v>0.0770314533190061</v>
       </c>
     </row>
     <row r="7">
@@ -3091,37 +3091,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0704988802954504</v>
+        <v>0.07049888029545048</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08684277913777577</v>
+        <v>0.08684277913777572</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08689546288259734</v>
+        <v>0.08689546288259732</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1084821984347044</v>
+        <v>0.1084821984347045</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08956089823516407</v>
+        <v>0.08956089823516415</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08729502300779216</v>
+        <v>0.0872950230077922</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08689551323167126</v>
+        <v>0.08689551323167127</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08956098235352039</v>
+        <v>0.0895609823535204</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08689551323167126</v>
+        <v>0.08689551323167127</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06624923862573885</v>
+        <v>0.07739521853725675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08689551323167126</v>
+        <v>0.08689551323167127</v>
       </c>
     </row>
     <row r="8">
@@ -3131,13 +3131,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.006351056312792684</v>
+        <v>-0.006351056312792689</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9332419448808507</v>
+        <v>0.9332419448808508</v>
       </c>
       <c r="D8" t="n">
-        <v>1.062223480073339</v>
+        <v>1.062223480073341</v>
       </c>
       <c r="E8" t="n">
         <v>1.042438151930787</v>
@@ -3146,7 +3146,7 @@
         <v>1.042438151930787</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5370662490239764</v>
+        <v>0.5370662490239768</v>
       </c>
       <c r="H8" t="n">
         <v>0.9397181918161982</v>
@@ -3155,10 +3155,10 @@
         <v>1.042438151930787</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6326566563487815</v>
+        <v>0.6326566563487834</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7402823315297559</v>
+        <v>0.7402823315297554</v>
       </c>
       <c r="L8" t="n">
         <v>1.202664089661443</v>
@@ -3171,19 +3171,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01332405639739617</v>
+        <v>0.0133240563973962</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9211702470162508</v>
+        <v>0.9211702470162513</v>
       </c>
       <c r="D9" t="n">
-        <v>1.068149755253655</v>
+        <v>1.068149755253656</v>
       </c>
       <c r="E9" t="n">
-        <v>1.039273161791285</v>
+        <v>1.039273161791286</v>
       </c>
       <c r="F9" t="n">
-        <v>1.039273161791285</v>
+        <v>1.039273161791286</v>
       </c>
       <c r="G9" t="n">
         <v>0.545971823772437</v>
@@ -3192,13 +3192,13 @@
         <v>1.018403523625264</v>
       </c>
       <c r="I9" t="n">
-        <v>1.039273161791285</v>
+        <v>1.039273161791286</v>
       </c>
       <c r="J9" t="n">
-        <v>0.654367478746804</v>
+        <v>0.6543674787468047</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7420201222058008</v>
+        <v>0.742020122205801</v>
       </c>
       <c r="L9" t="n">
         <v>1.185934405794514</v>
@@ -3287,37 +3287,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6193486447824766</v>
+        <v>0.6193486447824748</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08531576319712454</v>
+        <v>0.08531576319712451</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563254771769568</v>
+        <v>1.563254771769569</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2655385165724852</v>
+        <v>0.2655385165724848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2655385165724852</v>
+        <v>0.2655385165724848</v>
       </c>
       <c r="G2" t="n">
         <v>0.7675489936075058</v>
       </c>
       <c r="H2" t="n">
-        <v>5.387212611858693</v>
+        <v>5.387212611858689</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2655385165724852</v>
+        <v>0.2655385165724848</v>
       </c>
       <c r="J2" t="n">
-        <v>1.326804953757652</v>
+        <v>1.326804953757654</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2474445491499483</v>
+        <v>0.2474445491499484</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05347117959582267</v>
+        <v>0.0534711795958223</v>
       </c>
     </row>
     <row r="3">
@@ -3327,37 +3327,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01332421253608821</v>
+        <v>0.01332421253608602</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01086114650649174</v>
+        <v>0.01086114650649175</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01332421253608821</v>
+        <v>0.01332421253608602</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01484128469186276</v>
+        <v>0.01484128469186279</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01484128469186276</v>
+        <v>0.01484128469186279</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01371750154849006</v>
+        <v>0.01371750154848801</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01332421253608821</v>
+        <v>0.01332421253608602</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01594984727540628</v>
+        <v>0.01594984727540543</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01332421253608821</v>
+        <v>0.01332421253608602</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01332421253608821</v>
+        <v>0.01332421253608602</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01332421253608821</v>
+        <v>0.01332421253608602</v>
       </c>
     </row>
     <row r="4">
@@ -3367,7 +3367,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.24868512641651</v>
+        <v>38.24868512641653</v>
       </c>
       <c r="C4" t="n">
         <v>10.05966368285087</v>
@@ -3376,28 +3376,28 @@
         <v>10.06302574457075</v>
       </c>
       <c r="E4" t="n">
-        <v>6.199168189685284</v>
+        <v>6.199168189685286</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06373003164411</v>
+        <v>10.06373003164412</v>
       </c>
       <c r="G4" t="n">
-        <v>38.24907841542891</v>
+        <v>38.24907841542894</v>
       </c>
       <c r="H4" t="n">
-        <v>38.25960984112437</v>
+        <v>10.06298267085956</v>
       </c>
       <c r="I4" t="n">
-        <v>10.06396029237373</v>
+        <v>38.25131076115587</v>
       </c>
       <c r="J4" t="n">
-        <v>38.25179088188035</v>
+        <v>10.57276221746122</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06029716798881</v>
+        <v>10.06029716798885</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06112023974037</v>
+        <v>10.06112023974036</v>
       </c>
     </row>
     <row r="5">
@@ -3407,37 +3407,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02247479205166924</v>
+        <v>0.02247479205166843</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02243501344126068</v>
+        <v>0.02243501344126069</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02247467076796004</v>
+        <v>0.02247467076795894</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0249084976691289</v>
+        <v>0.02490849766912896</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0249084976691289</v>
+        <v>0.02490849766912896</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02286808106406996</v>
+        <v>0.02286808106406913</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02247479205166924</v>
+        <v>0.02247479205166843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02510042679098624</v>
+        <v>0.02510042679098631</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02247479205166924</v>
+        <v>0.02247479205166843</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02247479205166924</v>
+        <v>0.02247479205166843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02247479205166924</v>
+        <v>0.02247479205166843</v>
       </c>
     </row>
     <row r="6">
@@ -3447,37 +3447,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03155308579073192</v>
+        <v>0.0315530857907317</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04609344622136509</v>
+        <v>0.04609344622166026</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04937448635881024</v>
+        <v>0.0493744863588099</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04474112995114234</v>
+        <v>0.04474112995114232</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0345321885648315</v>
+        <v>0.03453218856483153</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04670705266288316</v>
+        <v>0.04670705266288323</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04631376365210731</v>
+        <v>0.04631376365210672</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04893939838979957</v>
+        <v>0.04893939838979951</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04631666450568742</v>
+        <v>0.04631666450568539</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03127889862500829</v>
+        <v>0.03127889862500743</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06173252590420994</v>
+        <v>0.06173252590421061</v>
       </c>
     </row>
     <row r="7">
@@ -3487,37 +3487,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04986325935653554</v>
+        <v>0.04986325935653482</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06131192922032586</v>
+        <v>0.06131192922032595</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06135166835388565</v>
+        <v>0.0613516683538856</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07723465117822492</v>
+        <v>0.07723465117822551</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06397727724976104</v>
+        <v>0.06397727724976111</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06174499684313501</v>
+        <v>0.06174499684313488</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06135170783073431</v>
+        <v>0.06135170783073312</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0639773425700515</v>
+        <v>0.06397734257005151</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06135170783073431</v>
+        <v>0.06135170783073312</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05442517931767193</v>
+        <v>0.05469523906235971</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06135170783073431</v>
+        <v>0.06135170783073312</v>
       </c>
     </row>
     <row r="8">
@@ -3527,34 +3527,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.00895510195585422</v>
+        <v>0.008955101955853967</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9348323752604306</v>
+        <v>0.9348323752604311</v>
       </c>
       <c r="D8" t="n">
-        <v>1.058479422140232</v>
+        <v>1.058479422140231</v>
       </c>
       <c r="E8" t="n">
-        <v>1.056780367294897</v>
+        <v>1.056780367294898</v>
       </c>
       <c r="F8" t="n">
-        <v>1.056780367294897</v>
+        <v>1.056780367294898</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5463704478814925</v>
+        <v>0.546370447881492</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9806728201718673</v>
+        <v>0.9806728201718665</v>
       </c>
       <c r="I8" t="n">
-        <v>1.056780367294897</v>
+        <v>1.056780367294898</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6534358120997124</v>
+        <v>0.6534358120997118</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7565597770485626</v>
+        <v>0.7565597770485621</v>
       </c>
       <c r="L8" t="n">
         <v>1.203235028977705</v>
@@ -3567,13 +3567,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01716248127608208</v>
+        <v>0.01716248127608194</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9212673145918675</v>
+        <v>0.9212673145918687</v>
       </c>
       <c r="D9" t="n">
-        <v>1.063815374991317</v>
+        <v>1.063815374991318</v>
       </c>
       <c r="E9" t="n">
         <v>1.043793790260949</v>
@@ -3582,7 +3582,7 @@
         <v>1.043793790260949</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5482024652082261</v>
+        <v>0.5482024652082256</v>
       </c>
       <c r="H9" t="n">
         <v>1.032232027756985</v>
@@ -3591,13 +3591,13 @@
         <v>1.043793790260949</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6608554852011878</v>
+        <v>0.6608554852011882</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7480811145937166</v>
+        <v>0.7480811145937164</v>
       </c>
       <c r="L9" t="n">
-        <v>1.184964208803501</v>
+        <v>1.1849642088035</v>
       </c>
     </row>
   </sheetData>
@@ -3683,37 +3683,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.903588045814501</v>
+        <v>2.903588045814502</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4084694818238299</v>
+        <v>0.4084694818240382</v>
       </c>
       <c r="D2" t="n">
-        <v>1.90118349154802</v>
+        <v>1.901183491548013</v>
       </c>
       <c r="E2" t="n">
-        <v>2.32630959540825</v>
+        <v>2.326309595408255</v>
       </c>
       <c r="F2" t="n">
-        <v>2.32630959540825</v>
+        <v>2.326309595408255</v>
       </c>
       <c r="G2" t="n">
         <v>2.082457240133768</v>
       </c>
       <c r="H2" t="n">
-        <v>5.208858633866038</v>
+        <v>5.208858633866049</v>
       </c>
       <c r="I2" t="n">
-        <v>2.32630959540825</v>
+        <v>2.326309595408255</v>
       </c>
       <c r="J2" t="n">
-        <v>4.83002542245891</v>
+        <v>4.830025422458882</v>
       </c>
       <c r="K2" t="n">
-        <v>2.437459202341746</v>
+        <v>2.437459202341776</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3872807613629927</v>
+        <v>0.3872807613629943</v>
       </c>
     </row>
     <row r="3">
@@ -3723,37 +3723,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02260284929879032</v>
+        <v>0.02260284929879109</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02004352652127637</v>
+        <v>0.02004352652127579</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02260284929879032</v>
+        <v>0.02260284929879109</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02549397725209235</v>
+        <v>0.02549397725209251</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02549397725209235</v>
+        <v>0.02549397725209237</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0230236175558412</v>
+        <v>0.02302361755584194</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02260284929879032</v>
+        <v>0.02260284929879109</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0254050955746499</v>
+        <v>0.02540509557464984</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02260284929879032</v>
+        <v>0.02260284929879109</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02260284929879032</v>
+        <v>0.02260284929879109</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02260284929879032</v>
+        <v>0.02260284929879109</v>
       </c>
     </row>
     <row r="4">
@@ -3763,7 +3763,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.63706173772527</v>
+        <v>10.63706173772528</v>
       </c>
       <c r="C4" t="n">
         <v>10.63311733651147</v>
@@ -3772,25 +3772,25 @@
         <v>10.63632282083305</v>
       </c>
       <c r="E4" t="n">
-        <v>6.560466596381143</v>
+        <v>6.560466596381139</v>
       </c>
       <c r="F4" t="n">
-        <v>10.63972474771523</v>
+        <v>10.63972474771522</v>
       </c>
       <c r="G4" t="n">
-        <v>40.40237141708314</v>
+        <v>10.63748250598233</v>
       </c>
       <c r="H4" t="n">
-        <v>40.40751802543393</v>
+        <v>40.40751802543394</v>
       </c>
       <c r="I4" t="n">
-        <v>40.40475289510195</v>
+        <v>10.63986398400113</v>
       </c>
       <c r="J4" t="n">
-        <v>40.40494562313336</v>
+        <v>11.17769233324638</v>
       </c>
       <c r="K4" t="n">
-        <v>10.63736301050355</v>
+        <v>10.63736301050364</v>
       </c>
       <c r="L4" t="n">
         <v>10.63621422948431</v>
@@ -3803,37 +3803,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03891972187444628</v>
+        <v>0.03891972187444868</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0388530602354427</v>
+        <v>0.03885306023544322</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03891931420915939</v>
+        <v>0.03891931420916211</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04171587181477542</v>
+        <v>0.04171587181477568</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04171587181477542</v>
+        <v>0.04171587181477568</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03934049013149581</v>
+        <v>0.03934049013149771</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03891972187444628</v>
+        <v>0.03891972187444868</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04172196815030496</v>
+        <v>0.04172196815030613</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03891972187444628</v>
+        <v>0.03891972187444868</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03891972187444628</v>
+        <v>0.03891972187444868</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03891972187444628</v>
+        <v>0.03891972187444868</v>
       </c>
     </row>
     <row r="6">
@@ -3843,37 +3843,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05265008667581751</v>
+        <v>0.05265008667581928</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07617142182058111</v>
+        <v>0.07617142182000543</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08113010532540683</v>
+        <v>0.08113010532540618</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07258905192205385</v>
+        <v>0.07258905192205346</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05619666603736666</v>
+        <v>0.05619666603736594</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07665959472338439</v>
+        <v>0.07665959472338625</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07623882646647655</v>
+        <v>0.07623882646647676</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07904107274219344</v>
+        <v>0.0790410727421933</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07624346228576744</v>
+        <v>0.07624346228576803</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05221191372747489</v>
+        <v>0.05221191372747634</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1008792375954437</v>
+        <v>0.1008792375954451</v>
       </c>
     </row>
     <row r="7">
@@ -3883,37 +3883,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1085880407449879</v>
+        <v>0.1085880407449913</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1342583812848698</v>
+        <v>0.1342583812848738</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1343250488253635</v>
+        <v>0.1343250488253642</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1668272028688207</v>
+        <v>0.1668272028688214</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1371272520256716</v>
+        <v>0.1371272520256708</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1347458111809229</v>
+        <v>0.1347458111809214</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1343250429238728</v>
+        <v>0.1343250429238758</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1371272891997321</v>
+        <v>0.1371272891997294</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1343250429238728</v>
+        <v>0.1343250429238758</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1194129252665656</v>
+        <v>0.1194129252665668</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1343250429238728</v>
+        <v>0.1343250429238758</v>
       </c>
     </row>
     <row r="8">
@@ -3923,37 +3923,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03009455303866835</v>
+        <v>-0.03009455303866786</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9275379268549532</v>
+        <v>0.9275379268549314</v>
       </c>
       <c r="D8" t="n">
         <v>1.06575585492323</v>
       </c>
       <c r="E8" t="n">
-        <v>1.017908776610086</v>
+        <v>1.017908776610085</v>
       </c>
       <c r="F8" t="n">
-        <v>1.017908776610086</v>
+        <v>1.017908776610085</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5250976296088525</v>
+        <v>0.5250976296088534</v>
       </c>
       <c r="H8" t="n">
         <v>1.003481752851723</v>
       </c>
       <c r="I8" t="n">
-        <v>1.017908776610086</v>
+        <v>1.017908776610085</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5871306634276962</v>
+        <v>0.5871306634276954</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7147006373500354</v>
+        <v>0.7147006373500369</v>
       </c>
       <c r="L8" t="n">
-        <v>1.201517651756433</v>
+        <v>1.201517651756434</v>
       </c>
     </row>
     <row r="9">
@@ -3963,19 +3963,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.007732092404525104</v>
+        <v>0.007732092404525686</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9181506980715427</v>
+        <v>0.9181506980715444</v>
       </c>
       <c r="D9" t="n">
         <v>1.074251903882499</v>
       </c>
       <c r="E9" t="n">
-        <v>1.032478963231196</v>
+        <v>1.032478963231195</v>
       </c>
       <c r="F9" t="n">
-        <v>1.032478963231196</v>
+        <v>1.032478963231195</v>
       </c>
       <c r="G9" t="n">
         <v>0.5436703270668851</v>
@@ -3984,13 +3984,13 @@
         <v>1.048985464522121</v>
       </c>
       <c r="I9" t="n">
-        <v>1.032478963231196</v>
+        <v>1.032478963231195</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6389694023106245</v>
+        <v>0.6389694023106239</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7357100914785096</v>
+        <v>0.7357100914785099</v>
       </c>
       <c r="L9" t="n">
         <v>1.187036240809044</v>
@@ -4085,31 +4085,31 @@
         <v>0.1858525524607738</v>
       </c>
       <c r="D2" t="n">
-        <v>1.907896124115106</v>
+        <v>1.907896124115105</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8609165703685415</v>
+        <v>0.8609165703685506</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8609165703685415</v>
+        <v>0.8609165703685506</v>
       </c>
       <c r="G2" t="n">
-        <v>1.344311576691635</v>
+        <v>1.344311576691634</v>
       </c>
       <c r="H2" t="n">
-        <v>6.768073975336796</v>
+        <v>6.768073975336802</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8609165703685415</v>
+        <v>0.8609165703685506</v>
       </c>
       <c r="J2" t="n">
-        <v>2.410709824575229</v>
+        <v>2.410709824575246</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9221026410195751</v>
+        <v>0.9221026410195748</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09165518102479145</v>
+        <v>0.09165518102479177</v>
       </c>
     </row>
     <row r="3">
@@ -4119,37 +4119,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01625240095023286</v>
+        <v>0.01625240095023283</v>
       </c>
       <c r="C3" t="n">
         <v>0.01409420903199882</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01625240095023286</v>
+        <v>0.01625240095023283</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01833310666165951</v>
+        <v>0.01833310666165957</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01833310666165951</v>
+        <v>0.01833310666165957</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01664464177856842</v>
+        <v>0.0166446417785684</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01625240095023286</v>
+        <v>0.01625240095023283</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01887088041350175</v>
+        <v>0.01887088041350181</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01625240095023286</v>
+        <v>0.01625240095023283</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01625240095023286</v>
+        <v>0.01625240095023283</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01625240095023286</v>
+        <v>0.01625240095023283</v>
       </c>
     </row>
     <row r="4">
@@ -4159,16 +4159,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.06619825122398</v>
+        <v>38.25595536183861</v>
       </c>
       <c r="C4" t="n">
-        <v>10.06366660257708</v>
+        <v>10.06366660257707</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06741466619206</v>
+        <v>10.06741468470701</v>
       </c>
       <c r="E4" t="n">
-        <v>6.204071161583099</v>
+        <v>6.204071161583109</v>
       </c>
       <c r="F4" t="n">
         <v>10.06858293632509</v>
@@ -4180,10 +4180,10 @@
         <v>38.26463625788895</v>
       </c>
       <c r="I4" t="n">
-        <v>38.25857384130192</v>
+        <v>38.2585738413019</v>
       </c>
       <c r="J4" t="n">
-        <v>38.25889806978539</v>
+        <v>10.57780145636981</v>
       </c>
       <c r="K4" t="n">
         <v>10.06539271149165</v>
@@ -4199,37 +4199,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02800423446109355</v>
+        <v>0.02800423446109353</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02794776033556164</v>
+        <v>0.02794776033556162</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02800395386373685</v>
+        <v>0.02800395386373675</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03058064580641452</v>
+        <v>0.03058064580641449</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03058064580641452</v>
+        <v>0.03058064580641449</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02839647528942908</v>
+        <v>0.02839647528942901</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02800423446109355</v>
+        <v>0.02800423446109353</v>
       </c>
       <c r="I5" t="n">
         <v>0.03062271392436247</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02800423446109355</v>
+        <v>0.02800423446109353</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02800423446109355</v>
+        <v>0.02800423446109353</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02800423446109355</v>
+        <v>0.02800423446109353</v>
       </c>
     </row>
     <row r="6">
@@ -4239,37 +4239,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03866510511751956</v>
+        <v>0.0386651051175196</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05627640661567937</v>
+        <v>0.05627640661567934</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06004041127091832</v>
+        <v>0.06004041127091824</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0541132558337986</v>
+        <v>0.05411325583379857</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04181985277557746</v>
+        <v>0.04181985277557752</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05676156661387892</v>
+        <v>0.05676156661387888</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0563693257866351</v>
+        <v>0.05636932578663498</v>
       </c>
       <c r="I6" t="n">
         <v>0.05898780524881234</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05637280513635754</v>
+        <v>0.05637280513635753</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03833624013238678</v>
+        <v>0.03833624013238672</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07486286464286532</v>
+        <v>0.07486286464286522</v>
       </c>
     </row>
     <row r="7">
@@ -4279,37 +4279,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07035035118135369</v>
+        <v>0.07035035118135363</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0867624560229293</v>
+        <v>0.08676245602292938</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08681889185840864</v>
+        <v>0.08681889185840862</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1084416721572395</v>
+        <v>0.1084416721572396</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08943733458864156</v>
+        <v>0.08943733458864159</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08721117097679679</v>
+        <v>0.08721117097679668</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08681893014846126</v>
+        <v>0.08681893014846137</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08943740961173012</v>
+        <v>0.0894374096117303</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08681893014846126</v>
+        <v>0.08681893014846137</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07727695471317418</v>
+        <v>0.06608205952188254</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08681893014846126</v>
+        <v>0.08681893014846137</v>
       </c>
     </row>
     <row r="8">
@@ -4319,37 +4319,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.068177539190944e-05</v>
+        <v>7.068177539187729e-05</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9266588446536171</v>
+        <v>0.9266588446536187</v>
       </c>
       <c r="D8" t="n">
-        <v>1.054111737153135</v>
+        <v>1.054111737153136</v>
       </c>
       <c r="E8" t="n">
-        <v>1.041135607516666</v>
+        <v>1.041135607516667</v>
       </c>
       <c r="F8" t="n">
-        <v>1.041135607516666</v>
+        <v>1.041135607516667</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5338960657418261</v>
+        <v>0.5338960657418269</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9549930739582034</v>
+        <v>0.9549930739582049</v>
       </c>
       <c r="I8" t="n">
-        <v>1.041135607516666</v>
+        <v>1.041135607516667</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6310906603318256</v>
+        <v>0.6310906603318258</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7327277562699422</v>
+        <v>0.7327277562699415</v>
       </c>
       <c r="L8" t="n">
-        <v>1.204161003984842</v>
+        <v>1.204161003984844</v>
       </c>
     </row>
     <row r="9">
@@ -4359,34 +4359,34 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.01831245886937309</v>
+        <v>0.0183124588693731</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9145724532691989</v>
+        <v>0.9145724532692006</v>
       </c>
       <c r="D9" t="n">
-        <v>1.064341306760499</v>
+        <v>1.0643413067605</v>
       </c>
       <c r="E9" t="n">
-        <v>1.036666090129655</v>
+        <v>1.036666090129656</v>
       </c>
       <c r="F9" t="n">
-        <v>1.036666090129655</v>
+        <v>1.036666090129656</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5437824107084048</v>
+        <v>0.5437824107084062</v>
       </c>
       <c r="H9" t="n">
-        <v>1.024105093269191</v>
+        <v>1.024105093269192</v>
       </c>
       <c r="I9" t="n">
-        <v>1.036666090129655</v>
+        <v>1.036666090129656</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6533329580106739</v>
+        <v>0.6533329580106743</v>
       </c>
       <c r="K9" t="n">
-        <v>0.734054833380508</v>
+        <v>0.7340548333805075</v>
       </c>
       <c r="L9" t="n">
         <v>1.18631896876919</v>
@@ -4478,34 +4478,34 @@
         <v>0.6258312111887093</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0893472828183547</v>
+        <v>0.08934728281835455</v>
       </c>
       <c r="D2" t="n">
-        <v>2.02152437665848</v>
+        <v>2.021524376658474</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2379512882338541</v>
+        <v>0.2379512882338538</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2379512882338541</v>
+        <v>0.2379512882338538</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9111029128113961</v>
+        <v>0.9111029128113936</v>
       </c>
       <c r="H2" t="n">
-        <v>5.144967367735346</v>
+        <v>5.144967367735338</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2379512882338541</v>
+        <v>0.2379512882338538</v>
       </c>
       <c r="J2" t="n">
-        <v>1.330752135447428</v>
+        <v>1.330752135447426</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3214102268436434</v>
+        <v>0.321410226843643</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0525278935793954</v>
+        <v>0.05252789357939559</v>
       </c>
     </row>
     <row r="3">
@@ -4515,37 +4515,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01221439674909703</v>
+        <v>0.01221439674909712</v>
       </c>
       <c r="C3" t="n">
         <v>0.01030537846684926</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01221439674909703</v>
+        <v>0.01221439674909712</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01405528082489355</v>
+        <v>0.0140552808248935</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01405528082489355</v>
+        <v>0.01405528082489351</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01260191082459668</v>
+        <v>0.01260191082459674</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01221439674909703</v>
+        <v>0.01221439674909712</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01480246003620344</v>
+        <v>0.0148024600362034</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01221439674909703</v>
+        <v>0.01221439674909712</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01221439674909703</v>
+        <v>0.01221439674909712</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01221439674909703</v>
+        <v>0.01221439674909712</v>
       </c>
     </row>
     <row r="4">
@@ -4555,31 +4555,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.0598350329816</v>
+        <v>38.24695118691499</v>
       </c>
       <c r="C4" t="n">
-        <v>10.0581044605412</v>
+        <v>10.05810446054121</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06226369987075</v>
+        <v>10.06226365870364</v>
       </c>
       <c r="E4" t="n">
-        <v>6.19759785335435</v>
+        <v>6.197597853354351</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06218488854183</v>
+        <v>10.06218488854184</v>
       </c>
       <c r="G4" t="n">
-        <v>38.24733870099047</v>
+        <v>10.06022254705711</v>
       </c>
       <c r="H4" t="n">
         <v>38.25584543195808</v>
       </c>
       <c r="I4" t="n">
-        <v>38.24953925020208</v>
+        <v>10.06242309626871</v>
       </c>
       <c r="J4" t="n">
-        <v>10.57114604361334</v>
+        <v>38.24980529410128</v>
       </c>
       <c r="K4" t="n">
         <v>10.05882312085034</v>
@@ -4595,37 +4595,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02119495556216839</v>
+        <v>0.02119495556216843</v>
       </c>
       <c r="C5" t="n">
         <v>0.02115058194702734</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02119474028107255</v>
+        <v>0.02119474028107287</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02372058752173421</v>
+        <v>0.02372058752173419</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02372058752173421</v>
+        <v>0.02372058752173419</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02158246963766802</v>
+        <v>0.02158246963766814</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02119495556216839</v>
+        <v>0.02119495556216843</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0237830188492748</v>
+        <v>0.02378301884927476</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02119495556216839</v>
+        <v>0.02119495556216843</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02119495556216839</v>
+        <v>0.02119495556216843</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02119495556216839</v>
+        <v>0.02119495556216843</v>
       </c>
     </row>
     <row r="6">
@@ -4635,37 +4635,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02972826793381212</v>
+        <v>0.02972826793381217</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04337955503036442</v>
+        <v>0.04337955503011665</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04633236619459009</v>
+        <v>0.04633236619459007</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0422568413999982</v>
+        <v>0.04225684139999807</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03271514746374007</v>
+        <v>0.03271514746374001</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04386822220789152</v>
+        <v>0.04386822220789166</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04348070813369643</v>
+        <v>0.04348070813369653</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04606877141949827</v>
+        <v>0.04606877141949823</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04348341085489444</v>
+        <v>0.04348341085489441</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02947280929887027</v>
+        <v>0.02947280929887023</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05784628185576882</v>
+        <v>0.05784628185576892</v>
       </c>
     </row>
     <row r="7">
@@ -4675,37 +4675,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05073142147480258</v>
+        <v>0.05073142147480265</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06248140727273713</v>
+        <v>0.06248140727273711</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06252574872874637</v>
+        <v>0.06252574872874629</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07872417828798382</v>
+        <v>0.07872417828798367</v>
       </c>
       <c r="F7" t="n">
         <v>0.06511378217682208</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06291329496337779</v>
+        <v>0.0629132949633778</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06252578088787814</v>
+        <v>0.06252578088787827</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06511384417498457</v>
+        <v>0.06511384417498449</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06252578088787814</v>
+        <v>0.06252578088787827</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05541481818711948</v>
+        <v>0.05541481818711971</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06252578088787814</v>
+        <v>0.06252578088787827</v>
       </c>
     </row>
     <row r="8">
@@ -4715,34 +4715,34 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01759237189909972</v>
+        <v>0.01759237189909983</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9249606572598369</v>
+        <v>0.924960657259836</v>
       </c>
       <c r="D8" t="n">
         <v>1.046047538484215</v>
       </c>
       <c r="E8" t="n">
-        <v>1.054802856206777</v>
+        <v>1.054802856206776</v>
       </c>
       <c r="F8" t="n">
-        <v>1.054802856206777</v>
+        <v>1.054802856206776</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5419211879297843</v>
+        <v>0.5419211879297839</v>
       </c>
       <c r="H8" t="n">
-        <v>0.98463566369194</v>
+        <v>0.9846356636919389</v>
       </c>
       <c r="I8" t="n">
-        <v>1.054802856206777</v>
+        <v>1.054802856206776</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6513777839982461</v>
+        <v>0.6513777839982445</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7495683907234063</v>
+        <v>0.7495683907234059</v>
       </c>
       <c r="L8" t="n">
         <v>1.202557810122987</v>
@@ -4755,37 +4755,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02575675300807703</v>
+        <v>0.0257567530080771</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9116079363732325</v>
+        <v>0.9116079363732333</v>
       </c>
       <c r="D9" t="n">
-        <v>1.058033778695846</v>
+        <v>1.058033778695844</v>
       </c>
       <c r="E9" t="n">
-        <v>1.04146507843502</v>
+        <v>1.041465078435019</v>
       </c>
       <c r="F9" t="n">
-        <v>1.04146507843502</v>
+        <v>1.041465078435019</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5457881099931733</v>
+        <v>0.5457881099931725</v>
       </c>
       <c r="H9" t="n">
-        <v>1.033122785933239</v>
+        <v>1.033122785933238</v>
       </c>
       <c r="I9" t="n">
-        <v>1.04146507843502</v>
+        <v>1.041465078435019</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6588854230065737</v>
+        <v>0.6588854230065724</v>
       </c>
       <c r="K9" t="n">
-        <v>0.742239412336216</v>
+        <v>0.7422394123362154</v>
       </c>
       <c r="L9" t="n">
-        <v>1.184288755447979</v>
+        <v>1.184288755447981</v>
       </c>
     </row>
   </sheetData>
@@ -4871,37 +4871,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1242535799683244</v>
+        <v>0.1242535799683379</v>
       </c>
       <c r="C2" t="n">
-        <v>4.335246877166784</v>
+        <v>4.335246877166773</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9368530088032229</v>
+        <v>0.9368530088032224</v>
       </c>
       <c r="E2" t="n">
-        <v>4.335246877166784</v>
+        <v>4.335246877166773</v>
       </c>
       <c r="F2" t="n">
-        <v>4.335246877166784</v>
+        <v>4.335246877166773</v>
       </c>
       <c r="G2" t="n">
-        <v>2.39038460110791</v>
+        <v>2.390384601107914</v>
       </c>
       <c r="H2" t="n">
-        <v>1.599038994266163</v>
+        <v>1.599038994266162</v>
       </c>
       <c r="I2" t="n">
-        <v>4.335246877166784</v>
+        <v>4.335246877166773</v>
       </c>
       <c r="J2" t="n">
-        <v>7.352009281699722</v>
+        <v>7.352009281699717</v>
       </c>
       <c r="K2" t="n">
-        <v>4.390613384984459</v>
+        <v>4.390613384984458</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2448958427016453</v>
+        <v>0.2448958427016479</v>
       </c>
     </row>
     <row r="3">
@@ -4911,13 +4911,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03286033572997875</v>
+        <v>0.03286033572997978</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03853912356884832</v>
+        <v>0.03853912356884831</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03286033572997875</v>
+        <v>0.03286033572997978</v>
       </c>
       <c r="E3" t="n">
         <v>0.03891417067751818</v>
@@ -4926,22 +4926,22 @@
         <v>0.03891417067751818</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03348318142957708</v>
+        <v>0.03348318142957755</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03286033572997875</v>
+        <v>0.03286033572997978</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03698975519013432</v>
+        <v>0.03698975519013429</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03286033572997875</v>
+        <v>0.03286033572997978</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03286033572997875</v>
+        <v>0.03286033572997978</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03286033572997875</v>
+        <v>0.03286033572997978</v>
       </c>
     </row>
     <row r="4">
@@ -4951,31 +4951,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.09062859625051</v>
+        <v>10.83272268775578</v>
       </c>
       <c r="C4" t="n">
         <v>10.83938926933231</v>
       </c>
       <c r="D4" t="n">
-        <v>10.8274428649973</v>
+        <v>10.82744273621123</v>
       </c>
       <c r="E4" t="n">
-        <v>6.692045131214753</v>
+        <v>6.692045131214747</v>
       </c>
       <c r="F4" t="n">
         <v>10.83663604753641</v>
       </c>
       <c r="G4" t="n">
-        <v>41.09125144195009</v>
+        <v>10.83334553345539</v>
       </c>
       <c r="H4" t="n">
-        <v>41.09340021470117</v>
+        <v>41.09340021470116</v>
       </c>
       <c r="I4" t="n">
-        <v>41.09475801571062</v>
+        <v>41.09475801571061</v>
       </c>
       <c r="J4" t="n">
-        <v>41.09276858809034</v>
+        <v>11.38236566917724</v>
       </c>
       <c r="K4" t="n">
         <v>10.83458287117105</v>
@@ -4991,13 +4991,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05149071663393541</v>
+        <v>0.05149071663393531</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05562013609409087</v>
+        <v>0.05562013609409085</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05148979519241358</v>
+        <v>0.05148979519241421</v>
       </c>
       <c r="E5" t="n">
         <v>0.05573271982539228</v>
@@ -5006,22 +5006,22 @@
         <v>0.05573271982539228</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05211356233353367</v>
+        <v>0.05211356233353392</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05149071663393541</v>
+        <v>0.05149071663393531</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05562013609409087</v>
+        <v>0.05562013609409085</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05149071663393541</v>
+        <v>0.05149071663393531</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05149071663393541</v>
+        <v>0.05149071663393531</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05149071663393541</v>
+        <v>0.05149071663393531</v>
       </c>
     </row>
     <row r="6">
@@ -5031,37 +5031,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0658937761644619</v>
+        <v>0.06589377616446201</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0956598758592698</v>
+        <v>0.09565987585986832</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09670911016675443</v>
+        <v>0.09670911016675478</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08866738043474931</v>
+        <v>0.08866738043474927</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07089994599368514</v>
+        <v>0.07089994599368507</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09203960007156232</v>
+        <v>0.0920396000715626</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09141675437198012</v>
+        <v>0.09141675437198074</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0955461738321194</v>
+        <v>0.09554617383211937</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09142177032601952</v>
+        <v>0.09142177032601977</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06541967374432818</v>
+        <v>0.06541967374432821</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1180776392669887</v>
+        <v>0.1180776392669884</v>
       </c>
     </row>
     <row r="7">
@@ -5071,37 +5071,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1448418153880123</v>
+        <v>0.1448418153880118</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1819136488488363</v>
+        <v>0.1819136488488362</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1777842634854175</v>
+        <v>0.1777842634854177</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2199285383526052</v>
+        <v>0.2199285383526051</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1819136579818529</v>
+        <v>0.1819136579818527</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1784070750882793</v>
+        <v>0.1784070750882794</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1777842293886813</v>
+        <v>0.1777842293886806</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1819136488488363</v>
+        <v>0.1819136488488362</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1777842293886813</v>
+        <v>0.1777842293886806</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1586972796828059</v>
+        <v>0.1586972796828053</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1777842293886813</v>
+        <v>0.1777842293886806</v>
       </c>
     </row>
     <row r="8">
@@ -5111,37 +5111,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6258330838306557</v>
+        <v>0.6258330838306558</v>
       </c>
       <c r="C8" t="n">
-        <v>1.004828651558832</v>
+        <v>1.004828651558831</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6070238678615877</v>
+        <v>0.6070238678615881</v>
       </c>
       <c r="E8" t="n">
-        <v>1.004828651558832</v>
+        <v>1.004828651558831</v>
       </c>
       <c r="F8" t="n">
-        <v>1.004828651558832</v>
+        <v>1.004828651558831</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5750517474769324</v>
+        <v>0.5750517474769316</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5959691628935057</v>
+        <v>0.5959691628935053</v>
       </c>
       <c r="I8" t="n">
-        <v>1.004828651558832</v>
+        <v>1.004828651558831</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4692080935396272</v>
+        <v>0.4692080935396263</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5272043066063178</v>
+        <v>0.5272043066063189</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6235578974287787</v>
+        <v>0.6235578974287782</v>
       </c>
     </row>
     <row r="9">
@@ -5151,13 +5151,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6173756973265643</v>
+        <v>0.6173756973265633</v>
       </c>
       <c r="C9" t="n">
         <v>1.049793323130445</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6097153784107749</v>
+        <v>0.6097153784107746</v>
       </c>
       <c r="E9" t="n">
         <v>1.049793323130445</v>
@@ -5166,7 +5166,7 @@
         <v>1.049793323130445</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5969303968912687</v>
+        <v>0.5969303968912679</v>
       </c>
       <c r="H9" t="n">
         <v>0.60524208272249</v>
@@ -5175,13 +5175,13 @@
         <v>1.049793323130445</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5536438978862335</v>
+        <v>0.553643897886233</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5772101531688025</v>
+        <v>0.5772101531688018</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6164523036586739</v>
+        <v>0.6130175145416678</v>
       </c>
     </row>
   </sheetData>
@@ -5267,37 +5267,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2216838688477219</v>
+        <v>0.2216838688477199</v>
       </c>
       <c r="C2" t="n">
-        <v>2.991289698298492</v>
+        <v>2.991289698298489</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6912939597222554</v>
+        <v>0.6912939597222607</v>
       </c>
       <c r="E2" t="n">
-        <v>2.991289698298492</v>
+        <v>2.991289698298489</v>
       </c>
       <c r="F2" t="n">
-        <v>2.991289698298492</v>
+        <v>2.991289698298489</v>
       </c>
       <c r="G2" t="n">
-        <v>1.675699060304482</v>
+        <v>1.675699060304488</v>
       </c>
       <c r="H2" t="n">
-        <v>1.253194264488358</v>
+        <v>1.253194264488357</v>
       </c>
       <c r="I2" t="n">
-        <v>2.991289698298492</v>
+        <v>2.991289698298489</v>
       </c>
       <c r="J2" t="n">
-        <v>5.595391334199205</v>
+        <v>5.595391334199208</v>
       </c>
       <c r="K2" t="n">
-        <v>2.323498709889595</v>
+        <v>2.323498709889597</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2691355411526296</v>
+        <v>0.2691355411526308</v>
       </c>
     </row>
     <row r="3">
@@ -5307,37 +5307,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02608963641165016</v>
+        <v>0.02608963641165003</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03086377582055356</v>
+        <v>0.03086377582055355</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02608963641165018</v>
+        <v>0.02608963641164998</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03117960046540181</v>
+        <v>0.0311796004654018</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03117960046540181</v>
+        <v>0.0311796004654018</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02669227275840654</v>
+        <v>0.02669227275840677</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02608963641165018</v>
+        <v>0.02608963641164998</v>
       </c>
       <c r="I3" t="n">
         <v>0.03008975063229362</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02608963641165018</v>
+        <v>0.02608963641164998</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02608963641165018</v>
+        <v>0.02608963641164998</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02608963641165018</v>
+        <v>0.02608963641164998</v>
       </c>
     </row>
     <row r="4">
@@ -5347,7 +5347,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.27598029646879</v>
+        <v>10.08473798617769</v>
       </c>
       <c r="C4" t="n">
         <v>10.09087565353528</v>
@@ -5356,22 +5356,22 @@
         <v>10.08151434332728</v>
       </c>
       <c r="E4" t="n">
-        <v>6.226633046312212</v>
+        <v>6.226633046312207</v>
       </c>
       <c r="F4" t="n">
         <v>10.08895683983584</v>
       </c>
       <c r="G4" t="n">
-        <v>38.27658293281553</v>
+        <v>10.08534062252444</v>
       </c>
       <c r="H4" t="n">
-        <v>38.27851943556378</v>
+        <v>38.27851943556377</v>
       </c>
       <c r="I4" t="n">
-        <v>38.2799804106894</v>
+        <v>38.27998041068944</v>
       </c>
       <c r="J4" t="n">
-        <v>38.27794125299145</v>
+        <v>10.59713169718851</v>
       </c>
       <c r="K4" t="n">
         <v>10.08528050570703</v>
@@ -5387,37 +5387,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04013029783590195</v>
+        <v>0.04013029783590241</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04413041205654551</v>
+        <v>0.04413041205654553</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04012961342298866</v>
+        <v>0.0401296134229886</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04413962997381745</v>
+        <v>0.04413962997381746</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04413962997381745</v>
+        <v>0.04413962997381747</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04073293418265841</v>
+        <v>0.04073293418265831</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04013029783590197</v>
+        <v>0.04013029783590243</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04413041205654551</v>
+        <v>0.04413041205654553</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04013029783590197</v>
+        <v>0.04013029783590243</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04013029783590197</v>
+        <v>0.04013029783590243</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04013029783590197</v>
+        <v>0.04013029783590243</v>
       </c>
     </row>
     <row r="6">
@@ -5427,37 +5427,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05138307070738975</v>
+        <v>0.05138307070738996</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07489869032258917</v>
+        <v>0.07489869032258935</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07492910024976648</v>
+        <v>0.07492910024976657</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06956355650765257</v>
+        <v>0.06956355650765272</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05600727972928578</v>
+        <v>0.05600727972928588</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07148784189518237</v>
+        <v>0.07148784189518231</v>
       </c>
       <c r="H6" t="n">
-        <v>0.0708852055484647</v>
+        <v>0.07088520554846477</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07488531976906938</v>
+        <v>0.07488531976906948</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07088903824370425</v>
+        <v>0.0708890382437045</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05102080854314872</v>
+        <v>0.05102080854314871</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09125681610117378</v>
+        <v>0.0912568161011738</v>
       </c>
     </row>
     <row r="7">
@@ -5467,37 +5467,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1034727101087507</v>
+        <v>0.1034727101087511</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1303668325222637</v>
+        <v>0.130366832522264</v>
       </c>
       <c r="D7" t="n">
         <v>0.1263667378905635</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1567860513416711</v>
+        <v>0.1567860513416714</v>
       </c>
       <c r="F7" t="n">
-        <v>0.130366833392847</v>
+        <v>0.1303668333928473</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1269693546483768</v>
+        <v>0.126969354648377</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1263667183016202</v>
+        <v>0.1263667183016206</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1303668325222637</v>
+        <v>0.130366832522264</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1263667183016202</v>
+        <v>0.1263667183016206</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0975390703437556</v>
+        <v>0.1131018482819975</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1263667183016202</v>
+        <v>0.1263667183016206</v>
       </c>
     </row>
     <row r="8">
@@ -5510,34 +5510,34 @@
         <v>0.6173830557208828</v>
       </c>
       <c r="C8" t="n">
-        <v>1.024215407007019</v>
+        <v>1.02421540700702</v>
       </c>
       <c r="D8" t="n">
         <v>0.6054944507529557</v>
       </c>
       <c r="E8" t="n">
-        <v>1.024215407007019</v>
+        <v>1.02421540700702</v>
       </c>
       <c r="F8" t="n">
-        <v>1.024215407007019</v>
+        <v>1.02421540700702</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5820132784661662</v>
+        <v>0.582013278466166</v>
       </c>
       <c r="H8" t="n">
-        <v>0.595433285865996</v>
+        <v>0.5954332858659955</v>
       </c>
       <c r="I8" t="n">
-        <v>1.024215407007019</v>
+        <v>1.02421540700702</v>
       </c>
       <c r="J8" t="n">
-        <v>0.492702034651038</v>
+        <v>0.4927020346510382</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5613482875303408</v>
+        <v>0.5613482875303407</v>
       </c>
       <c r="L8" t="n">
-        <v>0.616853236219208</v>
+        <v>0.6168532362192076</v>
       </c>
     </row>
     <row r="9">
@@ -5547,13 +5547,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6106337838702204</v>
+        <v>0.6106337838702207</v>
       </c>
       <c r="C9" t="n">
         <v>1.053731453017323</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6057920756933013</v>
+        <v>0.6057920756933014</v>
       </c>
       <c r="E9" t="n">
         <v>1.053731453017323</v>
@@ -5562,7 +5562,7 @@
         <v>1.053731453017323</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5964040738226137</v>
+        <v>0.5964040738226128</v>
       </c>
       <c r="H9" t="n">
         <v>0.601718763383374</v>
@@ -5571,13 +5571,13 @@
         <v>1.053731453017323</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5599014292167077</v>
+        <v>0.5599014292167082</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5878144019125198</v>
+        <v>0.5878144019125203</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6104220317965737</v>
+        <v>0.6084880957322857</v>
       </c>
     </row>
   </sheetData>
@@ -5663,37 +5663,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3171117189433663</v>
+        <v>0.3171117189433773</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9117973034433594</v>
+        <v>0.9117973034435745</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7488213551010457</v>
+        <v>0.7488213551010512</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9117973034433594</v>
+        <v>0.9117973034435745</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9117973034433594</v>
+        <v>0.9117973034435745</v>
       </c>
       <c r="G2" t="n">
-        <v>1.343400349221434</v>
+        <v>1.343400349221445</v>
       </c>
       <c r="H2" t="n">
-        <v>2.591070816450765</v>
+        <v>2.591070816450771</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9117973034433594</v>
+        <v>0.9117973034435745</v>
       </c>
       <c r="J2" t="n">
-        <v>4.217985729546887</v>
+        <v>4.217985729546898</v>
       </c>
       <c r="K2" t="n">
-        <v>0.692016840915975</v>
+        <v>0.6920168409159859</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4138099388897047</v>
+        <v>0.9415321513670034</v>
       </c>
     </row>
     <row r="3">
@@ -5703,37 +5703,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01615964062339327</v>
+        <v>0.01615964062339775</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01826169611503708</v>
+        <v>0.01826169611504286</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01615964062339327</v>
+        <v>0.01615964062339776</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01865117285275366</v>
+        <v>0.01865117285275877</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01865117285275365</v>
+        <v>0.01865117285276024</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0166898503571954</v>
+        <v>0.01668985035719643</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01615964062339327</v>
+        <v>0.01615964062339776</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01969747053254719</v>
+        <v>0.01969747053254775</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01615964062339327</v>
+        <v>0.01615964062339702</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01615964062339327</v>
+        <v>0.01615964062339776</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01615964062339327</v>
+        <v>0.01615964062339776</v>
       </c>
     </row>
     <row r="4">
@@ -5746,31 +5746,31 @@
         <v>10.06830202191764</v>
       </c>
       <c r="C4" t="n">
-        <v>10.07100668473107</v>
+        <v>10.07100668473108</v>
       </c>
       <c r="D4" t="n">
-        <v>38.25764576541981</v>
+        <v>10.06724276742443</v>
       </c>
       <c r="E4" t="n">
-        <v>6.207186360435776</v>
+        <v>6.207186360435789</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07170324611435</v>
+        <v>10.07170324611436</v>
       </c>
       <c r="G4" t="n">
-        <v>10.06883223165144</v>
+        <v>38.25796174978183</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26066696608909</v>
+        <v>38.26066696608908</v>
       </c>
       <c r="I4" t="n">
-        <v>38.2609693699572</v>
+        <v>10.07183985182679</v>
       </c>
       <c r="J4" t="n">
-        <v>10.58067450992286</v>
+        <v>38.25960918575012</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06738086603335</v>
+        <v>10.06738086603337</v>
       </c>
       <c r="L4" t="n">
         <v>10.06808566120696</v>
@@ -5783,37 +5783,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02702321416605397</v>
+        <v>0.02702321416605985</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03056104407520787</v>
+        <v>0.03056104407521049</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02702290163008165</v>
+        <v>0.02702290163008391</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03032596274293056</v>
+        <v>0.03032596274293298</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03032596274293056</v>
+        <v>0.03032596274293298</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0275534238998561</v>
+        <v>0.02755342389986063</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02702321416605396</v>
+        <v>0.02702321416605988</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03056104407520787</v>
+        <v>0.03056104407521049</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02702321416605396</v>
+        <v>0.02702321416605988</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02702321416605396</v>
+        <v>0.02702321416605988</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02702321416605396</v>
+        <v>0.02702321416605988</v>
       </c>
     </row>
     <row r="6">
@@ -5823,37 +5823,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0370326912501376</v>
+        <v>0.03703269125013804</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05651517891264907</v>
+        <v>0.05651517891265211</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05655084793012302</v>
+        <v>0.05655084793012648</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0521174538549165</v>
+        <v>0.05211745385492109</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04094290825269332</v>
+        <v>0.04094290825269451</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05372892688390478</v>
+        <v>0.05372892688391014</v>
       </c>
       <c r="H6" t="n">
-        <v>0.053198717150166</v>
+        <v>0.05319871715017076</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05673654705925657</v>
+        <v>0.05673654705925927</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05320189420886283</v>
+        <v>0.0532018942088671</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03673239902183043</v>
+        <v>0.03673239902183459</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07008548295723145</v>
+        <v>0.07008548295723636</v>
       </c>
     </row>
     <row r="7">
@@ -5863,37 +5863,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.06991961044916863</v>
+        <v>0.0699196104491768</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08958880281207872</v>
+        <v>0.08958880281208592</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08605097518856464</v>
+        <v>0.08605097518857605</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1082040120740144</v>
+        <v>0.1082040120740158</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08958876838348864</v>
+        <v>0.08958876838350062</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08658118263672711</v>
+        <v>0.08658118263673804</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08605097290292485</v>
+        <v>0.08605097290293458</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08958880281207872</v>
+        <v>0.08958880281208592</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08605097290292485</v>
+        <v>0.08605097290293458</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07670439910580189</v>
+        <v>0.07670439910580544</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08605097290292485</v>
+        <v>0.08605097290293458</v>
       </c>
     </row>
     <row r="8">
@@ -5903,37 +5903,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6074837246741293</v>
+        <v>0.607483724674132</v>
       </c>
       <c r="C8" t="n">
-        <v>1.06821438209385</v>
+        <v>1.068214382093827</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5961029914309175</v>
+        <v>0.5961029914309185</v>
       </c>
       <c r="E8" t="n">
-        <v>1.06821438209385</v>
+        <v>1.068214382093827</v>
       </c>
       <c r="F8" t="n">
-        <v>1.06821438209385</v>
+        <v>1.068214382093827</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5817054701048059</v>
+        <v>0.581705470104807</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5563025282299847</v>
+        <v>0.5563025282299841</v>
       </c>
       <c r="I8" t="n">
-        <v>1.06821438209385</v>
+        <v>1.068214382093827</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5176702293644796</v>
+        <v>0.5176702293644806</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5963336001799249</v>
+        <v>0.5963336001799243</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6067906971884408</v>
+        <v>0.6067906971884424</v>
       </c>
     </row>
     <row r="9">
@@ -5943,37 +5943,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6025183360010667</v>
+        <v>0.6025183360010671</v>
       </c>
       <c r="C9" t="n">
-        <v>1.065327175243392</v>
+        <v>1.065327175243391</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5978835434000408</v>
+        <v>0.5978835434000404</v>
       </c>
       <c r="E9" t="n">
-        <v>1.065327175243392</v>
+        <v>1.065327175243391</v>
       </c>
       <c r="F9" t="n">
-        <v>1.065327175243392</v>
+        <v>1.065327175243391</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5919834542020127</v>
+        <v>0.5919834542020129</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5817274268844375</v>
+        <v>0.5817274268844401</v>
       </c>
       <c r="I9" t="n">
-        <v>1.065327175243392</v>
+        <v>1.065327175243391</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5659750944515871</v>
+        <v>0.5659750944515881</v>
       </c>
       <c r="K9" t="n">
-        <v>0.597977961228717</v>
+        <v>0.5979779612287199</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6022424668612832</v>
+        <v>0.602242466861285</v>
       </c>
     </row>
   </sheetData>
@@ -6059,34 +6059,34 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.167330314446228</v>
+        <v>0.167330314446233</v>
       </c>
       <c r="C2" t="n">
-        <v>4.612570278743782</v>
+        <v>4.612570278743778</v>
       </c>
       <c r="D2" t="n">
-        <v>2.472370714428738</v>
+        <v>2.472370714428741</v>
       </c>
       <c r="E2" t="n">
-        <v>4.612570278743782</v>
+        <v>4.612570278743778</v>
       </c>
       <c r="F2" t="n">
-        <v>4.612570278743782</v>
+        <v>4.612570278743778</v>
       </c>
       <c r="G2" t="n">
-        <v>3.738352655538463</v>
+        <v>3.738352655538465</v>
       </c>
       <c r="H2" t="n">
-        <v>5.727586894743957</v>
+        <v>5.727586894743959</v>
       </c>
       <c r="I2" t="n">
-        <v>4.612570278743782</v>
+        <v>4.612570278743778</v>
       </c>
       <c r="J2" t="n">
-        <v>10.64136125462161</v>
+        <v>10.6413612546216</v>
       </c>
       <c r="K2" t="n">
-        <v>4.94557794907408</v>
+        <v>4.945577949074085</v>
       </c>
       <c r="L2" t="n">
         <v>4.565046466293285</v>
@@ -6099,37 +6099,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03612569439359836</v>
+        <v>0.03612569439359852</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04006045030050724</v>
+        <v>0.04006045030050719</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03612569439359836</v>
+        <v>0.03612569439359852</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04055440348226372</v>
+        <v>0.04055440348226361</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04055440348226373</v>
+        <v>0.04055440348226361</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03670319102191342</v>
+        <v>0.03670319102191344</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03612569439359836</v>
+        <v>0.03612569439359852</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03996651574010617</v>
+        <v>0.03996651574010609</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03612569439359836</v>
+        <v>0.03612569439359852</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03612569439359836</v>
+        <v>0.03612569439359852</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03612569439359836</v>
+        <v>0.03612569439359852</v>
       </c>
     </row>
     <row r="4">
@@ -6139,31 +6139,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.84081660748373</v>
+        <v>41.10570050932419</v>
       </c>
       <c r="C4" t="n">
         <v>10.84510083064795</v>
       </c>
       <c r="D4" t="n">
-        <v>41.10634276588195</v>
+        <v>41.10634276588193</v>
       </c>
       <c r="E4" t="n">
-        <v>6.697540763555265</v>
+        <v>6.697540763555269</v>
       </c>
       <c r="F4" t="n">
         <v>10.84406780108459</v>
       </c>
       <c r="G4" t="n">
-        <v>10.84139410411205</v>
+        <v>41.1062780059525</v>
       </c>
       <c r="H4" t="n">
-        <v>41.10999985196143</v>
+        <v>10.84039987426875</v>
       </c>
       <c r="I4" t="n">
-        <v>10.84465742883025</v>
+        <v>41.10954133067072</v>
       </c>
       <c r="J4" t="n">
-        <v>41.10863975724838</v>
+        <v>41.10863975724841</v>
       </c>
       <c r="K4" t="n">
         <v>10.8420857943722</v>
@@ -6179,37 +6179,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06013610997549471</v>
+        <v>0.06013610997549469</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06397693132200249</v>
+        <v>0.06397693132200231</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06013529852476632</v>
+        <v>0.06013529852476643</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06391575842889129</v>
+        <v>0.06391575842889119</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06391575842889129</v>
+        <v>0.06391575842889119</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06071360660380953</v>
+        <v>0.06071360660380968</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06013610997549471</v>
+        <v>0.06013610997549469</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06397693132200249</v>
+        <v>0.06397693132200231</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06013610997549471</v>
+        <v>0.06013610997549469</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06013610997549471</v>
+        <v>0.06013610997549469</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06013610997549471</v>
+        <v>0.06013610997549469</v>
       </c>
     </row>
     <row r="6">
@@ -6219,34 +6219,34 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07960499462486414</v>
+        <v>0.0796049946248642</v>
       </c>
       <c r="C6" t="n">
         <v>0.1165316092753366</v>
       </c>
       <c r="D6" t="n">
-        <v>0.119613077501063</v>
+        <v>0.1196130775010632</v>
       </c>
       <c r="E6" t="n">
         <v>0.1074743246033717</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08446019683665827</v>
+        <v>0.08446019683665811</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1133194167613682</v>
+        <v>0.1133194167613681</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1127419201330862</v>
+        <v>0.1127419201330863</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1165827414795611</v>
+        <v>0.1165827414795609</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1127484324478998</v>
+        <v>0.1127484324478997</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07898945922438794</v>
+        <v>0.07898945922438802</v>
       </c>
       <c r="L6" t="n">
         <v>0.1473562096535372</v>
@@ -6259,37 +6259,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1861618332455527</v>
+        <v>0.1861618332455529</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2338944341230432</v>
+        <v>0.2338944341230433</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2300536326261678</v>
+        <v>0.2300536326261681</v>
       </c>
       <c r="E7" t="n">
         <v>0.2845445693529115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.233894381613855</v>
+        <v>0.2338943816138552</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2306311094048504</v>
+        <v>0.2306311094048505</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2300536127765355</v>
+        <v>0.2300536127765358</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2338944341230432</v>
+        <v>0.2338944341230433</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2300536127765355</v>
+        <v>0.2300536127765358</v>
       </c>
       <c r="K7" t="n">
-        <v>0.204622551688645</v>
+        <v>0.2046225516886452</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2300536127765355</v>
+        <v>0.2300536127765358</v>
       </c>
     </row>
     <row r="8">
@@ -6299,19 +6299,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6315226092764856</v>
+        <v>0.6315226092764852</v>
       </c>
       <c r="C8" t="n">
-        <v>1.002031322262652</v>
+        <v>1.002031322262651</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5721642971736478</v>
+        <v>0.5721642971736475</v>
       </c>
       <c r="E8" t="n">
-        <v>1.002031322262652</v>
+        <v>1.002031322262651</v>
       </c>
       <c r="F8" t="n">
-        <v>1.002031322262652</v>
+        <v>1.002031322262651</v>
       </c>
       <c r="G8" t="n">
         <v>0.5455257820898115</v>
@@ -6320,16 +6320,16 @@
         <v>0.5048063335201151</v>
       </c>
       <c r="I8" t="n">
-        <v>1.002031322262652</v>
+        <v>1.002031322262651</v>
       </c>
       <c r="J8" t="n">
         <v>0.4044316249367654</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5129209872291063</v>
+        <v>0.5129209872291066</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6241119428034476</v>
+        <v>0.5417937563053152</v>
       </c>
     </row>
     <row r="9">
@@ -6339,37 +6339,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6235231770419748</v>
+        <v>0.6235231770419752</v>
       </c>
       <c r="C9" t="n">
-        <v>1.051225653374082</v>
+        <v>1.051225653374081</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5993485686712005</v>
+        <v>0.5993485686712001</v>
       </c>
       <c r="E9" t="n">
-        <v>1.051225653374082</v>
+        <v>1.051225653374081</v>
       </c>
       <c r="F9" t="n">
-        <v>1.051225653374082</v>
+        <v>1.051225653374081</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5886160168632991</v>
+        <v>0.5886160168632992</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5720332161151566</v>
+        <v>0.5720332161151568</v>
       </c>
       <c r="I9" t="n">
-        <v>1.051225653374082</v>
+        <v>1.051225653374081</v>
       </c>
       <c r="J9" t="n">
         <v>0.5311182520918576</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5752239241152639</v>
+        <v>0.5752239241152637</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5870474319302548</v>
+        <v>0.587047431930254</v>
       </c>
     </row>
   </sheetData>
@@ -6455,37 +6455,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1008363085834129</v>
+        <v>0.1008363085834132</v>
       </c>
       <c r="C2" t="n">
-        <v>2.889620865043844</v>
+        <v>2.889620865043845</v>
       </c>
       <c r="D2" t="n">
         <v>2.192089015196613</v>
       </c>
       <c r="E2" t="n">
-        <v>2.889620865043844</v>
+        <v>2.889620865043845</v>
       </c>
       <c r="F2" t="n">
-        <v>2.889620865043844</v>
+        <v>2.889620865043845</v>
       </c>
       <c r="G2" t="n">
-        <v>2.660143901551328</v>
+        <v>2.660143901551334</v>
       </c>
       <c r="H2" t="n">
-        <v>4.15544131064299</v>
+        <v>4.155441310642987</v>
       </c>
       <c r="I2" t="n">
-        <v>2.889620865043844</v>
+        <v>2.889620865043845</v>
       </c>
       <c r="J2" t="n">
-        <v>5.753769594337482</v>
+        <v>5.753769594337486</v>
       </c>
       <c r="K2" t="n">
         <v>1.620966911867651</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2141997802228859</v>
+        <v>0.2141997802228863</v>
       </c>
     </row>
     <row r="3">
@@ -6495,37 +6495,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02735388854811438</v>
+        <v>0.02735388854811423</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03059733022293521</v>
+        <v>0.03059733022293523</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02735388854811438</v>
+        <v>0.02735388854811423</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03098294264181662</v>
+        <v>0.03098294264181667</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03098294264181664</v>
+        <v>0.03098294264181666</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02790833223798551</v>
+        <v>0.0279083322379858</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02735388854811438</v>
+        <v>0.02735388854811423</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03104665468023643</v>
+        <v>0.03104665468023649</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02735388854811438</v>
+        <v>0.02735388854811423</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02735388854811438</v>
+        <v>0.02735388854811423</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02735388854811438</v>
+        <v>0.02735388854811423</v>
       </c>
     </row>
     <row r="4">
@@ -6535,34 +6535,34 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.28453688228209</v>
+        <v>38.28453688228208</v>
       </c>
       <c r="C4" t="n">
-        <v>10.09150861610127</v>
+        <v>10.09150861610128</v>
       </c>
       <c r="D4" t="n">
-        <v>10.08652864290189</v>
+        <v>10.08652851764003</v>
       </c>
       <c r="E4" t="n">
-        <v>6.227284726362002</v>
+        <v>6.227284726362006</v>
       </c>
       <c r="F4" t="n">
         <v>10.09113480527776</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08764970280258</v>
+        <v>38.28509132597195</v>
       </c>
       <c r="H4" t="n">
-        <v>10.08788799125727</v>
+        <v>38.2883059500851</v>
       </c>
       <c r="I4" t="n">
-        <v>10.09078802524482</v>
+        <v>38.28822964841422</v>
       </c>
       <c r="J4" t="n">
-        <v>38.28735389187705</v>
+        <v>10.60017005520723</v>
       </c>
       <c r="K4" t="n">
-        <v>10.08501633475016</v>
+        <v>10.08501633475017</v>
       </c>
       <c r="L4" t="n">
         <v>10.0878183732954</v>
@@ -6575,37 +6575,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0451931592476595</v>
+        <v>0.04519315924765945</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04888592537978157</v>
+        <v>0.04888592537978162</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04519254278917334</v>
+        <v>0.04519254278917328</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04878038044696701</v>
+        <v>0.04878038044696707</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04878038044696701</v>
+        <v>0.04878038044696707</v>
       </c>
       <c r="G5" t="n">
-        <v>0.045747602937531</v>
+        <v>0.04574760293753091</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0451931592476595</v>
+        <v>0.04519315924765945</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04888592537978157</v>
+        <v>0.04888592537978162</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0451931592476595</v>
+        <v>0.04519315924765945</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0451931592476595</v>
+        <v>0.04519315924765945</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0451931592476595</v>
+        <v>0.04519315924765945</v>
       </c>
     </row>
     <row r="6">
@@ -6615,37 +6615,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05996061070522555</v>
+        <v>0.0599606107052256</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08833753173530166</v>
+        <v>0.08833753173530173</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08987842134196662</v>
+        <v>0.08987842134196695</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08157064773848602</v>
+        <v>0.08157064773848613</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06437625696177653</v>
+        <v>0.06437625696177662</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08529465369508143</v>
+        <v>0.08529465369508132</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08474021000521853</v>
+        <v>0.08474021000521871</v>
       </c>
       <c r="I6" t="n">
         <v>0.0884329761373321</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08474507987780147</v>
+        <v>0.08474507987780179</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05950031692878358</v>
+        <v>0.05950031692878378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1106245734839152</v>
+        <v>0.1106245734839157</v>
       </c>
     </row>
     <row r="7">
@@ -6655,37 +6655,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1290702688513797</v>
+        <v>0.1290702688513799</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1626610622226391</v>
+        <v>0.1626610622226393</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1589683044025288</v>
+        <v>0.1589683044025295</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1971626963273869</v>
+        <v>0.1971626963273872</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1626610119006172</v>
+        <v>0.1626610119006175</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1595227397803882</v>
+        <v>0.1595227397803886</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1589682960905166</v>
+        <v>0.1589682960905172</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1626610622226391</v>
+        <v>0.1626610622226393</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1589682960905166</v>
+        <v>0.1589682960905172</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1409424476022423</v>
+        <v>0.1416452651855497</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1589682960905166</v>
+        <v>0.1589682960905172</v>
       </c>
     </row>
     <row r="8">
@@ -6695,37 +6695,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6232372536661319</v>
+        <v>0.6232372536661317</v>
       </c>
       <c r="C8" t="n">
-        <v>1.02696327530413</v>
+        <v>1.026963275304131</v>
       </c>
       <c r="D8" t="n">
         <v>0.5634707596631188</v>
       </c>
       <c r="E8" t="n">
-        <v>1.02696327530413</v>
+        <v>1.026963275304131</v>
       </c>
       <c r="F8" t="n">
-        <v>1.02696327530413</v>
+        <v>1.026963275304131</v>
       </c>
       <c r="G8" t="n">
         <v>0.5549104509018186</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5162257176357685</v>
+        <v>0.5162257176357689</v>
       </c>
       <c r="I8" t="n">
-        <v>1.02696327530413</v>
+        <v>1.026963275304131</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4825721140537807</v>
+        <v>0.4825721140537805</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5821913855986642</v>
+        <v>0.5821913855986648</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5229848217361492</v>
+        <v>0.6207815632602773</v>
       </c>
     </row>
     <row r="9">
@@ -6735,13 +6735,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6146311803270038</v>
+        <v>0.614631180327004</v>
       </c>
       <c r="C9" t="n">
         <v>1.055631385151081</v>
       </c>
       <c r="D9" t="n">
-        <v>0.5902903004469384</v>
+        <v>0.590290300446939</v>
       </c>
       <c r="E9" t="n">
         <v>1.055631385151081</v>
@@ -6750,10 +6750,10 @@
         <v>1.055631385151081</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5868484835990451</v>
+        <v>0.5868484835990455</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5711473512587388</v>
+        <v>0.5711473512587385</v>
       </c>
       <c r="I9" t="n">
         <v>1.055631385151081</v>
@@ -6765,7 +6765,7 @@
         <v>0.5979157251622972</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5738762940192774</v>
+        <v>0.6136341577634533</v>
       </c>
     </row>
   </sheetData>
@@ -6851,13 +6851,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09437802176290264</v>
+        <v>0.09437802176290272</v>
       </c>
       <c r="C2" t="n">
         <v>1.465335809898434</v>
       </c>
       <c r="D2" t="n">
-        <v>1.104720419027534</v>
+        <v>1.104720419027536</v>
       </c>
       <c r="E2" t="n">
         <v>1.465335809898434</v>
@@ -6866,22 +6866,22 @@
         <v>1.465335809898434</v>
       </c>
       <c r="G2" t="n">
-        <v>1.708064654915967</v>
+        <v>1.708064654915964</v>
       </c>
       <c r="H2" t="n">
-        <v>3.950566189615344</v>
+        <v>3.950566189615341</v>
       </c>
       <c r="I2" t="n">
         <v>1.465335809898434</v>
       </c>
       <c r="J2" t="n">
-        <v>2.101777064239767</v>
+        <v>2.101777064239765</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3970182440324518</v>
+        <v>0.3970182440324508</v>
       </c>
       <c r="L2" t="n">
-        <v>3.595600971792674</v>
+        <v>0.4208478776188948</v>
       </c>
     </row>
     <row r="3">
@@ -6891,37 +6891,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01874666526735133</v>
+        <v>0.01874666526735135</v>
       </c>
       <c r="C3" t="n">
         <v>0.02133695193560996</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01874666526735133</v>
+        <v>0.01874666526735135</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02167952470390081</v>
+        <v>0.0216795247039008</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02167952470390079</v>
+        <v>0.0216795247039008</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01928213136544816</v>
+        <v>0.01928213136544824</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01874666526735133</v>
+        <v>0.01874666526735135</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0223174684347043</v>
+        <v>0.02231746843470425</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01874666526735133</v>
+        <v>0.01874666526735135</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01874666526735133</v>
+        <v>0.01874666526735135</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01874666526735133</v>
+        <v>0.01874666526735135</v>
       </c>
     </row>
     <row r="4">
@@ -6931,37 +6931,37 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.07087923233083</v>
+        <v>10.07087923233082</v>
       </c>
       <c r="C4" t="n">
         <v>10.07450354766287</v>
       </c>
       <c r="D4" t="n">
-        <v>10.0703265506182</v>
+        <v>10.07032655061821</v>
       </c>
       <c r="E4" t="n">
-        <v>6.210762486249222</v>
+        <v>6.210762486249224</v>
       </c>
       <c r="F4" t="n">
         <v>10.07483750082018</v>
       </c>
       <c r="G4" t="n">
-        <v>38.26400109291245</v>
+        <v>10.07141469842891</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26689664679211</v>
+        <v>38.26689664679212</v>
       </c>
       <c r="I4" t="n">
-        <v>10.07445003549818</v>
+        <v>10.07445003549816</v>
       </c>
       <c r="J4" t="n">
-        <v>38.26587915918515</v>
+        <v>10.58291432515451</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06877900585781</v>
+        <v>10.06877900585783</v>
       </c>
       <c r="L4" t="n">
-        <v>10.07195720452278</v>
+        <v>10.07195720452279</v>
       </c>
     </row>
     <row r="5">
@@ -6974,25 +6974,25 @@
         <v>0.0312617151734602</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03483251834081307</v>
+        <v>0.03483251834081304</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03126129164733375</v>
+        <v>0.03126129164733369</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03467664852969043</v>
+        <v>0.03467664852969038</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03467664852969043</v>
+        <v>0.03467664852969038</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0317971812715571</v>
+        <v>0.03179718127155694</v>
       </c>
       <c r="H5" t="n">
         <v>0.0312617151734602</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03483251834081307</v>
+        <v>0.03483251834081304</v>
       </c>
       <c r="J5" t="n">
         <v>0.0312617151734602</v>
@@ -7011,37 +7011,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04205500981425515</v>
+        <v>0.0420550098142552</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06325678226351625</v>
+        <v>0.06325678226351619</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06351715092083621</v>
+        <v>0.0635171509208361</v>
       </c>
       <c r="E6" t="n">
         <v>0.05841059585061319</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04609655800089767</v>
+        <v>0.04609655800089765</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06036661813085867</v>
+        <v>0.06036661813085858</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05983115203277021</v>
+        <v>0.05983115203277001</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06340195520011464</v>
+        <v>0.06340195520011457</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05983464553134335</v>
+        <v>0.05983464553134323</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0417248088481354</v>
+        <v>0.04172480884813528</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07839981897595556</v>
+        <v>0.0783998189759554</v>
       </c>
     </row>
     <row r="7">
@@ -7051,37 +7051,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08284248633156456</v>
+        <v>0.08284248633156437</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1054304146745595</v>
+        <v>0.1054304146745593</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1018595991621081</v>
+        <v>0.101859599162108</v>
       </c>
       <c r="E7" t="n">
         <v>0.127375694171753</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1054303598204743</v>
+        <v>0.1054303598204742</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1023950776053034</v>
+        <v>0.1023950776053033</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1018596115072065</v>
+        <v>0.1018596115072064</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1054304146745595</v>
+        <v>0.1054304146745593</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1018596115072065</v>
+        <v>0.1018596115072064</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09039397119294573</v>
+        <v>0.09039397119294562</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1018596115072065</v>
+        <v>0.1018596115072064</v>
       </c>
     </row>
     <row r="8">
@@ -7091,13 +7091,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6142741618688412</v>
+        <v>0.6142741618688408</v>
       </c>
       <c r="C8" t="n">
         <v>1.05573911630181</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5870290749113347</v>
+        <v>0.5870290749113352</v>
       </c>
       <c r="E8" t="n">
         <v>1.05573911630181</v>
@@ -7106,22 +7106,22 @@
         <v>1.05573911630181</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5725301901955395</v>
+        <v>0.57253019019554</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5222781257722848</v>
+        <v>0.5222781257722847</v>
       </c>
       <c r="I8" t="n">
         <v>1.05573911630181</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5654421092827859</v>
+        <v>0.5654421092827858</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6058700512926019</v>
+        <v>0.6058700512926013</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6068063756606309</v>
+        <v>0.537388284837011</v>
       </c>
     </row>
     <row r="9">
@@ -7131,13 +7131,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6058183994809051</v>
+        <v>0.6058183994809055</v>
       </c>
       <c r="C9" t="n">
         <v>1.061177261831145</v>
       </c>
       <c r="D9" t="n">
-        <v>0.594722421221118</v>
+        <v>0.5947224212211182</v>
       </c>
       <c r="E9" t="n">
         <v>1.061177261831145</v>
@@ -7146,22 +7146,22 @@
         <v>1.061177261831145</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5888013377896174</v>
+        <v>0.588801337789617</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5684363851075577</v>
+        <v>0.5684363851075572</v>
       </c>
       <c r="I9" t="n">
         <v>1.061177261831145</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5859487578168101</v>
+        <v>0.5859487578168097</v>
       </c>
       <c r="K9" t="n">
         <v>0.6023960020531581</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5745629246972244</v>
+        <v>0.5745629246972247</v>
       </c>
     </row>
   </sheetData>
@@ -7247,37 +7247,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1396959017844443</v>
+        <v>0.139695901784433</v>
       </c>
       <c r="C2" t="n">
-        <v>4.438656632232634</v>
+        <v>4.438656632232633</v>
       </c>
       <c r="D2" t="n">
-        <v>1.086474333092605</v>
+        <v>1.086474333092758</v>
       </c>
       <c r="E2" t="n">
-        <v>4.438656632232634</v>
+        <v>4.438656632232633</v>
       </c>
       <c r="F2" t="n">
-        <v>4.438656632232634</v>
+        <v>4.438656632232633</v>
       </c>
       <c r="G2" t="n">
-        <v>2.641256196054666</v>
+        <v>2.641256196054715</v>
       </c>
       <c r="H2" t="n">
-        <v>2.004847323074885</v>
+        <v>2.00484732307511</v>
       </c>
       <c r="I2" t="n">
-        <v>4.438656632232634</v>
+        <v>4.438656632232633</v>
       </c>
       <c r="J2" t="n">
-        <v>9.685434219495336</v>
+        <v>9.685434219495294</v>
       </c>
       <c r="K2" t="n">
-        <v>4.693591645060521</v>
+        <v>4.693591645060528</v>
       </c>
       <c r="L2" t="n">
-        <v>1.103213777181782</v>
+        <v>0.42217430986719</v>
       </c>
     </row>
     <row r="3">
@@ -7287,37 +7287,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03357123929464209</v>
+        <v>0.03357123929464845</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03888042604873193</v>
+        <v>0.03888042604873904</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03357123929464209</v>
+        <v>0.03357123929464845</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03928307800019318</v>
+        <v>0.03928307800019418</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03928307800018947</v>
+        <v>0.03928307800019407</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03418745167000167</v>
+        <v>0.03418745167000247</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03357123929464209</v>
+        <v>0.03357123929464845</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03765875339046065</v>
+        <v>0.03765875339046328</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03357123929464209</v>
+        <v>0.03357123929464845</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03357123929464209</v>
+        <v>0.03357123929464845</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03357123929464209</v>
+        <v>0.03357123929464845</v>
       </c>
     </row>
     <row r="4">
@@ -7330,31 +7330,31 @@
         <v>10.83540618926669</v>
       </c>
       <c r="C4" t="n">
-        <v>10.84157608654277</v>
+        <v>10.84157608654279</v>
       </c>
       <c r="D4" t="n">
-        <v>10.829860111021</v>
+        <v>10.82986011102102</v>
       </c>
       <c r="E4" t="n">
-        <v>6.694106130898023</v>
+        <v>6.694106130898017</v>
       </c>
       <c r="F4" t="n">
-        <v>10.83912875681332</v>
+        <v>10.83912875681331</v>
       </c>
       <c r="G4" t="n">
-        <v>41.09458193595858</v>
+        <v>41.09458193595853</v>
       </c>
       <c r="H4" t="n">
         <v>41.09681674968916</v>
       </c>
       <c r="I4" t="n">
-        <v>41.09805323767891</v>
+        <v>41.098053237679</v>
       </c>
       <c r="J4" t="n">
-        <v>41.09619567379492</v>
+        <v>41.09619567379494</v>
       </c>
       <c r="K4" t="n">
-        <v>10.83748627470402</v>
+        <v>10.83748627470404</v>
       </c>
       <c r="L4" t="n">
         <v>10.83343414618965</v>
@@ -7367,37 +7367,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05318684024011153</v>
+        <v>0.05318684024012361</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05727435433596374</v>
+        <v>0.05727435433593828</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0531859550816505</v>
+        <v>0.0531859550816292</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05733250992629255</v>
+        <v>0.05733250992630697</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05733250992629255</v>
+        <v>0.05733250992630697</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05380305261547584</v>
+        <v>0.05380305261547723</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05318684024011153</v>
+        <v>0.05318684024012361</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05727435433596374</v>
+        <v>0.05727435433593828</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05318684024011153</v>
+        <v>0.05318684024012361</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05318684024011153</v>
+        <v>0.05318684024012361</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05318684024011153</v>
+        <v>0.05318684024012361</v>
       </c>
     </row>
     <row r="6">
@@ -7407,37 +7407,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06867351395825964</v>
+        <v>0.06867351395822739</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09982612259257426</v>
+        <v>0.09982612259202631</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1012760096817585</v>
+        <v>0.1012760096817584</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09243431667108405</v>
+        <v>0.09243431667111103</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07365220866070489</v>
+        <v>0.07365220866070962</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09629293154933198</v>
+        <v>0.09629293154935339</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09567671917403017</v>
+        <v>0.09567671917400464</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09976423326979429</v>
+        <v>0.09976423326981447</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09568202603567458</v>
+        <v>0.09568202603572307</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06817191556137535</v>
+        <v>0.06817191556139254</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1238838249543946</v>
+        <v>0.1238838249543677</v>
       </c>
     </row>
     <row r="7">
@@ -7447,37 +7447,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1537782036437425</v>
+        <v>0.1537782036437962</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1931550561448176</v>
+        <v>0.193155056144804</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1890675787530548</v>
+        <v>0.1890675787530691</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2338782411701066</v>
+        <v>0.233878241170129</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1931550590095068</v>
+        <v>0.1931550590094905</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1896837544243295</v>
+        <v>0.1896837544243425</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1890675420489916</v>
+        <v>0.1890675420489891</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1931550561448176</v>
+        <v>0.193155056144804</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1890675420489916</v>
+        <v>0.1890675420489891</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1686207762226849</v>
+        <v>0.1686207762226876</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1890675420489916</v>
+        <v>0.1890675420489891</v>
       </c>
     </row>
     <row r="8">
@@ -7487,37 +7487,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6274403553950191</v>
+        <v>0.6274403553950175</v>
       </c>
       <c r="C8" t="n">
-        <v>1.00346148995825</v>
+        <v>1.003461489958253</v>
       </c>
       <c r="D8" t="n">
-        <v>0.604453395326735</v>
+        <v>0.6044533953267257</v>
       </c>
       <c r="E8" t="n">
-        <v>1.00346148995825</v>
+        <v>1.003461489958253</v>
       </c>
       <c r="F8" t="n">
-        <v>1.00346148995825</v>
+        <v>1.003461489958253</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5694720214692891</v>
+        <v>0.5694720214692918</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5861378459541245</v>
+        <v>0.5861378459541217</v>
       </c>
       <c r="I8" t="n">
-        <v>1.00346148995825</v>
+        <v>1.003461489958253</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4204901962895892</v>
+        <v>0.4204901962895875</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5192158799061568</v>
+        <v>0.5192158799061583</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6088287918999442</v>
+        <v>0.6088287918999415</v>
       </c>
     </row>
     <row r="9">
@@ -7527,37 +7527,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6191597055665224</v>
+        <v>0.6191597055665284</v>
       </c>
       <c r="C9" t="n">
-        <v>1.050174396659428</v>
+        <v>1.05017439665943</v>
       </c>
       <c r="D9" t="n">
-        <v>0.6097979378730145</v>
+        <v>0.6097979378730144</v>
       </c>
       <c r="E9" t="n">
-        <v>1.050174396659428</v>
+        <v>1.05017439665943</v>
       </c>
       <c r="F9" t="n">
-        <v>1.050174396659428</v>
+        <v>1.05017439665943</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5957686828488001</v>
+        <v>0.5957686828488034</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6023781911595852</v>
+        <v>0.602378191159585</v>
       </c>
       <c r="I9" t="n">
-        <v>1.050174396659428</v>
+        <v>1.05017439665943</v>
       </c>
       <c r="J9" t="n">
-        <v>0.5349501145829257</v>
+        <v>0.5349501145829269</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5750864200843063</v>
+        <v>0.5750864200843104</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6115952888502358</v>
+        <v>0.6168989517891275</v>
       </c>
     </row>
   </sheetData>
@@ -7643,37 +7643,37 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07778142155586688</v>
+        <v>0.07778142155586668</v>
       </c>
       <c r="C2" t="n">
-        <v>2.744550095700991</v>
+        <v>2.744550095700992</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9082887058755852</v>
+        <v>0.9082887058755847</v>
       </c>
       <c r="E2" t="n">
-        <v>2.744550095700991</v>
+        <v>2.744550095700992</v>
       </c>
       <c r="F2" t="n">
-        <v>2.744550095700991</v>
+        <v>2.744550095700992</v>
       </c>
       <c r="G2" t="n">
-        <v>2.264147542509961</v>
+        <v>2.264147542509959</v>
       </c>
       <c r="H2" t="n">
-        <v>8.052083237719208</v>
+        <v>8.05208323771922</v>
       </c>
       <c r="I2" t="n">
-        <v>2.744550095700991</v>
+        <v>2.744550095700992</v>
       </c>
       <c r="J2" t="n">
-        <v>6.44733241015767</v>
+        <v>6.447332410157684</v>
       </c>
       <c r="K2" t="n">
-        <v>2.093963470468322</v>
+        <v>2.093963470468324</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1523588442896019</v>
+        <v>2.51367451513398</v>
       </c>
     </row>
     <row r="3">
@@ -7683,37 +7683,37 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02626278084114242</v>
+        <v>0.02626278084114255</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02994380495198267</v>
+        <v>0.02994380495198273</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02626278084114242</v>
+        <v>0.02626278084114255</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03031284899495767</v>
+        <v>0.03031284899495769</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03031284899495766</v>
+        <v>0.03031284899495769</v>
       </c>
       <c r="G3" t="n">
         <v>0.02682849724310813</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02626278084114242</v>
+        <v>0.02626278084114255</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03002733710560631</v>
+        <v>0.03002733710560628</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02626278084114242</v>
+        <v>0.02626278084114255</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02626278084114242</v>
+        <v>0.02626278084114255</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02626278084114242</v>
+        <v>0.02626278084114255</v>
       </c>
     </row>
     <row r="4">
@@ -7729,25 +7729,25 @@
         <v>10.09014850121162</v>
       </c>
       <c r="D4" t="n">
-        <v>10.08230643944038</v>
+        <v>10.08230630897605</v>
       </c>
       <c r="E4" t="n">
-        <v>6.225900620053297</v>
+        <v>6.225900620053298</v>
       </c>
       <c r="F4" t="n">
-        <v>10.08948484814314</v>
+        <v>10.08948484814313</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08652721349604</v>
+        <v>38.28113890693876</v>
       </c>
       <c r="H4" t="n">
-        <v>38.28527874230883</v>
+        <v>38.28527874230884</v>
       </c>
       <c r="I4" t="n">
-        <v>38.28433774680125</v>
+        <v>38.28433774680124</v>
       </c>
       <c r="J4" t="n">
-        <v>10.59849882408579</v>
+        <v>10.5984988240858</v>
       </c>
       <c r="K4" t="n">
         <v>10.08500237030977</v>
@@ -7763,37 +7763,37 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04257201397699435</v>
+        <v>0.04257201397699428</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04633657024145824</v>
+        <v>0.04633657024145815</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04257138717317423</v>
+        <v>0.04257138717317421</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04628372153347773</v>
+        <v>0.04628372153347769</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04628372153347775</v>
+        <v>0.04628372153347769</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04313773037896006</v>
+        <v>0.04313773037895993</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04257201397699435</v>
+        <v>0.04257201397699428</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04633657024145824</v>
+        <v>0.04633657024145815</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04257201397699435</v>
+        <v>0.04257201397699428</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04257201397699435</v>
+        <v>0.04257201397699428</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04257201397699435</v>
+        <v>0.04257201397699428</v>
       </c>
     </row>
     <row r="6">
@@ -7803,37 +7803,37 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05618819020403162</v>
+        <v>0.05618819020403169</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08279433302185885</v>
+        <v>0.08279433302185878</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08382094029190602</v>
+        <v>0.08382094029190609</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07653973515733431</v>
+        <v>0.07653973515733413</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06064707566219178</v>
+        <v>0.06064707566219175</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07964089132085198</v>
+        <v>0.07964089132085179</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07907517491896587</v>
+        <v>0.07907517491896575</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08283973118335018</v>
+        <v>0.08283973118335006</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07907967283546347</v>
+        <v>0.07907967283546341</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05576305271547955</v>
+        <v>0.05576305271547947</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1029825442026526</v>
+        <v>0.1029825442026525</v>
       </c>
     </row>
     <row r="7">
@@ -7843,34 +7843,34 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1165419358137284</v>
+        <v>0.1165419358137283</v>
       </c>
       <c r="C7" t="n">
-        <v>0.146959327703189</v>
+        <v>0.1469593277031889</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1431947120705622</v>
+        <v>0.143194712070562</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1777159510318394</v>
+        <v>0.1777159510318393</v>
       </c>
       <c r="F7" t="n">
         <v>0.1469592235562777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1437604878406905</v>
+        <v>0.1437604878406904</v>
       </c>
       <c r="H7" t="n">
         <v>0.1431947714387249</v>
       </c>
       <c r="I7" t="n">
-        <v>0.146959327703189</v>
+        <v>0.1469593277031889</v>
       </c>
       <c r="J7" t="n">
         <v>0.1431947714387249</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1096341092594724</v>
+        <v>0.1277519888338249</v>
       </c>
       <c r="L7" t="n">
         <v>0.1431947714387249</v>
@@ -7883,37 +7883,37 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6230490485258396</v>
+        <v>0.6230490485258391</v>
       </c>
       <c r="C8" t="n">
-        <v>1.030759833191594</v>
+        <v>1.030759833191592</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6004761247477474</v>
+        <v>0.6004761247477464</v>
       </c>
       <c r="E8" t="n">
-        <v>1.030759833191594</v>
+        <v>1.030759833191592</v>
       </c>
       <c r="F8" t="n">
-        <v>1.030759833191594</v>
+        <v>1.030759833191592</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5666271554476517</v>
+        <v>0.5666271554476512</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4274787248575954</v>
+        <v>0.4274787248575955</v>
       </c>
       <c r="I8" t="n">
-        <v>1.030759833191594</v>
+        <v>1.030759833191592</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4748960910546521</v>
+        <v>0.4748960910546512</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5688114422432906</v>
+        <v>0.5688114422432896</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5703995346714181</v>
+        <v>0.5703995346714174</v>
       </c>
     </row>
     <row r="9">
@@ -7923,37 +7923,37 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.6141252786688199</v>
+        <v>0.6141252786688195</v>
       </c>
       <c r="C9" t="n">
-        <v>1.056639954436509</v>
+        <v>1.056639954436508</v>
       </c>
       <c r="D9" t="n">
         <v>0.6049321023668814</v>
       </c>
       <c r="E9" t="n">
-        <v>1.056639954436509</v>
+        <v>1.056639954436508</v>
       </c>
       <c r="F9" t="n">
-        <v>1.056639954436509</v>
+        <v>1.056639954436508</v>
       </c>
       <c r="G9" t="n">
-        <v>0.591222399359889</v>
+        <v>0.5912223993598884</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5346539668959568</v>
+        <v>0.534653966895957</v>
       </c>
       <c r="I9" t="n">
-        <v>1.056639954436509</v>
+        <v>1.056639954436508</v>
       </c>
       <c r="J9" t="n">
-        <v>0.553840521484761</v>
+        <v>0.5538405214847616</v>
       </c>
       <c r="K9" t="n">
-        <v>0.5920375818717997</v>
+        <v>0.5920375818717998</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5927222921816677</v>
+        <v>0.5927222921816674</v>
       </c>
     </row>
   </sheetData>

--- a/Results/Hydrogen/hydrogen ionising radiation results.xlsx
+++ b/Results/Hydrogen/hydrogen ionising radiation results.xlsx
@@ -443,7 +443,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -511,321 +511,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1960553098999518</v>
+        <v>0.6189526875410797</v>
       </c>
       <c r="C2" t="n">
-        <v>4.325006008434366</v>
+        <v>1.096478061410914</v>
       </c>
       <c r="D2" t="n">
-        <v>1.259704037882085</v>
+        <v>0.6200396748397466</v>
       </c>
       <c r="E2" t="n">
-        <v>4.325006008434366</v>
+        <v>1.096478061410914</v>
       </c>
       <c r="F2" t="n">
-        <v>4.325006008434366</v>
+        <v>1.096478061410914</v>
       </c>
       <c r="G2" t="n">
-        <v>2.923106055940242</v>
+        <v>0.6219308538516646</v>
       </c>
       <c r="H2" t="n">
-        <v>2.574194643174236</v>
+        <v>0.6211321729781929</v>
       </c>
       <c r="I2" t="n">
-        <v>4.325006008434366</v>
+        <v>1.096478061410914</v>
       </c>
       <c r="J2" t="n">
-        <v>8.526089849471239</v>
+        <v>0.6270727823875427</v>
       </c>
       <c r="K2" t="n">
-        <v>4.886761723680758</v>
+        <v>0.6237568854938776</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7705894485987509</v>
+        <v>0.6194767424053703</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0329638269173558</v>
+        <v>0.6284907305255082</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03778238176121539</v>
+        <v>1.10920575858777</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0329638269173558</v>
+        <v>0.6284907305255082</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03826467204741115</v>
+        <v>1.10920575858777</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03826467204741115</v>
+        <v>1.10920575858777</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03355958211431152</v>
+        <v>0.6287352975707197</v>
       </c>
       <c r="H3" t="n">
-        <v>0.0329638269173558</v>
+        <v>0.6284907305255082</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03692082551381447</v>
+        <v>1.10920575858777</v>
       </c>
       <c r="J3" t="n">
-        <v>0.0329638269173558</v>
+        <v>0.6284907305255082</v>
       </c>
       <c r="K3" t="n">
-        <v>0.0329638269173558</v>
+        <v>0.6284907305255082</v>
       </c>
       <c r="L3" t="n">
-        <v>0.0329638269173558</v>
+        <v>0.6284907305255082</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>11.57477339792477</v>
+        <v>0.196055309899951</v>
       </c>
       <c r="C4" t="n">
-        <v>11.57971226689881</v>
+        <v>4.325006008434451</v>
       </c>
       <c r="D4" t="n">
-        <v>11.56926556127892</v>
+        <v>1.259704037881435</v>
       </c>
       <c r="E4" t="n">
-        <v>7.147526065242538</v>
+        <v>4.325006008434451</v>
       </c>
       <c r="F4" t="n">
-        <v>11.57795047849279</v>
+        <v>4.325006008434451</v>
       </c>
       <c r="G4" t="n">
-        <v>43.91295034856396</v>
+        <v>2.923106055940208</v>
       </c>
       <c r="H4" t="n">
-        <v>43.91571162157847</v>
+        <v>2.574194643174112</v>
       </c>
       <c r="I4" t="n">
-        <v>43.91631159196346</v>
+        <v>4.325006008434451</v>
       </c>
       <c r="J4" t="n">
-        <v>43.91486381961504</v>
+        <v>8.526089849471392</v>
       </c>
       <c r="K4" t="n">
-        <v>11.57653230419806</v>
+        <v>4.886761723680759</v>
       </c>
       <c r="L4" t="n">
-        <v>11.57245861523564</v>
+        <v>0.7705894485987751</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05390690453333383</v>
+        <v>0.03296382691735986</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0578639031297925</v>
+        <v>0.03778238176121122</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05390601571753477</v>
+        <v>0.03296382691735986</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05793839572930755</v>
+        <v>0.03826467204740686</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05793839572930755</v>
+        <v>0.03826467204740809</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05450265973028955</v>
+        <v>0.0335595821143085</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05390690453333383</v>
+        <v>0.03296382691735986</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0578639031297925</v>
+        <v>0.03692082551381605</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05390690453333383</v>
+        <v>0.03296382691735986</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05390690453333383</v>
+        <v>0.03296382691735986</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05390690453333383</v>
+        <v>0.03296382691735986</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.07086292183957421</v>
+        <v>11.5747733979248</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1042335877843662</v>
+        <v>11.57971226689882</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1062815471969315</v>
+        <v>11.56926556127894</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09620215150936688</v>
+        <v>7.147526065242532</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07579478492320381</v>
+        <v>11.57795047849277</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1007943578719724</v>
+        <v>43.91295034856395</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1001986026750251</v>
+        <v>43.91571162157849</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1041556012714753</v>
+        <v>43.91631159196339</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1002043679278607</v>
+        <v>43.91486381961509</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07031799651125037</v>
+        <v>11.57653230419809</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1308421742718099</v>
+        <v>11.57245861523566</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1727775396232705</v>
+        <v>0.05390690453339506</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2176879615655749</v>
+        <v>0.05786390312977607</v>
       </c>
       <c r="D7" t="n">
-        <v>0.21373100399739</v>
+        <v>0.05390601571755806</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2649473761386699</v>
+        <v>0.05793839572932059</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2176879578024838</v>
+        <v>0.05793839572932059</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2143267181660719</v>
+        <v>0.05450265973036586</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2137309629691162</v>
+        <v>0.05390690453339506</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2176879615655749</v>
+        <v>0.05786390312977607</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2137309629691162</v>
+        <v>0.05390690453339506</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1621632821828374</v>
+        <v>0.05390690453339506</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2137309629691162</v>
+        <v>0.05390690453339506</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6249452246918714</v>
+        <v>0.07086292183957014</v>
       </c>
       <c r="C8" t="n">
-        <v>1.015193910563293</v>
+        <v>0.1042335877843427</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6021764319636749</v>
+        <v>0.1062815471969535</v>
       </c>
       <c r="E8" t="n">
-        <v>1.015193910563293</v>
+        <v>0.096202151509389</v>
       </c>
       <c r="F8" t="n">
-        <v>1.015193910563293</v>
+        <v>0.07579478492319487</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5681917716274731</v>
+        <v>0.1007943578719696</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5802053287495579</v>
+        <v>0.1001986026750531</v>
       </c>
       <c r="I8" t="n">
-        <v>1.015193910563293</v>
+        <v>0.1041556012714824</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4561251798564361</v>
+        <v>0.1002043679278652</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5243639154386325</v>
+        <v>0.0703179965112348</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6141849535654176</v>
+        <v>0.130842174271903</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1727775396232555</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2176879615655387</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.2137310039973739</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2649473761387057</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2176879578024749</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2143267181660961</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2137309629690958</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2176879615655387</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2137309629690958</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1621632821828347</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2137309629690958</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.624945224691872</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.015193910563298</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.602176431963675</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.015193910563298</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.015193910563298</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5681917716274696</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.580205328749557</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.015193910563298</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.456125179856432</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5243639154386284</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6141849535654202</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.61733947108792</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.053702370961794</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6080665851354208</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.053702370961794</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.053702370961794</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.594383356606718</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5991621612936827</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.053702370961794</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5486459075366954</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5763788527968787</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.6132796857662609</v>
+      <c r="B11" t="n">
+        <v>0.617339471087918</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.053702370961795</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6080665851354244</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.053702370961795</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.053702370961795</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.594383356606722</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5991621612936815</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.053702370961795</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5486459075366902</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5763788527968793</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6132796857662622</v>
       </c>
     </row>
   </sheetData>
@@ -839,7 +919,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -907,321 +987,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.06164263840607528</v>
+        <v>0.6094320229726964</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9697890330236296</v>
+        <v>1.078311609814761</v>
       </c>
       <c r="D2" t="n">
-        <v>2.769417898482206</v>
+        <v>0.6129018559592064</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9697890330236296</v>
+        <v>1.078311609814761</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9697890330236296</v>
+        <v>1.078311609814761</v>
       </c>
       <c r="G2" t="n">
-        <v>2.388325005553826</v>
+        <v>0.6120187980255865</v>
       </c>
       <c r="H2" t="n">
-        <v>5.153737879151559</v>
+        <v>0.6151898584834528</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9697890330236296</v>
+        <v>1.078311609814761</v>
       </c>
       <c r="J2" t="n">
-        <v>3.992506952498963</v>
+        <v>0.6138669033175413</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6579462034500211</v>
+        <v>0.6102178166737495</v>
       </c>
       <c r="L2" t="n">
-        <v>2.40837232866053</v>
+        <v>0.6097113975451347</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01855084700518965</v>
+        <v>0.6189718018950525</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01972269426337986</v>
+        <v>1.094159511920598</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01855084700518965</v>
+        <v>0.6189718018950525</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02016957627116284</v>
+        <v>1.094159511920598</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02016957627116282</v>
+        <v>1.094159511920598</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01903952992783582</v>
+        <v>0.6187061059596081</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01855084700518965</v>
+        <v>0.6189718018950525</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02182384692286235</v>
+        <v>1.094159511920598</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01855084700518965</v>
+        <v>0.6189718018950525</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01855084700518965</v>
+        <v>0.6189718018950525</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01855084700518965</v>
+        <v>0.6189718018950525</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.07232644913677</v>
+        <v>0.06164263840607501</v>
       </c>
       <c r="C4" t="n">
-        <v>10.07322207224974</v>
+        <v>0.9697890330236304</v>
       </c>
       <c r="D4" t="n">
-        <v>38.26842142192113</v>
+        <v>2.769417898482206</v>
       </c>
       <c r="E4" t="n">
-        <v>6.209390110534451</v>
+        <v>0.9697890330236304</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07524269748449</v>
+        <v>0.9697890330236304</v>
       </c>
       <c r="G4" t="n">
-        <v>38.26790202878298</v>
+        <v>2.388325005553829</v>
       </c>
       <c r="H4" t="n">
-        <v>38.27156530350516</v>
+        <v>5.153737879151552</v>
       </c>
       <c r="I4" t="n">
-        <v>10.07559944905444</v>
+        <v>0.9697890330236304</v>
       </c>
       <c r="J4" t="n">
-        <v>10.58470269869223</v>
+        <v>3.992506952498954</v>
       </c>
       <c r="K4" t="n">
-        <v>10.0697357627558</v>
+        <v>0.6579462034500211</v>
       </c>
       <c r="L4" t="n">
-        <v>10.0726479959372</v>
+        <v>2.408372328660531</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03321332059392356</v>
+        <v>0.01855084700518976</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03648632051159577</v>
+        <v>0.01972269426337987</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03321298417640864</v>
+        <v>0.01855084700518976</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03626024506770469</v>
+        <v>0.02016957627116282</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03626024506770471</v>
+        <v>0.02016957627116282</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0337020035165695</v>
+        <v>0.019039529927836</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03321332059392356</v>
+        <v>0.01855084700518976</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03648632051159577</v>
+        <v>0.02182384692286236</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03321332059392356</v>
+        <v>0.01855084700518976</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03321332059392356</v>
+        <v>0.01855084700518976</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03321332059392356</v>
+        <v>0.01855084700518976</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.04715722835051202</v>
+        <v>10.07232644913676</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07205569035303527</v>
+        <v>10.07322207224974</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07352236941657307</v>
+        <v>38.26842142192115</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06610594905841949</v>
+        <v>6.209390110534462</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05098776572316672</v>
+        <v>10.07524269748448</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06948299150081022</v>
+        <v>38.26790202878298</v>
       </c>
       <c r="H6" t="n">
-        <v>0.06899430857823718</v>
+        <v>38.27156530350516</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07226730849583626</v>
+        <v>10.07559944905445</v>
       </c>
       <c r="J6" t="n">
-        <v>0.06899860016164081</v>
+        <v>10.58470269869222</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04675159337655652</v>
+        <v>10.06973576275579</v>
       </c>
       <c r="L6" t="n">
-        <v>0.09180496483645086</v>
+        <v>10.0726479959372</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.09380751597339507</v>
+        <v>0.0332133205939231</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1194865554227326</v>
+        <v>0.03648632051159584</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1162135566927847</v>
+        <v>0.03321298417640813</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1453425619159412</v>
+        <v>0.0362602450677047</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1194864841305422</v>
+        <v>0.0362602450677047</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1167022384277065</v>
+        <v>0.03370200351656961</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1162135555050603</v>
+        <v>0.0332133205939231</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1194865554227326</v>
+        <v>0.03648632051159584</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1162135555050603</v>
+        <v>0.0332133205939231</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1032314087046611</v>
+        <v>0.0332133205939231</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1162135555050603</v>
+        <v>0.0332133205939231</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6179879649091979</v>
+        <v>0.0471572283505125</v>
       </c>
       <c r="C8" t="n">
-        <v>1.069263967757615</v>
+        <v>0.07205569035303538</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5453006662249501</v>
+        <v>0.07352236941657293</v>
       </c>
       <c r="E8" t="n">
-        <v>1.069263967757615</v>
+        <v>0.06610594905841956</v>
       </c>
       <c r="F8" t="n">
-        <v>1.069263967757615</v>
+        <v>0.05098776572316675</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5582333638568512</v>
+        <v>0.06948299150080987</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4996318233978235</v>
+        <v>0.06899430857823677</v>
       </c>
       <c r="I8" t="n">
-        <v>1.069263967757615</v>
+        <v>0.07226730849583633</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5257775037864504</v>
+        <v>0.06899860016164081</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6015369461170821</v>
+        <v>0.04675159337655588</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5672854966150294</v>
+        <v>0.09180496483645095</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.09380751597339505</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1194865554227326</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1162135566927847</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1453425619159414</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1194864841305424</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1167022384277063</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.11621355550506</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1194865554227326</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.11621355550506</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1032314087046608</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.11621355550506</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6179879649091984</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.069263967757616</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.54530066622495</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.069263967757616</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.069263967757616</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.558233363856852</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4996318233978237</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.069263967757616</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5257775037864499</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6015369461170825</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5672854966150311</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6089843740088297</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.066984057883211</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5793812544533302</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.066984057883211</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.066984057883211</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5845035076536377</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5608897879532675</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.066984057883211</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5714632006855206</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.6022849017331845</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5883727424032549</v>
+      <c r="B11" t="n">
+        <v>0.6089843740088301</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.066984057883212</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5793812544533309</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.066984057883212</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.066984057883212</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5845035076536378</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5608897879532685</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.066984057883212</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5714632006855205</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6022849017331847</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5883727424032552</v>
       </c>
     </row>
   </sheetData>
@@ -1235,7 +1395,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1303,320 +1463,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3.046116129654661</v>
+        <v>0.03428034328106405</v>
       </c>
       <c r="C2" t="n">
-        <v>0.6403633215199011</v>
+        <v>0.9266361660677938</v>
       </c>
       <c r="D2" t="n">
-        <v>1.478134101825914</v>
+        <v>1.09566759402195</v>
       </c>
       <c r="E2" t="n">
-        <v>2.762144075844979</v>
+        <v>1.058706907998262</v>
       </c>
       <c r="F2" t="n">
-        <v>2.762144075844979</v>
+        <v>1.058706907998262</v>
       </c>
       <c r="G2" t="n">
-        <v>1.980426758706899</v>
+        <v>0.565202679473736</v>
       </c>
       <c r="H2" t="n">
-        <v>2.7458594839327</v>
+        <v>1.096761206888935</v>
       </c>
       <c r="I2" t="n">
-        <v>2.762144075844979</v>
+        <v>1.058706907998262</v>
       </c>
       <c r="J2" t="n">
-        <v>4.070241217360011</v>
+        <v>0.6856264188482437</v>
       </c>
       <c r="K2" t="n">
-        <v>2.744385242897013</v>
+        <v>0.7651474485675427</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8917835784817464</v>
+        <v>1.191248077002458</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02378906340013709</v>
+        <v>0.03141983445985243</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02150353132817731</v>
+        <v>0.9405878402813906</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02378906340013709</v>
+        <v>1.111351999167491</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02731373472559914</v>
+        <v>1.072387891434389</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02731373472559914</v>
+        <v>1.072387891434389</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02422939951143913</v>
+        <v>0.5719418344245334</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02378906340013709</v>
+        <v>1.111351999167491</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02671629461435237</v>
+        <v>1.072387891434389</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02378906340013709</v>
+        <v>0.6920810965577985</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02378906340013709</v>
+        <v>0.7741675583986996</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02378906340013709</v>
+        <v>1.209228530724101</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>40.40325772281095</v>
+        <v>3.046116129654669</v>
       </c>
       <c r="C4" t="n">
-        <v>10.63490111895241</v>
+        <v>0.6403633215199026</v>
       </c>
       <c r="D4" t="n">
-        <v>10.63670557441538</v>
+        <v>1.478134101825914</v>
       </c>
       <c r="E4" t="n">
-        <v>6.562795912322084</v>
+        <v>2.762144075844975</v>
       </c>
       <c r="F4" t="n">
-        <v>10.6413435423474</v>
+        <v>2.762144075844975</v>
       </c>
       <c r="G4" t="n">
-        <v>10.6388071341742</v>
+        <v>1.980426758706901</v>
       </c>
       <c r="H4" t="n">
-        <v>40.40807774265987</v>
+        <v>2.745859483932702</v>
       </c>
       <c r="I4" t="n">
-        <v>10.64129402927711</v>
+        <v>2.762144075844975</v>
       </c>
       <c r="J4" t="n">
-        <v>40.40608309637921</v>
+        <v>4.070241217360009</v>
       </c>
       <c r="K4" t="n">
-        <v>10.63919488846955</v>
+        <v>2.744385242897014</v>
       </c>
       <c r="L4" t="n">
-        <v>10.63762014578711</v>
+        <v>0.8917835784817459</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03996393506799598</v>
+        <v>0.02378906340013706</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03991309207036278</v>
+        <v>0.02150353132817735</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03996350298001253</v>
+        <v>0.02378906340013706</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0429326630780768</v>
+        <v>0.02731373472559908</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0429326630780768</v>
+        <v>0.02731373472559909</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04040427117929801</v>
+        <v>0.02422939951143905</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03996393506799598</v>
+        <v>0.02378906340013706</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04289116628221133</v>
+        <v>0.02671629461435234</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03996393506799598</v>
+        <v>0.02378906340013706</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03996393506799598</v>
+        <v>0.02378906340013706</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03996393506799598</v>
+        <v>0.02378906340013706</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05348472076636267</v>
+        <v>40.40325772281093</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07678137377308349</v>
+        <v>10.63490111895242</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08161948568627263</v>
+        <v>10.63670557441538</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07338157160429329</v>
+        <v>6.562795912322088</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05717562680898793</v>
+        <v>10.6413435423474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07722783827430985</v>
+        <v>10.6388071341742</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07678750216312165</v>
+        <v>40.40807774265988</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07971473337722315</v>
+        <v>10.64129402927711</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07679208178352936</v>
+        <v>40.40608309637917</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05305185964198363</v>
+        <v>10.63919488846955</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1011292058383582</v>
+        <v>10.6376201457871</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.10992822299319</v>
+        <v>0.03996393506799602</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1356297041720912</v>
+        <v>0.03991309207036276</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1356805785749404</v>
+        <v>0.03996350298001258</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1683254390764167</v>
+        <v>0.04293266307807682</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1386077753764018</v>
+        <v>0.04293266307807682</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1361208832810266</v>
+        <v>0.040404271179298</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1356805471697247</v>
+        <v>0.03996393506799602</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1386077783839398</v>
+        <v>0.0428911662822113</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1356805471697247</v>
+        <v>0.03996393506799602</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1207595626135711</v>
+        <v>0.03996393506799602</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1356805471697247</v>
+        <v>0.03996393506799602</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03626645087264685</v>
+        <v>0.05348472076636261</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9266937570077319</v>
+        <v>0.0767813737730835</v>
       </c>
       <c r="D8" t="n">
-        <v>1.07770639854991</v>
+        <v>0.08161948568627252</v>
       </c>
       <c r="E8" t="n">
-        <v>1.009780938293802</v>
+        <v>0.07338157160429318</v>
       </c>
       <c r="F8" t="n">
-        <v>1.009780938293802</v>
+        <v>0.05717562680898781</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5280301881075241</v>
+        <v>0.07722783827430986</v>
       </c>
       <c r="H8" t="n">
-        <v>1.055850584457575</v>
+        <v>0.07678750216312159</v>
       </c>
       <c r="I8" t="n">
-        <v>1.009780938293802</v>
+        <v>0.07971473337722319</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6032715131673448</v>
+        <v>0.07679208178352924</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7115230680668366</v>
+        <v>0.05305185964198361</v>
       </c>
       <c r="L8" t="n">
-        <v>1.191867489734711</v>
+        <v>0.101129205838358</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1099282229931901</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1356297041720913</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1356805785749403</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1683254390764168</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.138607775376402</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1361208832810267</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1356805471697246</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1386077783839399</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1356805471697246</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1207595626135711</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1356805471697246</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.03626645087264697</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9266937570077315</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.07770639854991</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.009780938293802</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.009780938293802</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5280301881075238</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.055850584457575</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.009780938293802</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6032715131673454</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7115230680668362</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.19186748973471</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.003482867751384055</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9203143139004628</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.003482867751384009</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9203143139004624</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.080358738518784</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.030220544802773</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.030220544802773</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5452227404613829</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="E11" t="n">
+        <v>1.030220544802774</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.030220544802774</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5452227404613827</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.07150788632341</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.030220544802773</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6452177753862379</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7366440058304005</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="I11" t="n">
+        <v>1.030220544802774</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6452177753862376</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7366440058303997</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.183348748025931</v>
       </c>
     </row>
@@ -1631,7 +1871,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1699,321 +1939,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.664242935536041</v>
+        <v>0.02749005459451577</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4048636521308361</v>
+        <v>0.9241268627094995</v>
       </c>
       <c r="D2" t="n">
-        <v>1.512657121738278</v>
+        <v>1.08729735515946</v>
       </c>
       <c r="E2" t="n">
-        <v>1.313714705599412</v>
+        <v>1.051472254722973</v>
       </c>
       <c r="F2" t="n">
-        <v>1.313714705599412</v>
+        <v>1.051472254722973</v>
       </c>
       <c r="G2" t="n">
-        <v>1.297873658794061</v>
+        <v>0.5600175100718795</v>
       </c>
       <c r="H2" t="n">
-        <v>2.214748472458764</v>
+        <v>1.087855289901527</v>
       </c>
       <c r="I2" t="n">
-        <v>1.313714705599412</v>
+        <v>1.051472254722973</v>
       </c>
       <c r="J2" t="n">
-        <v>2.780524617824658</v>
+        <v>0.6795077513510904</v>
       </c>
       <c r="K2" t="n">
-        <v>1.355063623393793</v>
+        <v>0.7565036328983729</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6512552293962188</v>
+        <v>1.188092303437739</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01767294305015751</v>
+        <v>0.02594820100418873</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01587094121639201</v>
+        <v>0.9382922436475493</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01767294305015751</v>
+        <v>1.102735925476312</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02035092678417914</v>
+        <v>1.066592597649728</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02035092678417914</v>
+        <v>1.066592597649728</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01808797219969788</v>
+        <v>0.5673634932963006</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01767294305015751</v>
+        <v>1.102735925476312</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02043788176339836</v>
+        <v>1.066592597649728</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01767294305015751</v>
+        <v>0.6871025124387881</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01767294305015751</v>
+        <v>0.7668738055956634</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01767294305015751</v>
+        <v>1.206244675085143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.25803499646351</v>
+        <v>1.664242935536041</v>
       </c>
       <c r="C4" t="n">
-        <v>10.06623177732575</v>
+        <v>0.4048636521308372</v>
       </c>
       <c r="D4" t="n">
-        <v>38.2585054481635</v>
+        <v>1.512657121738281</v>
       </c>
       <c r="E4" t="n">
-        <v>6.207173109228791</v>
+        <v>1.31371470559941</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07102515673249</v>
+        <v>1.31371470559941</v>
       </c>
       <c r="G4" t="n">
-        <v>38.25845002561306</v>
+        <v>1.297873658794059</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26233550208968</v>
+        <v>2.214748472458764</v>
       </c>
       <c r="I4" t="n">
-        <v>10.07113182438911</v>
+        <v>1.31371470559941</v>
       </c>
       <c r="J4" t="n">
-        <v>10.58000844617902</v>
+        <v>2.780524617824655</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06827730722448</v>
+        <v>1.355063623393794</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06801721542149</v>
+        <v>0.6512552293962206</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02930873607868764</v>
+        <v>0.01767294305015699</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02926666441068767</v>
+        <v>0.015870941216392</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02930835438254917</v>
+        <v>0.01767294305015699</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03206133926601117</v>
+        <v>0.02035092678417914</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03206133926601117</v>
+        <v>0.02035092678417912</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02972376522822802</v>
+        <v>0.01808797219969784</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02930873607868764</v>
+        <v>0.01767294305015699</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03207367479192849</v>
+        <v>0.02043788176339834</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02930873607868764</v>
+        <v>0.01767294305015699</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02930873607868764</v>
+        <v>0.01767294305015699</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02930873607868764</v>
+        <v>0.01767294305015699</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03958238905424772</v>
+        <v>38.25803499646352</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05684332092649917</v>
+        <v>10.06623177732574</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06048289802436737</v>
+        <v>38.25850544816348</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05491672872710197</v>
+        <v>6.207173109228787</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04288892767786284</v>
+        <v>10.07102515673248</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05730838536495751</v>
+        <v>38.25845002561307</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05689335621554303</v>
+        <v>38.26233550208966</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05965829492865771</v>
+        <v>10.07113182438911</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05689675828091657</v>
+        <v>10.58000844617901</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0392608289548919</v>
+        <v>10.06827730722447</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07497610890205401</v>
+        <v>10.06801721542149</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07301680347412519</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08975583262821354</v>
+        <v>0.02926666441068763</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08979792055234392</v>
+        <v>0.02930835438254918</v>
       </c>
       <c r="E7" t="n">
-        <v>0.111927875510787</v>
+        <v>0.03206133926601115</v>
       </c>
       <c r="F7" t="n">
-        <v>0.09256282962885888</v>
+        <v>0.03206133926601115</v>
       </c>
       <c r="G7" t="n">
-        <v>0.09021293344575385</v>
+        <v>0.0297237652282278</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08979790429621355</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="I7" t="n">
-        <v>0.09256284300945437</v>
+        <v>0.03207367479192845</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08979790429621355</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="K7" t="n">
-        <v>0.08007487541269277</v>
+        <v>0.02930873607868767</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08979790429621355</v>
+        <v>0.02930873607868767</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.01298949236560181</v>
+        <v>0.03958238905424707</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9290764566008631</v>
+        <v>0.05684332092649905</v>
       </c>
       <c r="D8" t="n">
-        <v>1.066232243776106</v>
+        <v>0.0604828980243674</v>
       </c>
       <c r="E8" t="n">
-        <v>1.035332730748298</v>
+        <v>0.05491672872710194</v>
       </c>
       <c r="F8" t="n">
-        <v>1.035332730748298</v>
+        <v>0.04288892767786288</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5370309806331444</v>
+        <v>0.05730838536495751</v>
       </c>
       <c r="H8" t="n">
-        <v>1.055442700981085</v>
+        <v>0.05689335621554194</v>
       </c>
       <c r="I8" t="n">
-        <v>1.035332730748298</v>
+        <v>0.0596582949286578</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6230816348252317</v>
+        <v>0.05689675828091654</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7343528221950625</v>
+        <v>0.03926082895489239</v>
       </c>
       <c r="L8" t="n">
-        <v>1.192865831955772</v>
+        <v>0.07497610890205361</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.07301680347412483</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.08975583262821339</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08979792055234385</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1119278755107868</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.09256282962885871</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.09021293344575332</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.08979790429621337</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.09256284300945423</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.08979790429621337</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.08007487541269229</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.08979790429621337</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.01298949236560174</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9290764566008627</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.066232243776105</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.035332730748298</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.035332730748298</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5370309806331449</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.055442700981085</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.035332730748298</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.623081634825232</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7343528221950621</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.192865831955772</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.009773280024194737</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9199336502342866</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.070688063655535</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.037248915663538</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.037248915663538</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5462161201461616</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.066336722041636</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.037248915663538</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6503780480144914</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7417064818128742</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.18200488717803</v>
+      <c r="B11" t="n">
+        <v>0.009773280024194584</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.919933650234286</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.070688063655534</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.037248915663537</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.037248915663537</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5462161201461613</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.066336722041634</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.037248915663537</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6503780480144904</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7417064818128739</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.182004887178031</v>
       </c>
     </row>
   </sheetData>
@@ -2027,7 +2347,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2095,321 +2415,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8205170598971161</v>
+        <v>0.02264659030937808</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2603663900424644</v>
+        <v>0.9224943112157435</v>
       </c>
       <c r="D2" t="n">
-        <v>1.634523997004006</v>
+        <v>1.081373348226835</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4536471152291348</v>
+        <v>1.047052040990707</v>
       </c>
       <c r="F2" t="n">
-        <v>0.4536471152291348</v>
+        <v>1.047052040990707</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9138048723027484</v>
+        <v>0.5565023212484529</v>
       </c>
       <c r="H2" t="n">
-        <v>1.791896253236251</v>
+        <v>1.081346393596739</v>
       </c>
       <c r="I2" t="n">
-        <v>0.4536471152291348</v>
+        <v>1.047052040990707</v>
       </c>
       <c r="J2" t="n">
-        <v>2.21059567862122</v>
+        <v>0.6750092033819216</v>
       </c>
       <c r="K2" t="n">
-        <v>0.5160070554283337</v>
+        <v>0.752517292135889</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3504569570316196</v>
+        <v>1.185389969080974</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01353020126459328</v>
+        <v>0.02201410811119961</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01222286857983233</v>
+        <v>0.9368154798599493</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01353020126459327</v>
+        <v>1.09658822777794</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01554141074782475</v>
+        <v>1.063129518578741</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01554141074782476</v>
+        <v>1.063129518578741</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01392916878544551</v>
+        <v>0.5642515345316715</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01353020126459327</v>
+        <v>1.09658822777794</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01619210020985768</v>
+        <v>1.063129518578741</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01353020126459327</v>
+        <v>0.6831925154459271</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01353020126459327</v>
+        <v>0.7638279788635937</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01353020126459327</v>
+        <v>1.203827176688313</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.06193008645181</v>
+        <v>0.8205170598971171</v>
       </c>
       <c r="C4" t="n">
-        <v>10.06059835433641</v>
+        <v>0.2603663900424644</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06353710181743</v>
+        <v>1.634523997004009</v>
       </c>
       <c r="E4" t="n">
-        <v>6.200073086571381</v>
+        <v>0.4536471152291345</v>
       </c>
       <c r="F4" t="n">
-        <v>10.0643876746881</v>
+        <v>0.4536471152291345</v>
       </c>
       <c r="G4" t="n">
-        <v>38.24965498650504</v>
+        <v>0.913804872302735</v>
       </c>
       <c r="H4" t="n">
-        <v>38.25326815095776</v>
+        <v>1.791896253236256</v>
       </c>
       <c r="I4" t="n">
-        <v>38.25191791792945</v>
+        <v>0.4536471152291345</v>
       </c>
       <c r="J4" t="n">
-        <v>38.2517715532467</v>
+        <v>2.210595678621221</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06123138573822</v>
+        <v>0.516007055428322</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06178500206281</v>
+        <v>0.3504569570316199</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0224896425993104</v>
+        <v>0.01353020126459333</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02245364066034333</v>
+        <v>0.01222286857983233</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02248923156270692</v>
+        <v>0.01353020126459333</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02506207283333804</v>
+        <v>0.01554141074782481</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02506207283333804</v>
+        <v>0.0155414107478248</v>
       </c>
       <c r="G5" t="n">
-        <v>0.0228886101201626</v>
+        <v>0.01392916878544551</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0224896425993104</v>
+        <v>0.01353020126459333</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02515154154457476</v>
+        <v>0.01619210020985772</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0224896425993104</v>
+        <v>0.01353020126459333</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0224896425993104</v>
+        <v>0.01353020126459333</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0224896425993104</v>
+        <v>0.01353020126459333</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.030851189561743</v>
+        <v>10.0619300864518</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04440583812064931</v>
+        <v>10.06059835433642</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04735937693239529</v>
+        <v>10.06353710181743</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04337292818552024</v>
+        <v>6.200073086571384</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03389337433116513</v>
+        <v>10.0643876746881</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04492315853306948</v>
+        <v>38.24965498650504</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04452419101237357</v>
+        <v>38.25326815095776</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04718608995748165</v>
+        <v>38.25191791792943</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0445268781211255</v>
+        <v>38.2517715532467</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03059720654257621</v>
+        <v>10.06123138573804</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05880678431956845</v>
+        <v>10.06178500206282</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05299326383181791</v>
+        <v>0.02248964259931025</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06503197832492801</v>
+        <v>0.02245364066034328</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06506798939745381</v>
+        <v>0.02248923156270686</v>
       </c>
       <c r="E7" t="n">
-        <v>0.08166383139810945</v>
+        <v>0.02506207283333793</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06772986096526502</v>
+        <v>0.02506207283333793</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06546694778474726</v>
+        <v>0.02288861012016247</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06506798026389522</v>
+        <v>0.02248964259931025</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06772987920915942</v>
+        <v>0.02515154154457481</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06506798026389522</v>
+        <v>0.02248964259931025</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05778800360786734</v>
+        <v>0.02248964259931025</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06506798026389522</v>
+        <v>0.02248964259931025</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.002929264260533969</v>
+        <v>0.03085118956174294</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9309413586115592</v>
+        <v>0.04440583812064933</v>
       </c>
       <c r="D8" t="n">
-        <v>1.057021002846224</v>
+        <v>0.04735937693239504</v>
       </c>
       <c r="E8" t="n">
-        <v>1.052549184758659</v>
+        <v>0.04337292818552013</v>
       </c>
       <c r="F8" t="n">
-        <v>1.052549184758659</v>
+        <v>0.03389337433116513</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5429265792016402</v>
+        <v>0.04492315853306919</v>
       </c>
       <c r="H8" t="n">
-        <v>1.058313305265897</v>
+        <v>0.04452419101237322</v>
       </c>
       <c r="I8" t="n">
-        <v>1.052549184758659</v>
+        <v>0.04718608995748128</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6322873573263379</v>
+        <v>0.0445268781211248</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7516035942988911</v>
+        <v>0.03059720654257626</v>
       </c>
       <c r="L8" t="n">
-        <v>1.196713579601303</v>
+        <v>0.05880678431956805</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.05299326383181777</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06503197832492755</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06506798939745394</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.08166383139810918</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.06772986096526469</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.0654669477847472</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.06506798026389433</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.06772987920915949</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.06506798026389433</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.057788003607867</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.06506798026389433</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.002929264260533944</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9309413586115585</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.057021002846224</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.052549184758659</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.052549184758659</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5429265792016408</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.058313305265897</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.052549184758659</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6322873573263388</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7516035942988921</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.196713579601303</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01396292553753658</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9198215673280123</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.01396292553753654</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9198215673280128</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.063370134789639</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.042237955385043</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.042237955385043</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5467993986146892</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="E11" t="n">
+        <v>1.042237955385044</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.042237955385044</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5467993986146888</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.063931181878818</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.042237955385043</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6518471942123946</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7469551582021484</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.182153259736697</v>
+      <c r="I11" t="n">
+        <v>1.042237955385044</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6518471942123945</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7469551582021483</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.182153259736696</v>
       </c>
     </row>
   </sheetData>
@@ -2423,7 +2823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2491,321 +2891,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.963693015655052</v>
+        <v>0.03640632676615568</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4885787337731562</v>
+        <v>0.9257101080547834</v>
       </c>
       <c r="D2" t="n">
-        <v>1.559134217022473</v>
+        <v>1.09441965563176</v>
       </c>
       <c r="E2" t="n">
-        <v>2.517142796928533</v>
+        <v>1.057302547283586</v>
       </c>
       <c r="F2" t="n">
-        <v>2.517142796928533</v>
+        <v>1.057302547283586</v>
       </c>
       <c r="G2" t="n">
-        <v>1.948324188744592</v>
+        <v>0.5647557404744789</v>
       </c>
       <c r="H2" t="n">
-        <v>5.201077989882064</v>
+        <v>1.097857792607192</v>
       </c>
       <c r="I2" t="n">
-        <v>2.517142796928533</v>
+        <v>1.057302547283586</v>
       </c>
       <c r="J2" t="n">
-        <v>4.022819101598184</v>
+        <v>0.6852786220788443</v>
       </c>
       <c r="K2" t="n">
-        <v>2.440162760863803</v>
+        <v>0.7623723115219615</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4776289383961775</v>
+        <v>1.19042548047313</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02298377229411371</v>
+        <v>0.03367113252855546</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02056728801463127</v>
+        <v>0.9398148181909455</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02298377229411371</v>
+        <v>1.109995011727349</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0261926813163945</v>
+        <v>1.071236658682384</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0261926813163945</v>
+        <v>1.071236658682384</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02341572994424402</v>
+        <v>0.5715250225630428</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02298377229411371</v>
+        <v>1.109995011727349</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02585735547118062</v>
+        <v>1.071236658682384</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02298377229411371</v>
+        <v>0.6917802314437238</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02298377229411371</v>
+        <v>0.7716895746519699</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02298377229411371</v>
+        <v>1.208802249047171</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.63712249891232</v>
+        <v>2.963693015655042</v>
       </c>
       <c r="C4" t="n">
-        <v>10.63347906060107</v>
+        <v>0.488578733773147</v>
       </c>
       <c r="D4" t="n">
-        <v>10.63578927791338</v>
+        <v>1.559134217022454</v>
       </c>
       <c r="E4" t="n">
-        <v>6.561145615295805</v>
+        <v>2.517142796928557</v>
       </c>
       <c r="F4" t="n">
-        <v>10.63995166019024</v>
+        <v>2.517142796928557</v>
       </c>
       <c r="G4" t="n">
-        <v>10.63755445656245</v>
+        <v>1.948324188744553</v>
       </c>
       <c r="H4" t="n">
-        <v>40.40724691257221</v>
+        <v>5.201077989882034</v>
       </c>
       <c r="I4" t="n">
-        <v>40.40462865754921</v>
+        <v>2.517142796928557</v>
       </c>
       <c r="J4" t="n">
-        <v>11.17744757392963</v>
+        <v>4.022819101598255</v>
       </c>
       <c r="K4" t="n">
-        <v>10.63751661898261</v>
+        <v>2.440162760863783</v>
       </c>
       <c r="L4" t="n">
-        <v>10.636280947643</v>
+        <v>0.4776289383961511</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03895287330394701</v>
+        <v>0.02298377229411601</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0388964085378998</v>
+        <v>0.02056728801463086</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03895246359745817</v>
+        <v>0.02298377229411601</v>
       </c>
       <c r="E5" t="n">
-        <v>0.0418344175442181</v>
+        <v>0.02619268131639337</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0418344175442181</v>
+        <v>0.02619268131639334</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03938483095407729</v>
+        <v>0.02341572994424046</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03895287330394701</v>
+        <v>0.02298377229411601</v>
       </c>
       <c r="I5" t="n">
-        <v>0.0418264564810139</v>
+        <v>0.02585735547117836</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03895287330394701</v>
+        <v>0.02298377229411601</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03895287330394701</v>
+        <v>0.02298377229411601</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03895287330394701</v>
+        <v>0.02298377229411601</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05238115697573838</v>
+        <v>10.63712249891232</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07545052630736568</v>
+        <v>10.63347906060108</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08028707118513785</v>
+        <v>10.63578927791336</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07205793424122403</v>
+        <v>6.561145615295814</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05599238759276927</v>
+        <v>10.63995166019028</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07592634910099082</v>
+        <v>10.63755445656244</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07549439145099113</v>
+        <v>40.40724691257221</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07836797462792743</v>
+        <v>40.40462865754921</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07549893381953594</v>
+        <v>11.17744757392964</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05195181678277874</v>
+        <v>10.63751661898261</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0996380975166216</v>
+        <v>10.63628094764298</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1070380840844688</v>
+        <v>0.03895287330398772</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1321573871035031</v>
+        <v>0.03889640853791612</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1322138522754604</v>
+        <v>0.03895246359741687</v>
       </c>
       <c r="E7" t="n">
-        <v>0.164139692546476</v>
+        <v>0.04183441754423012</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1350873989837701</v>
+        <v>0.04183441754423012</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1326458095196807</v>
+        <v>0.03938483095408461</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1322138518695504</v>
+        <v>0.03895287330398772</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1350874350466173</v>
+        <v>0.04182645648103852</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1322138518695504</v>
+        <v>0.03895287330398772</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1176269133127303</v>
+        <v>0.03895287330398772</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1322138518695504</v>
+        <v>0.03895287330398772</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03218921087411608</v>
+        <v>0.05238115697572608</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9293127130399674</v>
+        <v>0.07545052630733523</v>
       </c>
       <c r="D8" t="n">
-        <v>1.074457604608388</v>
+        <v>0.08028707118510046</v>
       </c>
       <c r="E8" t="n">
-        <v>1.014213224905566</v>
+        <v>0.07205793424125513</v>
       </c>
       <c r="F8" t="n">
-        <v>1.014213224905566</v>
+        <v>0.05599238759277961</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5283139872980309</v>
+        <v>0.07592634910097903</v>
       </c>
       <c r="H8" t="n">
-        <v>1.00443605542748</v>
+        <v>0.07549439145100334</v>
       </c>
       <c r="I8" t="n">
-        <v>1.014213224905566</v>
+        <v>0.0783679746279414</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6039922116336292</v>
+        <v>0.07549893381956202</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7160264712456533</v>
+        <v>0.05195181678275616</v>
       </c>
       <c r="L8" t="n">
-        <v>1.199697804762867</v>
+        <v>0.09963809751664077</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1070380840844915</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.132157387103492</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1322138522754355</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1641396925464283</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1350873989837203</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1326458095197101</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.132213851869554</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1350874350466211</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.132213851869554</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1176269133127086</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.132213851869554</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.03218921087411552</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9293127130399683</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.074457604608386</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.014213224905566</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.014213224905566</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5283139872980248</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.004436055427482</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.014213224905566</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6039922116336247</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.716026471245651</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.199697804762859</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.006439660633475847</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9209316167428691</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.078250022141638</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.031356703192231</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.031356703192231</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5450945817234989</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.049828131094318</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.031356703192231</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6453347933014336</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7370454220843047</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.186282929309624</v>
+      <c r="B11" t="n">
+        <v>0.006439660633473613</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9209316167428647</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.078250022141628</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.031356703192232</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.031356703192232</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5450945817234961</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.049828131094314</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.031356703192232</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6453347933014295</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7370454220843046</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.186282929309617</v>
       </c>
     </row>
   </sheetData>
@@ -2819,7 +3299,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2887,320 +3367,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.444451810011891</v>
+        <v>0.02869005516813145</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1947636355479004</v>
+        <v>0.9231072422734249</v>
       </c>
       <c r="D2" t="n">
-        <v>1.611626490461505</v>
+        <v>1.085869796220353</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9562582942841555</v>
+        <v>1.049581516144681</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9562582942841555</v>
+        <v>1.049581516144681</v>
       </c>
       <c r="G2" t="n">
-        <v>1.276512866966089</v>
+        <v>0.5595548893986804</v>
       </c>
       <c r="H2" t="n">
-        <v>7.518928521791651</v>
+        <v>1.091863861150151</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9562582942841555</v>
+        <v>1.049581516144681</v>
       </c>
       <c r="J2" t="n">
-        <v>2.373142965962558</v>
+        <v>0.6792149443445905</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9601655268521173</v>
+        <v>0.7524636021993548</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1813258419793944</v>
+        <v>1.187522325282691</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01693795533799916</v>
+        <v>0.02742013302421936</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01471676235264083</v>
+        <v>0.9374990474975377</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01693795533799916</v>
+        <v>1.101168352285984</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01922309703409544</v>
+        <v>1.065093717105275</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01922309703409544</v>
+        <v>1.065093717105275</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01733746511412003</v>
+        <v>0.5669189314226322</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01693795533799916</v>
+        <v>1.101168352285984</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01960342445984825</v>
+        <v>1.065093717105275</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01693795533799916</v>
+        <v>0.6872660883660406</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01693795533799916</v>
+        <v>0.7632348740531432</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01693795533799916</v>
+        <v>1.206153998159242</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.0671067370399</v>
+        <v>1.444451810011889</v>
       </c>
       <c r="C4" t="n">
-        <v>10.0646065231555</v>
+        <v>0.1947636355479004</v>
       </c>
       <c r="D4" t="n">
-        <v>38.25785574375224</v>
+        <v>1.611626490461502</v>
       </c>
       <c r="E4" t="n">
-        <v>6.205211587243014</v>
+        <v>0.9562582942841561</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06956586374593</v>
+        <v>0.9562582942841561</v>
       </c>
       <c r="G4" t="n">
-        <v>10.067506246816</v>
+        <v>1.276512866966096</v>
       </c>
       <c r="H4" t="n">
-        <v>38.2661913639696</v>
+        <v>7.518928521791654</v>
       </c>
       <c r="I4" t="n">
-        <v>38.25968934120586</v>
+        <v>0.9562582942841561</v>
       </c>
       <c r="J4" t="n">
-        <v>38.259974663973</v>
+        <v>2.373142965962557</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06641808967417</v>
+        <v>0.96016552685212</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06668108931284</v>
+        <v>0.181325841979393</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0289642768675587</v>
+        <v>0.016937955337999</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02891154277366317</v>
+        <v>0.0147167623526408</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02896401196405926</v>
+        <v>0.016937955337999</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03160729873396542</v>
+        <v>0.01922309703409546</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03160729873396542</v>
+        <v>0.01922309703409546</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02936378664367958</v>
+        <v>0.01733746511411917</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0289642768675587</v>
+        <v>0.016937955337999</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03162974598940785</v>
+        <v>0.01960342445984827</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0289642768675587</v>
+        <v>0.016937955337999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0289642768675587</v>
+        <v>0.016937955337999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0289642768675587</v>
+        <v>0.016937955337999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0398392853477459</v>
+        <v>10.0671067370399</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05795951561200353</v>
+        <v>10.06460652315551</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06180180422642663</v>
+        <v>38.25785574375225</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05570461590378402</v>
+        <v>6.205211587243014</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04306813503610202</v>
+        <v>10.06956586374593</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05842937812029035</v>
+        <v>10.06750624681601</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05802986834533099</v>
+        <v>38.2661913639696</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06069533746601854</v>
+        <v>38.25968934120583</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05803344327535722</v>
+        <v>38.259974663973</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03950138593298866</v>
+        <v>10.06641808967428</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0770314533190061</v>
+        <v>10.06668108931284</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07049888029545048</v>
+        <v>0.0289642768675583</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08684277913777572</v>
+        <v>0.02891154277366314</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08689546288259732</v>
+        <v>0.028964011964059</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1084821984347045</v>
+        <v>0.03160729873396545</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08956089823516415</v>
+        <v>0.03160729873396545</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0872950230077922</v>
+        <v>0.02936378664367904</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08689551323167127</v>
+        <v>0.0289642768675583</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0895609823535204</v>
+        <v>0.03162974598940783</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08689551323167127</v>
+        <v>0.0289642768675583</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07739521853725675</v>
+        <v>0.0289642768675583</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08689551323167127</v>
+        <v>0.0289642768675583</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.006351056312792689</v>
+        <v>0.03983928534774567</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9332419448808508</v>
+        <v>0.05795951561200362</v>
       </c>
       <c r="D8" t="n">
-        <v>1.062223480073341</v>
+        <v>0.06180180422642551</v>
       </c>
       <c r="E8" t="n">
-        <v>1.042438151930787</v>
+        <v>0.05570461590378413</v>
       </c>
       <c r="F8" t="n">
-        <v>1.042438151930787</v>
+        <v>0.04306813503610202</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5370662490239768</v>
+        <v>0.05842937812028931</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9397181918161982</v>
+        <v>0.05802986834533005</v>
       </c>
       <c r="I8" t="n">
-        <v>1.042438151930787</v>
+        <v>0.06069533746601855</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6326566563487834</v>
+        <v>0.05803344327535687</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7402823315297554</v>
+        <v>0.0395013859329878</v>
       </c>
       <c r="L8" t="n">
-        <v>1.202664089661443</v>
+        <v>0.07703145331900478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.07049888029544917</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.08684277913777592</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08689546288259564</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1084821984347046</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.08956089823516424</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.08729502300779247</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0868955132316713</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08956098235352046</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0868955132316713</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.07739521853725619</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0868955132316713</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.006351056312793043</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.933241944880852</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.062223480073341</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.042438151930788</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.042438151930788</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5370662490239765</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9397181918161981</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.042438151930788</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6326566563487817</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7402823315297555</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.202664089661444</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.0133240563973962</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9211702470162513</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.01332405639739606</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9211702470162507</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.068149755253656</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>1.039273161791286</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.039273161791286</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.545971823772437</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.5459718237724379</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.018403523625264</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>1.039273161791286</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.6543674787468047</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.742020122205801</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J11" t="n">
+        <v>0.6543674787468039</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7420201222058003</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.185934405794514</v>
       </c>
     </row>
@@ -3215,7 +3775,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3283,321 +3843,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6193486447824748</v>
+        <v>0.02369394839720323</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08531576319712451</v>
+        <v>0.9220617412463565</v>
       </c>
       <c r="D2" t="n">
-        <v>1.563254771769569</v>
+        <v>1.081038705467808</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2655385165724848</v>
+        <v>1.046552427469986</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2655385165724848</v>
+        <v>1.046552427469986</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7675489936075058</v>
+        <v>0.5563405120355822</v>
       </c>
       <c r="H2" t="n">
-        <v>5.387212611858689</v>
+        <v>1.08485761008401</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2655385165724848</v>
+        <v>1.046552427469986</v>
       </c>
       <c r="J2" t="n">
-        <v>1.326804953757654</v>
+        <v>0.6747134728869697</v>
       </c>
       <c r="K2" t="n">
-        <v>0.2474445491499484</v>
+        <v>0.7506855488815245</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0534711795958223</v>
+        <v>1.185360589961722</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01332421253608602</v>
+        <v>0.0233098742089888</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01086114650649175</v>
+        <v>0.9365783556788464</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01332421253608602</v>
+        <v>1.09633263059182</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01484128469186279</v>
+        <v>1.062843263751453</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01484128469186279</v>
+        <v>1.062843263751453</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01371750154848801</v>
+        <v>0.5642561398134434</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01332421253608602</v>
+        <v>1.09633263059182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01594984727540543</v>
+        <v>1.062843263751453</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01332421253608602</v>
+        <v>0.6838927145731017</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01332421253608602</v>
+        <v>0.7622837683596172</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01332421253608602</v>
+        <v>1.204106190256813</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.24868512641653</v>
+        <v>0.6193486447824773</v>
       </c>
       <c r="C4" t="n">
-        <v>10.05966368285087</v>
+        <v>0.08531576319712468</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06302574457075</v>
+        <v>1.563254771769573</v>
       </c>
       <c r="E4" t="n">
-        <v>6.199168189685286</v>
+        <v>0.265538516572485</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06373003164412</v>
+        <v>0.265538516572485</v>
       </c>
       <c r="G4" t="n">
-        <v>38.24907841542894</v>
+        <v>0.7675489936075055</v>
       </c>
       <c r="H4" t="n">
-        <v>10.06298267085956</v>
+        <v>5.387212611858695</v>
       </c>
       <c r="I4" t="n">
-        <v>38.25131076115587</v>
+        <v>0.265538516572485</v>
       </c>
       <c r="J4" t="n">
-        <v>10.57276221746122</v>
+        <v>1.326804953757656</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06029716798885</v>
+        <v>0.2474445491499508</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06112023974036</v>
+        <v>0.05347117959582277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02247479205166843</v>
+        <v>0.01332421253608828</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02243501344126069</v>
+        <v>0.01086114650649135</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02247467076795894</v>
+        <v>0.01332421253608828</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02490849766912896</v>
+        <v>0.01484128469186284</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02490849766912896</v>
+        <v>0.01484128469186286</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02286808106406913</v>
+        <v>0.01371750154848893</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02247479205166843</v>
+        <v>0.01332421253608828</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02510042679098631</v>
+        <v>0.01594984727540523</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02247479205166843</v>
+        <v>0.01332421253608828</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02247479205166843</v>
+        <v>0.01332421253608828</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02247479205166843</v>
+        <v>0.01332421253608828</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0315530857907317</v>
+        <v>38.24868512641653</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04609344622166026</v>
+        <v>10.05966368285087</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0493744863588099</v>
+        <v>10.06302574457076</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04474112995114232</v>
+        <v>6.19916818968529</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03453218856483153</v>
+        <v>10.06373003164412</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04670705266288323</v>
+        <v>38.24907841542896</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04631376365210672</v>
+        <v>10.06298267085956</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04893939838979951</v>
+        <v>38.25131076115578</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04631666450568539</v>
+        <v>10.57276221746121</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03127889862500743</v>
+        <v>10.06029716798885</v>
       </c>
       <c r="L6" t="n">
-        <v>0.06173252590421061</v>
+        <v>10.06112023974037</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.04986325935653482</v>
+        <v>0.02247479205166926</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06131192922032595</v>
+        <v>0.02243501344126056</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0613516683538856</v>
+        <v>0.02247467076796005</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07723465117822551</v>
+        <v>0.02490849766912892</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06397727724976111</v>
+        <v>0.02490849766912892</v>
       </c>
       <c r="G7" t="n">
-        <v>0.06174499684313488</v>
+        <v>0.02286808106406997</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06135170783073312</v>
+        <v>0.02247479205166926</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06397734257005151</v>
+        <v>0.02510042679098628</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06135170783073312</v>
+        <v>0.02247479205166926</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05469523906235971</v>
+        <v>0.02247479205166926</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06135170783073312</v>
+        <v>0.02247479205166926</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.008955101955853967</v>
+        <v>0.03155308579073192</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9348323752604311</v>
+        <v>0.04609344622166018</v>
       </c>
       <c r="D8" t="n">
-        <v>1.058479422140231</v>
+        <v>0.04937448635881021</v>
       </c>
       <c r="E8" t="n">
-        <v>1.056780367294898</v>
+        <v>0.04474112995114233</v>
       </c>
       <c r="F8" t="n">
-        <v>1.056780367294898</v>
+        <v>0.03453218856483145</v>
       </c>
       <c r="G8" t="n">
-        <v>0.546370447881492</v>
+        <v>0.04670705266288321</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9806728201718665</v>
+        <v>0.04631376365210735</v>
       </c>
       <c r="I8" t="n">
-        <v>1.056780367294898</v>
+        <v>0.04893939838979948</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6534358120997118</v>
+        <v>0.04631666450568739</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7565597770485621</v>
+        <v>0.03127889862500832</v>
       </c>
       <c r="L8" t="n">
-        <v>1.203235028977705</v>
+        <v>0.06173252590420999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.04986325935653556</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06131192922032579</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06135166835388552</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.07723465117822542</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.06397727724976117</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06174499684313522</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.06135170783073455</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.0639773425700515</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.06135170783073455</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.05469523906235806</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.06135170783073455</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.008955101955854259</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9348323752604314</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.058479422140231</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.056780367294898</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.056780367294898</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5463704478814927</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9806728201718665</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.056780367294898</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6534358120997125</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.756559777048562</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.203235028977705</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.01716248127608194</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9212673145918687</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.01716248127608211</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9212673145918681</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.063815374991318</v>
       </c>
-      <c r="E9" t="n">
-        <v>1.043793790260949</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.043793790260949</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5482024652082256</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1.032232027756985</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.043793790260949</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6608554852011882</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7480811145937164</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.1849642088035</v>
+      <c r="E11" t="n">
+        <v>1.04379379026095</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.04379379026095</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5482024652082268</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1.032232027756986</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.04379379026095</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6608554852011879</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7480811145937166</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.184964208803502</v>
       </c>
     </row>
   </sheetData>
@@ -3611,7 +4251,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3679,320 +4319,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2.903588045814502</v>
+        <v>0.03709126592187778</v>
       </c>
       <c r="C2" t="n">
-        <v>0.4084694818240382</v>
+        <v>0.9221132441039165</v>
       </c>
       <c r="D2" t="n">
-        <v>1.901183491548013</v>
+        <v>1.094021680825702</v>
       </c>
       <c r="E2" t="n">
-        <v>2.326309595408255</v>
+        <v>1.056442658986795</v>
       </c>
       <c r="F2" t="n">
-        <v>2.326309595408255</v>
+        <v>1.056442658986795</v>
       </c>
       <c r="G2" t="n">
-        <v>2.082457240133768</v>
+        <v>0.5647038585844768</v>
       </c>
       <c r="H2" t="n">
-        <v>5.208858633866049</v>
+        <v>1.097090156363649</v>
       </c>
       <c r="I2" t="n">
-        <v>2.326309595408255</v>
+        <v>1.056442658986795</v>
       </c>
       <c r="J2" t="n">
-        <v>4.830025422458882</v>
+        <v>0.6869746105113879</v>
       </c>
       <c r="K2" t="n">
-        <v>2.437459202341776</v>
+        <v>0.7610120363718413</v>
       </c>
       <c r="L2" t="n">
-        <v>0.3872807613629943</v>
+        <v>1.190360331343018</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02260284929879109</v>
+        <v>0.0344306511101837</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02004352652127579</v>
+        <v>0.9362467582373168</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02260284929879109</v>
+        <v>1.109205609817845</v>
       </c>
       <c r="E3" t="n">
-        <v>0.02549397725209251</v>
+        <v>1.070575870929929</v>
       </c>
       <c r="F3" t="n">
-        <v>0.02549397725209237</v>
+        <v>1.070575870929929</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02302361755584194</v>
+        <v>0.5713248476312455</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02260284929879109</v>
+        <v>1.109205609817845</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02540509557464984</v>
+        <v>1.070575870929929</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02260284929879109</v>
+        <v>0.6926358765608791</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02260284929879109</v>
+        <v>0.7703089179659848</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02260284929879109</v>
+        <v>1.208823294069123</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.63706173772528</v>
+        <v>2.9035880458145</v>
       </c>
       <c r="C4" t="n">
-        <v>10.63311733651147</v>
+        <v>0.4084694818238296</v>
       </c>
       <c r="D4" t="n">
-        <v>10.63632282083305</v>
+        <v>1.901183491548023</v>
       </c>
       <c r="E4" t="n">
-        <v>6.560466596381139</v>
+        <v>2.326309595408259</v>
       </c>
       <c r="F4" t="n">
-        <v>10.63972474771522</v>
+        <v>2.326309595408259</v>
       </c>
       <c r="G4" t="n">
-        <v>10.63748250598233</v>
+        <v>2.082457240133772</v>
       </c>
       <c r="H4" t="n">
-        <v>40.40751802543394</v>
+        <v>5.208858633866044</v>
       </c>
       <c r="I4" t="n">
-        <v>10.63986398400113</v>
+        <v>2.326309595408259</v>
       </c>
       <c r="J4" t="n">
-        <v>11.17769233324638</v>
+        <v>4.830025422458913</v>
       </c>
       <c r="K4" t="n">
-        <v>10.63736301050364</v>
+        <v>2.437459202341735</v>
       </c>
       <c r="L4" t="n">
-        <v>10.63621422948431</v>
+        <v>0.3872807613629936</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.03891972187444868</v>
+        <v>0.02260284929879121</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03885306023544322</v>
+        <v>0.02004352652127661</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03891931420916211</v>
+        <v>0.02260284929879121</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04171587181477568</v>
+        <v>0.02549397725209229</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04171587181477568</v>
+        <v>0.02549397725209235</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03934049013149771</v>
+        <v>0.02302361755584124</v>
       </c>
       <c r="H5" t="n">
-        <v>0.03891972187444868</v>
+        <v>0.02260284929879121</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04172196815030613</v>
+        <v>0.02540509557464998</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03891972187444868</v>
+        <v>0.02260284929879121</v>
       </c>
       <c r="K5" t="n">
-        <v>0.03891972187444868</v>
+        <v>0.02260284929879121</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03891972187444868</v>
+        <v>0.02260284929879121</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05265008667581928</v>
+        <v>10.63706173772528</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07617142182000543</v>
+        <v>10.63311733651147</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08113010532540618</v>
+        <v>10.63632282083305</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07258905192205346</v>
+        <v>6.560466596381142</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05619666603736594</v>
+        <v>10.63972474771523</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07665959472338625</v>
+        <v>10.63748250598232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07623882646647676</v>
+        <v>40.40751802543394</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0790410727421933</v>
+        <v>10.63986398400113</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07624346228576803</v>
+        <v>11.17769233324637</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05221191372747634</v>
+        <v>10.6373630105036</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1008792375954451</v>
+        <v>10.63621422948431</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1085880407449913</v>
+        <v>0.03891972187444631</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1342583812848738</v>
+        <v>0.03885306023544274</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1343250488253642</v>
+        <v>0.03891931420915987</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1668272028688214</v>
+        <v>0.04171587181477541</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1371272520256708</v>
+        <v>0.04171587181477541</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1347458111809214</v>
+        <v>0.03934049013149629</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1343250429238758</v>
+        <v>0.03891972187444631</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1371272891997294</v>
+        <v>0.04172196815030497</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1343250429238758</v>
+        <v>0.03891972187444631</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1194129252665668</v>
+        <v>0.03891972187444631</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1343250429238758</v>
+        <v>0.03891972187444631</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.03009455303866786</v>
+        <v>0.05265008667581803</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9275379268549314</v>
+        <v>0.07617142182000619</v>
       </c>
       <c r="D8" t="n">
-        <v>1.06575585492323</v>
+        <v>0.08113010532540779</v>
       </c>
       <c r="E8" t="n">
-        <v>1.017908776610085</v>
+        <v>0.07258905192205374</v>
       </c>
       <c r="F8" t="n">
-        <v>1.017908776610085</v>
+        <v>0.05619666603736659</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5250976296088534</v>
+        <v>0.0766595947233847</v>
       </c>
       <c r="H8" t="n">
-        <v>1.003481752851723</v>
+        <v>0.07623882646647662</v>
       </c>
       <c r="I8" t="n">
-        <v>1.017908776610085</v>
+        <v>0.07904107274219353</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5871306634276954</v>
+        <v>0.07624346228576781</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7147006373500369</v>
+        <v>0.05221191372747519</v>
       </c>
       <c r="L8" t="n">
-        <v>1.201517651756434</v>
+        <v>0.1008792375954436</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1085880407449885</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1342583812848696</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1343250488253637</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1668272028688205</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1371272520256714</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.134745811180923</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1343250429238732</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1371272891997318</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1343250429238732</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1194129252665659</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1343250429238732</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>-0.03009455303866799</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9275379268549523</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.06575585492323</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.017908776610086</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.017908776610086</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5250976296088516</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.003481752851723</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.017908776610086</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5871306634276957</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7147006373500367</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.201517651756433</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.007732092404525686</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9181506980715444</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="B11" t="n">
+        <v>0.007732092404525504</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9181506980715417</v>
+      </c>
+      <c r="D11" t="n">
         <v>1.074251903882499</v>
       </c>
-      <c r="E9" t="n">
+      <c r="E11" t="n">
         <v>1.032478963231195</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.032478963231195</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.5436703270668851</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.5436703270668849</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.048985464522121</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>1.032478963231195</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.6389694023106239</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7357100914785099</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="J11" t="n">
+        <v>0.6389694023106246</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7357100914785089</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.187036240809044</v>
       </c>
     </row>
@@ -4007,7 +4727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4075,320 +4795,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1.346363529729434</v>
+        <v>0.03262892630892211</v>
       </c>
       <c r="C2" t="n">
-        <v>0.1858525524607738</v>
+        <v>0.91641757771536</v>
       </c>
       <c r="D2" t="n">
-        <v>1.907896124115105</v>
+        <v>1.085355128238686</v>
       </c>
       <c r="E2" t="n">
-        <v>0.8609165703685506</v>
+        <v>1.045931902459034</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8609165703685506</v>
+        <v>1.045931902459034</v>
       </c>
       <c r="G2" t="n">
-        <v>1.344311576691634</v>
+        <v>0.5581006360985835</v>
       </c>
       <c r="H2" t="n">
-        <v>6.768073975336802</v>
+        <v>1.09021822237351</v>
       </c>
       <c r="I2" t="n">
-        <v>0.8609165703685506</v>
+        <v>1.045931902459034</v>
       </c>
       <c r="J2" t="n">
-        <v>2.410709824575246</v>
+        <v>0.6785807953108495</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9221026410195748</v>
+        <v>0.7440821712997612</v>
       </c>
       <c r="L2" t="n">
-        <v>0.09165518102479177</v>
+        <v>1.187050374589438</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01625240095023283</v>
+        <v>0.03153522500176451</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01409420903199882</v>
+        <v>0.9307140348141458</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01625240095023283</v>
+        <v>1.100295636711008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01833310666165957</v>
+        <v>1.061499887587585</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01833310666165957</v>
+        <v>1.061499887587585</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0166446417785684</v>
+        <v>0.5653644725688955</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01625240095023283</v>
+        <v>1.100295636711008</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01887088041350181</v>
+        <v>1.061499887587585</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01625240095023283</v>
+        <v>0.6865800239935083</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01625240095023283</v>
+        <v>0.7547657072336162</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01625240095023283</v>
+        <v>1.205768478045355</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.25595536183861</v>
+        <v>1.346363529729434</v>
       </c>
       <c r="C4" t="n">
-        <v>10.06366660257707</v>
+        <v>0.1858525524600641</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06741468470701</v>
+        <v>1.907896124115103</v>
       </c>
       <c r="E4" t="n">
-        <v>6.204071161583109</v>
+        <v>0.8609165703685414</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06858293632509</v>
+        <v>0.8609165703685414</v>
       </c>
       <c r="G4" t="n">
-        <v>10.06659049205232</v>
+        <v>1.344311576691631</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26463625788895</v>
+        <v>6.768073975336795</v>
       </c>
       <c r="I4" t="n">
-        <v>38.2585738413019</v>
+        <v>0.8609165703685414</v>
       </c>
       <c r="J4" t="n">
-        <v>10.57780145636981</v>
+        <v>2.410709824575226</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06539271149165</v>
+        <v>0.9221026410195723</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06578576422994</v>
+        <v>0.09165518102478928</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02800423446109353</v>
+        <v>0.01625240095023143</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02794776033556162</v>
+        <v>0.01409420903199708</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02800395386373675</v>
+        <v>0.01625240095023143</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03058064580641449</v>
+        <v>0.01833310666165905</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03058064580641449</v>
+        <v>0.01833310666165905</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02839647528942901</v>
+        <v>0.01664464177856697</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02800423446109353</v>
+        <v>0.01625240095023143</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03062271392436247</v>
+        <v>0.01887088041350125</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02800423446109353</v>
+        <v>0.0162524009502314</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02800423446109353</v>
+        <v>0.01625240095023143</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02800423446109353</v>
+        <v>0.01625240095023143</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0386651051175196</v>
+        <v>38.25595536183868</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05627640661567934</v>
+        <v>10.06366660257707</v>
       </c>
       <c r="D6" t="n">
-        <v>0.06004041127091824</v>
+        <v>10.06741468470701</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05411325583379857</v>
+        <v>6.204071161583102</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04181985277557752</v>
+        <v>10.06858293632509</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05676156661387888</v>
+        <v>10.06659049205232</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05636932578663498</v>
+        <v>38.26463625788895</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05898780524881234</v>
+        <v>38.25857384130194</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05637280513635753</v>
+        <v>10.5778014563698</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03833624013238672</v>
+        <v>10.06539271149165</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07486286464286522</v>
+        <v>10.06578576422993</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.07035035118135363</v>
+        <v>0.0280042344610934</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08676245602292938</v>
+        <v>0.02794776033556071</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08681889185840862</v>
+        <v>0.02800395386373613</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1084416721572396</v>
+        <v>0.03058064580641283</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08943733458864159</v>
+        <v>0.03058064580641283</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08721117097679668</v>
+        <v>0.02839647528942728</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08681893014846137</v>
+        <v>0.0280042344610934</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0894374096117303</v>
+        <v>0.03062271392436124</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08681893014846137</v>
+        <v>0.0280042344610934</v>
       </c>
       <c r="K7" t="n">
-        <v>0.06608205952188254</v>
+        <v>0.0280042344610934</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08681893014846137</v>
+        <v>0.0280042344610934</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>7.068177539187729e-05</v>
+        <v>0.03866510511751806</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9266588446536187</v>
+        <v>0.05627640661567741</v>
       </c>
       <c r="D8" t="n">
-        <v>1.054111737153136</v>
+        <v>0.0600404112709179</v>
       </c>
       <c r="E8" t="n">
-        <v>1.041135607516667</v>
+        <v>0.05411325583379724</v>
       </c>
       <c r="F8" t="n">
-        <v>1.041135607516667</v>
+        <v>0.04181985277557721</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5338960657418269</v>
+        <v>0.05676156661387783</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9549930739582049</v>
+        <v>0.05636932578663288</v>
       </c>
       <c r="I8" t="n">
-        <v>1.041135607516667</v>
+        <v>0.05898780524881133</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6310906603318258</v>
+        <v>0.0563728051363569</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7327277562699415</v>
+        <v>0.03833624013238555</v>
       </c>
       <c r="L8" t="n">
-        <v>1.204161003984844</v>
+        <v>0.07486286464286562</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.07035035118135169</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.08676245602292836</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08681889185840733</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1084416721572375</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.08943733458863953</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.08721117097679548</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.0868189301484617</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08943740961172758</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.0868189301484617</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.06608205952188048</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.0868189301484617</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7.068177539190881e-05</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9266588446536155</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.054111737153136</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.041135607516664</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.041135607516664</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5338960657418254</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9549930739582042</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.041135607516664</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6310906603318258</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7327277562699404</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.204161003984843</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.0183124588693731</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9145724532692006</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.0643413067605</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.036666090129656</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.036666090129656</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5437824107084062</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="B11" t="n">
+        <v>0.01831245886937285</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9145724532691939</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.064341306760499</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.036666090129654</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.036666090129654</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5437824107084047</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.024105093269192</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.036666090129656</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.6533329580106743</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7340548333805075</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="I11" t="n">
+        <v>1.036666090129654</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.6533329580106737</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.734054833380506</v>
+      </c>
+      <c r="L11" t="n">
         <v>1.18631896876919</v>
       </c>
     </row>
@@ -4403,7 +5203,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4471,321 +5271,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.6258312111887093</v>
+        <v>0.0323612875396934</v>
       </c>
       <c r="C2" t="n">
-        <v>0.08934728281835455</v>
+        <v>0.9124483470760576</v>
       </c>
       <c r="D2" t="n">
-        <v>2.021524376658474</v>
+        <v>1.080347569151583</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2379512882338538</v>
+        <v>1.04392381549699</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2379512882338538</v>
+        <v>1.04392381549699</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9111029128113936</v>
+        <v>0.5554758323785002</v>
       </c>
       <c r="H2" t="n">
-        <v>5.144967367735338</v>
+        <v>1.083379175127496</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2379512882338538</v>
+        <v>1.04392381549699</v>
       </c>
       <c r="J2" t="n">
-        <v>1.330752135447426</v>
+        <v>0.6727877344317313</v>
       </c>
       <c r="K2" t="n">
-        <v>0.321410226843643</v>
+        <v>0.7456643930054773</v>
       </c>
       <c r="L2" t="n">
-        <v>0.05252789357939559</v>
+        <v>1.18467857483127</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01221439674909712</v>
+        <v>0.03210773074286327</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01030537846684926</v>
+        <v>0.9268077008129039</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01221439674909712</v>
+        <v>1.095088492707269</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0140552808248935</v>
+        <v>1.060206636077429</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01405528082489351</v>
+        <v>1.060206636077429</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01260191082459674</v>
+        <v>0.5632127363543749</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01221439674909712</v>
+        <v>1.095088492707269</v>
       </c>
       <c r="I3" t="n">
-        <v>0.0148024600362034</v>
+        <v>1.060206636077429</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01221439674909712</v>
+        <v>0.6819321006011663</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01221439674909712</v>
+        <v>0.7570957680441377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01221439674909712</v>
+        <v>1.203414550019736</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.24695118691499</v>
+        <v>0.6258312111887089</v>
       </c>
       <c r="C4" t="n">
-        <v>10.05810446054121</v>
+        <v>0.08934728281835475</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06226365870364</v>
+        <v>2.021524376658479</v>
       </c>
       <c r="E4" t="n">
-        <v>6.197597853354351</v>
+        <v>0.2379512882338538</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06218488854184</v>
+        <v>0.2379512882338538</v>
       </c>
       <c r="G4" t="n">
-        <v>10.06022254705711</v>
+        <v>0.9111029128113972</v>
       </c>
       <c r="H4" t="n">
-        <v>38.25584543195808</v>
+        <v>5.144967367735338</v>
       </c>
       <c r="I4" t="n">
-        <v>10.06242309626871</v>
+        <v>0.2379512882338538</v>
       </c>
       <c r="J4" t="n">
-        <v>38.24980529410128</v>
+        <v>1.330752135447427</v>
       </c>
       <c r="K4" t="n">
-        <v>10.05882312085034</v>
+        <v>0.3214102268436433</v>
       </c>
       <c r="L4" t="n">
-        <v>10.05964027569308</v>
+        <v>0.05252789357939706</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02119495556216843</v>
+        <v>0.012214396749097</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02115058194702734</v>
+        <v>0.01030537846684959</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02119474028107287</v>
+        <v>0.012214396749097</v>
       </c>
       <c r="E5" t="n">
-        <v>0.02372058752173419</v>
+        <v>0.01405528082489349</v>
       </c>
       <c r="F5" t="n">
-        <v>0.02372058752173419</v>
+        <v>0.01405528082489349</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02158246963766814</v>
+        <v>0.01260191082459663</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02119495556216843</v>
+        <v>0.012214396749097</v>
       </c>
       <c r="I5" t="n">
-        <v>0.02378301884927476</v>
+        <v>0.01480246003620339</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02119495556216843</v>
+        <v>0.012214396749097</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02119495556216843</v>
+        <v>0.012214396749097</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02119495556216843</v>
+        <v>0.012214396749097</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.02972826793381217</v>
+        <v>38.24695118691496</v>
       </c>
       <c r="C6" t="n">
-        <v>0.04337955503011665</v>
+        <v>10.05810446054121</v>
       </c>
       <c r="D6" t="n">
-        <v>0.04633236619459007</v>
+        <v>10.06226365870364</v>
       </c>
       <c r="E6" t="n">
-        <v>0.04225684139999807</v>
+        <v>6.197597853354353</v>
       </c>
       <c r="F6" t="n">
-        <v>0.03271514746374001</v>
+        <v>10.06218488854185</v>
       </c>
       <c r="G6" t="n">
-        <v>0.04386822220789166</v>
+        <v>10.06022254705711</v>
       </c>
       <c r="H6" t="n">
-        <v>0.04348070813369653</v>
+        <v>38.25584543195807</v>
       </c>
       <c r="I6" t="n">
-        <v>0.04606877141949823</v>
+        <v>10.06242309626871</v>
       </c>
       <c r="J6" t="n">
-        <v>0.04348341085489441</v>
+        <v>38.24980529410127</v>
       </c>
       <c r="K6" t="n">
-        <v>0.02947280929887023</v>
+        <v>10.05882312085034</v>
       </c>
       <c r="L6" t="n">
-        <v>0.05784628185576892</v>
+        <v>10.05964027569307</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.05073142147480265</v>
+        <v>0.02119495556216833</v>
       </c>
       <c r="C7" t="n">
-        <v>0.06248140727273711</v>
+        <v>0.0211505819470275</v>
       </c>
       <c r="D7" t="n">
-        <v>0.06252574872874629</v>
+        <v>0.02119474028107257</v>
       </c>
       <c r="E7" t="n">
-        <v>0.07872417828798367</v>
+        <v>0.02372058752173419</v>
       </c>
       <c r="F7" t="n">
-        <v>0.06511378217682208</v>
+        <v>0.02372058752173419</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0629132949633778</v>
+        <v>0.02158246963766804</v>
       </c>
       <c r="H7" t="n">
-        <v>0.06252578088787827</v>
+        <v>0.02119495556216833</v>
       </c>
       <c r="I7" t="n">
-        <v>0.06511384417498449</v>
+        <v>0.02378301884927478</v>
       </c>
       <c r="J7" t="n">
-        <v>0.06252578088787827</v>
+        <v>0.02119495556216833</v>
       </c>
       <c r="K7" t="n">
-        <v>0.05541481818711971</v>
+        <v>0.02119495556216833</v>
       </c>
       <c r="L7" t="n">
-        <v>0.06252578088787827</v>
+        <v>0.02119495556216833</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.01759237189909983</v>
+        <v>0.02972826793381209</v>
       </c>
       <c r="C8" t="n">
-        <v>0.924960657259836</v>
+        <v>0.04337955503011652</v>
       </c>
       <c r="D8" t="n">
-        <v>1.046047538484215</v>
+        <v>0.04633236619459002</v>
       </c>
       <c r="E8" t="n">
-        <v>1.054802856206776</v>
+        <v>0.04225684139999808</v>
       </c>
       <c r="F8" t="n">
-        <v>1.054802856206776</v>
+        <v>0.03271514746374003</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5419211879297839</v>
+        <v>0.04386822220789151</v>
       </c>
       <c r="H8" t="n">
-        <v>0.9846356636919389</v>
+        <v>0.04348070813369637</v>
       </c>
       <c r="I8" t="n">
-        <v>1.054802856206776</v>
+        <v>0.04606877141949824</v>
       </c>
       <c r="J8" t="n">
-        <v>0.6513777839982445</v>
+        <v>0.04348341085489438</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7495683907234059</v>
+        <v>0.02947280929887025</v>
       </c>
       <c r="L8" t="n">
-        <v>1.202557810122987</v>
+        <v>0.05784628185576875</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.05073142147480259</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.06248140727273752</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.06252574872874639</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.07872417828798386</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.06511378217682215</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.06291329496337789</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.06252578088787822</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.06511384417498463</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.06252578088787822</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.05541481818711956</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.06252578088787822</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.01759237189909977</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.9249606572598368</v>
+      </c>
+      <c r="D10" t="n">
+        <v>1.046047538484214</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.054802856206775</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.054802856206775</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5419211879297845</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9846356636919382</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.054802856206775</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.6513777839982451</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7495683907234059</v>
+      </c>
+      <c r="L10" t="n">
+        <v>1.202557810122986</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.0257567530080771</v>
-      </c>
-      <c r="C9" t="n">
-        <v>0.9116079363732333</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.058033778695844</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="B11" t="n">
+        <v>0.02575675300807704</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.9116079363732331</v>
+      </c>
+      <c r="D11" t="n">
+        <v>1.058033778695846</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.041465078435019</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.041465078435019</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.5457881099931725</v>
-      </c>
-      <c r="H9" t="n">
+      <c r="G11" t="n">
+        <v>0.545788109993173</v>
+      </c>
+      <c r="H11" t="n">
         <v>1.033122785933238</v>
       </c>
-      <c r="I9" t="n">
+      <c r="I11" t="n">
         <v>1.041465078435019</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.6588854230065724</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.7422394123362154</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.184288755447981</v>
+      <c r="J11" t="n">
+        <v>0.6588854230065719</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.742239412336216</v>
+      </c>
+      <c r="L11" t="n">
+        <v>1.184288755447979</v>
       </c>
     </row>
   </sheetData>
@@ -4799,7 +5679,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4867,321 +5747,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1242535799683379</v>
+        <v>0.6183317864028345</v>
       </c>
       <c r="C2" t="n">
-        <v>4.335246877166773</v>
+        <v>1.097529448680865</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9368530088032224</v>
+        <v>0.6192297206943863</v>
       </c>
       <c r="E2" t="n">
-        <v>4.335246877166773</v>
+        <v>1.097529448680865</v>
       </c>
       <c r="F2" t="n">
-        <v>4.335246877166773</v>
+        <v>1.097529448680865</v>
       </c>
       <c r="G2" t="n">
-        <v>2.390384601107914</v>
+        <v>0.6211649546435981</v>
       </c>
       <c r="H2" t="n">
-        <v>1.599038994266162</v>
+        <v>0.6197863509958333</v>
       </c>
       <c r="I2" t="n">
-        <v>4.335246877166773</v>
+        <v>1.097529448680865</v>
       </c>
       <c r="J2" t="n">
-        <v>7.352009281699717</v>
+        <v>0.6258648566791499</v>
       </c>
       <c r="K2" t="n">
-        <v>4.390613384984458</v>
+        <v>0.6230426501934101</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2448958427016479</v>
+        <v>0.618443609798388</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03286033572997978</v>
+        <v>0.6279343637864575</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03853912356884831</v>
+        <v>1.109742478393759</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03286033572997978</v>
+        <v>0.6279343637864575</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03891417067751818</v>
+        <v>1.109742478393759</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03891417067751818</v>
+        <v>1.109742478393759</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03348318142957755</v>
+        <v>0.6283141387190436</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03286033572997978</v>
+        <v>0.6279343637864575</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03698975519013429</v>
+        <v>1.109742478393759</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03286033572997978</v>
+        <v>0.6279343637864575</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03286033572997978</v>
+        <v>0.6279343637864575</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03286033572997978</v>
+        <v>0.6279343637864575</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.83272268775578</v>
+        <v>0.1242535799683007</v>
       </c>
       <c r="C4" t="n">
-        <v>10.83938926933231</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="D4" t="n">
-        <v>10.82744273621123</v>
+        <v>0.9368530088032176</v>
       </c>
       <c r="E4" t="n">
-        <v>6.692045131214747</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="F4" t="n">
-        <v>10.83663604753641</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="G4" t="n">
-        <v>10.83334553345539</v>
+        <v>2.390384601107918</v>
       </c>
       <c r="H4" t="n">
-        <v>41.09340021470116</v>
+        <v>1.599038994266162</v>
       </c>
       <c r="I4" t="n">
-        <v>41.09475801571061</v>
+        <v>4.335246877166784</v>
       </c>
       <c r="J4" t="n">
-        <v>11.38236566917724</v>
+        <v>7.352009281699713</v>
       </c>
       <c r="K4" t="n">
-        <v>10.83458287117105</v>
+        <v>4.390613384984466</v>
       </c>
       <c r="L4" t="n">
-        <v>10.83077494908724</v>
+        <v>0.2448958427016513</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05149071663393531</v>
+        <v>0.03286033572997884</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05562013609409085</v>
+        <v>0.03853912356884825</v>
       </c>
       <c r="D5" t="n">
-        <v>0.05148979519241421</v>
+        <v>0.03286033572997884</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05573271982539228</v>
+        <v>0.03891417067751814</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05573271982539228</v>
+        <v>0.03891417067751817</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05211356233353392</v>
+        <v>0.03348318142957708</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05149071663393531</v>
+        <v>0.03286033572997884</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05562013609409085</v>
+        <v>0.03698975519013425</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05149071663393531</v>
+        <v>0.03286033572997884</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05149071663393531</v>
+        <v>0.03286033572997884</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05149071663393531</v>
+        <v>0.03286033572997884</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06589377616446201</v>
+        <v>10.83272268775579</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09565987585986832</v>
+        <v>10.83938926933231</v>
       </c>
       <c r="D6" t="n">
-        <v>0.09670911016675478</v>
+        <v>10.82744273621123</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08866738043474927</v>
+        <v>6.692045131214745</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07089994599368507</v>
+        <v>10.83663604753641</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0920396000715626</v>
+        <v>10.83334553345541</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09141675437198074</v>
+        <v>41.09340021470116</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09554617383211937</v>
+        <v>41.09475801571058</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09142177032601977</v>
+        <v>11.38236566917722</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06541967374432821</v>
+        <v>10.83458287117105</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1180776392669884</v>
+        <v>10.83077494908723</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1448418153880118</v>
+        <v>0.05149071663393529</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1819136488488362</v>
+        <v>0.05562013609409074</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1777842634854177</v>
+        <v>0.05148979519241326</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2199285383526051</v>
+        <v>0.05573271982539221</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1819136579818527</v>
+        <v>0.05573271982539221</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1784070750882794</v>
+        <v>0.05211356233353354</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1777842293886806</v>
+        <v>0.05149071663393529</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1819136488488362</v>
+        <v>0.05562013609409074</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1777842293886806</v>
+        <v>0.05149071663393529</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1586972796828053</v>
+        <v>0.05149071663393529</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1777842293886806</v>
+        <v>0.05149071663393529</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6258330838306558</v>
+        <v>0.06589377616446199</v>
       </c>
       <c r="C8" t="n">
-        <v>1.004828651558831</v>
+        <v>0.09565987585986804</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6070238678615881</v>
+        <v>0.09670911016675435</v>
       </c>
       <c r="E8" t="n">
-        <v>1.004828651558831</v>
+        <v>0.08866738043474924</v>
       </c>
       <c r="F8" t="n">
-        <v>1.004828651558831</v>
+        <v>0.07089994599368503</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5750517474769316</v>
+        <v>0.09203960007156234</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5959691628935053</v>
+        <v>0.09141675437197989</v>
       </c>
       <c r="I8" t="n">
-        <v>1.004828651558831</v>
+        <v>0.09554617383211923</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4692080935396263</v>
+        <v>0.09142177032601924</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5272043066063189</v>
+        <v>0.06541967374432799</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6235578974287782</v>
+        <v>0.1180776392669883</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1448418153880119</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1819136488488357</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1777842634854171</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.219928538352605</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1819136579818522</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1784070750882786</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1777842293886804</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1819136488488357</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1777842293886804</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1586972796828052</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1777842293886804</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6258330838306564</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.004828651558831</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6070238678615875</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.004828651558831</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.004828651558831</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5750517474769307</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5959691628935052</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.004828651558831</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4692080935396263</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.527204306606317</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6235578974287781</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6173756973265633</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.049793323130445</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6097153784107746</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.049793323130445</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.049793323130445</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5969303968912679</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.60524208272249</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.049793323130445</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.553643897886233</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5772101531688018</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.6130175145416678</v>
+      <c r="B11" t="n">
+        <v>0.6173756973265632</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.049793323130444</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6097153784107744</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.049793323130444</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.049793323130444</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5969303968912671</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6052420827224895</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.049793323130444</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5536438978862317</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5772101531688006</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6130175145416673</v>
       </c>
     </row>
   </sheetData>
@@ -5195,7 +6155,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5263,321 +6223,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.2216838688477199</v>
+        <v>0.612850666162628</v>
       </c>
       <c r="C2" t="n">
-        <v>2.991289698298489</v>
+        <v>1.089549256183899</v>
       </c>
       <c r="D2" t="n">
-        <v>0.6912939597222607</v>
+        <v>0.6134183111328506</v>
       </c>
       <c r="E2" t="n">
-        <v>2.991289698298489</v>
+        <v>1.089549256183899</v>
       </c>
       <c r="F2" t="n">
-        <v>2.991289698298489</v>
+        <v>1.089549256183899</v>
       </c>
       <c r="G2" t="n">
-        <v>1.675699060304488</v>
+        <v>0.6148422494164026</v>
       </c>
       <c r="H2" t="n">
-        <v>1.253194264488357</v>
+        <v>0.6139228609095208</v>
       </c>
       <c r="I2" t="n">
-        <v>2.991289698298489</v>
+        <v>1.089549256183899</v>
       </c>
       <c r="J2" t="n">
-        <v>5.595391334199208</v>
+        <v>0.6188485734307324</v>
       </c>
       <c r="K2" t="n">
-        <v>2.323498709889597</v>
+        <v>0.6155272823038341</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2691355411526308</v>
+        <v>0.6128799836506769</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02608963641165003</v>
+        <v>0.6222552903703719</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03086377582055355</v>
+        <v>1.102935302174391</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02608963641164998</v>
+        <v>0.6222552903703719</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0311796004654018</v>
+        <v>1.102935302174391</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0311796004654018</v>
+        <v>1.102935302174391</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02669227275840677</v>
+        <v>0.6225364574861239</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02608963641164998</v>
+        <v>0.6222552903703719</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03008975063229362</v>
+        <v>1.102935302174391</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02608963641164998</v>
+        <v>0.6222552903703719</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02608963641164998</v>
+        <v>0.6222552903703719</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02608963641164998</v>
+        <v>0.6222552903703719</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.08473798617769</v>
+        <v>0.2216838688477267</v>
       </c>
       <c r="C4" t="n">
-        <v>10.09087565353528</v>
+        <v>2.991289698298496</v>
       </c>
       <c r="D4" t="n">
-        <v>10.08151434332728</v>
+        <v>0.6912939597222614</v>
       </c>
       <c r="E4" t="n">
-        <v>6.226633046312207</v>
+        <v>2.991289698298496</v>
       </c>
       <c r="F4" t="n">
-        <v>10.08895683983584</v>
+        <v>2.991289698298496</v>
       </c>
       <c r="G4" t="n">
-        <v>10.08534062252444</v>
+        <v>1.675699060304488</v>
       </c>
       <c r="H4" t="n">
-        <v>38.27851943556377</v>
+        <v>1.253194264488357</v>
       </c>
       <c r="I4" t="n">
-        <v>38.27998041068944</v>
+        <v>2.991289698298496</v>
       </c>
       <c r="J4" t="n">
-        <v>10.59713169718851</v>
+        <v>5.595391334199198</v>
       </c>
       <c r="K4" t="n">
-        <v>10.08528050570703</v>
+        <v>2.323498709889593</v>
       </c>
       <c r="L4" t="n">
-        <v>10.08378481815163</v>
+        <v>0.2691355411526289</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04013029783590241</v>
+        <v>0.02608963641165018</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04413041205654553</v>
+        <v>0.03086377582055357</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0401296134229886</v>
+        <v>0.02608963641165017</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04413962997381746</v>
+        <v>0.03117960046540177</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04413962997381747</v>
+        <v>0.03117960046540183</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04073293418265831</v>
+        <v>0.02669227275840648</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04013029783590243</v>
+        <v>0.02608963641165017</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04413041205654553</v>
+        <v>0.03008975063229359</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04013029783590243</v>
+        <v>0.02608963641165017</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04013029783590243</v>
+        <v>0.02608963641165017</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04013029783590243</v>
+        <v>0.02608963641165017</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05138307070738996</v>
+        <v>10.08473798617769</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07489869032258935</v>
+        <v>10.09087565353528</v>
       </c>
       <c r="D6" t="n">
-        <v>0.07492910024976657</v>
+        <v>10.08151434332728</v>
       </c>
       <c r="E6" t="n">
-        <v>0.06956355650765272</v>
+        <v>6.22663304631221</v>
       </c>
       <c r="F6" t="n">
-        <v>0.05600727972928588</v>
+        <v>10.08895683983584</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07148784189518231</v>
+        <v>10.08534062252444</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07088520554846477</v>
+        <v>38.27851943556377</v>
       </c>
       <c r="I6" t="n">
-        <v>0.07488531976906948</v>
+        <v>38.27998041068941</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0708890382437045</v>
+        <v>10.5971316971885</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05102080854314871</v>
+        <v>10.08528050570703</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0912568161011738</v>
+        <v>10.08378481815163</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1034727101087511</v>
+        <v>0.04013029783590193</v>
       </c>
       <c r="C7" t="n">
-        <v>0.130366832522264</v>
+        <v>0.04413041205654551</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1263667378905635</v>
+        <v>0.04012961342298837</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1567860513416714</v>
+        <v>0.04413962997381742</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1303668333928473</v>
+        <v>0.04413962997381742</v>
       </c>
       <c r="G7" t="n">
-        <v>0.126969354648377</v>
+        <v>0.0407329341826585</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1263667183016206</v>
+        <v>0.04013029783590194</v>
       </c>
       <c r="I7" t="n">
-        <v>0.130366832522264</v>
+        <v>0.04413041205654551</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1263667183016206</v>
+        <v>0.04013029783590194</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1131018482819975</v>
+        <v>0.04013029783590194</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1263667183016206</v>
+        <v>0.04013029783590194</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6173830557208828</v>
+        <v>0.05138307070738979</v>
       </c>
       <c r="C8" t="n">
-        <v>1.02421540700702</v>
+        <v>0.07489869032258928</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6054944507529557</v>
+        <v>0.07492910024976679</v>
       </c>
       <c r="E8" t="n">
-        <v>1.02421540700702</v>
+        <v>0.06956355650765263</v>
       </c>
       <c r="F8" t="n">
-        <v>1.02421540700702</v>
+        <v>0.05600727972928581</v>
       </c>
       <c r="G8" t="n">
-        <v>0.582013278466166</v>
+        <v>0.07148784189518231</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5954332858659955</v>
+        <v>0.07088520554846484</v>
       </c>
       <c r="I8" t="n">
-        <v>1.02421540700702</v>
+        <v>0.07488531976906947</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4927020346510382</v>
+        <v>0.07088903824370432</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5613482875303407</v>
+        <v>0.05102080854314849</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6168532362192076</v>
+        <v>0.09125681610117393</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1034727101087508</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1303668325222641</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1263667378905634</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1567860513416715</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1303668333928473</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1269693546483769</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1263667183016207</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1303668325222641</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1263667183016207</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1131018482819971</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1263667183016207</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6173830557208815</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.02421540700702</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6054944507529543</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.02421540700702</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.02421540700702</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5820132784661662</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.595433285865995</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.02421540700702</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4927020346510372</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5613482875303394</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6168532362192074</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6106337838702207</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.053731453017323</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6057920756933014</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.053731453017323</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.053731453017323</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5964040738226128</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.601718763383374</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.053731453017323</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5599014292167082</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5878144019125203</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.6084880957322857</v>
+      <c r="B11" t="n">
+        <v>0.6106337838702202</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.053731453017322</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6057920756932993</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.053731453017322</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.053731453017322</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5964040738226118</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.6017187633833734</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.053731453017322</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5599014292167075</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.5878144019125192</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.6084880957322849</v>
       </c>
     </row>
   </sheetData>
@@ -5591,7 +6631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5659,321 +6699,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.3171117189433773</v>
+        <v>0.6060409242188968</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9117973034435745</v>
+        <v>1.076176223672876</v>
       </c>
       <c r="D2" t="n">
-        <v>0.7488213551010512</v>
+        <v>0.6065844015117775</v>
       </c>
       <c r="E2" t="n">
-        <v>0.9117973034435745</v>
+        <v>1.076176223672876</v>
       </c>
       <c r="F2" t="n">
-        <v>0.9117973034435745</v>
+        <v>1.076176223672876</v>
       </c>
       <c r="G2" t="n">
-        <v>1.343400349221445</v>
+        <v>0.6072018727132623</v>
       </c>
       <c r="H2" t="n">
-        <v>2.591070816450771</v>
+        <v>0.6085376225891492</v>
       </c>
       <c r="I2" t="n">
-        <v>0.9117973034435745</v>
+        <v>1.076176223672876</v>
       </c>
       <c r="J2" t="n">
-        <v>4.217985729546898</v>
+        <v>0.6103631092539346</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6920168409159859</v>
+        <v>0.6065738916247476</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9415321513670034</v>
+        <v>0.6060803847936489</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01615964062339775</v>
+        <v>0.6152256225771299</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01826169611504286</v>
+        <v>1.092058277574065</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01615964062339776</v>
+        <v>0.6152256225771299</v>
       </c>
       <c r="E3" t="n">
-        <v>0.01865117285275877</v>
+        <v>1.092058277574065</v>
       </c>
       <c r="F3" t="n">
-        <v>0.01865117285276024</v>
+        <v>1.092058277574065</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01668985035719643</v>
+        <v>0.6151523094949082</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01615964062339776</v>
+        <v>0.6152256225771299</v>
       </c>
       <c r="I3" t="n">
-        <v>0.01969747053254775</v>
+        <v>1.092058277574065</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01615964062339702</v>
+        <v>0.6152256225771299</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01615964062339776</v>
+        <v>0.6152256225771299</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01615964062339776</v>
+        <v>0.6152256225771299</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.06830202191764</v>
+        <v>0.3171117189433641</v>
       </c>
       <c r="C4" t="n">
-        <v>10.07100668473108</v>
+        <v>0.9117973034433613</v>
       </c>
       <c r="D4" t="n">
-        <v>10.06724276742443</v>
+        <v>0.748821355101046</v>
       </c>
       <c r="E4" t="n">
-        <v>6.207186360435789</v>
+        <v>0.9117973034433613</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07170324611436</v>
+        <v>0.9117973034433613</v>
       </c>
       <c r="G4" t="n">
-        <v>38.25796174978183</v>
+        <v>1.343400349221431</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26066696608908</v>
+        <v>2.591070816450767</v>
       </c>
       <c r="I4" t="n">
-        <v>10.07183985182679</v>
+        <v>0.9117973034433613</v>
       </c>
       <c r="J4" t="n">
-        <v>38.25960918575012</v>
+        <v>4.217985729546895</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06738086603337</v>
+        <v>0.692016840915976</v>
       </c>
       <c r="L4" t="n">
-        <v>10.06808566120696</v>
+        <v>0.9415321513670042</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02702321416605985</v>
+        <v>0.01615964062339352</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03056104407521049</v>
+        <v>0.01826169611503708</v>
       </c>
       <c r="D5" t="n">
-        <v>0.02702290163008391</v>
+        <v>0.01615964062339356</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03032596274293298</v>
+        <v>0.01865117285275362</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03032596274293298</v>
+        <v>0.01865117285275362</v>
       </c>
       <c r="G5" t="n">
-        <v>0.02755342389986063</v>
+        <v>0.01668985035719555</v>
       </c>
       <c r="H5" t="n">
-        <v>0.02702321416605988</v>
+        <v>0.01615964062339356</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03056104407521049</v>
+        <v>0.01969747053254717</v>
       </c>
       <c r="J5" t="n">
-        <v>0.02702321416605988</v>
+        <v>0.01615964062339356</v>
       </c>
       <c r="K5" t="n">
-        <v>0.02702321416605988</v>
+        <v>0.01615964062339356</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02702321416605988</v>
+        <v>0.01615964062339356</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.03703269125013804</v>
+        <v>10.06830202191763</v>
       </c>
       <c r="C6" t="n">
-        <v>0.05651517891265211</v>
+        <v>10.07100668473107</v>
       </c>
       <c r="D6" t="n">
-        <v>0.05655084793012648</v>
+        <v>10.06724276742442</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05211745385492109</v>
+        <v>6.207186360435774</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04094290825269451</v>
+        <v>10.07170324611435</v>
       </c>
       <c r="G6" t="n">
-        <v>0.05372892688391014</v>
+        <v>38.25796174978186</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05319871715017076</v>
+        <v>38.26066696608908</v>
       </c>
       <c r="I6" t="n">
-        <v>0.05673654705925927</v>
+        <v>10.0718398518268</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0532018942088671</v>
+        <v>38.25960918575013</v>
       </c>
       <c r="K6" t="n">
-        <v>0.03673239902183459</v>
+        <v>10.06738086603336</v>
       </c>
       <c r="L6" t="n">
-        <v>0.07008548295723636</v>
+        <v>10.06808566120696</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.0699196104491768</v>
+        <v>0.02702321416605499</v>
       </c>
       <c r="C7" t="n">
-        <v>0.08958880281208592</v>
+        <v>0.03056104407520795</v>
       </c>
       <c r="D7" t="n">
-        <v>0.08605097518857605</v>
+        <v>0.02702290163008214</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1082040120740158</v>
+        <v>0.03032596274293056</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08958876838350062</v>
+        <v>0.03032596274293056</v>
       </c>
       <c r="G7" t="n">
-        <v>0.08658118263673804</v>
+        <v>0.02755342389985643</v>
       </c>
       <c r="H7" t="n">
-        <v>0.08605097290293458</v>
+        <v>0.0270232141660551</v>
       </c>
       <c r="I7" t="n">
-        <v>0.08958880281208592</v>
+        <v>0.03056104407520795</v>
       </c>
       <c r="J7" t="n">
-        <v>0.08605097290293458</v>
+        <v>0.0270232141660551</v>
       </c>
       <c r="K7" t="n">
-        <v>0.07670439910580544</v>
+        <v>0.0270232141660551</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08605097290293458</v>
+        <v>0.0270232141660551</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.607483724674132</v>
+        <v>0.03703269125013922</v>
       </c>
       <c r="C8" t="n">
-        <v>1.068214382093827</v>
+        <v>0.05651517891264916</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5961029914309185</v>
+        <v>0.05655084793012392</v>
       </c>
       <c r="E8" t="n">
-        <v>1.068214382093827</v>
+        <v>0.05211745385491651</v>
       </c>
       <c r="F8" t="n">
-        <v>1.068214382093827</v>
+        <v>0.04094290825269332</v>
       </c>
       <c r="G8" t="n">
-        <v>0.581705470104807</v>
+        <v>0.05372892688390516</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5563025282299841</v>
+        <v>0.05319871715016752</v>
       </c>
       <c r="I8" t="n">
-        <v>1.068214382093827</v>
+        <v>0.05673654705925665</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5176702293644806</v>
+        <v>0.0532018942088643</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5963336001799243</v>
+        <v>0.03673239902183107</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6067906971884424</v>
+        <v>0.07008548295723253</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.06991961044916987</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.08958880281207883</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.08605097518856522</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1082040120740145</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.0895887683834888</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.08658118263672811</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.08605097290292608</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.08958880281207883</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.08605097290292608</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.07670439910580278</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.08605097290292608</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6074837246741286</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.068214382093849</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5961029914309169</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.068214382093849</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.068214382093849</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5817054701048058</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5563025282299839</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.068214382093849</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5176702293644795</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5963336001799245</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6067906971884409</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6025183360010671</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.065327175243391</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.5978835434000404</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.065327175243391</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.065327175243391</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5919834542020129</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5817274268844401</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.065327175243391</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5659750944515881</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.5979779612287199</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.602242466861285</v>
+      <c r="B11" t="n">
+        <v>0.6025183360010663</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.065327175243393</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.5978835434000401</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.065327175243393</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.065327175243393</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5919834542020124</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5817274268844377</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.065327175243393</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5659750944515871</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.597977961228717</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.602242466861283</v>
       </c>
     </row>
   </sheetData>
@@ -5987,7 +7107,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6055,321 +7175,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.167330314446233</v>
+        <v>0.6248842874082683</v>
       </c>
       <c r="C2" t="n">
-        <v>4.612570278743778</v>
+        <v>1.102243651787432</v>
       </c>
       <c r="D2" t="n">
-        <v>2.472370714428741</v>
+        <v>0.6277179002080019</v>
       </c>
       <c r="E2" t="n">
-        <v>4.612570278743778</v>
+        <v>1.102243651787432</v>
       </c>
       <c r="F2" t="n">
-        <v>4.612570278743778</v>
+        <v>1.102243651787432</v>
       </c>
       <c r="G2" t="n">
-        <v>3.738352655538465</v>
+        <v>0.6291810339429669</v>
       </c>
       <c r="H2" t="n">
-        <v>5.727586894743959</v>
+        <v>0.6310506357714089</v>
       </c>
       <c r="I2" t="n">
-        <v>4.612570278743778</v>
+        <v>1.102243651787432</v>
       </c>
       <c r="J2" t="n">
-        <v>10.6413612546216</v>
+        <v>0.6358064840287504</v>
       </c>
       <c r="K2" t="n">
-        <v>4.945577949074085</v>
+        <v>0.6305491504740579</v>
       </c>
       <c r="L2" t="n">
-        <v>4.565046466293285</v>
+        <v>0.6252456224164601</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03612569439359852</v>
+        <v>0.6345140396790563</v>
       </c>
       <c r="C3" t="n">
-        <v>0.04006045030050719</v>
+        <v>1.114158005969928</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03612569439359852</v>
+        <v>0.6345140396790563</v>
       </c>
       <c r="E3" t="n">
-        <v>0.04055440348226361</v>
+        <v>1.114158005969928</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04055440348226361</v>
+        <v>1.114158005969928</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03670319102191344</v>
+        <v>0.6346790413537424</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03612569439359852</v>
+        <v>0.6345140396790563</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03996651574010609</v>
+        <v>1.114158005969928</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03612569439359852</v>
+        <v>0.6345140396790563</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03612569439359852</v>
+        <v>0.6345140396790563</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03612569439359852</v>
+        <v>0.6345140396790563</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>41.10570050932419</v>
+        <v>0.1673303144462297</v>
       </c>
       <c r="C4" t="n">
-        <v>10.84510083064795</v>
+        <v>4.612570278743783</v>
       </c>
       <c r="D4" t="n">
-        <v>41.10634276588193</v>
+        <v>2.472370714428739</v>
       </c>
       <c r="E4" t="n">
-        <v>6.697540763555269</v>
+        <v>4.612570278743783</v>
       </c>
       <c r="F4" t="n">
-        <v>10.84406780108459</v>
+        <v>4.612570278743783</v>
       </c>
       <c r="G4" t="n">
-        <v>41.1062780059525</v>
+        <v>3.738352655538463</v>
       </c>
       <c r="H4" t="n">
-        <v>10.84039987426875</v>
+        <v>5.727586894743958</v>
       </c>
       <c r="I4" t="n">
-        <v>41.10954133067072</v>
+        <v>4.612570278743783</v>
       </c>
       <c r="J4" t="n">
-        <v>41.10863975724841</v>
+        <v>10.64136125462162</v>
       </c>
       <c r="K4" t="n">
-        <v>10.8420857943722</v>
+        <v>4.945577949074085</v>
       </c>
       <c r="L4" t="n">
-        <v>10.83983775976722</v>
+        <v>4.565046466293277</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.06013610997549469</v>
+        <v>0.03612569439359854</v>
       </c>
       <c r="C5" t="n">
-        <v>0.06397693132200231</v>
+        <v>0.04006045030050723</v>
       </c>
       <c r="D5" t="n">
-        <v>0.06013529852476643</v>
+        <v>0.03612569439359854</v>
       </c>
       <c r="E5" t="n">
-        <v>0.06391575842889119</v>
+        <v>0.04055440348226371</v>
       </c>
       <c r="F5" t="n">
-        <v>0.06391575842889119</v>
+        <v>0.04055440348226371</v>
       </c>
       <c r="G5" t="n">
-        <v>0.06071360660380968</v>
+        <v>0.0367031910219135</v>
       </c>
       <c r="H5" t="n">
-        <v>0.06013610997549469</v>
+        <v>0.03612569439359856</v>
       </c>
       <c r="I5" t="n">
-        <v>0.06397693132200231</v>
+        <v>0.03996651574010614</v>
       </c>
       <c r="J5" t="n">
-        <v>0.06013610997549469</v>
+        <v>0.03612569439359855</v>
       </c>
       <c r="K5" t="n">
-        <v>0.06013610997549469</v>
+        <v>0.03612569439359854</v>
       </c>
       <c r="L5" t="n">
-        <v>0.06013610997549469</v>
+        <v>0.03612569439359854</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0796049946248642</v>
+        <v>41.10570050932418</v>
       </c>
       <c r="C6" t="n">
-        <v>0.1165316092753366</v>
+        <v>10.84510083064795</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1196130775010632</v>
+        <v>41.10634276588192</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1074743246033717</v>
+        <v>6.69754076355527</v>
       </c>
       <c r="F6" t="n">
-        <v>0.08446019683665811</v>
+        <v>10.84406780108459</v>
       </c>
       <c r="G6" t="n">
-        <v>0.1133194167613681</v>
+        <v>41.10627800595251</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1127419201330863</v>
+        <v>10.84039987426875</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1165827414795609</v>
+        <v>41.10954133067077</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1127484324478997</v>
+        <v>41.1086397572484</v>
       </c>
       <c r="K6" t="n">
-        <v>0.07898945922438802</v>
+        <v>10.8420857943722</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1473562096535372</v>
+        <v>10.83983775976721</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1861618332455529</v>
+        <v>0.06013610997549483</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2338944341230433</v>
+        <v>0.06397693132200243</v>
       </c>
       <c r="D7" t="n">
-        <v>0.2300536326261681</v>
+        <v>0.06013529852476655</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2845445693529115</v>
+        <v>0.06391575842889136</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2338943816138552</v>
+        <v>0.06391575842889136</v>
       </c>
       <c r="G7" t="n">
-        <v>0.2306311094048505</v>
+        <v>0.06071360660380981</v>
       </c>
       <c r="H7" t="n">
-        <v>0.2300536127765358</v>
+        <v>0.06013610997549483</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2338944341230433</v>
+        <v>0.06397693132200243</v>
       </c>
       <c r="J7" t="n">
-        <v>0.2300536127765358</v>
+        <v>0.06013610997549483</v>
       </c>
       <c r="K7" t="n">
-        <v>0.2046225516886452</v>
+        <v>0.06013610997549483</v>
       </c>
       <c r="L7" t="n">
-        <v>0.2300536127765358</v>
+        <v>0.06013610997549483</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6315226092764852</v>
+        <v>0.07960499462486438</v>
       </c>
       <c r="C8" t="n">
-        <v>1.002031322262651</v>
+        <v>0.1165316092753367</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5721642971736475</v>
+        <v>0.1196130775010634</v>
       </c>
       <c r="E8" t="n">
-        <v>1.002031322262651</v>
+        <v>0.1074743246033719</v>
       </c>
       <c r="F8" t="n">
-        <v>1.002031322262651</v>
+        <v>0.08446019683665826</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5455257820898115</v>
+        <v>0.1133194167613684</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5048063335201151</v>
+        <v>0.1127419201330866</v>
       </c>
       <c r="I8" t="n">
-        <v>1.002031322262651</v>
+        <v>0.1165827414795611</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4044316249367654</v>
+        <v>0.1127484324479001</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5129209872291066</v>
+        <v>0.07898945922438814</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5417937563053152</v>
+        <v>0.1473562096535374</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1861618332455528</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2338944341230431</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.230053632626168</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2845445693529114</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.2338943816138551</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.2306311094048506</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.2300536127765355</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.2338944341230431</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.2300536127765355</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.2046225516886451</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.2300536127765355</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6315226092764852</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.002031322262651</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5721642971736475</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.002031322262651</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.002031322262651</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5455257820898121</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5048063335201147</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.002031322262651</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4044316249367649</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5129209872291061</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5417937563053149</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6235231770419752</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.623523177041975</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.051225653374081</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.5993485686712001</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.5993485686712003</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.051225653374081</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.051225653374081</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.5886160168632992</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5720332161151568</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.5886160168632988</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5720332161151562</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.051225653374081</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.5311182520918576</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0.5311182520918568</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.5752239241152637</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.587047431930254</v>
+      <c r="L11" t="n">
+        <v>0.5870474319302543</v>
       </c>
     </row>
   </sheetData>
@@ -6383,7 +7583,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6451,321 +7651,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.1008363085834132</v>
+        <v>0.615436984081964</v>
       </c>
       <c r="C2" t="n">
-        <v>2.889620865043845</v>
+        <v>1.090804024813836</v>
       </c>
       <c r="D2" t="n">
-        <v>2.192089015196613</v>
+        <v>0.6182900494377855</v>
       </c>
       <c r="E2" t="n">
-        <v>2.889620865043845</v>
+        <v>1.090804024813836</v>
       </c>
       <c r="F2" t="n">
-        <v>2.889620865043845</v>
+        <v>1.090804024813836</v>
       </c>
       <c r="G2" t="n">
-        <v>2.660143901551334</v>
+        <v>0.6187661094054493</v>
       </c>
       <c r="H2" t="n">
-        <v>4.155441310642987</v>
+        <v>0.6206437449330454</v>
       </c>
       <c r="I2" t="n">
-        <v>2.889620865043845</v>
+        <v>1.090804024813836</v>
       </c>
       <c r="J2" t="n">
-        <v>5.753769594337486</v>
+        <v>0.6222024024876599</v>
       </c>
       <c r="K2" t="n">
-        <v>1.620966911867651</v>
+        <v>0.6173975296933759</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2141997802228863</v>
+        <v>0.615557308478898</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02735388854811423</v>
+        <v>0.6250082385258373</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03059733022293523</v>
+        <v>1.104265238636028</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02735388854811423</v>
+        <v>0.6250082385258373</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03098294264181667</v>
+        <v>1.104265238636028</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03098294264181666</v>
+        <v>1.104265238636028</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0279083322379858</v>
+        <v>0.6250585877316115</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02735388854811423</v>
+        <v>0.6250082385258373</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03104665468023649</v>
+        <v>1.104265238636028</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02735388854811423</v>
+        <v>0.6250082385258373</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02735388854811423</v>
+        <v>0.6250082385258373</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02735388854811423</v>
+        <v>0.6250082385258373</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.28453688228208</v>
+        <v>0.1008363085834133</v>
       </c>
       <c r="C4" t="n">
-        <v>10.09150861610128</v>
+        <v>2.889620865043841</v>
       </c>
       <c r="D4" t="n">
-        <v>10.08652851764003</v>
+        <v>2.192089015196611</v>
       </c>
       <c r="E4" t="n">
-        <v>6.227284726362006</v>
+        <v>2.889620865043841</v>
       </c>
       <c r="F4" t="n">
-        <v>10.09113480527776</v>
+        <v>2.889620865043841</v>
       </c>
       <c r="G4" t="n">
-        <v>38.28509132597195</v>
+        <v>2.66014390155133</v>
       </c>
       <c r="H4" t="n">
-        <v>38.2883059500851</v>
+        <v>4.155441310642989</v>
       </c>
       <c r="I4" t="n">
-        <v>38.28822964841422</v>
+        <v>2.889620865043841</v>
       </c>
       <c r="J4" t="n">
-        <v>10.60017005520723</v>
+        <v>5.753769594337471</v>
       </c>
       <c r="K4" t="n">
-        <v>10.08501633475017</v>
+        <v>1.62096691186765</v>
       </c>
       <c r="L4" t="n">
-        <v>10.0878183732954</v>
+        <v>0.2141997802228861</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04519315924765945</v>
+        <v>0.02735388854811446</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04888592537978162</v>
+        <v>0.03059733022293524</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04519254278917328</v>
+        <v>0.02735388854811446</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04878038044696707</v>
+        <v>0.03098294264181665</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04878038044696707</v>
+        <v>0.03098294264181665</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04574760293753091</v>
+        <v>0.02790833223798601</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04519315924765945</v>
+        <v>0.02735388854811446</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04888592537978162</v>
+        <v>0.03104665468023648</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04519315924765945</v>
+        <v>0.02735388854811446</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04519315924765945</v>
+        <v>0.02735388854811446</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04519315924765945</v>
+        <v>0.02735388854811446</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0599606107052256</v>
+        <v>38.28453688228208</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08833753173530173</v>
+        <v>10.09150861610128</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08987842134196695</v>
+        <v>10.08652851764002</v>
       </c>
       <c r="E6" t="n">
-        <v>0.08157064773848613</v>
+        <v>6.227284726362009</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06437625696177662</v>
+        <v>10.09113480527777</v>
       </c>
       <c r="G6" t="n">
-        <v>0.08529465369508132</v>
+        <v>38.28509132597202</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08474021000521871</v>
+        <v>38.28830595008512</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0884329761373321</v>
+        <v>38.28822964841422</v>
       </c>
       <c r="J6" t="n">
-        <v>0.08474507987780179</v>
+        <v>10.60017005520722</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05950031692878378</v>
+        <v>10.08501633475017</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1106245734839157</v>
+        <v>10.0878183732954</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1290702688513799</v>
+        <v>0.04519315924765955</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1626610622226393</v>
+        <v>0.04888592537978161</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1589683044025295</v>
+        <v>0.0451925427891734</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1971626963273872</v>
+        <v>0.04878038044696702</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1626610119006175</v>
+        <v>0.04878038044696702</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1595227397803886</v>
+        <v>0.04574760293753104</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1589682960905172</v>
+        <v>0.04519315924765955</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1626610622226393</v>
+        <v>0.04888592537978161</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1589682960905172</v>
+        <v>0.04519315924765955</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1416452651855497</v>
+        <v>0.04519315924765955</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1589682960905172</v>
+        <v>0.04519315924765955</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6232372536661317</v>
+        <v>0.05996061070522558</v>
       </c>
       <c r="C8" t="n">
-        <v>1.026963275304131</v>
+        <v>0.08833753173530164</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5634707596631188</v>
+        <v>0.08987842134196704</v>
       </c>
       <c r="E8" t="n">
-        <v>1.026963275304131</v>
+        <v>0.08157064773848603</v>
       </c>
       <c r="F8" t="n">
-        <v>1.026963275304131</v>
+        <v>0.06437625696177655</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5549104509018186</v>
+        <v>0.08529465369508152</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5162257176357689</v>
+        <v>0.0847402100052187</v>
       </c>
       <c r="I8" t="n">
-        <v>1.026963275304131</v>
+        <v>0.088432976137332</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4825721140537805</v>
+        <v>0.08474507987780179</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5821913855986648</v>
+        <v>0.05950031692878387</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6207815632602773</v>
+        <v>0.1106245734839157</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1290702688513799</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.162661062222639</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1589683044025293</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1971626963273869</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1626610119006172</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1595227397803883</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1589682960905172</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.162661062222639</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1589682960905172</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1416452651855497</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1589682960905172</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.623237253666132</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.02696327530413</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5634707596631192</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.02696327530413</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.02696327530413</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5549104509018189</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5162257176357692</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.02696327530413</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4825721140537808</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5821913855986646</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6207815632602778</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.614631180327004</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.6146311803270047</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.055631385151081</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.590290300446939</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.5902903004469395</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.055631385151081</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.055631385151081</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.5868484835990455</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5711473512587385</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.5868484835990456</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5711473512587392</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.055631385151081</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.5573935119358779</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="J11" t="n">
+        <v>0.5573935119358788</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.5979157251622972</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.6136341577634533</v>
+      <c r="L11" t="n">
+        <v>0.6136341577634538</v>
       </c>
     </row>
   </sheetData>
@@ -6779,7 +8059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6847,321 +8127,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09437802176290272</v>
+        <v>0.6066627943214422</v>
       </c>
       <c r="C2" t="n">
-        <v>1.465335809898434</v>
+        <v>1.078424949169269</v>
       </c>
       <c r="D2" t="n">
-        <v>1.104720419027536</v>
+        <v>0.6079634174522616</v>
       </c>
       <c r="E2" t="n">
-        <v>1.465335809898434</v>
+        <v>1.078424949169269</v>
       </c>
       <c r="F2" t="n">
-        <v>1.465335809898434</v>
+        <v>1.078424949169269</v>
       </c>
       <c r="G2" t="n">
-        <v>1.708064654915964</v>
+        <v>0.6086199663113939</v>
       </c>
       <c r="H2" t="n">
-        <v>3.950566189615341</v>
+        <v>0.611139269546</v>
       </c>
       <c r="I2" t="n">
-        <v>1.465335809898434</v>
+        <v>1.078424949169269</v>
       </c>
       <c r="J2" t="n">
-        <v>2.101777064239765</v>
+        <v>0.6090118922025205</v>
       </c>
       <c r="K2" t="n">
-        <v>0.3970182440324508</v>
+        <v>0.6070642939881957</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4208478776188948</v>
+        <v>0.6070260460225176</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.01874666526735135</v>
+        <v>0.6161299617072014</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02133695193560996</v>
+        <v>1.093645855942494</v>
       </c>
       <c r="D3" t="n">
-        <v>0.01874666526735135</v>
+        <v>0.6161299617072014</v>
       </c>
       <c r="E3" t="n">
-        <v>0.0216795247039008</v>
+        <v>1.093645855942494</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0216795247039008</v>
+        <v>1.093645855942494</v>
       </c>
       <c r="G3" t="n">
-        <v>0.01928213136544824</v>
+        <v>0.6160873104449249</v>
       </c>
       <c r="H3" t="n">
-        <v>0.01874666526735135</v>
+        <v>0.6161299617072014</v>
       </c>
       <c r="I3" t="n">
-        <v>0.02231746843470425</v>
+        <v>1.093645855942494</v>
       </c>
       <c r="J3" t="n">
-        <v>0.01874666526735135</v>
+        <v>0.6161299617072014</v>
       </c>
       <c r="K3" t="n">
-        <v>0.01874666526735135</v>
+        <v>0.6161299617072014</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01874666526735135</v>
+        <v>0.6161299617072014</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.07087923233082</v>
+        <v>0.09437802176290275</v>
       </c>
       <c r="C4" t="n">
-        <v>10.07450354766287</v>
+        <v>1.465335809898435</v>
       </c>
       <c r="D4" t="n">
-        <v>10.07032655061821</v>
+        <v>1.104720419027534</v>
       </c>
       <c r="E4" t="n">
-        <v>6.210762486249224</v>
+        <v>1.465335809898435</v>
       </c>
       <c r="F4" t="n">
-        <v>10.07483750082018</v>
+        <v>1.465335809898435</v>
       </c>
       <c r="G4" t="n">
-        <v>10.07141469842891</v>
+        <v>1.708064654915965</v>
       </c>
       <c r="H4" t="n">
-        <v>38.26689664679212</v>
+        <v>3.950566189615342</v>
       </c>
       <c r="I4" t="n">
-        <v>10.07445003549816</v>
+        <v>1.465335809898435</v>
       </c>
       <c r="J4" t="n">
-        <v>10.58291432515451</v>
+        <v>2.101777064239768</v>
       </c>
       <c r="K4" t="n">
-        <v>10.06877900585783</v>
+        <v>0.397018244032451</v>
       </c>
       <c r="L4" t="n">
-        <v>10.07195720452279</v>
+        <v>0.4208478776188948</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0312617151734602</v>
+        <v>0.01874666526735129</v>
       </c>
       <c r="C5" t="n">
-        <v>0.03483251834081304</v>
+        <v>0.02133695193560994</v>
       </c>
       <c r="D5" t="n">
-        <v>0.03126129164733369</v>
+        <v>0.01874666526735129</v>
       </c>
       <c r="E5" t="n">
-        <v>0.03467664852969038</v>
+        <v>0.02167952470390077</v>
       </c>
       <c r="F5" t="n">
-        <v>0.03467664852969038</v>
+        <v>0.02167952470390077</v>
       </c>
       <c r="G5" t="n">
-        <v>0.03179718127155694</v>
+        <v>0.01928213136544813</v>
       </c>
       <c r="H5" t="n">
-        <v>0.0312617151734602</v>
+        <v>0.01874666526735129</v>
       </c>
       <c r="I5" t="n">
-        <v>0.03483251834081304</v>
+        <v>0.02231746843470424</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0312617151734602</v>
+        <v>0.01874666526735129</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0312617151734602</v>
+        <v>0.01874666526735129</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0312617151734602</v>
+        <v>0.01874666526735129</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0420550098142552</v>
+        <v>10.07087923233084</v>
       </c>
       <c r="C6" t="n">
-        <v>0.06325678226351619</v>
+        <v>10.07450354766288</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0635171509208361</v>
+        <v>10.07032655061821</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05841059585061319</v>
+        <v>6.210762486249222</v>
       </c>
       <c r="F6" t="n">
-        <v>0.04609655800089765</v>
+        <v>10.07483750082018</v>
       </c>
       <c r="G6" t="n">
-        <v>0.06036661813085858</v>
+        <v>10.07141469842892</v>
       </c>
       <c r="H6" t="n">
-        <v>0.05983115203277001</v>
+        <v>38.26689664679213</v>
       </c>
       <c r="I6" t="n">
-        <v>0.06340195520011457</v>
+        <v>10.07445003549818</v>
       </c>
       <c r="J6" t="n">
-        <v>0.05983464553134323</v>
+        <v>10.58291432515449</v>
       </c>
       <c r="K6" t="n">
-        <v>0.04172480884813528</v>
+        <v>10.06877900585781</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0783998189759554</v>
+        <v>10.07195720452278</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08284248633156437</v>
+        <v>0.03126171517345998</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1054304146745593</v>
+        <v>0.034832518340813</v>
       </c>
       <c r="D7" t="n">
-        <v>0.101859599162108</v>
+        <v>0.03126129164733357</v>
       </c>
       <c r="E7" t="n">
-        <v>0.127375694171753</v>
+        <v>0.03467664852969037</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1054303598204742</v>
+        <v>0.03467664852969037</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1023950776053033</v>
+        <v>0.03179718127155698</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1018596115072064</v>
+        <v>0.03126171517345998</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1054304146745593</v>
+        <v>0.034832518340813</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1018596115072064</v>
+        <v>0.03126171517345998</v>
       </c>
       <c r="K7" t="n">
-        <v>0.09039397119294562</v>
+        <v>0.03126171517345998</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1018596115072064</v>
+        <v>0.03126171517345998</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6142741618688408</v>
+        <v>0.04205500981425507</v>
       </c>
       <c r="C8" t="n">
-        <v>1.05573911630181</v>
+        <v>0.06325678226351615</v>
       </c>
       <c r="D8" t="n">
-        <v>0.5870290749113352</v>
+        <v>0.06351715092083594</v>
       </c>
       <c r="E8" t="n">
-        <v>1.05573911630181</v>
+        <v>0.05841059585061319</v>
       </c>
       <c r="F8" t="n">
-        <v>1.05573911630181</v>
+        <v>0.04609655800089765</v>
       </c>
       <c r="G8" t="n">
-        <v>0.57253019019554</v>
+        <v>0.06036661813085843</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5222781257722847</v>
+        <v>0.05983115203276977</v>
       </c>
       <c r="I8" t="n">
-        <v>1.05573911630181</v>
+        <v>0.06340195520011466</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5654421092827858</v>
+        <v>0.05983464553134308</v>
       </c>
       <c r="K8" t="n">
-        <v>0.6058700512926013</v>
+        <v>0.04172480884813524</v>
       </c>
       <c r="L8" t="n">
-        <v>0.537388284837011</v>
+        <v>0.07839981897595526</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.08284248633156434</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1054304146745593</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1018595991621081</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1273756941717529</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1054303598204742</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1023950776053032</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1018596115072063</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1054304146745593</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1018596115072063</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.0903939711929455</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1018596115072063</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6142741618688401</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.05573911630181</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.5870290749113348</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.05573911630181</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.05573911630181</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5725301901955395</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5222781257722845</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.05573911630181</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.5654421092827852</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.6058700512926013</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.537388284837011</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6058183994809055</v>
-      </c>
-      <c r="C9" t="n">
+      <c r="B11" t="n">
+        <v>0.6058183994809048</v>
+      </c>
+      <c r="C11" t="n">
         <v>1.061177261831145</v>
       </c>
-      <c r="D9" t="n">
-        <v>0.5947224212211182</v>
-      </c>
-      <c r="E9" t="n">
+      <c r="D11" t="n">
+        <v>0.5947224212211174</v>
+      </c>
+      <c r="E11" t="n">
         <v>1.061177261831145</v>
       </c>
-      <c r="F9" t="n">
+      <c r="F11" t="n">
         <v>1.061177261831145</v>
       </c>
-      <c r="G9" t="n">
-        <v>0.588801337789617</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.5684363851075572</v>
-      </c>
-      <c r="I9" t="n">
+      <c r="G11" t="n">
+        <v>0.5888013377896166</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.5684363851075569</v>
+      </c>
+      <c r="I11" t="n">
         <v>1.061177261831145</v>
       </c>
-      <c r="J9" t="n">
-        <v>0.5859487578168097</v>
-      </c>
-      <c r="K9" t="n">
-        <v>0.6023960020531581</v>
-      </c>
-      <c r="L9" t="n">
-        <v>0.5745629246972247</v>
+      <c r="J11" t="n">
+        <v>0.5859487578168091</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.6023960020531574</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.5745629246972237</v>
       </c>
     </row>
   </sheetData>
@@ -7175,7 +8535,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7243,321 +8603,401 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.139695901784433</v>
+        <v>0.6202694673391967</v>
       </c>
       <c r="C2" t="n">
-        <v>4.438656632232633</v>
+        <v>1.099267699990982</v>
       </c>
       <c r="D2" t="n">
-        <v>1.086474333092758</v>
+        <v>0.6213668397318508</v>
       </c>
       <c r="E2" t="n">
-        <v>4.438656632232633</v>
+        <v>1.099267699990982</v>
       </c>
       <c r="F2" t="n">
-        <v>4.438656632232633</v>
+        <v>1.099267699990982</v>
       </c>
       <c r="G2" t="n">
-        <v>2.641256196054715</v>
+        <v>0.6234114568774006</v>
       </c>
       <c r="H2" t="n">
-        <v>2.00484732307511</v>
+        <v>0.6222807263511488</v>
       </c>
       <c r="I2" t="n">
-        <v>4.438656632232633</v>
+        <v>1.099267699990982</v>
       </c>
       <c r="J2" t="n">
-        <v>9.685434219495294</v>
+        <v>0.6302228582595905</v>
       </c>
       <c r="K2" t="n">
-        <v>4.693591645060528</v>
+        <v>0.6254386630953486</v>
       </c>
       <c r="L2" t="n">
-        <v>0.42217430986719</v>
+        <v>0.6211733713246993</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03357123929464845</v>
+        <v>0.6298793751751771</v>
       </c>
       <c r="C3" t="n">
-        <v>0.03888042604873904</v>
+        <v>1.111358104211974</v>
       </c>
       <c r="D3" t="n">
-        <v>0.03357123929464845</v>
+        <v>0.6298793751751771</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03928307800019418</v>
+        <v>1.111358104211974</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03928307800019407</v>
+        <v>1.111358104211974</v>
       </c>
       <c r="G3" t="n">
-        <v>0.03418745167000247</v>
+        <v>0.6302249454704275</v>
       </c>
       <c r="H3" t="n">
-        <v>0.03357123929464845</v>
+        <v>0.6298793751751771</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03765875339046328</v>
+        <v>1.111358104211974</v>
       </c>
       <c r="J3" t="n">
-        <v>0.03357123929464845</v>
+        <v>0.6298793751751771</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03357123929464845</v>
+        <v>0.6298793751751771</v>
       </c>
       <c r="L3" t="n">
-        <v>0.03357123929464845</v>
+        <v>0.6298793751751771</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10.83540618926669</v>
+        <v>0.1396959017844336</v>
       </c>
       <c r="C4" t="n">
-        <v>10.84157608654279</v>
+        <v>4.438656632232628</v>
       </c>
       <c r="D4" t="n">
-        <v>10.82986011102102</v>
+        <v>1.086474333092771</v>
       </c>
       <c r="E4" t="n">
-        <v>6.694106130898017</v>
+        <v>4.438656632232628</v>
       </c>
       <c r="F4" t="n">
-        <v>10.83912875681331</v>
+        <v>4.438656632232628</v>
       </c>
       <c r="G4" t="n">
-        <v>41.09458193595853</v>
+        <v>2.641256196054719</v>
       </c>
       <c r="H4" t="n">
-        <v>41.09681674968916</v>
+        <v>2.004847323075107</v>
       </c>
       <c r="I4" t="n">
-        <v>41.098053237679</v>
+        <v>4.438656632232628</v>
       </c>
       <c r="J4" t="n">
-        <v>41.09619567379494</v>
+        <v>9.685434219495294</v>
       </c>
       <c r="K4" t="n">
-        <v>10.83748627470404</v>
+        <v>4.693591645060534</v>
       </c>
       <c r="L4" t="n">
-        <v>10.83343414618965</v>
+        <v>0.4221743098671954</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.05318684024012361</v>
+        <v>0.0335712392946485</v>
       </c>
       <c r="C5" t="n">
-        <v>0.05727435433593828</v>
+        <v>0.03888042604873895</v>
       </c>
       <c r="D5" t="n">
-        <v>0.0531859550816292</v>
+        <v>0.0335712392946485</v>
       </c>
       <c r="E5" t="n">
-        <v>0.05733250992630697</v>
+        <v>0.03928307800019411</v>
       </c>
       <c r="F5" t="n">
-        <v>0.05733250992630697</v>
+        <v>0.03928307800019411</v>
       </c>
       <c r="G5" t="n">
-        <v>0.05380305261547723</v>
+        <v>0.03418745167000233</v>
       </c>
       <c r="H5" t="n">
-        <v>0.05318684024012361</v>
+        <v>0.0335712392946485</v>
       </c>
       <c r="I5" t="n">
-        <v>0.05727435433593828</v>
+        <v>0.03765875339046321</v>
       </c>
       <c r="J5" t="n">
-        <v>0.05318684024012361</v>
+        <v>0.0335712392946485</v>
       </c>
       <c r="K5" t="n">
-        <v>0.05318684024012361</v>
+        <v>0.0335712392946485</v>
       </c>
       <c r="L5" t="n">
-        <v>0.05318684024012361</v>
+        <v>0.0335712392946485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.06867351395822739</v>
+        <v>10.8354061892667</v>
       </c>
       <c r="C6" t="n">
-        <v>0.09982612259202631</v>
+        <v>10.84157608654279</v>
       </c>
       <c r="D6" t="n">
-        <v>0.1012760096817584</v>
+        <v>10.82986011102105</v>
       </c>
       <c r="E6" t="n">
-        <v>0.09243431667111103</v>
+        <v>6.694106130898017</v>
       </c>
       <c r="F6" t="n">
-        <v>0.07365220866070962</v>
+        <v>10.83912875681331</v>
       </c>
       <c r="G6" t="n">
-        <v>0.09629293154935339</v>
+        <v>41.09458193595852</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09567671917400464</v>
+        <v>41.09681674968918</v>
       </c>
       <c r="I6" t="n">
-        <v>0.09976423326981447</v>
+        <v>41.098053237679</v>
       </c>
       <c r="J6" t="n">
-        <v>0.09568202603572307</v>
+        <v>41.09619567379495</v>
       </c>
       <c r="K6" t="n">
-        <v>0.06817191556139254</v>
+        <v>10.83748627470404</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1238838249543677</v>
+        <v>10.83343414618965</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1537782036437962</v>
+        <v>0.05318684024012349</v>
       </c>
       <c r="C7" t="n">
-        <v>0.193155056144804</v>
+        <v>0.0572743543359382</v>
       </c>
       <c r="D7" t="n">
-        <v>0.1890675787530691</v>
+        <v>0.05318595508162922</v>
       </c>
       <c r="E7" t="n">
-        <v>0.233878241170129</v>
+        <v>0.05733250992630695</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1931550590094905</v>
+        <v>0.05733250992630695</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1896837544243425</v>
+        <v>0.0538030526154774</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1890675420489891</v>
+        <v>0.05318684024012349</v>
       </c>
       <c r="I7" t="n">
-        <v>0.193155056144804</v>
+        <v>0.0572743543359382</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1890675420489891</v>
+        <v>0.05318684024012349</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1686207762226876</v>
+        <v>0.05318684024012349</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1890675420489891</v>
+        <v>0.05318684024012349</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6274403553950175</v>
+        <v>0.06867351395822716</v>
       </c>
       <c r="C8" t="n">
-        <v>1.003461489958253</v>
+        <v>0.09982612259202624</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6044533953267257</v>
+        <v>0.1012760096817593</v>
       </c>
       <c r="E8" t="n">
-        <v>1.003461489958253</v>
+        <v>0.09243431667111103</v>
       </c>
       <c r="F8" t="n">
-        <v>1.003461489958253</v>
+        <v>0.07365220866070958</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5694720214692918</v>
+        <v>0.09629293154935376</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5861378459541217</v>
+        <v>0.0956767191740049</v>
       </c>
       <c r="I8" t="n">
-        <v>1.003461489958253</v>
+        <v>0.09976423326981457</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4204901962895875</v>
+        <v>0.09568202603572298</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5192158799061583</v>
+        <v>0.06817191556139258</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6088287918999415</v>
+        <v>0.1238838249543678</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1537782036437965</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1931550561448042</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1890675787530693</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.2338782411701292</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1931550590094904</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1896837544243432</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1890675420489893</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1931550561448042</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1890675420489893</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1686207762226878</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1890675420489893</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6274403553950176</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.003461489958252</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6044533953267255</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.003461489958252</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.003461489958252</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.569472021469292</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.5861378459541212</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.003461489958252</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4204901962895877</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5192158799061586</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6088287918999412</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6191597055665284</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.05017439665943</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6097979378730144</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.05017439665943</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.05017439665943</v>
-      </c>
-      <c r="G9" t="n">
-        <v>0.5957686828488034</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0.602378191159585</v>
-      </c>
-      <c r="I9" t="n">
-        <v>1.05017439665943</v>
-      </c>
-      <c r="J9" t="n">
+      <c r="B11" t="n">
+        <v>0.6191597055665298</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.050174396659431</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.609797937873015</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.050174396659431</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.050174396659431</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5957686828488029</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.602378191159586</v>
+      </c>
+      <c r="I11" t="n">
+        <v>1.050174396659431</v>
+      </c>
+      <c r="J11" t="n">
         <v>0.5349501145829269</v>
       </c>
-      <c r="K9" t="n">
+      <c r="K11" t="n">
         <v>0.5750864200843104</v>
       </c>
-      <c r="L9" t="n">
-        <v>0.6168989517891275</v>
+      <c r="L11" t="n">
+        <v>0.6168989517891278</v>
       </c>
     </row>
   </sheetData>
@@ -7571,7 +9011,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L9"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7639,320 +9079,400 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
+          <t>hydrogen production without electricity, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.07778142155586668</v>
+        <v>0.6146869897807478</v>
       </c>
       <c r="C2" t="n">
-        <v>2.744550095700992</v>
+        <v>1.089667978648935</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9082887058755847</v>
+        <v>0.6157645657334813</v>
       </c>
       <c r="E2" t="n">
-        <v>2.744550095700992</v>
+        <v>1.089667978648935</v>
       </c>
       <c r="F2" t="n">
-        <v>2.744550095700992</v>
+        <v>1.089667978648935</v>
       </c>
       <c r="G2" t="n">
-        <v>2.264147542509959</v>
+        <v>0.6175052225279879</v>
       </c>
       <c r="H2" t="n">
-        <v>8.05208323771922</v>
+        <v>0.6242007985225776</v>
       </c>
       <c r="I2" t="n">
-        <v>2.744550095700992</v>
+        <v>1.089667978648935</v>
       </c>
       <c r="J2" t="n">
-        <v>6.447332410157684</v>
+        <v>0.6218123003815419</v>
       </c>
       <c r="K2" t="n">
-        <v>2.093963470468324</v>
+        <v>0.6172775766872831</v>
       </c>
       <c r="L2" t="n">
-        <v>2.51367451513398</v>
+        <v>0.6147635096339874</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
+          <t>hydrogen production without electricity, steam reforming of natural gas, 25 bar</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.02626278084114255</v>
+        <v>0.6242835697956018</v>
       </c>
       <c r="C3" t="n">
-        <v>0.02994380495198273</v>
+        <v>1.103348388985932</v>
       </c>
       <c r="D3" t="n">
-        <v>0.02626278084114255</v>
+        <v>0.6242835697956018</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03031284899495769</v>
+        <v>1.103348388985932</v>
       </c>
       <c r="F3" t="n">
-        <v>0.03031284899495769</v>
+        <v>1.103348388985932</v>
       </c>
       <c r="G3" t="n">
-        <v>0.02682849724310813</v>
+        <v>0.6243911973927518</v>
       </c>
       <c r="H3" t="n">
-        <v>0.02626278084114255</v>
+        <v>0.6242835697956018</v>
       </c>
       <c r="I3" t="n">
-        <v>0.03002733710560628</v>
+        <v>1.103348388985932</v>
       </c>
       <c r="J3" t="n">
-        <v>0.02626278084114255</v>
+        <v>0.6242835697956018</v>
       </c>
       <c r="K3" t="n">
-        <v>0.02626278084114255</v>
+        <v>0.6242835697956018</v>
       </c>
       <c r="L3" t="n">
-        <v>0.02626278084114255</v>
+        <v>0.6242835697956018</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from grid electricity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.28057319053681</v>
+        <v>0.07778142155586651</v>
       </c>
       <c r="C4" t="n">
-        <v>10.09014850121162</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="D4" t="n">
-        <v>10.08230630897605</v>
+        <v>0.9082887058755819</v>
       </c>
       <c r="E4" t="n">
-        <v>6.225900620053298</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="F4" t="n">
-        <v>10.08948484814313</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="G4" t="n">
-        <v>38.28113890693876</v>
+        <v>2.26414754250996</v>
       </c>
       <c r="H4" t="n">
-        <v>38.28527874230884</v>
+        <v>8.052083237719229</v>
       </c>
       <c r="I4" t="n">
-        <v>38.28433774680124</v>
+        <v>2.744550095700991</v>
       </c>
       <c r="J4" t="n">
-        <v>10.5984988240858</v>
+        <v>6.447332410157684</v>
       </c>
       <c r="K4" t="n">
-        <v>10.08500237030977</v>
+        <v>2.093963470468326</v>
       </c>
       <c r="L4" t="n">
-        <v>10.08541497108309</v>
+        <v>2.513674515133975</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from hydro electricity</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.04257201397699428</v>
+        <v>0.02626278084114245</v>
       </c>
       <c r="C5" t="n">
-        <v>0.04633657024145815</v>
+        <v>0.02994380495198281</v>
       </c>
       <c r="D5" t="n">
-        <v>0.04257138717317421</v>
+        <v>0.02626278084114245</v>
       </c>
       <c r="E5" t="n">
-        <v>0.04628372153347769</v>
+        <v>0.03031284899495767</v>
       </c>
       <c r="F5" t="n">
-        <v>0.04628372153347769</v>
+        <v>0.0303128489949577</v>
       </c>
       <c r="G5" t="n">
-        <v>0.04313773037895993</v>
+        <v>0.02682849724310812</v>
       </c>
       <c r="H5" t="n">
-        <v>0.04257201397699428</v>
+        <v>0.02626278084114245</v>
       </c>
       <c r="I5" t="n">
-        <v>0.04633657024145815</v>
+        <v>0.03002733710560631</v>
       </c>
       <c r="J5" t="n">
-        <v>0.04257201397699428</v>
+        <v>0.02626278084114245</v>
       </c>
       <c r="K5" t="n">
-        <v>0.04257201397699428</v>
+        <v>0.02626278084114245</v>
       </c>
       <c r="L5" t="n">
-        <v>0.04257201397699428</v>
+        <v>0.02626278084114245</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from nuclear electricity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.05618819020403169</v>
+        <v>38.28057319053681</v>
       </c>
       <c r="C6" t="n">
-        <v>0.08279433302185878</v>
+        <v>10.09014850121162</v>
       </c>
       <c r="D6" t="n">
-        <v>0.08382094029190609</v>
+        <v>10.08230630897605</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07653973515733413</v>
+        <v>6.225900620053295</v>
       </c>
       <c r="F6" t="n">
-        <v>0.06064707566219175</v>
+        <v>10.08948484814314</v>
       </c>
       <c r="G6" t="n">
-        <v>0.07964089132085179</v>
+        <v>38.28113890693874</v>
       </c>
       <c r="H6" t="n">
-        <v>0.07907517491896575</v>
+        <v>38.28527874230883</v>
       </c>
       <c r="I6" t="n">
-        <v>0.08283973118335006</v>
+        <v>38.28433774680126</v>
       </c>
       <c r="J6" t="n">
-        <v>0.07907967283546341</v>
+        <v>10.59849882408579</v>
       </c>
       <c r="K6" t="n">
-        <v>0.05576305271547947</v>
+        <v>10.08500237030977</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1029825442026525</v>
+        <v>10.0854149710831</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from offshore wind electricity</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1165419358137283</v>
+        <v>0.0425720139769943</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1469593277031889</v>
+        <v>0.04633657024145811</v>
       </c>
       <c r="D7" t="n">
-        <v>0.143194712070562</v>
+        <v>0.04257138717317419</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1777159510318393</v>
+        <v>0.04628372153347777</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1469592235562777</v>
+        <v>0.04628372153347777</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1437604878406904</v>
+        <v>0.04313773037896003</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1431947714387249</v>
+        <v>0.0425720139769943</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1469593277031889</v>
+        <v>0.04633657024145811</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1431947714387249</v>
+        <v>0.0425720139769943</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1277519888338249</v>
+        <v>0.0425720139769943</v>
       </c>
       <c r="L7" t="n">
-        <v>0.1431947714387249</v>
+        <v>0.0425720139769943</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from onshore wind electricity</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.6230490485258391</v>
+        <v>0.05618819020403169</v>
       </c>
       <c r="C8" t="n">
-        <v>1.030759833191592</v>
+        <v>0.08279433302185894</v>
       </c>
       <c r="D8" t="n">
-        <v>0.6004761247477464</v>
+        <v>0.08382094029190626</v>
       </c>
       <c r="E8" t="n">
-        <v>1.030759833191592</v>
+        <v>0.07653973515733434</v>
       </c>
       <c r="F8" t="n">
-        <v>1.030759833191592</v>
+        <v>0.06064707566219195</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5666271554476512</v>
+        <v>0.07964089132085204</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4274787248575955</v>
+        <v>0.07907517491896597</v>
       </c>
       <c r="I8" t="n">
-        <v>1.030759833191592</v>
+        <v>0.08283973118335025</v>
       </c>
       <c r="J8" t="n">
-        <v>0.4748960910546512</v>
+        <v>0.07907967283546355</v>
       </c>
       <c r="K8" t="n">
-        <v>0.5688114422432896</v>
+        <v>0.05576305271547958</v>
       </c>
       <c r="L8" t="n">
-        <v>0.5703995346714174</v>
+        <v>0.1029825442026528</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
+          <t>hydrogen production, gaseous, 200 bar, from PEM electrolysis, from solar electricity</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.1165419358137282</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.1469593277031887</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.1431947120705618</v>
+      </c>
+      <c r="E9" t="n">
+        <v>0.1777159510318391</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1469592235562773</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0.1437604878406905</v>
+      </c>
+      <c r="H9" t="n">
+        <v>0.1431947714387247</v>
+      </c>
+      <c r="I9" t="n">
+        <v>0.1469593277031887</v>
+      </c>
+      <c r="J9" t="n">
+        <v>0.1431947714387247</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.1277519888338249</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1431947714387247</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hydrogen production, steam methane reforming of natural gas, 25 bar</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.6230490485258401</v>
+      </c>
+      <c r="C10" t="n">
+        <v>1.030759833191594</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.6004761247477471</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1.030759833191594</v>
+      </c>
+      <c r="F10" t="n">
+        <v>1.030759833191594</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.566627155447652</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.4274787248575953</v>
+      </c>
+      <c r="I10" t="n">
+        <v>1.030759833191594</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0.4748960910546516</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.5688114422432904</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.5703995346714184</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>hydrogen production, steam methane reforming of natural gas, with CCS (MDEA, 98% eff.), 25 bar</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>0.6141252786688195</v>
-      </c>
-      <c r="C9" t="n">
-        <v>1.056639954436508</v>
-      </c>
-      <c r="D9" t="n">
-        <v>0.6049321023668814</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.056639954436508</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1.056639954436508</v>
-      </c>
-      <c r="G9" t="n">
+      <c r="B11" t="n">
+        <v>0.6141252786688205</v>
+      </c>
+      <c r="C11" t="n">
+        <v>1.05663995443651</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.6049321023668816</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1.05663995443651</v>
+      </c>
+      <c r="F11" t="n">
+        <v>1.05663995443651</v>
+      </c>
+      <c r="G11" t="n">
         <v>0.5912223993598884</v>
       </c>
-      <c r="H9" t="n">
+      <c r="H11" t="n">
         <v>0.534653966895957</v>
       </c>
-      <c r="I9" t="n">
-        <v>1.056639954436508</v>
-      </c>
-      <c r="J9" t="n">
-        <v>0.5538405214847616</v>
-      </c>
-      <c r="K9" t="n">
+      <c r="I11" t="n">
+        <v>1.05663995443651</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.5538405214847617</v>
+      </c>
+      <c r="K11" t="n">
         <v>0.5920375818717998</v>
       </c>
-      <c r="L9" t="n">
+      <c r="L11" t="n">
         <v>0.5927222921816674</v>
       </c>
     </row>
